--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esteb\Documents\proyecto_cursor\proyectoisaqwenvisor\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9F2A79-0051-4598-BA41-1F00488638CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90075A0A-0C6D-49CB-A4E0-D1F4E8A05D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RUTA 111" sheetId="1" r:id="rId1"/>
-    <sheet name="RUTA 222" sheetId="2" r:id="rId6"/>
+    <sheet name="RUTA 12345" sheetId="1" r:id="rId1"/>
+    <sheet name="RUTA 67890" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
   <si>
     <t>RECORRIDO</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>{{extraction.rendicion.detalles_cheques.total_monedas.valor}}</t>
+  </si>
+  <si>
+    <t>{{transf_banco}}</t>
   </si>
 </sst>
 </file>
@@ -1458,6 +1461,148 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1472,148 +1617,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1985,7 +1988,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA</t>
+          <t xml:space="preserve">JUAN PEREZ</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -2097,7 +2100,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">12345</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -2127,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -2156,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -2210,7 +2213,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="171">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="C9" s="172"/>
       <c r="D9" s="173"/>
@@ -2239,7 +2242,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="171">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="C10" s="172"/>
       <c r="D10" s="173"/>
@@ -2267,7 +2270,9 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="171"/>
+      <c r="B11" s="171">
+        <v>300000</v>
+      </c>
       <c r="C11" s="172"/>
       <c r="D11" s="173"/>
       <c r="E11" s="110"/>
@@ -2690,17 +2695,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="214" t="s">
+      <c r="M22" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="214"/>
-      <c r="O22" s="214"/>
-      <c r="P22" s="214"/>
-      <c r="Q22" s="214"/>
-      <c r="R22" s="214"/>
-      <c r="S22" s="214"/>
-      <c r="T22" s="214"/>
-      <c r="U22" s="214"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -2709,17 +2714,21 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221"/>
-      <c r="O23" s="222"/>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="222"/>
-      <c r="R23" s="222"/>
-      <c r="S23" s="223"/>
+      <c r="N23" s="185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24/06/2026</t>
+        </is>
+      </c>
+      <c r="O23" s="186"/>
+      <c r="P23" s="186"/>
+      <c r="Q23" s="186"/>
+      <c r="R23" s="186"/>
+      <c r="S23" s="187"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -2732,19 +2741,19 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="224" t="s">
+      <c r="N24" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="225"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="225"/>
-      <c r="R24" s="225"/>
-      <c r="S24" s="226"/>
+      <c r="O24" s="189"/>
+      <c r="P24" s="189"/>
+      <c r="Q24" s="189"/>
+      <c r="R24" s="189"/>
+      <c r="S24" s="190"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="W24" s="141" t="str">
         <f>U23</f>
@@ -2759,21 +2768,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="199" t="s">
+      <c r="M25" s="193" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="200"/>
-      <c r="O25" s="201"/>
-      <c r="P25" s="202"/>
+      <c r="N25" s="194"/>
+      <c r="O25" s="195"/>
+      <c r="P25" s="196"/>
       <c r="Q25" s="171">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="R25" s="172"/>
       <c r="S25" s="173"/>
-      <c r="T25" s="212" t="s">
+      <c r="T25" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="213"/>
+      <c r="U25" s="192"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -2790,7 +2799,7 @@
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
       <c r="Q26" s="171">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="R26" s="172"/>
       <c r="S26" s="173"/>
@@ -2811,15 +2820,17 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="203"/>
-      <c r="P27" s="204"/>
-      <c r="Q27" s="171"/>
+      <c r="O27" s="175"/>
+      <c r="P27" s="176"/>
+      <c r="Q27" s="171">
+        <v>300000</v>
+      </c>
       <c r="R27" s="172"/>
       <c r="S27" s="173"/>
-      <c r="T27" s="219" t="s">
+      <c r="T27" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="220"/>
+      <c r="U27" s="184"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97" t="str">
         <f>U24</f>
@@ -2835,19 +2846,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="194" t="s">
+      <c r="M28" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="195"/>
-      <c r="O28" s="203"/>
-      <c r="P28" s="204"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="175"/>
+      <c r="P28" s="176"/>
       <c r="Q28" s="171"/>
       <c r="R28" s="172"/>
       <c r="S28" s="173"/>
-      <c r="T28" s="217" t="s">
+      <c r="T28" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="218"/>
+      <c r="U28" s="180"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -2862,19 +2873,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="194" t="s">
+      <c r="M29" s="181" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="195"/>
-      <c r="O29" s="203"/>
-      <c r="P29" s="204"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="175"/>
+      <c r="P29" s="176"/>
       <c r="Q29" s="171"/>
       <c r="R29" s="172"/>
       <c r="S29" s="173"/>
-      <c r="T29" s="215" t="s">
+      <c r="T29" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="216"/>
+      <c r="U29" s="178"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -2890,19 +2901,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="194" t="s">
+      <c r="M30" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="195"/>
-      <c r="O30" s="203"/>
-      <c r="P30" s="209"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="175"/>
+      <c r="P30" s="203"/>
       <c r="Q30" s="171"/>
       <c r="R30" s="172"/>
       <c r="S30" s="173"/>
-      <c r="T30" s="210" t="s">
+      <c r="T30" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="211"/>
+      <c r="U30" s="205"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -2919,12 +2930,12 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="194" t="s">
+      <c r="M31" s="181" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="195"/>
-      <c r="O31" s="203"/>
-      <c r="P31" s="204"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="176"/>
       <c r="Q31" s="171"/>
       <c r="R31" s="172"/>
       <c r="S31" s="173"/>
@@ -2942,12 +2953,12 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="194" t="s">
+      <c r="M32" s="181" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="195"/>
-      <c r="O32" s="203"/>
-      <c r="P32" s="204"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="175"/>
+      <c r="P32" s="176"/>
       <c r="Q32" s="171"/>
       <c r="R32" s="172"/>
       <c r="S32" s="173"/>
@@ -2972,8 +2983,8 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="203"/>
-      <c r="P33" s="204"/>
+      <c r="O33" s="175"/>
+      <c r="P33" s="176"/>
       <c r="Q33" s="171"/>
       <c r="R33" s="172"/>
       <c r="S33" s="173"/>
@@ -2995,14 +3006,14 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="205" t="s">
+      <c r="M34" s="199" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="206"/>
-      <c r="O34" s="207"/>
-      <c r="P34" s="208"/>
+      <c r="N34" s="200"/>
+      <c r="O34" s="201"/>
+      <c r="P34" s="202"/>
       <c r="Q34" s="171">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="R34" s="172"/>
       <c r="S34" s="173"/>
@@ -3023,23 +3034,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="196" t="s">
+      <c r="M35" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="181" t="s">
+      <c r="N35" s="210"/>
+      <c r="O35" s="211"/>
+      <c r="P35" s="197" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="183"/>
-      <c r="R35" s="181" t="s">
+      <c r="Q35" s="198"/>
+      <c r="R35" s="197" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="183"/>
-      <c r="T35" s="181" t="s">
+      <c r="S35" s="198"/>
+      <c r="T35" s="197" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="183"/>
+      <c r="U35" s="198"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -3099,9 +3110,19 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="39"/>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
+      <c r="N37" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O37" s="39">
+        <v>100000</v>
+      </c>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -3121,11 +3142,13 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="179" t="s">
+      <c r="M38" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="180"/>
-      <c r="O38" s="46"/>
+      <c r="N38" s="208"/>
+      <c r="O38" s="46">
+        <v>300000</v>
+      </c>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -3232,8 +3255,8 @@
       <c r="A43" s="112"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="186"/>
-      <c r="E43" s="186"/>
+      <c r="D43" s="206"/>
+      <c r="E43" s="206"/>
       <c r="F43" s="51"/>
       <c r="G43" s="8"/>
       <c r="I43" s="136"/>
@@ -3259,8 +3282,8 @@
       <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="186"/>
-      <c r="E44" s="186"/>
+      <c r="D44" s="206"/>
+      <c r="E44" s="206"/>
       <c r="F44" s="52"/>
       <c r="H44" s="68"/>
       <c r="I44" s="13"/>
@@ -3283,8 +3306,8 @@
       <c r="A45" s="25"/>
       <c r="B45" s="25"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="186"/>
-      <c r="E45" s="186"/>
+      <c r="D45" s="206"/>
+      <c r="E45" s="206"/>
       <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
@@ -3306,8 +3329,8 @@
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="186"/>
-      <c r="E46" s="186"/>
+      <c r="D46" s="206"/>
+      <c r="E46" s="206"/>
       <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
@@ -3329,8 +3352,8 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="186"/>
-      <c r="E47" s="186"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
       <c r="H47" s="68"/>
@@ -3357,8 +3380,8 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="186"/>
-      <c r="E48" s="186"/>
+      <c r="D48" s="206"/>
+      <c r="E48" s="206"/>
       <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
@@ -3381,8 +3404,8 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="186"/>
-      <c r="E49" s="186"/>
+      <c r="D49" s="206"/>
+      <c r="E49" s="206"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
       <c r="H49" s="50"/>
@@ -3429,8 +3452,8 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="187"/>
-      <c r="E51" s="187"/>
+      <c r="D51" s="220"/>
+      <c r="E51" s="220"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
@@ -3453,8 +3476,8 @@
       <c r="A52" s="20"/>
       <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="185"/>
-      <c r="E52" s="185"/>
+      <c r="D52" s="221"/>
+      <c r="E52" s="221"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
@@ -3477,8 +3500,8 @@
       <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="184"/>
+      <c r="D53" s="217"/>
+      <c r="E53" s="217"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
@@ -3499,8 +3522,8 @@
       <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
+      <c r="D54" s="217"/>
+      <c r="E54" s="217"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -3631,8 +3654,8 @@
       <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="184"/>
-      <c r="E60" s="184"/>
+      <c r="D60" s="217"/>
+      <c r="E60" s="217"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -3719,8 +3742,8 @@
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="184"/>
-      <c r="E64" s="184"/>
+      <c r="D64" s="217"/>
+      <c r="E64" s="217"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -3741,18 +3764,18 @@
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="184"/>
-      <c r="E65" s="184"/>
+      <c r="D65" s="217"/>
+      <c r="E65" s="217"/>
       <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
       <c r="L65"/>
-      <c r="M65" s="179" t="s">
+      <c r="M65" s="207" t="s">
         <v>34</v>
       </c>
-      <c r="N65" s="180"/>
+      <c r="N65" s="208"/>
       <c r="O65" s="46"/>
       <c r="P65" s="56" t="s">
         <v>11</v>
@@ -3771,8 +3794,8 @@
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="95"/>
-      <c r="D66" s="184"/>
-      <c r="E66" s="184"/>
+      <c r="D66" s="217"/>
+      <c r="E66" s="217"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
@@ -3800,28 +3823,28 @@
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="181" t="s">
+      <c r="M67" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="N67" s="182"/>
-      <c r="O67" s="183"/>
-      <c r="P67" s="192"/>
-      <c r="Q67" s="193"/>
-      <c r="R67" s="181" t="s">
+      <c r="N67" s="216"/>
+      <c r="O67" s="198"/>
+      <c r="P67" s="218"/>
+      <c r="Q67" s="219"/>
+      <c r="R67" s="197" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="182"/>
-      <c r="T67" s="188" t="str">
+      <c r="S67" s="216"/>
+      <c r="T67" s="212" t="str">
         <f>Q25</f>
       </c>
-      <c r="U67" s="189"/>
+      <c r="U67" s="213"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
+      <c r="D68" s="217"/>
+      <c r="E68" s="217"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
@@ -3842,33 +3865,33 @@
       <c r="A69" s="25"/>
       <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="184"/>
-      <c r="E69" s="184"/>
+      <c r="D69" s="217"/>
+      <c r="E69" s="217"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="179" t="s">
+      <c r="M69" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="N69" s="190"/>
-      <c r="O69" s="190"/>
-      <c r="P69" s="190"/>
-      <c r="Q69" s="190"/>
-      <c r="R69" s="190"/>
-      <c r="S69" s="190"/>
-      <c r="T69" s="190"/>
-      <c r="U69" s="191"/>
+      <c r="N69" s="214"/>
+      <c r="O69" s="214"/>
+      <c r="P69" s="214"/>
+      <c r="Q69" s="214"/>
+      <c r="R69" s="214"/>
+      <c r="S69" s="214"/>
+      <c r="T69" s="214"/>
+      <c r="U69" s="215"/>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
       <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="184"/>
-      <c r="E70" s="184"/>
+      <c r="D70" s="217"/>
+      <c r="E70" s="217"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
@@ -3905,8 +3928,8 @@
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="184"/>
-      <c r="E71" s="184"/>
+      <c r="D71" s="217"/>
+      <c r="E71" s="217"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
@@ -3920,10 +3943,10 @@
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="65"/>
-      <c r="R71" s="178" t="s">
+      <c r="R71" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="S71" s="178"/>
+      <c r="S71" s="226"/>
       <c r="T71" s="159"/>
       <c r="U71" s="160"/>
       <c r="V71" s="55"/>
@@ -3931,8 +3954,8 @@
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" s="55"/>
       <c r="C72" s="94"/>
-      <c r="D72" s="184"/>
-      <c r="E72" s="184"/>
+      <c r="D72" s="217"/>
+      <c r="E72" s="217"/>
       <c r="F72" s="67"/>
       <c r="I72" s="130"/>
       <c r="L72"/>
@@ -3941,8 +3964,8 @@
       <c r="O72" s="18"/>
       <c r="P72" s="91"/>
       <c r="Q72" s="60"/>
-      <c r="R72" s="176"/>
-      <c r="S72" s="176"/>
+      <c r="R72" s="224"/>
+      <c r="S72" s="224"/>
       <c r="T72" s="69"/>
       <c r="U72" s="100"/>
       <c r="V72" s="55"/>
@@ -3955,20 +3978,38 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="89"/>
+      <c r="L73" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12345</t>
+        </is>
+      </c>
+      <c r="M73" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91"/>
+      <c r="P73" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F001</t>
+        </is>
+      </c>
       <c r="Q73" s="60"/>
-      <c r="R73" s="176" t="s">
+      <c r="R73" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="176"/>
-      <c r="T73" s="69"/>
-      <c r="U73" s="100"/>
+      <c r="S73" s="224"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U73" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -3978,8 +4019,8 @@
       <c r="O74" s="147"/>
       <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="176"/>
-      <c r="S74" s="176"/>
+      <c r="R74" s="224"/>
+      <c r="S74" s="224"/>
       <c r="T74" s="69"/>
       <c r="U74" s="100"/>
       <c r="V74" s="55"/>
@@ -3993,10 +4034,10 @@
       <c r="O75" s="165"/>
       <c r="P75" s="166"/>
       <c r="Q75" s="167"/>
-      <c r="R75" s="177"/>
-      <c r="S75" s="177"/>
-      <c r="T75" s="174"/>
-      <c r="U75" s="175"/>
+      <c r="R75" s="225"/>
+      <c r="S75" s="225"/>
+      <c r="T75" s="222"/>
+      <c r="U75" s="223"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -4010,8 +4051,8 @@
       <c r="Q76" s="167"/>
       <c r="R76" s="168"/>
       <c r="S76" s="168"/>
-      <c r="T76" s="174"/>
-      <c r="U76" s="175"/>
+      <c r="T76" s="222"/>
+      <c r="U76" s="223"/>
       <c r="V76" s="55"/>
     </row>
     <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -4160,6 +4201,71 @@
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
@@ -4176,71 +4282,6 @@
     <mergeCell ref="T27:U27"/>
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -4279,7 +4320,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOB</t>
+          <t xml:space="preserve">MARIA LOPEZ</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -4391,7 +4432,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">67890</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -4421,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -4450,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -4504,7 +4545,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="171">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="C9" s="172"/>
       <c r="D9" s="173"/>
@@ -4533,7 +4574,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="171">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="C10" s="172"/>
       <c r="D10" s="173"/>
@@ -4561,7 +4602,9 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="171"/>
+      <c r="B11" s="171">
+        <v>300000</v>
+      </c>
       <c r="C11" s="172"/>
       <c r="D11" s="173"/>
       <c r="E11" s="110"/>
@@ -4984,17 +5027,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="214" t="s">
+      <c r="M22" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="214"/>
-      <c r="O22" s="214"/>
-      <c r="P22" s="214"/>
-      <c r="Q22" s="214"/>
-      <c r="R22" s="214"/>
-      <c r="S22" s="214"/>
-      <c r="T22" s="214"/>
-      <c r="U22" s="214"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -5003,17 +5046,21 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221"/>
-      <c r="O23" s="222"/>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="222"/>
-      <c r="R23" s="222"/>
-      <c r="S23" s="223"/>
+      <c r="N23" s="185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24/06/2026</t>
+        </is>
+      </c>
+      <c r="O23" s="186"/>
+      <c r="P23" s="186"/>
+      <c r="Q23" s="186"/>
+      <c r="R23" s="186"/>
+      <c r="S23" s="187"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -5026,19 +5073,19 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="224" t="s">
+      <c r="N24" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="225"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="225"/>
-      <c r="R24" s="225"/>
-      <c r="S24" s="226"/>
+      <c r="O24" s="189"/>
+      <c r="P24" s="189"/>
+      <c r="Q24" s="189"/>
+      <c r="R24" s="189"/>
+      <c r="S24" s="190"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="W24" s="141" t="str">
         <f>U23</f>
@@ -5053,21 +5100,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="199" t="s">
+      <c r="M25" s="193" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="200"/>
-      <c r="O25" s="201"/>
-      <c r="P25" s="202"/>
+      <c r="N25" s="194"/>
+      <c r="O25" s="195"/>
+      <c r="P25" s="196"/>
       <c r="Q25" s="171">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="R25" s="172"/>
       <c r="S25" s="173"/>
-      <c r="T25" s="212" t="s">
+      <c r="T25" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="213"/>
+      <c r="U25" s="192"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -5084,7 +5131,7 @@
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
       <c r="Q26" s="171">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="R26" s="172"/>
       <c r="S26" s="173"/>
@@ -5105,15 +5152,17 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="203"/>
-      <c r="P27" s="204"/>
-      <c r="Q27" s="171"/>
+      <c r="O27" s="175"/>
+      <c r="P27" s="176"/>
+      <c r="Q27" s="171">
+        <v>300000</v>
+      </c>
       <c r="R27" s="172"/>
       <c r="S27" s="173"/>
-      <c r="T27" s="219" t="s">
+      <c r="T27" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="220"/>
+      <c r="U27" s="184"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97" t="str">
         <f>U24</f>
@@ -5129,19 +5178,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="194" t="s">
+      <c r="M28" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="195"/>
-      <c r="O28" s="203"/>
-      <c r="P28" s="204"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="175"/>
+      <c r="P28" s="176"/>
       <c r="Q28" s="171"/>
       <c r="R28" s="172"/>
       <c r="S28" s="173"/>
-      <c r="T28" s="217" t="s">
+      <c r="T28" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="218"/>
+      <c r="U28" s="180"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -5156,19 +5205,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="194" t="s">
+      <c r="M29" s="181" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="195"/>
-      <c r="O29" s="203"/>
-      <c r="P29" s="204"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="175"/>
+      <c r="P29" s="176"/>
       <c r="Q29" s="171"/>
       <c r="R29" s="172"/>
       <c r="S29" s="173"/>
-      <c r="T29" s="215" t="s">
+      <c r="T29" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="216"/>
+      <c r="U29" s="178"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -5184,19 +5233,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="194" t="s">
+      <c r="M30" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="195"/>
-      <c r="O30" s="203"/>
-      <c r="P30" s="209"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="175"/>
+      <c r="P30" s="203"/>
       <c r="Q30" s="171"/>
       <c r="R30" s="172"/>
       <c r="S30" s="173"/>
-      <c r="T30" s="210" t="s">
+      <c r="T30" s="204" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="211"/>
+      <c r="U30" s="205"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -5213,12 +5262,12 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="194" t="s">
+      <c r="M31" s="181" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="195"/>
-      <c r="O31" s="203"/>
-      <c r="P31" s="204"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="176"/>
       <c r="Q31" s="171"/>
       <c r="R31" s="172"/>
       <c r="S31" s="173"/>
@@ -5236,12 +5285,12 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="194" t="s">
+      <c r="M32" s="181" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="195"/>
-      <c r="O32" s="203"/>
-      <c r="P32" s="204"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="175"/>
+      <c r="P32" s="176"/>
       <c r="Q32" s="171"/>
       <c r="R32" s="172"/>
       <c r="S32" s="173"/>
@@ -5266,8 +5315,8 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="203"/>
-      <c r="P33" s="204"/>
+      <c r="O33" s="175"/>
+      <c r="P33" s="176"/>
       <c r="Q33" s="171"/>
       <c r="R33" s="172"/>
       <c r="S33" s="173"/>
@@ -5289,14 +5338,14 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="205" t="s">
+      <c r="M34" s="199" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="206"/>
-      <c r="O34" s="207"/>
-      <c r="P34" s="208"/>
+      <c r="N34" s="200"/>
+      <c r="O34" s="201"/>
+      <c r="P34" s="202"/>
       <c r="Q34" s="171">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="R34" s="172"/>
       <c r="S34" s="173"/>
@@ -5317,23 +5366,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="196" t="s">
+      <c r="M35" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="181" t="s">
+      <c r="N35" s="210"/>
+      <c r="O35" s="211"/>
+      <c r="P35" s="197" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="183"/>
-      <c r="R35" s="181" t="s">
+      <c r="Q35" s="198"/>
+      <c r="R35" s="197" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="183"/>
-      <c r="T35" s="181" t="s">
+      <c r="S35" s="198"/>
+      <c r="T35" s="197" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="183"/>
+      <c r="U35" s="198"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -5393,9 +5442,19 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="39"/>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
+      <c r="N37" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O37" s="39">
+        <v>100000</v>
+      </c>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -5415,11 +5474,13 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="179" t="s">
+      <c r="M38" s="207" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="180"/>
-      <c r="O38" s="46"/>
+      <c r="N38" s="208"/>
+      <c r="O38" s="46">
+        <v>300000</v>
+      </c>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -5526,8 +5587,8 @@
       <c r="A43" s="112"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="186"/>
-      <c r="E43" s="186"/>
+      <c r="D43" s="206"/>
+      <c r="E43" s="206"/>
       <c r="F43" s="51"/>
       <c r="G43" s="8"/>
       <c r="I43" s="136"/>
@@ -5553,8 +5614,8 @@
       <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="186"/>
-      <c r="E44" s="186"/>
+      <c r="D44" s="206"/>
+      <c r="E44" s="206"/>
       <c r="F44" s="52"/>
       <c r="H44" s="68"/>
       <c r="I44" s="13"/>
@@ -5577,8 +5638,8 @@
       <c r="A45" s="25"/>
       <c r="B45" s="25"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="186"/>
-      <c r="E45" s="186"/>
+      <c r="D45" s="206"/>
+      <c r="E45" s="206"/>
       <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
@@ -5600,8 +5661,8 @@
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="186"/>
-      <c r="E46" s="186"/>
+      <c r="D46" s="206"/>
+      <c r="E46" s="206"/>
       <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
@@ -5623,8 +5684,8 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="186"/>
-      <c r="E47" s="186"/>
+      <c r="D47" s="206"/>
+      <c r="E47" s="206"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
       <c r="H47" s="68"/>
@@ -5651,8 +5712,8 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="186"/>
-      <c r="E48" s="186"/>
+      <c r="D48" s="206"/>
+      <c r="E48" s="206"/>
       <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
@@ -5675,8 +5736,8 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="186"/>
-      <c r="E49" s="186"/>
+      <c r="D49" s="206"/>
+      <c r="E49" s="206"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
       <c r="H49" s="50"/>
@@ -5723,8 +5784,8 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="187"/>
-      <c r="E51" s="187"/>
+      <c r="D51" s="220"/>
+      <c r="E51" s="220"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
@@ -5747,8 +5808,8 @@
       <c r="A52" s="20"/>
       <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="185"/>
-      <c r="E52" s="185"/>
+      <c r="D52" s="221"/>
+      <c r="E52" s="221"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
@@ -5771,8 +5832,8 @@
       <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="184"/>
+      <c r="D53" s="217"/>
+      <c r="E53" s="217"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
@@ -5793,8 +5854,8 @@
       <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
+      <c r="D54" s="217"/>
+      <c r="E54" s="217"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -5925,8 +5986,8 @@
       <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="184"/>
-      <c r="E60" s="184"/>
+      <c r="D60" s="217"/>
+      <c r="E60" s="217"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -6013,8 +6074,8 @@
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="184"/>
-      <c r="E64" s="184"/>
+      <c r="D64" s="217"/>
+      <c r="E64" s="217"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -6035,18 +6096,18 @@
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="184"/>
-      <c r="E65" s="184"/>
+      <c r="D65" s="217"/>
+      <c r="E65" s="217"/>
       <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
       <c r="L65"/>
-      <c r="M65" s="179" t="s">
+      <c r="M65" s="207" t="s">
         <v>34</v>
       </c>
-      <c r="N65" s="180"/>
+      <c r="N65" s="208"/>
       <c r="O65" s="46"/>
       <c r="P65" s="56" t="s">
         <v>11</v>
@@ -6065,8 +6126,8 @@
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="95"/>
-      <c r="D66" s="184"/>
-      <c r="E66" s="184"/>
+      <c r="D66" s="217"/>
+      <c r="E66" s="217"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
@@ -6094,28 +6155,28 @@
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="181" t="s">
+      <c r="M67" s="197" t="s">
         <v>47</v>
       </c>
-      <c r="N67" s="182"/>
-      <c r="O67" s="183"/>
-      <c r="P67" s="192"/>
-      <c r="Q67" s="193"/>
-      <c r="R67" s="181" t="s">
+      <c r="N67" s="216"/>
+      <c r="O67" s="198"/>
+      <c r="P67" s="218"/>
+      <c r="Q67" s="219"/>
+      <c r="R67" s="197" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="182"/>
-      <c r="T67" s="188" t="str">
+      <c r="S67" s="216"/>
+      <c r="T67" s="212" t="str">
         <f>Q25</f>
       </c>
-      <c r="U67" s="189"/>
+      <c r="U67" s="213"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
+      <c r="D68" s="217"/>
+      <c r="E68" s="217"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
@@ -6136,33 +6197,33 @@
       <c r="A69" s="25"/>
       <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="184"/>
-      <c r="E69" s="184"/>
+      <c r="D69" s="217"/>
+      <c r="E69" s="217"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="179" t="s">
+      <c r="M69" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="N69" s="190"/>
-      <c r="O69" s="190"/>
-      <c r="P69" s="190"/>
-      <c r="Q69" s="190"/>
-      <c r="R69" s="190"/>
-      <c r="S69" s="190"/>
-      <c r="T69" s="190"/>
-      <c r="U69" s="191"/>
+      <c r="N69" s="214"/>
+      <c r="O69" s="214"/>
+      <c r="P69" s="214"/>
+      <c r="Q69" s="214"/>
+      <c r="R69" s="214"/>
+      <c r="S69" s="214"/>
+      <c r="T69" s="214"/>
+      <c r="U69" s="215"/>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
       <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="184"/>
-      <c r="E70" s="184"/>
+      <c r="D70" s="217"/>
+      <c r="E70" s="217"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
@@ -6199,8 +6260,8 @@
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="184"/>
-      <c r="E71" s="184"/>
+      <c r="D71" s="217"/>
+      <c r="E71" s="217"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
@@ -6214,10 +6275,10 @@
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="65"/>
-      <c r="R71" s="178" t="s">
+      <c r="R71" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="S71" s="178"/>
+      <c r="S71" s="226"/>
       <c r="T71" s="159"/>
       <c r="U71" s="160"/>
       <c r="V71" s="55"/>
@@ -6225,8 +6286,8 @@
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" s="55"/>
       <c r="C72" s="94"/>
-      <c r="D72" s="184"/>
-      <c r="E72" s="184"/>
+      <c r="D72" s="217"/>
+      <c r="E72" s="217"/>
       <c r="F72" s="67"/>
       <c r="I72" s="130"/>
       <c r="L72"/>
@@ -6235,8 +6296,8 @@
       <c r="O72" s="18"/>
       <c r="P72" s="91"/>
       <c r="Q72" s="60"/>
-      <c r="R72" s="176"/>
-      <c r="S72" s="176"/>
+      <c r="R72" s="224"/>
+      <c r="S72" s="224"/>
       <c r="T72" s="69"/>
       <c r="U72" s="100"/>
       <c r="V72" s="55"/>
@@ -6249,20 +6310,38 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="89"/>
+      <c r="L73" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67890</t>
+        </is>
+      </c>
+      <c r="M73" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91"/>
+      <c r="P73" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F001</t>
+        </is>
+      </c>
       <c r="Q73" s="60"/>
-      <c r="R73" s="176" t="s">
+      <c r="R73" s="224" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="176"/>
-      <c r="T73" s="69"/>
-      <c r="U73" s="100"/>
+      <c r="S73" s="224"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U73" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -6272,8 +6351,8 @@
       <c r="O74" s="147"/>
       <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="176"/>
-      <c r="S74" s="176"/>
+      <c r="R74" s="224"/>
+      <c r="S74" s="224"/>
       <c r="T74" s="69"/>
       <c r="U74" s="100"/>
       <c r="V74" s="55"/>
@@ -6287,10 +6366,10 @@
       <c r="O75" s="165"/>
       <c r="P75" s="166"/>
       <c r="Q75" s="167"/>
-      <c r="R75" s="177"/>
-      <c r="S75" s="177"/>
-      <c r="T75" s="174"/>
-      <c r="U75" s="175"/>
+      <c r="R75" s="225"/>
+      <c r="S75" s="225"/>
+      <c r="T75" s="222"/>
+      <c r="U75" s="223"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -6304,8 +6383,8 @@
       <c r="Q76" s="167"/>
       <c r="R76" s="168"/>
       <c r="S76" s="168"/>
-      <c r="T76" s="174"/>
-      <c r="U76" s="175"/>
+      <c r="T76" s="222"/>
+      <c r="U76" s="223"/>
       <c r="V76" s="55"/>
     </row>
     <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -6454,6 +6533,71 @@
     </row>
   </sheetData>
   <mergeCells count="81">
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
@@ -6470,71 +6614,6 @@
     <mergeCell ref="T27:U27"/>
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esteb\Documents\proyecto_cursor\proyectoisaqwenvisor\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90075A0A-0C6D-49CB-A4E0-D1F4E8A05D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703A2F14-26FE-40C5-A4C3-CF31C833DAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="RUTA 12345" sheetId="1" r:id="rId1"/>
-    <sheet name="RUTA 67890" sheetId="2" r:id="rId6"/>
+    <sheet name="Resumen" sheetId="1" r:id="rId1"/>
+    <sheet name="RUTA 111" sheetId="2" r:id="rId6"/>
+    <sheet name="RUTA 222" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="100">
   <si>
     <t>RECORRIDO</t>
   </si>
@@ -1012,7 +1013,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1452,6 +1453,15 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1461,15 +1471,118 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1482,12 +1595,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1512,111 +1619,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1958,2334 +1968,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W112"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="3" customWidth="1"/>
-    <col min="7" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.6640625" style="4" customWidth="1"/>
-    <col min="16" max="19" width="11.6640625" style="3" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="127" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PEREZ</t>
+          <t>CAMPO</t>
         </is>
       </c>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="129"/>
-    </row>
-    <row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="109"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="129"/>
-    </row>
-    <row r="3" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="146" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="143"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="143"/>
-      <c r="R3" s="143"/>
-      <c r="S3" s="143"/>
-      <c r="T3" s="143"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="131"/>
-      <c r="W3" s="132"/>
-    </row>
-    <row r="4" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="146" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
-      <c r="L4" s="143"/>
-      <c r="M4" s="143"/>
-      <c r="N4" s="143"/>
-      <c r="O4" s="143"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="143"/>
-      <c r="R4" s="143"/>
-      <c r="S4" s="143"/>
-      <c r="T4" s="143"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="131"/>
-      <c r="W4" s="132"/>
-    </row>
-    <row r="5" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="127" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="154" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">12345</t>
+          <t xml:space="preserve">111 · ANA</t>
         </is>
       </c>
-      <c r="C5" s="154"/>
-      <c r="D5" s="154"/>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154"/>
-      <c r="K5" s="154"/>
-      <c r="L5" s="154"/>
-      <c r="M5" s="154"/>
-      <c r="N5" s="154"/>
-      <c r="O5" s="154"/>
-      <c r="P5" s="154"/>
-      <c r="Q5" s="154"/>
-      <c r="R5" s="143"/>
-      <c r="S5" s="143"/>
-      <c r="T5" s="143"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="124"/>
-      <c r="W5" s="123"/>
-    </row>
-    <row r="6" spans="1:23" s="49" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="127" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222 · BOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CHOFER</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AUXILIAR / PEONETA</t>
+        </is>
+      </c>
+      <c r="B4"/>
+      <c r="C4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RECORRIDO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PATENTE</t>
+        </is>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>N° FACT.</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOTAL FACT.</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>500000</v>
+      </c>
+      <c r="C8">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EFECTIVO TOTAL</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>100000</v>
+      </c>
+      <c r="C9">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BILLETES</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>90000</v>
+      </c>
+      <c r="C10">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MONEDAS</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>10000</v>
+      </c>
+      <c r="C11">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHEQUES AL DÍA</t>
+        </is>
+      </c>
+      <c r="B12"/>
+      <c r="C12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHEQUES A FECHA</t>
+        </is>
+      </c>
+      <c r="B13"/>
+      <c r="C13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CRÉDITO VENDEDOR</t>
+        </is>
+      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NULOS (RETORNO TOTAL)</t>
+        </is>
+      </c>
+      <c r="B15"/>
+      <c r="C15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PARCIALES (RETORNO PARCIAL)</t>
+        </is>
+      </c>
+      <c r="B16"/>
+      <c r="C16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>N/C NEGOCIO</t>
+        </is>
+      </c>
+      <c r="B17"/>
+      <c r="C17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIAS</t>
+        </is>
+      </c>
+      <c r="B18"/>
+      <c r="C18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TOTAL RENDICIÓN</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>500000</v>
+      </c>
+      <c r="C19">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TOTALES CONSOLIDADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>N° FACT.</t>
+        </is>
+      </c>
+      <c r="B23">
         <v>10</v>
       </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6" s="123"/>
-      <c r="N6" s="123"/>
-      <c r="O6" s="123"/>
-      <c r="P6" s="123"/>
-      <c r="Q6" s="123"/>
-      <c r="R6" s="143"/>
-      <c r="S6" s="143"/>
-      <c r="T6" s="143"/>
-      <c r="U6" s="121"/>
-      <c r="V6" s="123"/>
-      <c r="W6" s="123"/>
-    </row>
-    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="127" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="155">
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TOTAL FACT.</t>
+        </is>
+      </c>
+      <c r="B24">
         <v>1000000</v>
       </c>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="155"/>
-      <c r="K7" s="155"/>
-      <c r="L7" s="155"/>
-      <c r="M7" s="155"/>
-      <c r="N7" s="155"/>
-      <c r="O7" s="155"/>
-      <c r="P7" s="155"/>
-      <c r="Q7" s="155"/>
-      <c r="R7" s="144"/>
-      <c r="S7" s="144"/>
-      <c r="T7" s="144"/>
-      <c r="U7" s="113"/>
-      <c r="V7" s="110"/>
-      <c r="W7" s="110"/>
-    </row>
-    <row r="8" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="123"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="119"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="121"/>
-      <c r="R8" s="140"/>
-      <c r="S8" s="123"/>
-      <c r="T8" s="140"/>
-      <c r="U8" s="121"/>
-      <c r="V8" s="119"/>
-      <c r="W8" s="123"/>
-    </row>
-    <row r="9" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="128" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="171">
-        <v>450000</v>
-      </c>
-      <c r="C9" s="172"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="140"/>
-      <c r="S9" s="137"/>
-      <c r="T9" s="139"/>
-      <c r="U9" s="113"/>
-      <c r="V9" s="119"/>
-      <c r="W9" s="110"/>
-    </row>
-    <row r="10" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="128" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="171">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="172"/>
-      <c r="D10" s="173"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="137"/>
-      <c r="T10" s="139"/>
-      <c r="U10" s="113"/>
-      <c r="V10" s="119"/>
-      <c r="W10" s="110"/>
-    </row>
-    <row r="11" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="128" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="171">
-        <v>300000</v>
-      </c>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="110"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="110"/>
-      <c r="P11" s="140"/>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="140"/>
-      <c r="S11" s="137"/>
-      <c r="T11" s="139"/>
-      <c r="U11" s="113"/>
-      <c r="V11" s="119"/>
-      <c r="W11" s="110"/>
-    </row>
-    <row r="12" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="128" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="171"/>
-      <c r="C12" s="172"/>
-      <c r="D12" s="173"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="119"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="110"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="140"/>
-      <c r="S12" s="137"/>
-      <c r="T12" s="139"/>
-      <c r="U12" s="113"/>
-      <c r="V12" s="119"/>
-      <c r="W12" s="110"/>
-    </row>
-    <row r="13" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="128" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="173"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="119"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="110"/>
-      <c r="P13" s="140"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="140"/>
-      <c r="S13" s="137"/>
-      <c r="T13" s="139"/>
-      <c r="U13" s="113"/>
-      <c r="V13" s="119"/>
-      <c r="W13" s="110"/>
-    </row>
-    <row r="14" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="171"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="140"/>
-      <c r="Q14" s="113"/>
-      <c r="R14" s="140"/>
-      <c r="S14" s="137"/>
-      <c r="T14" s="139"/>
-      <c r="U14" s="113"/>
-      <c r="V14" s="119"/>
-      <c r="W14" s="110"/>
-    </row>
-    <row r="15" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="128" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="171"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="119"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="110"/>
-      <c r="P15" s="140"/>
-      <c r="Q15" s="113"/>
-      <c r="R15" s="140"/>
-      <c r="S15" s="137"/>
-      <c r="T15" s="139"/>
-      <c r="U15" s="113"/>
-      <c r="V15" s="119"/>
-      <c r="W15" s="110"/>
-    </row>
-    <row r="16" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="128" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="171"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="110"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="110"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="137"/>
-      <c r="T16" s="139"/>
-      <c r="U16" s="113"/>
-      <c r="V16" s="119"/>
-      <c r="W16" s="110"/>
-    </row>
-    <row r="17" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="128" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="171"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="110"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="110"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="119"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="119"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="120"/>
-      <c r="O17" s="110"/>
-      <c r="P17" s="140"/>
-      <c r="Q17" s="113"/>
-      <c r="R17" s="140"/>
-      <c r="S17" s="137"/>
-      <c r="T17" s="139"/>
-      <c r="U17" s="113"/>
-      <c r="V17" s="119"/>
-      <c r="W17" s="110"/>
-    </row>
-    <row r="18" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="128" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="119">
-        <f>SUM(B9:B17)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="119">
-        <f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="120">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="119">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="119">
-        <f t="shared" ref="P18" si="1">SUM(P9:P17)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="122">
-        <f>SUM(Q9:Q17)</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="122">
-        <f>SUM(R9:R17)</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="132">
-        <f>SUM(S9:S17)</f>
-        <v>0</v>
-      </c>
-      <c r="T18" s="132">
-        <f>SUM(T9:T17)</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="122">
-        <f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="119">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="119">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="128"/>
-      <c r="B19" s="119"/>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="119"/>
-      <c r="N19" s="120"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="122"/>
-      <c r="R19" s="122"/>
-      <c r="S19" s="132"/>
-      <c r="T19" s="132"/>
-      <c r="U19" s="122"/>
-      <c r="V19" s="119"/>
-      <c r="W19" s="119"/>
-    </row>
-    <row r="20" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="128" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="119" t="e">
-        <f t="shared" ref="B20:O20" si="3">B18-B7</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="120">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="119">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="119">
-        <f t="shared" ref="P20" si="4">P18-P7</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="122">
-        <f>Q18-Q7</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="122">
-        <f>R18-R7</f>
-        <v>0</v>
-      </c>
-      <c r="S20" s="119">
-        <f>S18-S7</f>
-        <v>0</v>
-      </c>
-      <c r="T20" s="119">
-        <f>T18-T7</f>
-        <v>0</v>
-      </c>
-      <c r="U20" s="122">
-        <f t="shared" ref="U20:W20" si="5">U18-U7</f>
-        <v>0</v>
-      </c>
-      <c r="V20" s="119">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="119">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="9"/>
-      <c r="U21" s="9"/>
-      <c r="V21" s="9"/>
-      <c r="W21" s="9"/>
-    </row>
-    <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D22" s="2"/>
-      <c r="M22" s="174" t="s">
-        <v>48</v>
-      </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
-    </row>
-    <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D23" s="6"/>
-      <c r="J23"/>
-      <c r="L23"/>
-      <c r="M23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="N23" s="185" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/06/2026</t>
+          <t>EFECTIVO TOTAL</t>
         </is>
       </c>
-      <c r="O23" s="186"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="186"/>
-      <c r="R23" s="186"/>
-      <c r="S23" s="187"/>
-      <c r="T23" s="142" t="s">
-        <v>38</v>
-      </c>
-      <c r="U23" s="115">
-        <v>10</v>
-      </c>
-      <c r="W23" s="96" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="2"/>
-      <c r="C24" s="18"/>
-      <c r="J24"/>
-      <c r="K24" s="15"/>
-      <c r="L24"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="188" t="s">
-        <v>49</v>
-      </c>
-      <c r="O24" s="189"/>
-      <c r="P24" s="189"/>
-      <c r="Q24" s="189"/>
-      <c r="R24" s="189"/>
-      <c r="S24" s="190"/>
-      <c r="T24" s="117" t="s">
-        <v>11</v>
-      </c>
-      <c r="U24" s="116">
+      <c r="B25">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BILLETES</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MONEDAS</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TOTAL RENDICIÓN</t>
+        </is>
+      </c>
+      <c r="B28">
         <v>1000000</v>
       </c>
-      <c r="W24" s="141" t="str">
-        <f>U23</f>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="4"/>
-      <c r="J25"/>
-      <c r="L25"/>
-      <c r="M25" s="193" t="s">
-        <v>16</v>
-      </c>
-      <c r="N25" s="194"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="196"/>
-      <c r="Q25" s="171">
-        <v>450000</v>
-      </c>
-      <c r="R25" s="172"/>
-      <c r="S25" s="173"/>
-      <c r="T25" s="191" t="s">
-        <v>17</v>
-      </c>
-      <c r="U25" s="192"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="86" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="E26" s="4"/>
-      <c r="J26"/>
-      <c r="L26"/>
-      <c r="M26" s="83" t="s">
-        <v>53</v>
-      </c>
-      <c r="N26" s="84"/>
-      <c r="O26" s="151"/>
-      <c r="P26" s="152"/>
-      <c r="Q26" s="171">
-        <v>50000</v>
-      </c>
-      <c r="R26" s="172"/>
-      <c r="S26" s="173"/>
-      <c r="T26" s="149"/>
-      <c r="U26" s="150"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="86"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="I27" s="118" t="str">
-        <f>B1</f>
-      </c>
-      <c r="J27" s="162" t="str">
-        <f>B9</f>
-      </c>
-      <c r="L27"/>
-      <c r="M27" s="83" t="s">
-        <v>18</v>
-      </c>
-      <c r="N27" s="84"/>
-      <c r="O27" s="175"/>
-      <c r="P27" s="176"/>
-      <c r="Q27" s="171">
-        <v>300000</v>
-      </c>
-      <c r="R27" s="172"/>
-      <c r="S27" s="173"/>
-      <c r="T27" s="183" t="s">
-        <v>19</v>
-      </c>
-      <c r="U27" s="184"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="97" t="str">
-        <f>U24</f>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="I28" s="118">
-        <f>C1</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="162">
-        <f>C9</f>
-        <v>0</v>
-      </c>
-      <c r="L28"/>
-      <c r="M28" s="181" t="s">
-        <v>20</v>
-      </c>
-      <c r="N28" s="182"/>
-      <c r="O28" s="175"/>
-      <c r="P28" s="176"/>
-      <c r="Q28" s="171"/>
-      <c r="R28" s="172"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="179" t="s">
-        <v>39</v>
-      </c>
-      <c r="U28" s="180"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="13"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="I29" s="118">
-        <f>D1</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="162">
-        <f>D9</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="24"/>
-      <c r="L29"/>
-      <c r="M29" s="181" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="182"/>
-      <c r="O29" s="175"/>
-      <c r="P29" s="176"/>
-      <c r="Q29" s="171"/>
-      <c r="R29" s="172"/>
-      <c r="S29" s="173"/>
-      <c r="T29" s="177" t="s">
-        <v>40</v>
-      </c>
-      <c r="U29" s="178"/>
-      <c r="W29" s="98" t="str">
-        <f>U23</f>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="I30" s="118">
-        <f>E1</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="162">
-        <f>E9</f>
-        <v>0</v>
-      </c>
-      <c r="L30"/>
-      <c r="M30" s="181" t="s">
-        <v>22</v>
-      </c>
-      <c r="N30" s="182"/>
-      <c r="O30" s="175"/>
-      <c r="P30" s="203"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="172"/>
-      <c r="S30" s="173"/>
-      <c r="T30" s="204" t="s">
-        <v>41</v>
-      </c>
-      <c r="U30" s="205"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="21" t="str">
-        <f>Q34</f>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="I31" s="118">
-        <f>F1</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="162">
-        <f>F9</f>
-        <v>0</v>
-      </c>
-      <c r="L31"/>
-      <c r="M31" s="181" t="s">
-        <v>23</v>
-      </c>
-      <c r="N31" s="182"/>
-      <c r="O31" s="175"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="171"/>
-      <c r="R31" s="172"/>
-      <c r="S31" s="173"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="26"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="I32" s="118">
-        <f>G1</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="162">
-        <f>G9</f>
-        <v>0</v>
-      </c>
-      <c r="L32"/>
-      <c r="M32" s="181" t="s">
-        <v>24</v>
-      </c>
-      <c r="N32" s="182"/>
-      <c r="O32" s="175"/>
-      <c r="P32" s="176"/>
-      <c r="Q32" s="171"/>
-      <c r="R32" s="172"/>
-      <c r="S32" s="173"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="26"/>
-      <c r="W32" s="86" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="I33" s="118">
-        <f>H1</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="162">
-        <f>H9</f>
-        <v>0</v>
-      </c>
-      <c r="L33"/>
-      <c r="M33" s="83" t="s">
-        <v>25</v>
-      </c>
-      <c r="N33" s="85"/>
-      <c r="O33" s="175"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="171"/>
-      <c r="R33" s="172"/>
-      <c r="S33" s="173"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="26"/>
-      <c r="W33" s="138" t="e">
-        <f>W30-W27</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
-      <c r="I34" s="118">
-        <f>I1</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="162">
-        <f>I9</f>
-        <v>0</v>
-      </c>
-      <c r="L34" s="8"/>
-      <c r="M34" s="199" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" s="200"/>
-      <c r="O34" s="201"/>
-      <c r="P34" s="202"/>
-      <c r="Q34" s="171">
-        <v>1000000</v>
-      </c>
-      <c r="R34" s="172"/>
-      <c r="S34" s="173"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="24"/>
-    </row>
-    <row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
-      <c r="D35" s="31"/>
-      <c r="I35" s="45">
-        <f>J1</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="27">
-        <f>J9</f>
-        <v>0</v>
-      </c>
-      <c r="L35"/>
-      <c r="M35" s="209" t="s">
-        <v>27</v>
-      </c>
-      <c r="N35" s="210"/>
-      <c r="O35" s="211"/>
-      <c r="P35" s="197" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="197" t="s">
-        <v>29</v>
-      </c>
-      <c r="S35" s="198"/>
-      <c r="T35" s="197" t="s">
-        <v>30</v>
-      </c>
-      <c r="U35" s="198"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-    </row>
-    <row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="9"/>
-      <c r="I36" s="45">
-        <f>K1</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="27">
-        <f>K9</f>
-        <v>0</v>
-      </c>
-      <c r="L36"/>
-      <c r="M36" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="N36" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q36" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="R36" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="S36" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="T36" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="U36" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-    </row>
-    <row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="1"/>
-      <c r="I37" s="45">
-        <f>L1</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="27">
-        <f>L9</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="148">
-        <f>SUM(O41)</f>
-        <v>0</v>
-      </c>
-      <c r="L37"/>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01/01/2026</t>
-        </is>
-      </c>
-      <c r="N37" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O37" s="39">
-        <v>100000</v>
-      </c>
-      <c r="P37" s="40"/>
-      <c r="Q37" s="81"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="82"/>
-      <c r="T37" s="42"/>
-      <c r="U37" s="78"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="20"/>
-      <c r="C38" s="32"/>
-      <c r="I38" s="134"/>
-      <c r="J38"/>
-      <c r="L38" s="114">
-        <v>2</v>
-      </c>
-      <c r="M38" s="207" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="208"/>
-      <c r="O38" s="46">
-        <v>300000</v>
-      </c>
-      <c r="P38" s="42"/>
-      <c r="Q38" s="79"/>
-      <c r="R38" s="44"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="42"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B39" s="20"/>
-      <c r="C39" s="32"/>
-      <c r="I39" s="134"/>
-      <c r="J39"/>
-      <c r="K39" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L39" s="114">
-        <v>3</v>
-      </c>
-      <c r="M39" s="37"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="42"/>
-      <c r="Q39" s="72"/>
-      <c r="R39" s="44"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="42"/>
-      <c r="U39" s="72"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-    </row>
-    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="20"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="47"/>
-      <c r="I40" s="134"/>
-      <c r="J40"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="114">
-        <v>4</v>
-      </c>
-      <c r="M40" s="37"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="42"/>
-      <c r="Q40" s="70"/>
-      <c r="R40" s="44"/>
-      <c r="S40" s="78"/>
-      <c r="T40" s="42"/>
-      <c r="U40" s="72"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-    </row>
-    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="20"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="I41" s="133"/>
-      <c r="J41"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="114">
-        <v>5</v>
-      </c>
-      <c r="M41" s="37"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="42"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="78"/>
-      <c r="T41" s="42"/>
-      <c r="U41" s="72"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-    </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B42" s="20"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="51"/>
-      <c r="I42" s="135"/>
-      <c r="J42" s="57"/>
-      <c r="L42" s="114">
-        <v>6</v>
-      </c>
-      <c r="M42" s="37"/>
-      <c r="N42" s="38"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="70"/>
-      <c r="R42" s="44"/>
-      <c r="S42" s="77"/>
-      <c r="T42" s="42"/>
-      <c r="U42" s="72"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-    </row>
-    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="112"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="206"/>
-      <c r="E43" s="206"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="8"/>
-      <c r="I43" s="136"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="24" t="e">
-        <f>O38+O65</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L43" s="114">
-        <v>7</v>
-      </c>
-      <c r="M43" s="37"/>
-      <c r="N43" s="38"/>
-      <c r="O43" s="39"/>
-      <c r="P43" s="42"/>
-      <c r="Q43" s="70"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="71"/>
-      <c r="T43" s="42"/>
-      <c r="U43" s="72"/>
-    </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="206"/>
-      <c r="E44" s="206"/>
-      <c r="F44" s="52"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="24"/>
-      <c r="L44" s="114">
-        <v>8</v>
-      </c>
-      <c r="M44" s="37"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="42"/>
-      <c r="Q44" s="70"/>
-      <c r="R44" s="42"/>
-      <c r="S44" s="71"/>
-      <c r="T44" s="42"/>
-      <c r="U44" s="72"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="206"/>
-      <c r="E45" s="206"/>
-      <c r="F45" s="23"/>
-      <c r="H45" s="68"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="57"/>
-      <c r="L45" s="114">
-        <v>9</v>
-      </c>
-      <c r="M45" s="37"/>
-      <c r="N45" s="38"/>
-      <c r="O45" s="39"/>
-      <c r="P45" s="42"/>
-      <c r="Q45" s="70"/>
-      <c r="R45" s="42"/>
-      <c r="S45" s="76"/>
-      <c r="T45" s="42"/>
-      <c r="U45" s="72"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="20"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="206"/>
-      <c r="E46" s="206"/>
-      <c r="F46" s="53"/>
-      <c r="H46" s="68"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="57"/>
-      <c r="L46" s="114">
-        <v>10</v>
-      </c>
-      <c r="M46" s="37"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="39"/>
-      <c r="P46" s="42"/>
-      <c r="Q46" s="70"/>
-      <c r="R46" s="42"/>
-      <c r="S46" s="71"/>
-      <c r="T46" s="42"/>
-      <c r="U46" s="72"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="206"/>
-      <c r="E47" s="206"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="57"/>
-      <c r="K47" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L47" s="114">
-        <v>11</v>
-      </c>
-      <c r="M47" s="37"/>
-      <c r="N47" s="38"/>
-      <c r="O47" s="39"/>
-      <c r="P47" s="42"/>
-      <c r="Q47" s="70"/>
-      <c r="R47" s="42"/>
-      <c r="S47" s="71"/>
-      <c r="T47" s="42"/>
-      <c r="U47" s="72"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="206"/>
-      <c r="E48" s="206"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="57"/>
-      <c r="L48" s="114">
-        <v>12</v>
-      </c>
-      <c r="M48" s="37"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="39"/>
-      <c r="P48" s="42"/>
-      <c r="Q48" s="70"/>
-      <c r="R48" s="42"/>
-      <c r="S48" s="71"/>
-      <c r="T48" s="44"/>
-      <c r="U48" s="72"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="206"/>
-      <c r="E49" s="206"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="57"/>
-      <c r="L49" s="114">
-        <v>13</v>
-      </c>
-      <c r="M49" s="37"/>
-      <c r="N49" s="38"/>
-      <c r="O49" s="39"/>
-      <c r="P49" s="42"/>
-      <c r="Q49" s="70"/>
-      <c r="R49" s="42"/>
-      <c r="S49" s="71"/>
-      <c r="T49" s="44"/>
-      <c r="U49" s="72"/>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="57"/>
-      <c r="L50" s="114">
-        <v>14</v>
-      </c>
-      <c r="M50" s="37"/>
-      <c r="N50" s="38"/>
-      <c r="O50" s="39"/>
-      <c r="P50" s="42"/>
-      <c r="Q50" s="70"/>
-      <c r="R50" s="42"/>
-      <c r="S50" s="71"/>
-      <c r="T50" s="44"/>
-      <c r="U50" s="72"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A51" s="20"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="220"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="50"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="57"/>
-      <c r="L51" s="114">
-        <v>15</v>
-      </c>
-      <c r="M51" s="37"/>
-      <c r="N51" s="38"/>
-      <c r="O51" s="39"/>
-      <c r="P51" s="40"/>
-      <c r="Q51" s="70"/>
-      <c r="R51" s="42"/>
-      <c r="S51" s="71"/>
-      <c r="T51" s="44"/>
-      <c r="U51" s="72"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A52" s="20"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="221"/>
-      <c r="E52" s="221"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="54"/>
-      <c r="J52" s="57"/>
-      <c r="L52" s="114">
-        <v>16</v>
-      </c>
-      <c r="M52" s="37"/>
-      <c r="N52" s="38"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="40"/>
-      <c r="Q52" s="70"/>
-      <c r="R52" s="42"/>
-      <c r="S52" s="71"/>
-      <c r="T52" s="44"/>
-      <c r="U52" s="72"/>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="25"/>
-      <c r="B53" s="55"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="217"/>
-      <c r="E53" s="217"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="54"/>
-      <c r="J53" s="57"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="37"/>
-      <c r="N53" s="38"/>
-      <c r="O53" s="39"/>
-      <c r="P53" s="42"/>
-      <c r="Q53" s="70"/>
-      <c r="R53" s="42"/>
-      <c r="S53" s="71"/>
-      <c r="T53" s="44"/>
-      <c r="U53" s="72"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="20"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="217"/>
-      <c r="E54" s="217"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="50"/>
-      <c r="I54" s="54"/>
-      <c r="J54" s="57"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="37"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="39"/>
-      <c r="P54" s="42"/>
-      <c r="Q54" s="70"/>
-      <c r="R54" s="42"/>
-      <c r="S54" s="71"/>
-      <c r="T54" s="44"/>
-      <c r="U54" s="72"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A55" s="20"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="50"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="57"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="37"/>
-      <c r="N55" s="38"/>
-      <c r="O55" s="39"/>
-      <c r="P55" s="42"/>
-      <c r="Q55" s="70"/>
-      <c r="R55" s="42"/>
-      <c r="S55" s="71"/>
-      <c r="T55" s="44"/>
-      <c r="U55" s="72"/>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A56" s="20"/>
-      <c r="B56"/>
-      <c r="C56" s="43"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="50"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="57"/>
-      <c r="L56" s="18"/>
-      <c r="M56" s="37"/>
-      <c r="N56" s="38"/>
-      <c r="O56" s="39"/>
-      <c r="P56" s="42"/>
-      <c r="Q56" s="70"/>
-      <c r="R56" s="42"/>
-      <c r="S56" s="71"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="72"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A57" s="20"/>
-      <c r="B57"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="50"/>
-      <c r="I57" s="54"/>
-      <c r="J57" s="57"/>
-      <c r="L57" s="18"/>
-      <c r="M57" s="37"/>
-      <c r="N57" s="38"/>
-      <c r="O57" s="39"/>
-      <c r="P57" s="42"/>
-      <c r="Q57" s="70"/>
-      <c r="R57" s="42"/>
-      <c r="S57" s="71"/>
-      <c r="T57" s="44"/>
-      <c r="U57" s="72"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A58" s="20"/>
-      <c r="B58"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="50"/>
-      <c r="I58" s="54"/>
-      <c r="J58" s="57"/>
-      <c r="L58" s="18"/>
-      <c r="M58" s="37"/>
-      <c r="N58" s="38"/>
-      <c r="O58" s="39"/>
-      <c r="P58" s="42"/>
-      <c r="Q58" s="70"/>
-      <c r="R58" s="42"/>
-      <c r="S58" s="71"/>
-      <c r="T58" s="44"/>
-      <c r="U58" s="72"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A59" s="20"/>
-      <c r="B59"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="50"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="57"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="37"/>
-      <c r="N59" s="38"/>
-      <c r="O59" s="39"/>
-      <c r="P59" s="42"/>
-      <c r="Q59" s="70"/>
-      <c r="R59" s="42"/>
-      <c r="S59" s="71"/>
-      <c r="T59" s="44"/>
-      <c r="U59" s="72"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="25"/>
-      <c r="B60"/>
-      <c r="C60" s="43"/>
-      <c r="D60" s="217"/>
-      <c r="E60" s="217"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="50"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="57"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="37"/>
-      <c r="N60" s="38"/>
-      <c r="O60" s="39"/>
-      <c r="P60" s="42"/>
-      <c r="Q60" s="70"/>
-      <c r="R60" s="42"/>
-      <c r="S60" s="71"/>
-      <c r="T60" s="44"/>
-      <c r="U60" s="72"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A61" s="25"/>
-      <c r="B61"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="50"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="57"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="37"/>
-      <c r="N61" s="38"/>
-      <c r="O61" s="39"/>
-      <c r="P61" s="42"/>
-      <c r="Q61" s="161"/>
-      <c r="R61" s="93"/>
-      <c r="S61" s="92"/>
-      <c r="T61" s="44"/>
-      <c r="U61" s="72"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A62" s="25"/>
-      <c r="B62"/>
-      <c r="C62" s="43"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="50"/>
-      <c r="I62" s="54"/>
-      <c r="J62" s="57"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="37"/>
-      <c r="N62" s="38"/>
-      <c r="O62" s="39"/>
-      <c r="P62" s="42"/>
-      <c r="Q62" s="161"/>
-      <c r="R62" s="93"/>
-      <c r="S62" s="92"/>
-      <c r="T62" s="44"/>
-      <c r="U62" s="72"/>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A63" s="25"/>
-      <c r="B63"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="50"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="57"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="37"/>
-      <c r="N63" s="38"/>
-      <c r="O63" s="39"/>
-      <c r="P63" s="42"/>
-      <c r="Q63" s="161"/>
-      <c r="R63" s="93"/>
-      <c r="S63" s="92"/>
-      <c r="T63" s="44"/>
-      <c r="U63" s="72"/>
-    </row>
-    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="25"/>
-      <c r="B64"/>
-      <c r="C64" s="43"/>
-      <c r="D64" s="217"/>
-      <c r="E64" s="217"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="50"/>
-      <c r="I64" s="54"/>
-      <c r="J64" s="57"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="37"/>
-      <c r="N64" s="38"/>
-      <c r="O64" s="39"/>
-      <c r="P64" s="42"/>
-      <c r="Q64" s="88"/>
-      <c r="R64" s="93"/>
-      <c r="S64" s="92"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="75"/>
-    </row>
-    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="25"/>
-      <c r="B65"/>
-      <c r="C65" s="43"/>
-      <c r="D65" s="217"/>
-      <c r="E65" s="217"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="50"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="57"/>
-      <c r="L65"/>
-      <c r="M65" s="207" t="s">
-        <v>34</v>
-      </c>
-      <c r="N65" s="208"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q65" s="46"/>
-      <c r="R65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S65" s="46"/>
-      <c r="T65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U65" s="46"/>
-    </row>
-    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="25"/>
-      <c r="B66"/>
-      <c r="C66" s="95"/>
-      <c r="D66" s="217"/>
-      <c r="E66" s="217"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="50"/>
-      <c r="I66" s="54"/>
-      <c r="J66"/>
-      <c r="L66"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="59"/>
-      <c r="O66" s="74"/>
-      <c r="P66" s="23"/>
-      <c r="Q66" s="73"/>
-      <c r="R66" s="74"/>
-      <c r="S66" s="74"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="25"/>
-      <c r="B67"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="50"/>
-      <c r="I67" s="54"/>
-      <c r="J67"/>
-      <c r="L67"/>
-      <c r="M67" s="197" t="s">
-        <v>47</v>
-      </c>
-      <c r="N67" s="216"/>
-      <c r="O67" s="198"/>
-      <c r="P67" s="218"/>
-      <c r="Q67" s="219"/>
-      <c r="R67" s="197" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" s="216"/>
-      <c r="T67" s="212" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U67" s="213"/>
-    </row>
-    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="25"/>
-      <c r="B68"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="217"/>
-      <c r="E68" s="217"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="50"/>
-      <c r="I68" s="54"/>
-      <c r="J68"/>
-      <c r="L68"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="87"/>
-      <c r="O68" s="87"/>
-      <c r="P68" s="61"/>
-      <c r="Q68" s="62"/>
-      <c r="R68" s="62"/>
-      <c r="S68" s="62"/>
-      <c r="T68" s="60"/>
-      <c r="U68" s="60"/>
-    </row>
-    <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="25"/>
-      <c r="B69" s="95"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="217"/>
-      <c r="E69" s="217"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="50"/>
-      <c r="I69" s="54"/>
-      <c r="J69"/>
-      <c r="L69"/>
-      <c r="M69" s="207" t="s">
-        <v>35</v>
-      </c>
-      <c r="N69" s="214"/>
-      <c r="O69" s="214"/>
-      <c r="P69" s="214"/>
-      <c r="Q69" s="214"/>
-      <c r="R69" s="214"/>
-      <c r="S69" s="214"/>
-      <c r="T69" s="214"/>
-      <c r="U69" s="215"/>
-      <c r="V69" s="55"/>
-    </row>
-    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="25"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="217"/>
-      <c r="E70" s="217"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="54"/>
-      <c r="J70"/>
-      <c r="L70" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M70" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N70" s="157"/>
-      <c r="O70" s="157"/>
-      <c r="P70" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q70" s="157"/>
-      <c r="R70" s="157"/>
-      <c r="S70" s="157"/>
-      <c r="T70" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U70" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V70" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W70" s="170" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="25"/>
-      <c r="B71" s="130"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="217"/>
-      <c r="E71" s="217"/>
-      <c r="F71" s="67"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="54"/>
-      <c r="J71" s="23"/>
-      <c r="L71"/>
-      <c r="M71" s="63"/>
-      <c r="N71" s="64"/>
-      <c r="O71" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P71" s="66"/>
-      <c r="Q71" s="65"/>
-      <c r="R71" s="226" t="s">
-        <v>6</v>
-      </c>
-      <c r="S71" s="226"/>
-      <c r="T71" s="159"/>
-      <c r="U71" s="160"/>
-      <c r="V71" s="55"/>
-    </row>
-    <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="55"/>
-      <c r="C72" s="94"/>
-      <c r="D72" s="217"/>
-      <c r="E72" s="217"/>
-      <c r="F72" s="67"/>
-      <c r="I72" s="130"/>
-      <c r="L72"/>
-      <c r="M72" s="89"/>
-      <c r="N72" s="90"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="91"/>
-      <c r="Q72" s="60"/>
-      <c r="R72" s="224"/>
-      <c r="S72" s="224"/>
-      <c r="T72" s="69"/>
-      <c r="U72" s="100"/>
-      <c r="V72" s="55"/>
-    </row>
-    <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="53"/>
-      <c r="B73" s="94"/>
-      <c r="C73" s="94"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="67"/>
-      <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12345</t>
-        </is>
-      </c>
-      <c r="M73" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
-      <c r="N73" s="90"/>
-      <c r="O73" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P73" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="224" t="s">
-        <v>10</v>
-      </c>
-      <c r="S73" s="224"/>
-      <c r="T73" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U73" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="V73" s="55"/>
-    </row>
-    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L74" s="49"/>
-      <c r="M74" s="89"/>
-      <c r="N74" s="90"/>
-      <c r="O74" s="147"/>
-      <c r="P74" s="91"/>
-      <c r="Q74" s="60"/>
-      <c r="R74" s="224"/>
-      <c r="S74" s="224"/>
-      <c r="T74" s="69"/>
-      <c r="U74" s="100"/>
-      <c r="V74" s="55"/>
-    </row>
-    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L75" s="49"/>
-      <c r="M75" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="N75" s="164"/>
-      <c r="O75" s="165"/>
-      <c r="P75" s="166"/>
-      <c r="Q75" s="167"/>
-      <c r="R75" s="225"/>
-      <c r="S75" s="225"/>
-      <c r="T75" s="222"/>
-      <c r="U75" s="223"/>
-      <c r="V75" s="55"/>
-    </row>
-    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L76" s="49"/>
-      <c r="M76" s="163" t="s">
-        <v>62</v>
-      </c>
-      <c r="N76" s="164"/>
-      <c r="O76" s="165"/>
-      <c r="P76" s="166"/>
-      <c r="Q76" s="167"/>
-      <c r="R76" s="168"/>
-      <c r="S76" s="168"/>
-      <c r="T76" s="222"/>
-      <c r="U76" s="223"/>
-      <c r="V76" s="55"/>
-    </row>
-    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L77" s="49"/>
-      <c r="M77" s="99"/>
-      <c r="N77" s="68"/>
-      <c r="O77" s="147"/>
-      <c r="P77" s="91"/>
-      <c r="Q77" s="60"/>
-      <c r="R77" s="60"/>
-      <c r="S77" s="60"/>
-      <c r="T77" s="69"/>
-      <c r="U77" s="100"/>
-      <c r="V77" s="55"/>
-    </row>
-    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L78" s="49"/>
-      <c r="M78" s="106" t="s">
-        <v>11</v>
-      </c>
-      <c r="N78" s="107">
-        <f>SUM(N76:N77)</f>
-        <v>0</v>
-      </c>
-      <c r="O78" s="101"/>
-      <c r="P78" s="103"/>
-      <c r="Q78" s="102"/>
-      <c r="R78" s="102"/>
-      <c r="S78" s="102"/>
-      <c r="T78" s="104"/>
-      <c r="U78" s="105"/>
-      <c r="V78" s="55"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M79"/>
-      <c r="O79" s="5"/>
-      <c r="Q79"/>
-      <c r="S79"/>
-      <c r="T79" s="6"/>
-      <c r="V79" s="55"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O80"/>
-      <c r="V80" s="55"/>
-    </row>
-    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
-      <c r="V81" s="55"/>
-    </row>
-    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V82" s="55"/>
-    </row>
-    <row r="83" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V83" s="55"/>
-    </row>
-    <row r="84" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V84" s="55"/>
-    </row>
-    <row r="85" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V85" s="55"/>
-    </row>
-    <row r="86" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V86" s="55"/>
-    </row>
-    <row r="87" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V87" s="55"/>
-    </row>
-    <row r="88" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V88" s="55"/>
-    </row>
-    <row r="89" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V89" s="55"/>
-    </row>
-    <row r="90" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V90" s="55"/>
-    </row>
-    <row r="91" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V91" s="55"/>
-    </row>
-    <row r="92" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V92" s="55"/>
-    </row>
-    <row r="93" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V93" s="55"/>
-    </row>
-    <row r="94" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V94" s="55"/>
-    </row>
-    <row r="95" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V95" s="55"/>
-    </row>
-    <row r="96" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V96" s="55"/>
-    </row>
-    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V97" s="55"/>
-    </row>
-    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V98" s="55"/>
-    </row>
-    <row r="99" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V99" s="55"/>
-    </row>
-    <row r="100" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V100" s="55"/>
-    </row>
-    <row r="101" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V101" s="55"/>
-    </row>
-    <row r="102" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V102" s="55"/>
-    </row>
-    <row r="103" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V103" s="55"/>
-    </row>
-    <row r="104" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V104" s="55"/>
-    </row>
-    <row r="105" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V105" s="55"/>
-    </row>
-    <row r="106" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V106" s="55"/>
-    </row>
-    <row r="107" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V107" s="55"/>
-    </row>
-    <row r="108" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V108" s="55"/>
-    </row>
-    <row r="109" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V109" s="55"/>
-    </row>
-    <row r="110" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V110" s="55"/>
-    </row>
-    <row r="111" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V111" s="55"/>
-    </row>
-    <row r="112" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V112" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="M22:U22"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N24:S24"/>
-  </mergeCells>
-  <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4320,7 +2293,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA LOPEZ</t>
+          <t xml:space="preserve">ANA</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -4432,7 +2405,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">67890</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -4462,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -4491,7 +2464,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -4544,11 +2517,11 @@
       <c r="A9" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="171">
-        <v>450000</v>
-      </c>
-      <c r="C9" s="172"/>
-      <c r="D9" s="173"/>
+      <c r="B9" s="227">
+        <v>90000</v>
+      </c>
+      <c r="C9" s="228"/>
+      <c r="D9" s="229"/>
       <c r="E9" s="110"/>
       <c r="F9" s="119"/>
       <c r="G9" s="110"/>
@@ -4573,11 +2546,11 @@
       <c r="A10" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="171">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="172"/>
-      <c r="D10" s="173"/>
+      <c r="B10" s="227">
+        <v>10000</v>
+      </c>
+      <c r="C10" s="228"/>
+      <c r="D10" s="229"/>
       <c r="E10" s="110"/>
       <c r="F10" s="119"/>
       <c r="G10" s="110"/>
@@ -4602,11 +2575,9 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="171">
-        <v>300000</v>
-      </c>
-      <c r="C11" s="172"/>
-      <c r="D11" s="173"/>
+      <c r="B11" s="227"/>
+      <c r="C11" s="228"/>
+      <c r="D11" s="229"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
       <c r="G11" s="110"/>
@@ -4631,9 +2602,9 @@
       <c r="A12" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="171"/>
-      <c r="C12" s="172"/>
-      <c r="D12" s="173"/>
+      <c r="B12" s="227"/>
+      <c r="C12" s="228"/>
+      <c r="D12" s="229"/>
       <c r="E12" s="110"/>
       <c r="F12" s="119"/>
       <c r="G12" s="110"/>
@@ -4658,9 +2629,9 @@
       <c r="A13" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="173"/>
+      <c r="B13" s="227"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="229"/>
       <c r="E13" s="110"/>
       <c r="F13" s="119"/>
       <c r="G13" s="110"/>
@@ -4685,9 +2656,9 @@
       <c r="A14" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="171"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="173"/>
+      <c r="B14" s="227"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="229"/>
       <c r="E14" s="110"/>
       <c r="F14" s="119"/>
       <c r="G14" s="110"/>
@@ -4712,9 +2683,9 @@
       <c r="A15" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="171"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="173"/>
+      <c r="B15" s="227"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="229"/>
       <c r="E15" s="110"/>
       <c r="F15" s="119"/>
       <c r="G15" s="110"/>
@@ -4739,9 +2710,9 @@
       <c r="A16" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="171"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="173"/>
+      <c r="B16" s="227"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="229"/>
       <c r="E16" s="110"/>
       <c r="F16" s="119"/>
       <c r="G16" s="110"/>
@@ -4766,9 +2737,9 @@
       <c r="A17" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="171"/>
-      <c r="C17" s="172"/>
-      <c r="D17" s="173"/>
+      <c r="B17" s="227"/>
+      <c r="C17" s="228"/>
+      <c r="D17" s="229"/>
       <c r="E17" s="110"/>
       <c r="F17" s="119"/>
       <c r="G17" s="110"/>
@@ -5027,17 +2998,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="174" t="s">
+      <c r="M22" s="214" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
+      <c r="N22" s="214"/>
+      <c r="O22" s="214"/>
+      <c r="P22" s="214"/>
+      <c r="Q22" s="214"/>
+      <c r="R22" s="214"/>
+      <c r="S22" s="214"/>
+      <c r="T22" s="214"/>
+      <c r="U22" s="214"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -5046,21 +3017,17 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24/06/2026</t>
-        </is>
-      </c>
-      <c r="O23" s="186"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="186"/>
-      <c r="R23" s="186"/>
-      <c r="S23" s="187"/>
+      <c r="N23" s="221"/>
+      <c r="O23" s="222"/>
+      <c r="P23" s="222"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="222"/>
+      <c r="S23" s="223"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -5073,22 +3040,22 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="188" t="s">
+      <c r="N24" s="224" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="189"/>
-      <c r="P24" s="189"/>
-      <c r="Q24" s="189"/>
-      <c r="R24" s="189"/>
-      <c r="S24" s="190"/>
+      <c r="O24" s="225"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="225"/>
+      <c r="R24" s="225"/>
+      <c r="S24" s="226"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>1000000</v>
-      </c>
-      <c r="W24" s="141" t="str">
-        <f>U23</f>
+        <v>500000</v>
+      </c>
+      <c r="W24" s="141">
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -5100,21 +3067,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="193" t="s">
+      <c r="M25" s="209" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="194"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="196"/>
-      <c r="Q25" s="171">
-        <v>450000</v>
-      </c>
-      <c r="R25" s="172"/>
-      <c r="S25" s="173"/>
-      <c r="T25" s="191" t="s">
+      <c r="N25" s="210"/>
+      <c r="O25" s="211"/>
+      <c r="P25" s="212"/>
+      <c r="Q25" s="174">
+        <v>90000</v>
+      </c>
+      <c r="R25" s="175"/>
+      <c r="S25" s="176"/>
+      <c r="T25" s="207" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="192"/>
+      <c r="U25" s="208"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -5130,11 +3097,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="171">
-        <v>50000</v>
-      </c>
-      <c r="R26" s="172"/>
-      <c r="S26" s="173"/>
+      <c r="Q26" s="174">
+        <v>10000</v>
+      </c>
+      <c r="R26" s="175"/>
+      <c r="S26" s="176"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -5152,20 +3119,18 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="175"/>
-      <c r="P27" s="176"/>
-      <c r="Q27" s="171">
-        <v>300000</v>
-      </c>
-      <c r="R27" s="172"/>
-      <c r="S27" s="173"/>
-      <c r="T27" s="183" t="s">
+      <c r="O27" s="199"/>
+      <c r="P27" s="200"/>
+      <c r="Q27" s="174"/>
+      <c r="R27" s="175"/>
+      <c r="S27" s="176"/>
+      <c r="T27" s="219" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="184"/>
+      <c r="U27" s="220"/>
       <c r="V27" s="19"/>
-      <c r="W27" s="97" t="str">
-        <f>U24</f>
+      <c r="W27" s="97">
+        <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -5178,19 +3143,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="181" t="s">
+      <c r="M28" s="194" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="182"/>
-      <c r="O28" s="175"/>
-      <c r="P28" s="176"/>
-      <c r="Q28" s="171"/>
-      <c r="R28" s="172"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="179" t="s">
+      <c r="N28" s="195"/>
+      <c r="O28" s="199"/>
+      <c r="P28" s="200"/>
+      <c r="Q28" s="174"/>
+      <c r="R28" s="175"/>
+      <c r="S28" s="176"/>
+      <c r="T28" s="217" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="180"/>
+      <c r="U28" s="218"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -5205,19 +3170,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="181" t="s">
+      <c r="M29" s="194" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="182"/>
-      <c r="O29" s="175"/>
-      <c r="P29" s="176"/>
-      <c r="Q29" s="171"/>
-      <c r="R29" s="172"/>
-      <c r="S29" s="173"/>
-      <c r="T29" s="177" t="s">
+      <c r="N29" s="195"/>
+      <c r="O29" s="199"/>
+      <c r="P29" s="200"/>
+      <c r="Q29" s="174"/>
+      <c r="R29" s="175"/>
+      <c r="S29" s="176"/>
+      <c r="T29" s="215" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="178"/>
+      <c r="U29" s="216"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -5233,19 +3198,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="181" t="s">
+      <c r="M30" s="194" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="182"/>
-      <c r="O30" s="175"/>
-      <c r="P30" s="203"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="172"/>
-      <c r="S30" s="173"/>
-      <c r="T30" s="204" t="s">
+      <c r="N30" s="195"/>
+      <c r="O30" s="199"/>
+      <c r="P30" s="213"/>
+      <c r="Q30" s="174"/>
+      <c r="R30" s="175"/>
+      <c r="S30" s="176"/>
+      <c r="T30" s="201" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="205"/>
+      <c r="U30" s="202"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -5262,15 +3227,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="181" t="s">
+      <c r="M31" s="194" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="182"/>
-      <c r="O31" s="175"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="171"/>
-      <c r="R31" s="172"/>
-      <c r="S31" s="173"/>
+      <c r="N31" s="195"/>
+      <c r="O31" s="199"/>
+      <c r="P31" s="200"/>
+      <c r="Q31" s="174"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="176"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -5285,15 +3250,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="181" t="s">
+      <c r="M32" s="194" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="182"/>
-      <c r="O32" s="175"/>
-      <c r="P32" s="176"/>
-      <c r="Q32" s="171"/>
-      <c r="R32" s="172"/>
-      <c r="S32" s="173"/>
+      <c r="N32" s="195"/>
+      <c r="O32" s="199"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="174"/>
+      <c r="R32" s="175"/>
+      <c r="S32" s="176"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -5315,11 +3280,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="175"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="171"/>
-      <c r="R33" s="172"/>
-      <c r="S33" s="173"/>
+      <c r="O33" s="199"/>
+      <c r="P33" s="200"/>
+      <c r="Q33" s="174"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="176"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -5338,17 +3303,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="199" t="s">
+      <c r="M34" s="203" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="200"/>
-      <c r="O34" s="201"/>
-      <c r="P34" s="202"/>
-      <c r="Q34" s="171">
-        <v>1000000</v>
-      </c>
-      <c r="R34" s="172"/>
-      <c r="S34" s="173"/>
+      <c r="N34" s="204"/>
+      <c r="O34" s="205"/>
+      <c r="P34" s="206"/>
+      <c r="Q34" s="174">
+        <v>500000</v>
+      </c>
+      <c r="R34" s="175"/>
+      <c r="S34" s="176"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -5366,23 +3331,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="209" t="s">
+      <c r="M35" s="196" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="210"/>
-      <c r="O35" s="211"/>
-      <c r="P35" s="197" t="s">
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="189" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="197" t="s">
+      <c r="Q35" s="193"/>
+      <c r="R35" s="189" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="198"/>
-      <c r="T35" s="197" t="s">
+      <c r="S35" s="193"/>
+      <c r="T35" s="189" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="198"/>
+      <c r="U35" s="193"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -5442,19 +3407,9 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01/01/2026</t>
-        </is>
-      </c>
-      <c r="N37" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O37" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -5474,13 +3429,11 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="207" t="s">
+      <c r="M38" s="179" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="208"/>
-      <c r="O38" s="46">
-        <v>300000</v>
-      </c>
+      <c r="N38" s="180"/>
+      <c r="O38" s="46"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -5587,8 +3540,8 @@
       <c r="A43" s="112"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="206"/>
-      <c r="E43" s="206"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
       <c r="F43" s="51"/>
       <c r="G43" s="8"/>
       <c r="I43" s="136"/>
@@ -5614,8 +3567,8 @@
       <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="206"/>
-      <c r="E44" s="206"/>
+      <c r="D44" s="183"/>
+      <c r="E44" s="183"/>
       <c r="F44" s="52"/>
       <c r="H44" s="68"/>
       <c r="I44" s="13"/>
@@ -5638,8 +3591,8 @@
       <c r="A45" s="25"/>
       <c r="B45" s="25"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="206"/>
-      <c r="E45" s="206"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
       <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
@@ -5661,8 +3614,8 @@
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="206"/>
-      <c r="E46" s="206"/>
+      <c r="D46" s="183"/>
+      <c r="E46" s="183"/>
       <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
@@ -5684,8 +3637,8 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="206"/>
-      <c r="E47" s="206"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="183"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
       <c r="H47" s="68"/>
@@ -5712,8 +3665,8 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="206"/>
-      <c r="E48" s="206"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="183"/>
       <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
@@ -5736,8 +3689,8 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="206"/>
-      <c r="E49" s="206"/>
+      <c r="D49" s="183"/>
+      <c r="E49" s="183"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
       <c r="H49" s="50"/>
@@ -5784,8 +3737,8 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="220"/>
+      <c r="D51" s="184"/>
+      <c r="E51" s="184"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
@@ -5808,8 +3761,8 @@
       <c r="A52" s="20"/>
       <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="221"/>
-      <c r="E52" s="221"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="182"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
@@ -5832,8 +3785,8 @@
       <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="217"/>
-      <c r="E53" s="217"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
@@ -5854,8 +3807,8 @@
       <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="217"/>
-      <c r="E54" s="217"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="181"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -5986,8 +3939,8 @@
       <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="217"/>
-      <c r="E60" s="217"/>
+      <c r="D60" s="181"/>
+      <c r="E60" s="181"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -6074,8 +4027,8 @@
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="217"/>
-      <c r="E64" s="217"/>
+      <c r="D64" s="181"/>
+      <c r="E64" s="181"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -6096,18 +4049,18 @@
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="217"/>
-      <c r="E65" s="217"/>
+      <c r="D65" s="181"/>
+      <c r="E65" s="181"/>
       <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
       <c r="L65"/>
-      <c r="M65" s="207" t="s">
+      <c r="M65" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="N65" s="208"/>
+      <c r="N65" s="180"/>
       <c r="O65" s="46"/>
       <c r="P65" s="56" t="s">
         <v>11</v>
@@ -6126,8 +4079,8 @@
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="95"/>
-      <c r="D66" s="217"/>
-      <c r="E66" s="217"/>
+      <c r="D66" s="181"/>
+      <c r="E66" s="181"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
@@ -6155,28 +4108,28 @@
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="197" t="s">
+      <c r="M67" s="189" t="s">
         <v>47</v>
       </c>
-      <c r="N67" s="216"/>
-      <c r="O67" s="198"/>
-      <c r="P67" s="218"/>
-      <c r="Q67" s="219"/>
-      <c r="R67" s="197" t="s">
+      <c r="N67" s="190"/>
+      <c r="O67" s="193"/>
+      <c r="P67" s="191"/>
+      <c r="Q67" s="192"/>
+      <c r="R67" s="189" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="216"/>
-      <c r="T67" s="212" t="str">
+      <c r="S67" s="190"/>
+      <c r="T67" s="185" t="str">
         <f>Q25</f>
       </c>
-      <c r="U67" s="213"/>
+      <c r="U67" s="186"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="217"/>
-      <c r="E68" s="217"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
@@ -6197,33 +4150,33 @@
       <c r="A69" s="25"/>
       <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="217"/>
-      <c r="E69" s="217"/>
+      <c r="D69" s="181"/>
+      <c r="E69" s="181"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="207" t="s">
+      <c r="M69" s="179" t="s">
         <v>35</v>
       </c>
-      <c r="N69" s="214"/>
-      <c r="O69" s="214"/>
-      <c r="P69" s="214"/>
-      <c r="Q69" s="214"/>
-      <c r="R69" s="214"/>
-      <c r="S69" s="214"/>
-      <c r="T69" s="214"/>
-      <c r="U69" s="215"/>
+      <c r="N69" s="187"/>
+      <c r="O69" s="187"/>
+      <c r="P69" s="187"/>
+      <c r="Q69" s="187"/>
+      <c r="R69" s="187"/>
+      <c r="S69" s="187"/>
+      <c r="T69" s="187"/>
+      <c r="U69" s="188"/>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
       <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="217"/>
-      <c r="E70" s="217"/>
+      <c r="D70" s="181"/>
+      <c r="E70" s="181"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
@@ -6260,8 +4213,8 @@
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="217"/>
-      <c r="E71" s="217"/>
+      <c r="D71" s="181"/>
+      <c r="E71" s="181"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
@@ -6275,10 +4228,10 @@
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="65"/>
-      <c r="R71" s="226" t="s">
+      <c r="R71" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="S71" s="226"/>
+      <c r="S71" s="178"/>
       <c r="T71" s="159"/>
       <c r="U71" s="160"/>
       <c r="V71" s="55"/>
@@ -6286,8 +4239,8 @@
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" s="55"/>
       <c r="C72" s="94"/>
-      <c r="D72" s="217"/>
-      <c r="E72" s="217"/>
+      <c r="D72" s="181"/>
+      <c r="E72" s="181"/>
       <c r="F72" s="67"/>
       <c r="I72" s="130"/>
       <c r="L72"/>
@@ -6296,8 +4249,8 @@
       <c r="O72" s="18"/>
       <c r="P72" s="91"/>
       <c r="Q72" s="60"/>
-      <c r="R72" s="224"/>
-      <c r="S72" s="224"/>
+      <c r="R72" s="173"/>
+      <c r="S72" s="173"/>
       <c r="T72" s="69"/>
       <c r="U72" s="100"/>
       <c r="V72" s="55"/>
@@ -6310,38 +4263,20 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67890</t>
-        </is>
-      </c>
-      <c r="M73" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
+      <c r="L73" s="49"/>
+      <c r="M73" s="89"/>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
+      <c r="P73" s="91"/>
       <c r="Q73" s="60"/>
-      <c r="R73" s="224" t="s">
+      <c r="R73" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="224"/>
-      <c r="T73" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U73" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
+      <c r="S73" s="173"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -6351,8 +4286,8 @@
       <c r="O74" s="147"/>
       <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="224"/>
-      <c r="S74" s="224"/>
+      <c r="R74" s="173"/>
+      <c r="S74" s="173"/>
       <c r="T74" s="69"/>
       <c r="U74" s="100"/>
       <c r="V74" s="55"/>
@@ -6366,10 +4301,10 @@
       <c r="O75" s="165"/>
       <c r="P75" s="166"/>
       <c r="Q75" s="167"/>
-      <c r="R75" s="225"/>
-      <c r="S75" s="225"/>
-      <c r="T75" s="222"/>
-      <c r="U75" s="223"/>
+      <c r="R75" s="177"/>
+      <c r="S75" s="177"/>
+      <c r="T75" s="171"/>
+      <c r="U75" s="172"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -6383,8 +4318,8 @@
       <c r="Q76" s="167"/>
       <c r="R76" s="168"/>
       <c r="S76" s="168"/>
-      <c r="T76" s="222"/>
-      <c r="U76" s="223"/>
+      <c r="T76" s="171"/>
+      <c r="U76" s="172"/>
       <c r="V76" s="55"/>
     </row>
     <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -6532,73 +4467,7 @@
       <c r="V112" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="B10:D10"/>
+  <mergeCells count="72">
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="O29:P29"/>
@@ -6614,6 +4483,2348 @@
     <mergeCell ref="T27:U27"/>
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+  </mergeCells>
+  <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="3" customWidth="1"/>
+    <col min="7" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" style="4" customWidth="1"/>
+    <col min="16" max="19" width="11.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOB</t>
+        </is>
+      </c>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="143"/>
+      <c r="T1" s="143"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="129"/>
+    </row>
+    <row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="143"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="109"/>
+      <c r="V2" s="108"/>
+      <c r="W2" s="129"/>
+    </row>
+    <row r="3" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="143"/>
+      <c r="R3" s="143"/>
+      <c r="S3" s="143"/>
+      <c r="T3" s="143"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="131"/>
+      <c r="W3" s="132"/>
+    </row>
+    <row r="4" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="143"/>
+      <c r="T4" s="143"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="131"/>
+      <c r="W4" s="132"/>
+    </row>
+    <row r="5" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222</t>
+        </is>
+      </c>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="154"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="154"/>
+      <c r="Q5" s="154"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="143"/>
+      <c r="T5" s="143"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="124"/>
+      <c r="W5" s="123"/>
+    </row>
+    <row r="6" spans="1:23" s="49" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="127" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="123"/>
+      <c r="R6" s="143"/>
+      <c r="S6" s="143"/>
+      <c r="T6" s="143"/>
+      <c r="U6" s="121"/>
+      <c r="V6" s="123"/>
+      <c r="W6" s="123"/>
+    </row>
+    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="155">
+        <v>500000</v>
+      </c>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
+      <c r="I7" s="155"/>
+      <c r="J7" s="155"/>
+      <c r="K7" s="155"/>
+      <c r="L7" s="155"/>
+      <c r="M7" s="155"/>
+      <c r="N7" s="155"/>
+      <c r="O7" s="155"/>
+      <c r="P7" s="155"/>
+      <c r="Q7" s="155"/>
+      <c r="R7" s="144"/>
+      <c r="S7" s="144"/>
+      <c r="T7" s="144"/>
+      <c r="U7" s="113"/>
+      <c r="V7" s="110"/>
+      <c r="W7" s="110"/>
+    </row>
+    <row r="8" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="123"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="123"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="123"/>
+      <c r="T8" s="140"/>
+      <c r="U8" s="121"/>
+      <c r="V8" s="119"/>
+      <c r="W8" s="123"/>
+    </row>
+    <row r="9" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="227">
+        <v>90000</v>
+      </c>
+      <c r="C9" s="228"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="140"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="137"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="110"/>
+    </row>
+    <row r="10" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="128" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="227">
+        <v>10000</v>
+      </c>
+      <c r="C10" s="228"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="137"/>
+      <c r="T10" s="139"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="119"/>
+      <c r="W10" s="110"/>
+    </row>
+    <row r="11" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="128" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="227"/>
+      <c r="C11" s="228"/>
+      <c r="D11" s="229"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="120"/>
+      <c r="O11" s="110"/>
+      <c r="P11" s="140"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="140"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="139"/>
+      <c r="U11" s="113"/>
+      <c r="V11" s="119"/>
+      <c r="W11" s="110"/>
+    </row>
+    <row r="12" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="128" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="227"/>
+      <c r="C12" s="228"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="140"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="140"/>
+      <c r="S12" s="137"/>
+      <c r="T12" s="139"/>
+      <c r="U12" s="113"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="110"/>
+    </row>
+    <row r="13" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="128" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="227"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="110"/>
+      <c r="P13" s="140"/>
+      <c r="Q13" s="113"/>
+      <c r="R13" s="140"/>
+      <c r="S13" s="137"/>
+      <c r="T13" s="139"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="119"/>
+      <c r="W13" s="110"/>
+    </row>
+    <row r="14" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="128" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="227"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="113"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="137"/>
+      <c r="T14" s="139"/>
+      <c r="U14" s="113"/>
+      <c r="V14" s="119"/>
+      <c r="W14" s="110"/>
+    </row>
+    <row r="15" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="128" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="227"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="140"/>
+      <c r="Q15" s="113"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="137"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="113"/>
+      <c r="V15" s="119"/>
+      <c r="W15" s="110"/>
+    </row>
+    <row r="16" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="227"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="229"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="113"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="110"/>
+    </row>
+    <row r="17" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="227"/>
+      <c r="C17" s="228"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="110"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="140"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="139"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="119"/>
+      <c r="W17" s="110"/>
+    </row>
+    <row r="18" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="128" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="119">
+        <f>SUM(B9:B17)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="119">
+        <f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="119">
+        <f t="shared" ref="P18" si="1">SUM(P9:P17)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="122">
+        <f>SUM(Q9:Q17)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="122">
+        <f>SUM(R9:R17)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="132">
+        <f>SUM(S9:S17)</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="132">
+        <f>SUM(T9:T17)</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="122">
+        <f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="128"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="122"/>
+      <c r="R19" s="122"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="132"/>
+      <c r="U19" s="122"/>
+      <c r="V19" s="119"/>
+      <c r="W19" s="119"/>
+    </row>
+    <row r="20" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="119" t="e">
+        <f t="shared" ref="B20:O20" si="3">B18-B7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="120">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="119">
+        <f t="shared" ref="P20" si="4">P18-P7</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="122">
+        <f>Q18-Q7</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="122">
+        <f>R18-R7</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="119">
+        <f>S18-S7</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="119">
+        <f>T18-T7</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="122">
+        <f t="shared" ref="U20:W20" si="5">U18-U7</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="119">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="119">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+    </row>
+    <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D22" s="2"/>
+      <c r="M22" s="214" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22" s="214"/>
+      <c r="O22" s="214"/>
+      <c r="P22" s="214"/>
+      <c r="Q22" s="214"/>
+      <c r="R22" s="214"/>
+      <c r="S22" s="214"/>
+      <c r="T22" s="214"/>
+      <c r="U22" s="214"/>
+    </row>
+    <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D23" s="6"/>
+      <c r="J23"/>
+      <c r="L23"/>
+      <c r="M23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="N23" s="221"/>
+      <c r="O23" s="222"/>
+      <c r="P23" s="222"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="222"/>
+      <c r="S23" s="223"/>
+      <c r="T23" s="142" t="s">
+        <v>38</v>
+      </c>
+      <c r="U23" s="115">
+        <v>5</v>
+      </c>
+      <c r="W23" s="96" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="2"/>
+      <c r="C24" s="18"/>
+      <c r="J24"/>
+      <c r="K24" s="15"/>
+      <c r="L24"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="224" t="s">
+        <v>49</v>
+      </c>
+      <c r="O24" s="225"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="225"/>
+      <c r="R24" s="225"/>
+      <c r="S24" s="226"/>
+      <c r="T24" s="117" t="s">
+        <v>11</v>
+      </c>
+      <c r="U24" s="116">
+        <v>500000</v>
+      </c>
+      <c r="W24" s="141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B25" s="2"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="J25"/>
+      <c r="L25"/>
+      <c r="M25" s="209" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" s="210"/>
+      <c r="O25" s="211"/>
+      <c r="P25" s="212"/>
+      <c r="Q25" s="174">
+        <v>90000</v>
+      </c>
+      <c r="R25" s="175"/>
+      <c r="S25" s="176"/>
+      <c r="T25" s="207" t="s">
+        <v>17</v>
+      </c>
+      <c r="U25" s="208"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="86" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="E26" s="4"/>
+      <c r="J26"/>
+      <c r="L26"/>
+      <c r="M26" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" s="84"/>
+      <c r="O26" s="151"/>
+      <c r="P26" s="152"/>
+      <c r="Q26" s="174">
+        <v>10000</v>
+      </c>
+      <c r="R26" s="175"/>
+      <c r="S26" s="176"/>
+      <c r="T26" s="149"/>
+      <c r="U26" s="150"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="86"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I27" s="118" t="str">
+        <f>B1</f>
+      </c>
+      <c r="J27" s="162" t="str">
+        <f>B9</f>
+      </c>
+      <c r="L27"/>
+      <c r="M27" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="84"/>
+      <c r="O27" s="199"/>
+      <c r="P27" s="200"/>
+      <c r="Q27" s="174"/>
+      <c r="R27" s="175"/>
+      <c r="S27" s="176"/>
+      <c r="T27" s="219" t="s">
+        <v>19</v>
+      </c>
+      <c r="U27" s="220"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="97">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I28" s="118">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="162">
+        <f>C9</f>
+        <v>0</v>
+      </c>
+      <c r="L28"/>
+      <c r="M28" s="194" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="195"/>
+      <c r="O28" s="199"/>
+      <c r="P28" s="200"/>
+      <c r="Q28" s="174"/>
+      <c r="R28" s="175"/>
+      <c r="S28" s="176"/>
+      <c r="T28" s="217" t="s">
+        <v>39</v>
+      </c>
+      <c r="U28" s="218"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="13"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I29" s="118">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="162">
+        <f>D9</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="24"/>
+      <c r="L29"/>
+      <c r="M29" s="194" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="195"/>
+      <c r="O29" s="199"/>
+      <c r="P29" s="200"/>
+      <c r="Q29" s="174"/>
+      <c r="R29" s="175"/>
+      <c r="S29" s="176"/>
+      <c r="T29" s="215" t="s">
+        <v>40</v>
+      </c>
+      <c r="U29" s="216"/>
+      <c r="W29" s="98" t="str">
+        <f>U23</f>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="I30" s="118">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="162">
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="L30"/>
+      <c r="M30" s="194" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="195"/>
+      <c r="O30" s="199"/>
+      <c r="P30" s="213"/>
+      <c r="Q30" s="174"/>
+      <c r="R30" s="175"/>
+      <c r="S30" s="176"/>
+      <c r="T30" s="201" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30" s="202"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="21" t="str">
+        <f>Q34</f>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="I31" s="118">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="162">
+        <f>F9</f>
+        <v>0</v>
+      </c>
+      <c r="L31"/>
+      <c r="M31" s="194" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="195"/>
+      <c r="O31" s="199"/>
+      <c r="P31" s="200"/>
+      <c r="Q31" s="174"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="176"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="26"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="I32" s="118">
+        <f>G1</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="162">
+        <f>G9</f>
+        <v>0</v>
+      </c>
+      <c r="L32"/>
+      <c r="M32" s="194" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" s="195"/>
+      <c r="O32" s="199"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="174"/>
+      <c r="R32" s="175"/>
+      <c r="S32" s="176"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="26"/>
+      <c r="W32" s="86" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="I33" s="118">
+        <f>H1</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="162">
+        <f>H9</f>
+        <v>0</v>
+      </c>
+      <c r="L33"/>
+      <c r="M33" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="N33" s="85"/>
+      <c r="O33" s="199"/>
+      <c r="P33" s="200"/>
+      <c r="Q33" s="174"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="176"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="26"/>
+      <c r="W33" s="138" t="e">
+        <f>W30-W27</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1"/>
+      <c r="I34" s="118">
+        <f>I1</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="162">
+        <f>I9</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="203" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="204"/>
+      <c r="O34" s="205"/>
+      <c r="P34" s="206"/>
+      <c r="Q34" s="174">
+        <v>500000</v>
+      </c>
+      <c r="R34" s="175"/>
+      <c r="S34" s="176"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="24"/>
+    </row>
+    <row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1"/>
+      <c r="D35" s="31"/>
+      <c r="I35" s="45">
+        <f>J1</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="27">
+        <f>J9</f>
+        <v>0</v>
+      </c>
+      <c r="L35"/>
+      <c r="M35" s="196" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="189" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35" s="193"/>
+      <c r="R35" s="189" t="s">
+        <v>29</v>
+      </c>
+      <c r="S35" s="193"/>
+      <c r="T35" s="189" t="s">
+        <v>30</v>
+      </c>
+      <c r="U35" s="193"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="9"/>
+      <c r="I36" s="45">
+        <f>K1</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="27">
+        <f>K9</f>
+        <v>0</v>
+      </c>
+      <c r="L36"/>
+      <c r="M36" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="T36" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="U36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1"/>
+      <c r="I37" s="45">
+        <f>L1</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="27">
+        <f>L9</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="148">
+        <f>SUM(O41)</f>
+        <v>0</v>
+      </c>
+      <c r="L37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="81"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="78"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="32"/>
+      <c r="I38" s="134"/>
+      <c r="J38"/>
+      <c r="L38" s="114">
+        <v>2</v>
+      </c>
+      <c r="M38" s="179" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="180"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="79"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="77"/>
+      <c r="T38" s="42"/>
+      <c r="U38" s="80"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B39" s="20"/>
+      <c r="C39" s="32"/>
+      <c r="I39" s="134"/>
+      <c r="J39"/>
+      <c r="K39" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L39" s="114">
+        <v>3</v>
+      </c>
+      <c r="M39" s="37"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="44"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="72"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="20"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="47"/>
+      <c r="I40" s="134"/>
+      <c r="J40"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="114">
+        <v>4</v>
+      </c>
+      <c r="M40" s="37"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="20"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="I41" s="133"/>
+      <c r="J41"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="114">
+        <v>5</v>
+      </c>
+      <c r="M41" s="37"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="70"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="72"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B42" s="20"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="51"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="57"/>
+      <c r="L42" s="114">
+        <v>6</v>
+      </c>
+      <c r="M42" s="37"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="70"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="72"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="112"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="8"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="24" t="e">
+        <f>O38+O65</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L43" s="114">
+        <v>7</v>
+      </c>
+      <c r="M43" s="37"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="70"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="71"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="72"/>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="183"/>
+      <c r="E44" s="183"/>
+      <c r="F44" s="52"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="114">
+        <v>8</v>
+      </c>
+      <c r="M44" s="37"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="70"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="71"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="72"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
+      <c r="F45" s="23"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="57"/>
+      <c r="L45" s="114">
+        <v>9</v>
+      </c>
+      <c r="M45" s="37"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="70"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="76"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="72"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="183"/>
+      <c r="E46" s="183"/>
+      <c r="F46" s="53"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="57"/>
+      <c r="L46" s="114">
+        <v>10</v>
+      </c>
+      <c r="M46" s="37"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="39"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="70"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="71"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="72"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="183"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L47" s="114">
+        <v>11</v>
+      </c>
+      <c r="M47" s="37"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="39"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="71"/>
+      <c r="T47" s="42"/>
+      <c r="U47" s="72"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="183"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="57"/>
+      <c r="L48" s="114">
+        <v>12</v>
+      </c>
+      <c r="M48" s="37"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="70"/>
+      <c r="R48" s="42"/>
+      <c r="S48" s="71"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="72"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="183"/>
+      <c r="E49" s="183"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="57"/>
+      <c r="L49" s="114">
+        <v>13</v>
+      </c>
+      <c r="M49" s="37"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="70"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="71"/>
+      <c r="T49" s="44"/>
+      <c r="U49" s="72"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="57"/>
+      <c r="L50" s="114">
+        <v>14</v>
+      </c>
+      <c r="M50" s="37"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="39"/>
+      <c r="P50" s="42"/>
+      <c r="Q50" s="70"/>
+      <c r="R50" s="42"/>
+      <c r="S50" s="71"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="72"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="184"/>
+      <c r="E51" s="184"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="50"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="57"/>
+      <c r="L51" s="114">
+        <v>15</v>
+      </c>
+      <c r="M51" s="37"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="39"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="70"/>
+      <c r="R51" s="42"/>
+      <c r="S51" s="71"/>
+      <c r="T51" s="44"/>
+      <c r="U51" s="72"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="182"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="57"/>
+      <c r="L52" s="114">
+        <v>16</v>
+      </c>
+      <c r="M52" s="37"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="70"/>
+      <c r="R52" s="42"/>
+      <c r="S52" s="71"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="72"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A53" s="25"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="50"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="57"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="37"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="42"/>
+      <c r="Q53" s="70"/>
+      <c r="R53" s="42"/>
+      <c r="S53" s="71"/>
+      <c r="T53" s="44"/>
+      <c r="U53" s="72"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A54" s="20"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="181"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="57"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="37"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="70"/>
+      <c r="R54" s="42"/>
+      <c r="S54" s="71"/>
+      <c r="T54" s="44"/>
+      <c r="U54" s="72"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A55" s="20"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="50"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="57"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="37"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="39"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="70"/>
+      <c r="R55" s="42"/>
+      <c r="S55" s="71"/>
+      <c r="T55" s="44"/>
+      <c r="U55" s="72"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A56" s="20"/>
+      <c r="B56"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="57"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="37"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="39"/>
+      <c r="P56" s="42"/>
+      <c r="Q56" s="70"/>
+      <c r="R56" s="42"/>
+      <c r="S56" s="71"/>
+      <c r="T56" s="44"/>
+      <c r="U56" s="72"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A57" s="20"/>
+      <c r="B57"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="57"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="37"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="39"/>
+      <c r="P57" s="42"/>
+      <c r="Q57" s="70"/>
+      <c r="R57" s="42"/>
+      <c r="S57" s="71"/>
+      <c r="T57" s="44"/>
+      <c r="U57" s="72"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58" s="20"/>
+      <c r="B58"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="57"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="37"/>
+      <c r="N58" s="38"/>
+      <c r="O58" s="39"/>
+      <c r="P58" s="42"/>
+      <c r="Q58" s="70"/>
+      <c r="R58" s="42"/>
+      <c r="S58" s="71"/>
+      <c r="T58" s="44"/>
+      <c r="U58" s="72"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59" s="20"/>
+      <c r="B59"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="50"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="57"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="37"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="39"/>
+      <c r="P59" s="42"/>
+      <c r="Q59" s="70"/>
+      <c r="R59" s="42"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="44"/>
+      <c r="U59" s="72"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60" s="25"/>
+      <c r="B60"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="181"/>
+      <c r="E60" s="181"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="50"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="57"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="37"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="42"/>
+      <c r="Q60" s="70"/>
+      <c r="R60" s="42"/>
+      <c r="S60" s="71"/>
+      <c r="T60" s="44"/>
+      <c r="U60" s="72"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A61" s="25"/>
+      <c r="B61"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="50"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="57"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="37"/>
+      <c r="N61" s="38"/>
+      <c r="O61" s="39"/>
+      <c r="P61" s="42"/>
+      <c r="Q61" s="161"/>
+      <c r="R61" s="93"/>
+      <c r="S61" s="92"/>
+      <c r="T61" s="44"/>
+      <c r="U61" s="72"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A62" s="25"/>
+      <c r="B62"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="50"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="57"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="37"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="42"/>
+      <c r="Q62" s="161"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="92"/>
+      <c r="T62" s="44"/>
+      <c r="U62" s="72"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A63" s="25"/>
+      <c r="B63"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="57"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="37"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="42"/>
+      <c r="Q63" s="161"/>
+      <c r="R63" s="93"/>
+      <c r="S63" s="92"/>
+      <c r="T63" s="44"/>
+      <c r="U63" s="72"/>
+    </row>
+    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="25"/>
+      <c r="B64"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="181"/>
+      <c r="E64" s="181"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="57"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="38"/>
+      <c r="O64" s="39"/>
+      <c r="P64" s="42"/>
+      <c r="Q64" s="88"/>
+      <c r="R64" s="93"/>
+      <c r="S64" s="92"/>
+      <c r="T64" s="44"/>
+      <c r="U64" s="75"/>
+    </row>
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="25"/>
+      <c r="B65"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="181"/>
+      <c r="E65" s="181"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="57"/>
+      <c r="L65"/>
+      <c r="M65" s="179" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="180"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="46"/>
+      <c r="R65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S65" s="46"/>
+      <c r="T65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="46"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="25"/>
+      <c r="B66"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="181"/>
+      <c r="E66" s="181"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="54"/>
+      <c r="J66"/>
+      <c r="L66"/>
+      <c r="M66" s="58"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="23"/>
+      <c r="Q66" s="73"/>
+      <c r="R66" s="74"/>
+      <c r="S66" s="74"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="25"/>
+      <c r="B67"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="54"/>
+      <c r="J67"/>
+      <c r="L67"/>
+      <c r="M67" s="189" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="190"/>
+      <c r="O67" s="193"/>
+      <c r="P67" s="191"/>
+      <c r="Q67" s="192"/>
+      <c r="R67" s="189" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="190"/>
+      <c r="T67" s="185" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U67" s="186"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="25"/>
+      <c r="B68"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="54"/>
+      <c r="J68"/>
+      <c r="L68"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="87"/>
+      <c r="O68" s="87"/>
+      <c r="P68" s="61"/>
+      <c r="Q68" s="62"/>
+      <c r="R68" s="62"/>
+      <c r="S68" s="62"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
+    </row>
+    <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="25"/>
+      <c r="B69" s="95"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="181"/>
+      <c r="E69" s="181"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="54"/>
+      <c r="J69"/>
+      <c r="L69"/>
+      <c r="M69" s="179" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="187"/>
+      <c r="O69" s="187"/>
+      <c r="P69" s="187"/>
+      <c r="Q69" s="187"/>
+      <c r="R69" s="187"/>
+      <c r="S69" s="187"/>
+      <c r="T69" s="187"/>
+      <c r="U69" s="188"/>
+      <c r="V69" s="55"/>
+    </row>
+    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="25"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="181"/>
+      <c r="E70" s="181"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="54"/>
+      <c r="J70"/>
+      <c r="L70" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="157"/>
+      <c r="O70" s="157"/>
+      <c r="P70" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q70" s="157"/>
+      <c r="R70" s="157"/>
+      <c r="S70" s="157"/>
+      <c r="T70" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U70" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V70" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W70" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="25"/>
+      <c r="B71" s="130"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="181"/>
+      <c r="E71" s="181"/>
+      <c r="F71" s="67"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="54"/>
+      <c r="J71" s="23"/>
+      <c r="L71"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="64"/>
+      <c r="O71" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="65"/>
+      <c r="R71" s="178" t="s">
+        <v>6</v>
+      </c>
+      <c r="S71" s="178"/>
+      <c r="T71" s="159"/>
+      <c r="U71" s="160"/>
+      <c r="V71" s="55"/>
+    </row>
+    <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B72" s="55"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="181"/>
+      <c r="E72" s="181"/>
+      <c r="F72" s="67"/>
+      <c r="I72" s="130"/>
+      <c r="L72"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="91"/>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="173"/>
+      <c r="S72" s="173"/>
+      <c r="T72" s="69"/>
+      <c r="U72" s="100"/>
+      <c r="V72" s="55"/>
+    </row>
+    <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="53"/>
+      <c r="B73" s="94"/>
+      <c r="C73" s="94"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="67"/>
+      <c r="I73" s="130"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="89"/>
+      <c r="N73" s="90"/>
+      <c r="O73" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P73" s="91"/>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="173" t="s">
+        <v>10</v>
+      </c>
+      <c r="S73" s="173"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
+      <c r="V73" s="55"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L74" s="49"/>
+      <c r="M74" s="89"/>
+      <c r="N74" s="90"/>
+      <c r="O74" s="147"/>
+      <c r="P74" s="91"/>
+      <c r="Q74" s="60"/>
+      <c r="R74" s="173"/>
+      <c r="S74" s="173"/>
+      <c r="T74" s="69"/>
+      <c r="U74" s="100"/>
+      <c r="V74" s="55"/>
+    </row>
+    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L75" s="49"/>
+      <c r="M75" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="165"/>
+      <c r="P75" s="166"/>
+      <c r="Q75" s="167"/>
+      <c r="R75" s="177"/>
+      <c r="S75" s="177"/>
+      <c r="T75" s="171"/>
+      <c r="U75" s="172"/>
+      <c r="V75" s="55"/>
+    </row>
+    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L76" s="49"/>
+      <c r="M76" s="163" t="s">
+        <v>62</v>
+      </c>
+      <c r="N76" s="164"/>
+      <c r="O76" s="165"/>
+      <c r="P76" s="166"/>
+      <c r="Q76" s="167"/>
+      <c r="R76" s="168"/>
+      <c r="S76" s="168"/>
+      <c r="T76" s="171"/>
+      <c r="U76" s="172"/>
+      <c r="V76" s="55"/>
+    </row>
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L77" s="49"/>
+      <c r="M77" s="99"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="147"/>
+      <c r="P77" s="91"/>
+      <c r="Q77" s="60"/>
+      <c r="R77" s="60"/>
+      <c r="S77" s="60"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="100"/>
+      <c r="V77" s="55"/>
+    </row>
+    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L78" s="49"/>
+      <c r="M78" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="107">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="101"/>
+      <c r="P78" s="103"/>
+      <c r="Q78" s="102"/>
+      <c r="R78" s="102"/>
+      <c r="S78" s="102"/>
+      <c r="T78" s="104"/>
+      <c r="U78" s="105"/>
+      <c r="V78" s="55"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
+      <c r="V79" s="55"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O80"/>
+      <c r="V80" s="55"/>
+    </row>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
+      <c r="V81" s="55"/>
+    </row>
+    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V82" s="55"/>
+    </row>
+    <row r="83" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V83" s="55"/>
+    </row>
+    <row r="84" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V84" s="55"/>
+    </row>
+    <row r="85" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V85" s="55"/>
+    </row>
+    <row r="86" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V86" s="55"/>
+    </row>
+    <row r="87" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V87" s="55"/>
+    </row>
+    <row r="88" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V88" s="55"/>
+    </row>
+    <row r="89" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V89" s="55"/>
+    </row>
+    <row r="90" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V90" s="55"/>
+    </row>
+    <row r="91" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V91" s="55"/>
+    </row>
+    <row r="92" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V92" s="55"/>
+    </row>
+    <row r="93" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V93" s="55"/>
+    </row>
+    <row r="94" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V94" s="55"/>
+    </row>
+    <row r="95" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V95" s="55"/>
+    </row>
+    <row r="96" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V96" s="55"/>
+    </row>
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V97" s="55"/>
+    </row>
+    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V98" s="55"/>
+    </row>
+    <row r="99" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V99" s="55"/>
+    </row>
+    <row r="100" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V100" s="55"/>
+    </row>
+    <row r="101" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V101" s="55"/>
+    </row>
+    <row r="102" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V102" s="55"/>
+    </row>
+    <row r="103" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V103" s="55"/>
+    </row>
+    <row r="104" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V104" s="55"/>
+    </row>
+    <row r="105" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V105" s="55"/>
+    </row>
+    <row r="106" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V106" s="55"/>
+    </row>
+    <row r="107" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V107" s="55"/>
+    </row>
+    <row r="108" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V108" s="55"/>
+    </row>
+    <row r="109" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V109" s="55"/>
+    </row>
+    <row r="110" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V110" s="55"/>
+    </row>
+    <row r="111" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V111" s="55"/>
+    </row>
+    <row r="112" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V112" s="55"/>
+    </row>
+  </sheetData>
+  <mergeCells count="72">
+    <mergeCell ref="M22:U22"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -1968,297 +1968,2326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W112"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="3" customWidth="1"/>
+    <col min="7" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" style="4" customWidth="1"/>
+    <col min="16" max="19" width="11.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="127" t="inlineStr">
         <is>
-          <t>CAMPO</t>
+          <t xml:space="preserve">ANA</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOB</t>
+        </is>
+      </c>
+      <c r="D1" s="143"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="143"/>
+      <c r="T1" s="143"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="129"/>
+    </row>
+    <row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUX ANA</t>
+        </is>
+      </c>
+      <c r="C2" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUX BOB</t>
+        </is>
+      </c>
+      <c r="D2" s="143"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="143"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="109"/>
+      <c r="V2" s="108"/>
+      <c r="W2" s="129"/>
+    </row>
+    <row r="3" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="146" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="143"/>
+      <c r="R3" s="143"/>
+      <c r="S3" s="143"/>
+      <c r="T3" s="143"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="131"/>
+      <c r="W3" s="132"/>
+    </row>
+    <row r="4" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="143" t="inlineStr">
         <is>
           <t xml:space="preserve">111 · ANA</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C4" s="143" t="inlineStr">
         <is>
           <t xml:space="preserve">222 · BOB</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="B2"/>
-      <c r="C2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CHOFER</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOB</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AUXILIAR / PEONETA</t>
-        </is>
-      </c>
-      <c r="B4"/>
-      <c r="C4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RECORRIDO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="143"/>
+      <c r="T4" s="143"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="131"/>
+      <c r="W4" s="132"/>
+    </row>
+    <row r="5" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="154" t="inlineStr">
         <is>
           <t xml:space="preserve">111</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="154" t="inlineStr">
         <is>
           <t xml:space="preserve">222</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="154"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="154"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
+      <c r="O5" s="154"/>
+      <c r="P5" s="154"/>
+      <c r="Q5" s="154"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="143"/>
+      <c r="T5" s="143"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="124"/>
+      <c r="W5" s="123"/>
+    </row>
+    <row r="6" spans="1:23" s="49" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="127" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="0">
+        <v>10</v>
+      </c>
+      <c r="C6" s="0">
+        <v>10</v>
+      </c>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="123"/>
+      <c r="R6" s="143"/>
+      <c r="S6" s="143"/>
+      <c r="T6" s="143"/>
+      <c r="U6" s="121"/>
+      <c r="V6" s="123"/>
+      <c r="W6" s="123"/>
+    </row>
+    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="155">
+        <v>1000000</v>
+      </c>
+      <c r="C7" s="155">
+        <v>1000000</v>
+      </c>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
+      <c r="I7" s="155"/>
+      <c r="J7" s="155"/>
+      <c r="K7" s="155"/>
+      <c r="L7" s="155"/>
+      <c r="M7" s="155"/>
+      <c r="N7" s="155"/>
+      <c r="O7" s="155"/>
+      <c r="P7" s="155"/>
+      <c r="Q7" s="155"/>
+      <c r="R7" s="144"/>
+      <c r="S7" s="144"/>
+      <c r="T7" s="144"/>
+      <c r="U7" s="113"/>
+      <c r="V7" s="110"/>
+      <c r="W7" s="110"/>
+    </row>
+    <row r="8" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="123"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="123"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="123"/>
+      <c r="T8" s="140"/>
+      <c r="U8" s="121"/>
+      <c r="V8" s="119"/>
+      <c r="W8" s="123"/>
+    </row>
+    <row r="9" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="227">
+        <v>450000</v>
+      </c>
+      <c r="C9" s="228">
+        <v>450000</v>
+      </c>
+      <c r="D9" s="229"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="140"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="137"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="113"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="110"/>
+    </row>
+    <row r="10" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="128" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="227">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="228">
+        <v>50000</v>
+      </c>
+      <c r="D10" s="229"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="137"/>
+      <c r="T10" s="139"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="119"/>
+      <c r="W10" s="110"/>
+    </row>
+    <row r="11" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="128" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="227">
+        <v>300000</v>
+      </c>
+      <c r="C11" s="228">
+        <v>300000</v>
+      </c>
+      <c r="D11" s="229"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="120"/>
+      <c r="O11" s="110"/>
+      <c r="P11" s="140"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="140"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="139"/>
+      <c r="U11" s="113"/>
+      <c r="V11" s="119"/>
+      <c r="W11" s="110"/>
+    </row>
+    <row r="12" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="128" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="227"/>
+      <c r="C12" s="228"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="140"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="140"/>
+      <c r="S12" s="137"/>
+      <c r="T12" s="139"/>
+      <c r="U12" s="113"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="110"/>
+    </row>
+    <row r="13" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="128" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="227"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="110"/>
+      <c r="P13" s="140"/>
+      <c r="Q13" s="113"/>
+      <c r="R13" s="140"/>
+      <c r="S13" s="137"/>
+      <c r="T13" s="139"/>
+      <c r="U13" s="113"/>
+      <c r="V13" s="119"/>
+      <c r="W13" s="110"/>
+    </row>
+    <row r="14" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="128" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="227"/>
+      <c r="C14" s="228"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="113"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="137"/>
+      <c r="T14" s="139"/>
+      <c r="U14" s="113"/>
+      <c r="V14" s="119"/>
+      <c r="W14" s="110"/>
+    </row>
+    <row r="15" spans="1:23" s="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="128" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="227"/>
+      <c r="C15" s="228"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="119"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="140"/>
+      <c r="Q15" s="113"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="137"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="113"/>
+      <c r="V15" s="119"/>
+      <c r="W15" s="110"/>
+    </row>
+    <row r="16" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="227"/>
+      <c r="C16" s="228"/>
+      <c r="D16" s="229"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="137"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="113"/>
+      <c r="V16" s="119"/>
+      <c r="W16" s="110"/>
+    </row>
+    <row r="17" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="227"/>
+      <c r="C17" s="228"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="119"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="110"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="110"/>
+      <c r="P17" s="140"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="140"/>
+      <c r="S17" s="137"/>
+      <c r="T17" s="139"/>
+      <c r="U17" s="113"/>
+      <c r="V17" s="119"/>
+      <c r="W17" s="110"/>
+    </row>
+    <row r="18" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="128" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="119">
+        <f>SUM(B9:B17)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="119">
+        <f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="120">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="119">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="119">
+        <f t="shared" ref="P18" si="1">SUM(P9:P17)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="122">
+        <f>SUM(Q9:Q17)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="122">
+        <f>SUM(R9:R17)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="132">
+        <f>SUM(S9:S17)</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="132">
+        <f>SUM(T9:T17)</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="122">
+        <f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="119">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="128"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="122"/>
+      <c r="R19" s="122"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="132"/>
+      <c r="U19" s="122"/>
+      <c r="V19" s="119"/>
+      <c r="W19" s="119"/>
+    </row>
+    <row r="20" spans="1:23" s="125" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="119" t="e">
+        <f t="shared" ref="B20:O20" si="3">B18-B7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="120">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="119">
+        <f t="shared" ref="P20" si="4">P18-P7</f>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="122">
+        <f>Q18-Q7</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="122">
+        <f>R18-R7</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="119">
+        <f>S18-S7</f>
+        <v>0</v>
+      </c>
+      <c r="T20" s="119">
+        <f>T18-T7</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="122">
+        <f t="shared" ref="U20:W20" si="5">U18-U7</f>
+        <v>0</v>
+      </c>
+      <c r="V20" s="119">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="119">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>PATENTE</t>
+          <t xml:space="preserve">TOTALES CONSOLIDADOS</t>
         </is>
       </c>
-      <c r="B6"/>
-      <c r="C6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>N° FACT.</t>
-        </is>
-      </c>
-      <c r="B7">
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+    </row>
+    <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="0">
+        <v>20</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="M22" s="214" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22" s="214"/>
+      <c r="O22" s="214"/>
+      <c r="P22" s="214"/>
+      <c r="Q22" s="214"/>
+      <c r="R22" s="214"/>
+      <c r="S22" s="214"/>
+      <c r="T22" s="214"/>
+      <c r="U22" s="214"/>
+    </row>
+    <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="0">
+        <v>2000000</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="J23"/>
+      <c r="L23"/>
+      <c r="M23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="N23" s="221"/>
+      <c r="O23" s="222"/>
+      <c r="P23" s="222"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="222"/>
+      <c r="S23" s="223"/>
+      <c r="T23" s="142" t="s">
+        <v>38</v>
+      </c>
+      <c r="U23" s="115"/>
+      <c r="W23" s="96" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="2">
+        <v>900000</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="J24"/>
+      <c r="K24" s="15"/>
+      <c r="L24"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="224" t="s">
+        <v>49</v>
+      </c>
+      <c r="O24" s="225"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="225"/>
+      <c r="R24" s="225"/>
+      <c r="S24" s="226"/>
+      <c r="T24" s="117" t="s">
+        <v>11</v>
+      </c>
+      <c r="U24" s="116"/>
+      <c r="W24" s="141"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="C25" s="111"/>
+      <c r="D25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="J25"/>
+      <c r="L25"/>
+      <c r="M25" s="209" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" s="210"/>
+      <c r="O25" s="211"/>
+      <c r="P25" s="212"/>
+      <c r="Q25" s="174"/>
+      <c r="R25" s="175"/>
+      <c r="S25" s="176"/>
+      <c r="T25" s="207" t="s">
+        <v>17</v>
+      </c>
+      <c r="U25" s="208"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="86" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B26" s="0">
+        <v>600000</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="J26"/>
+      <c r="L26"/>
+      <c r="M26" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="N26" s="84"/>
+      <c r="O26" s="151"/>
+      <c r="P26" s="152"/>
+      <c r="Q26" s="174"/>
+      <c r="R26" s="175"/>
+      <c r="S26" s="176"/>
+      <c r="T26" s="149"/>
+      <c r="U26" s="150"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="86"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I27" s="118" t="str">
+        <f>B1</f>
+      </c>
+      <c r="J27" s="162" t="str">
+        <f>B9</f>
+      </c>
+      <c r="L27"/>
+      <c r="M27" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="84"/>
+      <c r="O27" s="199"/>
+      <c r="P27" s="200"/>
+      <c r="Q27" s="174"/>
+      <c r="R27" s="175"/>
+      <c r="S27" s="176"/>
+      <c r="T27" s="219" t="s">
+        <v>19</v>
+      </c>
+      <c r="U27" s="220"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="97"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I28" s="118">
+        <f>C1</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="162">
+        <f>C9</f>
+        <v>0</v>
+      </c>
+      <c r="L28"/>
+      <c r="M28" s="194" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="195"/>
+      <c r="O28" s="199"/>
+      <c r="P28" s="200"/>
+      <c r="Q28" s="174"/>
+      <c r="R28" s="175"/>
+      <c r="S28" s="176"/>
+      <c r="T28" s="217" t="s">
+        <v>39</v>
+      </c>
+      <c r="U28" s="218"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="13"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I29" s="118">
+        <f>D1</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="162">
+        <f>D9</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="24"/>
+      <c r="L29"/>
+      <c r="M29" s="194" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="195"/>
+      <c r="O29" s="199"/>
+      <c r="P29" s="200"/>
+      <c r="Q29" s="174"/>
+      <c r="R29" s="175"/>
+      <c r="S29" s="176"/>
+      <c r="T29" s="215" t="s">
+        <v>40</v>
+      </c>
+      <c r="U29" s="216"/>
+      <c r="W29" s="98" t="str">
+        <f>U23</f>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="I30" s="118">
+        <f>E1</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="162">
+        <f>E9</f>
+        <v>0</v>
+      </c>
+      <c r="L30"/>
+      <c r="M30" s="194" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="195"/>
+      <c r="O30" s="199"/>
+      <c r="P30" s="213"/>
+      <c r="Q30" s="174"/>
+      <c r="R30" s="175"/>
+      <c r="S30" s="176"/>
+      <c r="T30" s="201" t="s">
+        <v>41</v>
+      </c>
+      <c r="U30" s="202"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="21" t="str">
+        <f>Q34</f>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="I31" s="118">
+        <f>F1</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="162">
+        <f>F9</f>
+        <v>0</v>
+      </c>
+      <c r="L31"/>
+      <c r="M31" s="194" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="195"/>
+      <c r="O31" s="199"/>
+      <c r="P31" s="200"/>
+      <c r="Q31" s="174"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="176"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="26"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="I32" s="118">
+        <f>G1</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="162">
+        <f>G9</f>
+        <v>0</v>
+      </c>
+      <c r="L32"/>
+      <c r="M32" s="194" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" s="195"/>
+      <c r="O32" s="199"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="174"/>
+      <c r="R32" s="175"/>
+      <c r="S32" s="176"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="26"/>
+      <c r="W32" s="86" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="I33" s="118">
+        <f>H1</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="162">
+        <f>H9</f>
+        <v>0</v>
+      </c>
+      <c r="L33"/>
+      <c r="M33" s="83" t="s">
+        <v>25</v>
+      </c>
+      <c r="N33" s="85"/>
+      <c r="O33" s="199"/>
+      <c r="P33" s="200"/>
+      <c r="Q33" s="174"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="176"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="26"/>
+      <c r="W33" s="138" t="e">
+        <f>W30-W27</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1"/>
+      <c r="I34" s="118">
+        <f>I1</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="162">
+        <f>I9</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="203" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="204"/>
+      <c r="O34" s="205"/>
+      <c r="P34" s="206"/>
+      <c r="Q34" s="174"/>
+      <c r="R34" s="175"/>
+      <c r="S34" s="176"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="24"/>
+    </row>
+    <row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1"/>
+      <c r="D35" s="31"/>
+      <c r="I35" s="45">
+        <f>J1</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="27">
+        <f>J9</f>
+        <v>0</v>
+      </c>
+      <c r="L35"/>
+      <c r="M35" s="196" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="197"/>
+      <c r="O35" s="198"/>
+      <c r="P35" s="189" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35" s="193"/>
+      <c r="R35" s="189" t="s">
+        <v>29</v>
+      </c>
+      <c r="S35" s="193"/>
+      <c r="T35" s="189" t="s">
+        <v>30</v>
+      </c>
+      <c r="U35" s="193"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="1"/>
+    </row>
+    <row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="9"/>
+      <c r="I36" s="45">
+        <f>K1</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="27">
+        <f>K9</f>
+        <v>0</v>
+      </c>
+      <c r="L36"/>
+      <c r="M36" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="T36" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="U36" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="V36" s="1"/>
+      <c r="W36" s="1"/>
+    </row>
+    <row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1"/>
+      <c r="I37" s="45">
+        <f>L1</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="27">
+        <f>L9</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="148">
+        <f>SUM(O41)</f>
+        <v>0</v>
+      </c>
+      <c r="L37"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="40"/>
+      <c r="Q37" s="81"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="82"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="78"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="32"/>
+      <c r="I38" s="134"/>
+      <c r="J38"/>
+      <c r="L38" s="114">
+        <v>2</v>
+      </c>
+      <c r="M38" s="179" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="180"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="79"/>
+      <c r="R38" s="44"/>
+      <c r="S38" s="77"/>
+      <c r="T38" s="42"/>
+      <c r="U38" s="80"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B39" s="20"/>
+      <c r="C39" s="32"/>
+      <c r="I39" s="134"/>
+      <c r="J39"/>
+      <c r="K39" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L39" s="114">
+        <v>3</v>
+      </c>
+      <c r="M39" s="37"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="44"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="72"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+    </row>
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="20"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="47"/>
+      <c r="I40" s="134"/>
+      <c r="J40"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="114">
+        <v>4</v>
+      </c>
+      <c r="M40" s="37"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="20"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="I41" s="133"/>
+      <c r="J41"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="114">
         <v>5</v>
       </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL FACT.</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>500000</v>
-      </c>
-      <c r="C8">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EFECTIVO TOTAL</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>100000</v>
-      </c>
-      <c r="C9">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>BILLETES</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>90000</v>
-      </c>
-      <c r="C10">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MONEDAS</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>10000</v>
-      </c>
-      <c r="C11">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHEQUES AL DÍA</t>
-        </is>
-      </c>
-      <c r="B12"/>
-      <c r="C12"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHEQUES A FECHA</t>
-        </is>
-      </c>
-      <c r="B13"/>
-      <c r="C13"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CRÉDITO VENDEDOR</t>
-        </is>
-      </c>
-      <c r="B14"/>
-      <c r="C14"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NULOS (RETORNO TOTAL)</t>
-        </is>
-      </c>
-      <c r="B15"/>
-      <c r="C15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PARCIALES (RETORNO PARCIAL)</t>
-        </is>
-      </c>
-      <c r="B16"/>
-      <c r="C16"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>N/C NEGOCIO</t>
-        </is>
-      </c>
-      <c r="B17"/>
-      <c r="C17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TRANSFERENCIAS</t>
-        </is>
-      </c>
-      <c r="B18"/>
-      <c r="C18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TOTAL RENDICIÓN</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>500000</v>
-      </c>
-      <c r="C19">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TOTALES CONSOLIDADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>N° FACT.</t>
-        </is>
-      </c>
-      <c r="B23">
+      <c r="M41" s="37"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="70"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="72"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+    </row>
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B42" s="20"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="51"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="57"/>
+      <c r="L42" s="114">
+        <v>6</v>
+      </c>
+      <c r="M42" s="37"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="70"/>
+      <c r="R42" s="44"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="72"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="112"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="183"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="8"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="24" t="e">
+        <f>O38+O65</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L43" s="114">
+        <v>7</v>
+      </c>
+      <c r="M43" s="37"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="39"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="70"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="71"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="72"/>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="183"/>
+      <c r="E44" s="183"/>
+      <c r="F44" s="52"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="114">
+        <v>8</v>
+      </c>
+      <c r="M44" s="37"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="39"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="70"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="71"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="72"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="183"/>
+      <c r="F45" s="23"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="57"/>
+      <c r="L45" s="114">
+        <v>9</v>
+      </c>
+      <c r="M45" s="37"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="39"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="70"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="76"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="72"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="183"/>
+      <c r="E46" s="183"/>
+      <c r="F46" s="53"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="57"/>
+      <c r="L46" s="114">
         <v>10</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TOTAL FACT.</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>EFECTIVO TOTAL</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BILLETES</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MONEDAS</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TOTAL RENDICIÓN</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>1000000</v>
-      </c>
+      <c r="M46" s="37"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="39"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="70"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="71"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="72"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="183"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L47" s="114">
+        <v>11</v>
+      </c>
+      <c r="M47" s="37"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="39"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="71"/>
+      <c r="T47" s="42"/>
+      <c r="U47" s="72"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="183"/>
+      <c r="E48" s="183"/>
+      <c r="F48" s="23"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="57"/>
+      <c r="L48" s="114">
+        <v>12</v>
+      </c>
+      <c r="M48" s="37"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="70"/>
+      <c r="R48" s="42"/>
+      <c r="S48" s="71"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="72"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="183"/>
+      <c r="E49" s="183"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="50"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="57"/>
+      <c r="L49" s="114">
+        <v>13</v>
+      </c>
+      <c r="M49" s="37"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="70"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="71"/>
+      <c r="T49" s="44"/>
+      <c r="U49" s="72"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="23"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="57"/>
+      <c r="L50" s="114">
+        <v>14</v>
+      </c>
+      <c r="M50" s="37"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="39"/>
+      <c r="P50" s="42"/>
+      <c r="Q50" s="70"/>
+      <c r="R50" s="42"/>
+      <c r="S50" s="71"/>
+      <c r="T50" s="44"/>
+      <c r="U50" s="72"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="184"/>
+      <c r="E51" s="184"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="50"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="57"/>
+      <c r="L51" s="114">
+        <v>15</v>
+      </c>
+      <c r="M51" s="37"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="39"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="70"/>
+      <c r="R51" s="42"/>
+      <c r="S51" s="71"/>
+      <c r="T51" s="44"/>
+      <c r="U51" s="72"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="182"/>
+      <c r="E52" s="182"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="50"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="57"/>
+      <c r="L52" s="114">
+        <v>16</v>
+      </c>
+      <c r="M52" s="37"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="39"/>
+      <c r="P52" s="40"/>
+      <c r="Q52" s="70"/>
+      <c r="R52" s="42"/>
+      <c r="S52" s="71"/>
+      <c r="T52" s="44"/>
+      <c r="U52" s="72"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A53" s="25"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="50"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="57"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="37"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="39"/>
+      <c r="P53" s="42"/>
+      <c r="Q53" s="70"/>
+      <c r="R53" s="42"/>
+      <c r="S53" s="71"/>
+      <c r="T53" s="44"/>
+      <c r="U53" s="72"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A54" s="20"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="181"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="57"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="37"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="70"/>
+      <c r="R54" s="42"/>
+      <c r="S54" s="71"/>
+      <c r="T54" s="44"/>
+      <c r="U54" s="72"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A55" s="20"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="50"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="57"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="37"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="39"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="70"/>
+      <c r="R55" s="42"/>
+      <c r="S55" s="71"/>
+      <c r="T55" s="44"/>
+      <c r="U55" s="72"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A56" s="20"/>
+      <c r="B56"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="50"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="57"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="37"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="39"/>
+      <c r="P56" s="42"/>
+      <c r="Q56" s="70"/>
+      <c r="R56" s="42"/>
+      <c r="S56" s="71"/>
+      <c r="T56" s="44"/>
+      <c r="U56" s="72"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A57" s="20"/>
+      <c r="B57"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="50"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="57"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="37"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="39"/>
+      <c r="P57" s="42"/>
+      <c r="Q57" s="70"/>
+      <c r="R57" s="42"/>
+      <c r="S57" s="71"/>
+      <c r="T57" s="44"/>
+      <c r="U57" s="72"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58" s="20"/>
+      <c r="B58"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="50"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="57"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="37"/>
+      <c r="N58" s="38"/>
+      <c r="O58" s="39"/>
+      <c r="P58" s="42"/>
+      <c r="Q58" s="70"/>
+      <c r="R58" s="42"/>
+      <c r="S58" s="71"/>
+      <c r="T58" s="44"/>
+      <c r="U58" s="72"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59" s="20"/>
+      <c r="B59"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="50"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="57"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="37"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="39"/>
+      <c r="P59" s="42"/>
+      <c r="Q59" s="70"/>
+      <c r="R59" s="42"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="44"/>
+      <c r="U59" s="72"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60" s="25"/>
+      <c r="B60"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="181"/>
+      <c r="E60" s="181"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="50"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="57"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="37"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="39"/>
+      <c r="P60" s="42"/>
+      <c r="Q60" s="70"/>
+      <c r="R60" s="42"/>
+      <c r="S60" s="71"/>
+      <c r="T60" s="44"/>
+      <c r="U60" s="72"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A61" s="25"/>
+      <c r="B61"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="50"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="57"/>
+      <c r="L61" s="18"/>
+      <c r="M61" s="37"/>
+      <c r="N61" s="38"/>
+      <c r="O61" s="39"/>
+      <c r="P61" s="42"/>
+      <c r="Q61" s="161"/>
+      <c r="R61" s="93"/>
+      <c r="S61" s="92"/>
+      <c r="T61" s="44"/>
+      <c r="U61" s="72"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A62" s="25"/>
+      <c r="B62"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="50"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="57"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="37"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="39"/>
+      <c r="P62" s="42"/>
+      <c r="Q62" s="161"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="92"/>
+      <c r="T62" s="44"/>
+      <c r="U62" s="72"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A63" s="25"/>
+      <c r="B63"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="57"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="37"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="39"/>
+      <c r="P63" s="42"/>
+      <c r="Q63" s="161"/>
+      <c r="R63" s="93"/>
+      <c r="S63" s="92"/>
+      <c r="T63" s="44"/>
+      <c r="U63" s="72"/>
+    </row>
+    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="25"/>
+      <c r="B64"/>
+      <c r="C64" s="43"/>
+      <c r="D64" s="181"/>
+      <c r="E64" s="181"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="57"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="38"/>
+      <c r="O64" s="39"/>
+      <c r="P64" s="42"/>
+      <c r="Q64" s="88"/>
+      <c r="R64" s="93"/>
+      <c r="S64" s="92"/>
+      <c r="T64" s="44"/>
+      <c r="U64" s="75"/>
+    </row>
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="25"/>
+      <c r="B65"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="181"/>
+      <c r="E65" s="181"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="50"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="57"/>
+      <c r="L65"/>
+      <c r="M65" s="179" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="180"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="46"/>
+      <c r="R65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S65" s="46"/>
+      <c r="T65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="46"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="25"/>
+      <c r="B66"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="181"/>
+      <c r="E66" s="181"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="54"/>
+      <c r="J66"/>
+      <c r="L66"/>
+      <c r="M66" s="58"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="23"/>
+      <c r="Q66" s="73"/>
+      <c r="R66" s="74"/>
+      <c r="S66" s="74"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="25"/>
+      <c r="B67"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="54"/>
+      <c r="J67"/>
+      <c r="L67"/>
+      <c r="M67" s="189" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="190"/>
+      <c r="O67" s="193"/>
+      <c r="P67" s="191"/>
+      <c r="Q67" s="192"/>
+      <c r="R67" s="189" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="190"/>
+      <c r="T67" s="185" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U67" s="186"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="25"/>
+      <c r="B68"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="54"/>
+      <c r="J68"/>
+      <c r="L68"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="87"/>
+      <c r="O68" s="87"/>
+      <c r="P68" s="61"/>
+      <c r="Q68" s="62"/>
+      <c r="R68" s="62"/>
+      <c r="S68" s="62"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
+    </row>
+    <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="25"/>
+      <c r="B69" s="95"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="181"/>
+      <c r="E69" s="181"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="54"/>
+      <c r="J69"/>
+      <c r="L69"/>
+      <c r="M69" s="179" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="187"/>
+      <c r="O69" s="187"/>
+      <c r="P69" s="187"/>
+      <c r="Q69" s="187"/>
+      <c r="R69" s="187"/>
+      <c r="S69" s="187"/>
+      <c r="T69" s="187"/>
+      <c r="U69" s="188"/>
+      <c r="V69" s="55"/>
+    </row>
+    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="25"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="181"/>
+      <c r="E70" s="181"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="54"/>
+      <c r="J70"/>
+      <c r="L70" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="157"/>
+      <c r="O70" s="157"/>
+      <c r="P70" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q70" s="157"/>
+      <c r="R70" s="157"/>
+      <c r="S70" s="157"/>
+      <c r="T70" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U70" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V70" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W70" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="25"/>
+      <c r="B71" s="130"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="181"/>
+      <c r="E71" s="181"/>
+      <c r="F71" s="67"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="54"/>
+      <c r="J71" s="23"/>
+      <c r="L71"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="64"/>
+      <c r="O71" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="65"/>
+      <c r="R71" s="178" t="s">
+        <v>6</v>
+      </c>
+      <c r="S71" s="178"/>
+      <c r="T71" s="159"/>
+      <c r="U71" s="160"/>
+      <c r="V71" s="55"/>
+    </row>
+    <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B72" s="55"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="181"/>
+      <c r="E72" s="181"/>
+      <c r="F72" s="67"/>
+      <c r="I72" s="130"/>
+      <c r="L72"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="91"/>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="173"/>
+      <c r="S72" s="173"/>
+      <c r="T72" s="69"/>
+      <c r="U72" s="100"/>
+      <c r="V72" s="55"/>
+    </row>
+    <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="53"/>
+      <c r="B73" s="94"/>
+      <c r="C73" s="94"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="67"/>
+      <c r="I73" s="130"/>
+      <c r="L73" s="49"/>
+      <c r="M73" s="89"/>
+      <c r="N73" s="90"/>
+      <c r="O73" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P73" s="91"/>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="173" t="s">
+        <v>10</v>
+      </c>
+      <c r="S73" s="173"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
+      <c r="V73" s="55"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L74" s="49"/>
+      <c r="M74" s="89"/>
+      <c r="N74" s="90"/>
+      <c r="O74" s="147"/>
+      <c r="P74" s="91"/>
+      <c r="Q74" s="60"/>
+      <c r="R74" s="173"/>
+      <c r="S74" s="173"/>
+      <c r="T74" s="69"/>
+      <c r="U74" s="100"/>
+      <c r="V74" s="55"/>
+    </row>
+    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L75" s="49"/>
+      <c r="M75" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="165"/>
+      <c r="P75" s="166"/>
+      <c r="Q75" s="167"/>
+      <c r="R75" s="177"/>
+      <c r="S75" s="177"/>
+      <c r="T75" s="171"/>
+      <c r="U75" s="172"/>
+      <c r="V75" s="55"/>
+    </row>
+    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L76" s="49"/>
+      <c r="M76" s="163" t="s">
+        <v>62</v>
+      </c>
+      <c r="N76" s="164"/>
+      <c r="O76" s="165"/>
+      <c r="P76" s="166"/>
+      <c r="Q76" s="167"/>
+      <c r="R76" s="168"/>
+      <c r="S76" s="168"/>
+      <c r="T76" s="171"/>
+      <c r="U76" s="172"/>
+      <c r="V76" s="55"/>
+    </row>
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L77" s="49"/>
+      <c r="M77" s="99"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="147"/>
+      <c r="P77" s="91"/>
+      <c r="Q77" s="60"/>
+      <c r="R77" s="60"/>
+      <c r="S77" s="60"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="100"/>
+      <c r="V77" s="55"/>
+    </row>
+    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L78" s="49"/>
+      <c r="M78" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="107">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="101"/>
+      <c r="P78" s="103"/>
+      <c r="Q78" s="102"/>
+      <c r="R78" s="102"/>
+      <c r="S78" s="102"/>
+      <c r="T78" s="104"/>
+      <c r="U78" s="105"/>
+      <c r="V78" s="55"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
+      <c r="V79" s="55"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O80"/>
+      <c r="V80" s="55"/>
+    </row>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
+      <c r="V81" s="55"/>
+    </row>
+    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V82" s="55"/>
+    </row>
+    <row r="83" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V83" s="55"/>
+    </row>
+    <row r="84" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V84" s="55"/>
+    </row>
+    <row r="85" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V85" s="55"/>
+    </row>
+    <row r="86" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V86" s="55"/>
+    </row>
+    <row r="87" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V87" s="55"/>
+    </row>
+    <row r="88" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V88" s="55"/>
+    </row>
+    <row r="89" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V89" s="55"/>
+    </row>
+    <row r="90" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V90" s="55"/>
+    </row>
+    <row r="91" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V91" s="55"/>
+    </row>
+    <row r="92" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V92" s="55"/>
+    </row>
+    <row r="93" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V93" s="55"/>
+    </row>
+    <row r="94" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V94" s="55"/>
+    </row>
+    <row r="95" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V95" s="55"/>
+    </row>
+    <row r="96" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="V96" s="55"/>
+    </row>
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V97" s="55"/>
+    </row>
+    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V98" s="55"/>
+    </row>
+    <row r="99" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V99" s="55"/>
+    </row>
+    <row r="100" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V100" s="55"/>
+    </row>
+    <row r="101" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V101" s="55"/>
+    </row>
+    <row r="102" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V102" s="55"/>
+    </row>
+    <row r="103" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V103" s="55"/>
+    </row>
+    <row r="104" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V104" s="55"/>
+    </row>
+    <row r="105" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V105" s="55"/>
+    </row>
+    <row r="106" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V106" s="55"/>
+    </row>
+    <row r="107" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V107" s="55"/>
+    </row>
+    <row r="108" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V108" s="55"/>
+    </row>
+    <row r="109" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V109" s="55"/>
+    </row>
+    <row r="110" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V110" s="55"/>
+    </row>
+    <row r="111" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V111" s="55"/>
+    </row>
+    <row r="112" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V112" s="55"/>
     </row>
   </sheetData>
+  <mergeCells count="72">
+    <mergeCell ref="M22:U22"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+  </mergeCells>
+  <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2322,7 +4351,11 @@
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127"/>
+      <c r="B2" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUX ANA</t>
+        </is>
+      </c>
       <c r="C2" s="143"/>
       <c r="D2" s="143"/>
       <c r="E2" s="127"/>
@@ -2435,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -2464,7 +4497,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -2518,7 +4551,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="227">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="C9" s="228"/>
       <c r="D9" s="229"/>
@@ -2547,7 +4580,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="227">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="C10" s="228"/>
       <c r="D10" s="229"/>
@@ -2575,7 +4608,9 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="227"/>
+      <c r="B11" s="227">
+        <v>300000</v>
+      </c>
       <c r="C11" s="228"/>
       <c r="D11" s="229"/>
       <c r="E11" s="110"/>
@@ -3027,7 +5062,7 @@
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -3052,10 +5087,10 @@
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="W24" s="141">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3074,7 +5109,7 @@
       <c r="O25" s="211"/>
       <c r="P25" s="212"/>
       <c r="Q25" s="174">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="R25" s="175"/>
       <c r="S25" s="176"/>
@@ -3098,7 +5133,7 @@
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
       <c r="Q26" s="174">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="R26" s="175"/>
       <c r="S26" s="176"/>
@@ -3121,7 +5156,9 @@
       <c r="N27" s="84"/>
       <c r="O27" s="199"/>
       <c r="P27" s="200"/>
-      <c r="Q27" s="174"/>
+      <c r="Q27" s="174">
+        <v>300000</v>
+      </c>
       <c r="R27" s="175"/>
       <c r="S27" s="176"/>
       <c r="T27" s="219" t="s">
@@ -3130,7 +5167,7 @@
       <c r="U27" s="220"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3310,7 +5347,7 @@
       <c r="O34" s="205"/>
       <c r="P34" s="206"/>
       <c r="Q34" s="174">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="R34" s="175"/>
       <c r="S34" s="176"/>
@@ -3433,7 +5470,9 @@
         <v>42</v>
       </c>
       <c r="N38" s="180"/>
-      <c r="O38" s="46"/>
+      <c r="O38" s="46">
+        <v>300000</v>
+      </c>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -4607,7 +6646,11 @@
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127"/>
+      <c r="B2" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUX BOB</t>
+        </is>
+      </c>
       <c r="C2" s="143"/>
       <c r="D2" s="143"/>
       <c r="E2" s="127"/>
@@ -4720,7 +6763,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -4749,7 +6792,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -4803,7 +6846,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="227">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="C9" s="228"/>
       <c r="D9" s="229"/>
@@ -4832,7 +6875,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="227">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="C10" s="228"/>
       <c r="D10" s="229"/>
@@ -4860,7 +6903,9 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="227"/>
+      <c r="B11" s="227">
+        <v>300000</v>
+      </c>
       <c r="C11" s="228"/>
       <c r="D11" s="229"/>
       <c r="E11" s="110"/>
@@ -5312,7 +7357,7 @@
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -5337,10 +7382,10 @@
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="W24" s="141">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -5359,7 +7404,7 @@
       <c r="O25" s="211"/>
       <c r="P25" s="212"/>
       <c r="Q25" s="174">
-        <v>90000</v>
+        <v>450000</v>
       </c>
       <c r="R25" s="175"/>
       <c r="S25" s="176"/>
@@ -5383,7 +7428,7 @@
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
       <c r="Q26" s="174">
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="R26" s="175"/>
       <c r="S26" s="176"/>
@@ -5406,7 +7451,9 @@
       <c r="N27" s="84"/>
       <c r="O27" s="199"/>
       <c r="P27" s="200"/>
-      <c r="Q27" s="174"/>
+      <c r="Q27" s="174">
+        <v>300000</v>
+      </c>
       <c r="R27" s="175"/>
       <c r="S27" s="176"/>
       <c r="T27" s="219" t="s">
@@ -5415,7 +7462,7 @@
       <c r="U27" s="220"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -5595,7 +7642,7 @@
       <c r="O34" s="205"/>
       <c r="P34" s="206"/>
       <c r="Q34" s="174">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="R34" s="175"/>
       <c r="S34" s="176"/>
@@ -5718,7 +7765,9 @@
         <v>42</v>
       </c>
       <c r="N38" s="180"/>
-      <c r="O38" s="46"/>
+      <c r="O38" s="46">
+        <v>300000</v>
+      </c>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -2762,6 +2762,10 @@
       <c r="B23" s="0">
         <v>2000000</v>
       </c>
+      <c r="AF23" s="0">
+        <v>10</v>
+      </c>
+      <c r="Y23" s="0"/>
       <c r="D23" s="6"/>
       <c r="J23"/>
       <c r="L23"/>
@@ -2777,12 +2781,17 @@
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="U23" s="115"/>
+      <c r="U23" s="115">
+        <v>10</v>
+      </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AF24" s="0">
+        <v>1000000</v>
+      </c>
       <c r="B24" s="2">
         <v>900000</v>
       </c>
@@ -2802,7 +2811,9 @@
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="U24" s="116"/>
+      <c r="U24" s="116">
+        <v>1000000</v>
+      </c>
       <c r="W24" s="141"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3137,6 +3148,25 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AF37" s="0"/>
+      <c r="AE37" s="0"/>
+      <c r="AD37" s="0"/>
+      <c r="AC37" s="0"/>
+      <c r="AB37" s="0"/>
+      <c r="AA37" s="0"/>
+      <c r="Z37" s="0">
+        <v>100000</v>
+      </c>
+      <c r="Y37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="X37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
       <c r="A37" s="1"/>
       <c r="I37" s="45">
         <f>L1</f>
@@ -3151,9 +3181,19 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="39"/>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
+      <c r="N37" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O37" s="39">
+        <v>100000</v>
+      </c>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -3790,6 +3830,9 @@
       <c r="U64" s="75"/>
     </row>
     <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AF65" s="0"/>
+      <c r="AD65" s="0"/>
+      <c r="AB65" s="0"/>
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
@@ -3954,6 +3997,10 @@
       </c>
     </row>
     <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="AG71" s="0"/>
+      <c r="AE71" s="0"/>
+      <c r="AA71" s="0"/>
+      <c r="X71" s="0"/>
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
@@ -4000,6 +4047,29 @@
       <c r="V72" s="55"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="AE73" s="0">
+        <v>150000</v>
+      </c>
+      <c r="AA73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F001</t>
+        </is>
+      </c>
+      <c r="Z73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="X73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
+      <c r="W73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222</t>
+        </is>
+      </c>
       <c r="A73" s="53"/>
       <c r="B73" s="94"/>
       <c r="C73" s="94"/>
@@ -4007,19 +4077,35 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="89"/>
+      <c r="L73" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111</t>
+        </is>
+      </c>
+      <c r="M73" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
       <c r="N73" s="90"/>
-      <c r="O73" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P73" s="91"/>
+      <c r="O73" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="P73" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F001</t>
+        </is>
+      </c>
       <c r="Q73" s="60"/>
       <c r="R73" s="173" t="s">
         <v>10</v>
       </c>
       <c r="S73" s="173"/>
-      <c r="T73" s="69"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
       <c r="U73" s="100"/>
       <c r="V73" s="55"/>
     </row>
@@ -5444,9 +5530,19 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="39"/>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
+      <c r="N37" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O37" s="39">
+        <v>100000</v>
+      </c>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -6302,20 +6398,38 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="89"/>
+      <c r="L73" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111</t>
+        </is>
+      </c>
+      <c r="M73" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91"/>
+      <c r="P73" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F001</t>
+        </is>
+      </c>
       <c r="Q73" s="60"/>
       <c r="R73" s="173" t="s">
         <v>10</v>
       </c>
       <c r="S73" s="173"/>
-      <c r="T73" s="69"/>
-      <c r="U73" s="100"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U73" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -7739,9 +7853,19 @@
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="39"/>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
+      <c r="N37" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O37" s="39">
+        <v>100000</v>
+      </c>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -8597,20 +8721,38 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="89"/>
+      <c r="L73" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222</t>
+        </is>
+      </c>
+      <c r="M73" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91"/>
+      <c r="P73" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F001</t>
+        </is>
+      </c>
       <c r="Q73" s="60"/>
       <c r="R73" s="173" t="s">
         <v>10</v>
       </c>
       <c r="S73" s="173"/>
-      <c r="T73" s="69"/>
-      <c r="U73" s="100"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U73" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -1969,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -1998,14 +1998,10 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA</t>
+          <t xml:space="preserve">VARIOS</t>
         </is>
       </c>
-      <c r="C1" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOB</t>
-        </is>
-      </c>
+      <c r="C1" s="143"/>
       <c r="D1" s="143"/>
       <c r="E1" s="127"/>
       <c r="F1" s="143"/>
@@ -2033,14 +2029,10 @@
       </c>
       <c r="B2" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUX ANA</t>
+          <t xml:space="preserve">VARIOS</t>
         </is>
       </c>
-      <c r="C2" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUX BOB</t>
-        </is>
-      </c>
+      <c r="C2" s="143"/>
       <c r="D2" s="143"/>
       <c r="E2" s="127"/>
       <c r="F2" s="143"/>
@@ -2093,16 +2085,8 @@
       <c r="A4" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111 · ANA</t>
-        </is>
-      </c>
-      <c r="C4" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222 · BOB</t>
-        </is>
-      </c>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
       <c r="F4" s="143"/>
@@ -2130,14 +2114,10 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">VARIOS</t>
         </is>
       </c>
-      <c r="C5" s="154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222</t>
-        </is>
-      </c>
+      <c r="C5" s="154"/>
       <c r="D5" s="154"/>
       <c r="E5" s="154"/>
       <c r="F5" s="154"/>
@@ -2163,12 +2143,10 @@
       <c r="A6" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="0">
-        <v>10</v>
-      </c>
-      <c r="C6" s="0">
-        <v>10</v>
-      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
@@ -2195,11 +2173,9 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>1000000</v>
-      </c>
-      <c r="C7" s="155">
-        <v>1000000</v>
-      </c>
+        <v>2000000</v>
+      </c>
+      <c r="C7" s="155"/>
       <c r="D7" s="155"/>
       <c r="E7" s="155"/>
       <c r="F7" s="155"/>
@@ -2251,11 +2227,9 @@
         <v>3</v>
       </c>
       <c r="B9" s="227">
-        <v>450000</v>
-      </c>
-      <c r="C9" s="228">
-        <v>450000</v>
-      </c>
+        <v>900000</v>
+      </c>
+      <c r="C9" s="228"/>
       <c r="D9" s="229"/>
       <c r="E9" s="110"/>
       <c r="F9" s="119"/>
@@ -2282,11 +2256,9 @@
         <v>54</v>
       </c>
       <c r="B10" s="227">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="228">
-        <v>50000</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="C10" s="228"/>
       <c r="D10" s="229"/>
       <c r="E10" s="110"/>
       <c r="F10" s="119"/>
@@ -2313,11 +2285,9 @@
         <v>4</v>
       </c>
       <c r="B11" s="227">
-        <v>300000</v>
-      </c>
-      <c r="C11" s="228">
-        <v>300000</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="C11" s="228"/>
       <c r="D11" s="229"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
@@ -2713,11 +2683,7 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTALES CONSOLIDADOS</t>
-        </is>
-      </c>
+      <c r="A21" s="1"/>
       <c r="B21" s="9"/>
       <c r="C21" s="10"/>
       <c r="D21" s="9"/>
@@ -2742,9 +2708,6 @@
       <c r="W21" s="9"/>
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="0">
-        <v>20</v>
-      </c>
       <c r="D22" s="2"/>
       <c r="M22" s="214" t="s">
         <v>48</v>
@@ -2759,20 +2722,17 @@
       <c r="U22" s="214"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="0">
-        <v>2000000</v>
-      </c>
-      <c r="AF23" s="0">
-        <v>10</v>
-      </c>
-      <c r="Y23" s="0"/>
       <c r="D23" s="6"/>
       <c r="J23"/>
       <c r="L23"/>
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221"/>
+      <c r="N23" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24/06/2026</t>
+        </is>
+      </c>
       <c r="O23" s="222"/>
       <c r="P23" s="222"/>
       <c r="Q23" s="222"/>
@@ -2782,19 +2742,14 @@
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AF24" s="0">
-        <v>1000000</v>
-      </c>
-      <c r="B24" s="2">
-        <v>900000</v>
-      </c>
+      <c r="B24" s="2"/>
       <c r="C24" s="18"/>
       <c r="J24"/>
       <c r="K24" s="15"/>
@@ -2812,14 +2767,14 @@
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>1000000</v>
-      </c>
-      <c r="W24" s="141"/>
+        <v>2000000</v>
+      </c>
+      <c r="W24" s="141">
+        <v>20</v>
+      </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B25" s="2">
-        <v>100000</v>
-      </c>
+      <c r="B25" s="2"/>
       <c r="C25" s="111"/>
       <c r="D25" s="3" t="s">
         <v>15</v>
@@ -2833,7 +2788,9 @@
       <c r="N25" s="210"/>
       <c r="O25" s="211"/>
       <c r="P25" s="212"/>
-      <c r="Q25" s="174"/>
+      <c r="Q25" s="174">
+        <v>900000</v>
+      </c>
       <c r="R25" s="175"/>
       <c r="S25" s="176"/>
       <c r="T25" s="207" t="s">
@@ -2846,9 +2803,6 @@
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B26" s="0">
-        <v>600000</v>
-      </c>
       <c r="E26" s="4"/>
       <c r="J26"/>
       <c r="L26"/>
@@ -2858,7 +2812,9 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="174"/>
+      <c r="Q26" s="174">
+        <v>100000</v>
+      </c>
       <c r="R26" s="175"/>
       <c r="S26" s="176"/>
       <c r="T26" s="149"/>
@@ -2880,7 +2836,9 @@
       <c r="N27" s="84"/>
       <c r="O27" s="199"/>
       <c r="P27" s="200"/>
-      <c r="Q27" s="174"/>
+      <c r="Q27" s="174">
+        <v>600000</v>
+      </c>
       <c r="R27" s="175"/>
       <c r="S27" s="176"/>
       <c r="T27" s="219" t="s">
@@ -2888,7 +2846,9 @@
       </c>
       <c r="U27" s="220"/>
       <c r="V27" s="19"/>
-      <c r="W27" s="97"/>
+      <c r="W27" s="97">
+        <v>2000000</v>
+      </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="I28" s="118">
@@ -3066,7 +3026,9 @@
       <c r="N34" s="204"/>
       <c r="O34" s="205"/>
       <c r="P34" s="206"/>
-      <c r="Q34" s="174"/>
+      <c r="Q34" s="174">
+        <v>2000000</v>
+      </c>
       <c r="R34" s="175"/>
       <c r="S34" s="176"/>
       <c r="T34" s="30"/>
@@ -3148,25 +3110,6 @@
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AF37" s="0"/>
-      <c r="AE37" s="0"/>
-      <c r="AD37" s="0"/>
-      <c r="AC37" s="0"/>
-      <c r="AB37" s="0"/>
-      <c r="AA37" s="0"/>
-      <c r="Z37" s="0">
-        <v>100000</v>
-      </c>
-      <c r="Y37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="X37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01/01/2026</t>
-        </is>
-      </c>
       <c r="A37" s="1"/>
       <c r="I37" s="45">
         <f>L1</f>
@@ -3177,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O41)</f>
+        <f>SUM(O44)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
@@ -3205,114 +3148,110 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="20"/>
-      <c r="C38" s="32"/>
-      <c r="I38" s="134"/>
-      <c r="J38"/>
-      <c r="L38" s="114">
-        <v>2</v>
-      </c>
-      <c r="M38" s="179" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="180"/>
-      <c r="O38" s="46"/>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M38" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/01/2026</t>
+        </is>
+      </c>
+      <c r="N38" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="O38" s="39">
+        <v>200000</v>
+      </c>
       <c r="P38" s="42"/>
-      <c r="Q38" s="79"/>
+      <c r="Q38" s="72"/>
       <c r="R38" s="44"/>
       <c r="S38" s="77"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
+      <c r="U38" s="72"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B39" s="20"/>
-      <c r="C39" s="32"/>
-      <c r="I39" s="134"/>
-      <c r="J39"/>
-      <c r="K39" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L39" s="114">
-        <v>3</v>
-      </c>
-      <c r="M39" s="37"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="39"/>
+      <c r="M39" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01/01/2026</t>
+        </is>
+      </c>
+      <c r="N39" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O39" s="39">
+        <v>100000</v>
+      </c>
       <c r="P39" s="42"/>
       <c r="Q39" s="72"/>
       <c r="R39" s="44"/>
       <c r="S39" s="77"/>
       <c r="T39" s="42"/>
       <c r="U39" s="72"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-    </row>
-    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="20"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="47"/>
-      <c r="I40" s="134"/>
-      <c r="J40"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="114">
-        <v>4</v>
-      </c>
-      <c r="M40" s="37"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="39"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M40" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/01/2026</t>
+        </is>
+      </c>
+      <c r="N40" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="O40" s="39">
+        <v>200000</v>
+      </c>
       <c r="P40" s="42"/>
-      <c r="Q40" s="70"/>
+      <c r="Q40" s="72"/>
       <c r="R40" s="44"/>
-      <c r="S40" s="78"/>
+      <c r="S40" s="77"/>
       <c r="T40" s="42"/>
       <c r="U40" s="72"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-    </row>
-    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="I41" s="133"/>
+      <c r="I41" s="134"/>
       <c r="J41"/>
-      <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>5</v>
-      </c>
-      <c r="M41" s="37"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="39"/>
+        <v>2</v>
+      </c>
+      <c r="M41" s="179" t="s">
+        <v>42</v>
+      </c>
+      <c r="N41" s="180"/>
+      <c r="O41" s="46">
+        <v>600000</v>
+      </c>
       <c r="P41" s="42"/>
-      <c r="Q41" s="70"/>
+      <c r="Q41" s="79"/>
       <c r="R41" s="44"/>
-      <c r="S41" s="78"/>
+      <c r="S41" s="77"/>
       <c r="T41" s="42"/>
-      <c r="U41" s="72"/>
+      <c r="U41" s="80"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B42" s="20"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="51"/>
-      <c r="I42" s="135"/>
-      <c r="J42" s="57"/>
+      <c r="C42" s="32"/>
+      <c r="I42" s="134"/>
+      <c r="J42"/>
+      <c r="K42" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L42" s="114">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
       <c r="O42" s="39"/>
       <c r="P42" s="42"/>
-      <c r="Q42" s="70"/>
+      <c r="Q42" s="72"/>
       <c r="R42" s="44"/>
       <c r="S42" s="77"/>
       <c r="T42" s="42"/>
@@ -3320,92 +3259,91 @@
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="112"/>
+    <row r="43" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="183"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="8"/>
-      <c r="I43" s="136"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="24" t="e">
-        <f>O38+O65</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="D43" s="48"/>
+      <c r="E43" s="47"/>
+      <c r="I43" s="134"/>
+      <c r="J43"/>
+      <c r="K43" s="24"/>
       <c r="L43" s="114">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="71"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="78"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
       <c r="B44" s="20"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="183"/>
-      <c r="E44" s="183"/>
-      <c r="F44" s="52"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="57"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="I44" s="133"/>
+      <c r="J44"/>
       <c r="K44" s="24"/>
       <c r="L44" s="114">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
       <c r="O44" s="39"/>
       <c r="P44" s="42"/>
       <c r="Q44" s="70"/>
-      <c r="R44" s="42"/>
-      <c r="S44" s="71"/>
+      <c r="R44" s="44"/>
+      <c r="S44" s="78"/>
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="183"/>
-      <c r="F45" s="23"/>
-      <c r="H45" s="68"/>
-      <c r="I45" s="13"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+    </row>
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B45" s="20"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="51"/>
+      <c r="I45" s="135"/>
       <c r="J45" s="57"/>
       <c r="L45" s="114">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
       <c r="O45" s="39"/>
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
-      <c r="R45" s="42"/>
-      <c r="S45" s="76"/>
+      <c r="R45" s="44"/>
+      <c r="S45" s="77"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="20"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+    </row>
+    <row r="46" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A46" s="112"/>
       <c r="B46" s="20"/>
-      <c r="C46" s="43"/>
+      <c r="C46" s="32"/>
       <c r="D46" s="183"/>
       <c r="E46" s="183"/>
-      <c r="F46" s="53"/>
-      <c r="H46" s="68"/>
-      <c r="I46" s="13"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="8"/>
+      <c r="I46" s="136"/>
       <c r="J46" s="57"/>
+      <c r="K46" s="24" t="e">
+        <f>O41+O68</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L46" s="114">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -3417,23 +3355,19 @@
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
+    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25"/>
       <c r="B47" s="20"/>
-      <c r="C47" s="43"/>
+      <c r="C47" s="25"/>
       <c r="D47" s="183"/>
       <c r="E47" s="183"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="1"/>
+      <c r="F47" s="52"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
-      <c r="K47" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K47" s="24"/>
       <c r="L47" s="114">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -3446,18 +3380,17 @@
       <c r="U47" s="72"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="25"/>
       <c r="C48" s="43"/>
       <c r="D48" s="183"/>
       <c r="E48" s="183"/>
       <c r="F48" s="23"/>
-      <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
       <c r="L48" s="114">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -3465,23 +3398,22 @@
       <c r="P48" s="42"/>
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
-      <c r="S48" s="71"/>
-      <c r="T48" s="44"/>
+      <c r="S48" s="76"/>
+      <c r="T48" s="42"/>
       <c r="U48" s="72"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
       <c r="D49" s="183"/>
       <c r="E49" s="183"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="50"/>
+      <c r="F49" s="53"/>
+      <c r="H49" s="68"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -3490,22 +3422,26 @@
       <c r="Q49" s="70"/>
       <c r="R49" s="42"/>
       <c r="S49" s="71"/>
-      <c r="T49" s="44"/>
+      <c r="T49" s="42"/>
       <c r="U49" s="72"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="23"/>
+      <c r="D50" s="183"/>
+      <c r="E50" s="183"/>
+      <c r="F50" s="17"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="50"/>
+      <c r="H50" s="68"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
+      <c r="K50" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L50" s="114">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -3514,27 +3450,27 @@
       <c r="Q50" s="70"/>
       <c r="R50" s="42"/>
       <c r="S50" s="71"/>
-      <c r="T50" s="44"/>
+      <c r="T50" s="42"/>
       <c r="U50" s="72"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="184"/>
-      <c r="E51" s="184"/>
+      <c r="D51" s="183"/>
+      <c r="E51" s="183"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="50"/>
+      <c r="H51" s="68"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="40"/>
+      <c r="P51" s="42"/>
       <c r="Q51" s="70"/>
       <c r="R51" s="42"/>
       <c r="S51" s="71"/>
@@ -3543,22 +3479,22 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="55"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="182"/>
-      <c r="E52" s="182"/>
+      <c r="D52" s="183"/>
+      <c r="E52" s="183"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
-      <c r="I52" s="54"/>
+      <c r="I52" s="13"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
       <c r="O52" s="39"/>
-      <c r="P52" s="40"/>
+      <c r="P52" s="42"/>
       <c r="Q52" s="70"/>
       <c r="R52" s="42"/>
       <c r="S52" s="71"/>
@@ -3566,17 +3502,19 @@
       <c r="U52" s="72"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="25"/>
-      <c r="B53" s="55"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="181"/>
-      <c r="E53" s="181"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="25"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
-      <c r="I53" s="54"/>
+      <c r="I53" s="13"/>
       <c r="J53" s="57"/>
-      <c r="L53" s="18"/>
+      <c r="L53" s="114">
+        <v>14</v>
+      </c>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
@@ -3589,20 +3527,22 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="20"/>
-      <c r="B54" s="55"/>
+      <c r="B54" s="20"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="181"/>
-      <c r="E54" s="181"/>
+      <c r="D54" s="184"/>
+      <c r="E54" s="184"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
-      <c r="I54" s="54"/>
+      <c r="I54" s="13"/>
       <c r="J54" s="57"/>
-      <c r="L54" s="18"/>
+      <c r="L54" s="114">
+        <v>15</v>
+      </c>
       <c r="M54" s="37"/>
       <c r="N54" s="38"/>
       <c r="O54" s="39"/>
-      <c r="P54" s="42"/>
+      <c r="P54" s="40"/>
       <c r="Q54" s="70"/>
       <c r="R54" s="42"/>
       <c r="S54" s="71"/>
@@ -3613,18 +3553,20 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
+      <c r="D55" s="182"/>
+      <c r="E55" s="182"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
       <c r="I55" s="54"/>
       <c r="J55" s="57"/>
-      <c r="L55" s="18"/>
+      <c r="L55" s="114">
+        <v>16</v>
+      </c>
       <c r="M55" s="37"/>
       <c r="N55" s="38"/>
       <c r="O55" s="39"/>
-      <c r="P55" s="42"/>
+      <c r="P55" s="40"/>
       <c r="Q55" s="70"/>
       <c r="R55" s="42"/>
       <c r="S55" s="71"/>
@@ -3632,11 +3574,11 @@
       <c r="U55" s="72"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A56" s="20"/>
-      <c r="B56"/>
+      <c r="A56" s="25"/>
+      <c r="B56" s="55"/>
       <c r="C56" s="43"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
+      <c r="D56" s="181"/>
+      <c r="E56" s="181"/>
       <c r="F56" s="23"/>
       <c r="G56" s="1"/>
       <c r="H56" s="50"/>
@@ -3655,10 +3597,10 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="20"/>
-      <c r="B57"/>
+      <c r="B57" s="55"/>
       <c r="C57" s="43"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
+      <c r="D57" s="181"/>
+      <c r="E57" s="181"/>
       <c r="F57" s="23"/>
       <c r="G57" s="1"/>
       <c r="H57" s="50"/>
@@ -3677,7 +3619,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="20"/>
-      <c r="B58"/>
+      <c r="B58" s="55"/>
       <c r="C58" s="43"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
@@ -3720,11 +3662,11 @@
       <c r="U59" s="72"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="25"/>
+      <c r="A60" s="20"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="181"/>
-      <c r="E60" s="181"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -3742,7 +3684,7 @@
       <c r="U60" s="72"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A61" s="25"/>
+      <c r="A61" s="20"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
       <c r="D61" s="22"/>
@@ -3757,14 +3699,14 @@
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
       <c r="P61" s="42"/>
-      <c r="Q61" s="161"/>
-      <c r="R61" s="93"/>
-      <c r="S61" s="92"/>
+      <c r="Q61" s="70"/>
+      <c r="R61" s="42"/>
+      <c r="S61" s="71"/>
       <c r="T61" s="44"/>
       <c r="U61" s="72"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A62" s="25"/>
+      <c r="A62" s="20"/>
       <c r="B62"/>
       <c r="C62" s="43"/>
       <c r="D62" s="22"/>
@@ -3779,9 +3721,9 @@
       <c r="N62" s="38"/>
       <c r="O62" s="39"/>
       <c r="P62" s="42"/>
-      <c r="Q62" s="161"/>
-      <c r="R62" s="93"/>
-      <c r="S62" s="92"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="42"/>
+      <c r="S62" s="71"/>
       <c r="T62" s="44"/>
       <c r="U62" s="72"/>
     </row>
@@ -3789,8 +3731,8 @@
       <c r="A63" s="25"/>
       <c r="B63"/>
       <c r="C63" s="43"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
+      <c r="D63" s="181"/>
+      <c r="E63" s="181"/>
       <c r="F63" s="23"/>
       <c r="G63" s="1"/>
       <c r="H63" s="50"/>
@@ -3801,18 +3743,18 @@
       <c r="N63" s="38"/>
       <c r="O63" s="39"/>
       <c r="P63" s="42"/>
-      <c r="Q63" s="161"/>
-      <c r="R63" s="93"/>
-      <c r="S63" s="92"/>
+      <c r="Q63" s="70"/>
+      <c r="R63" s="42"/>
+      <c r="S63" s="71"/>
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
-    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="181"/>
-      <c r="E64" s="181"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -3823,186 +3765,160 @@
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
       <c r="P64" s="42"/>
-      <c r="Q64" s="88"/>
+      <c r="Q64" s="161"/>
       <c r="R64" s="93"/>
       <c r="S64" s="92"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="75"/>
-    </row>
-    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="AF65" s="0"/>
-      <c r="AD65" s="0"/>
-      <c r="AB65" s="0"/>
+      <c r="U64" s="72"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="181"/>
-      <c r="E65" s="181"/>
-      <c r="F65" s="20"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="23"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
-      <c r="L65"/>
-      <c r="M65" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="N65" s="180"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q65" s="46"/>
-      <c r="R65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S65" s="46"/>
-      <c r="T65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U65" s="46"/>
-    </row>
-    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65" s="18"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="42"/>
+      <c r="Q65" s="161"/>
+      <c r="R65" s="93"/>
+      <c r="S65" s="92"/>
+      <c r="T65" s="44"/>
+      <c r="U65" s="72"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="95"/>
-      <c r="D66" s="181"/>
-      <c r="E66" s="181"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
-      <c r="J66"/>
-      <c r="L66"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="59"/>
-      <c r="O66" s="74"/>
-      <c r="P66" s="23"/>
-      <c r="Q66" s="73"/>
-      <c r="R66" s="74"/>
-      <c r="S66" s="74"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J66" s="57"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="37"/>
+      <c r="N66" s="38"/>
+      <c r="O66" s="39"/>
+      <c r="P66" s="42"/>
+      <c r="Q66" s="161"/>
+      <c r="R66" s="93"/>
+      <c r="S66" s="92"/>
+      <c r="T66" s="44"/>
+      <c r="U66" s="72"/>
+    </row>
+    <row r="67" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="181"/>
+      <c r="E67" s="181"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
-      <c r="J67"/>
-      <c r="L67"/>
-      <c r="M67" s="189" t="s">
-        <v>47</v>
-      </c>
-      <c r="N67" s="190"/>
-      <c r="O67" s="193"/>
-      <c r="P67" s="191"/>
-      <c r="Q67" s="192"/>
-      <c r="R67" s="189" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" s="190"/>
-      <c r="T67" s="185" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U67" s="186"/>
-    </row>
-    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J67" s="57"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="37"/>
+      <c r="N67" s="38"/>
+      <c r="O67" s="39"/>
+      <c r="P67" s="42"/>
+      <c r="Q67" s="88"/>
+      <c r="R67" s="93"/>
+      <c r="S67" s="92"/>
+      <c r="T67" s="44"/>
+      <c r="U67" s="75"/>
+    </row>
+    <row r="68" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
-      <c r="C68" s="25"/>
+      <c r="C68" s="43"/>
       <c r="D68" s="181"/>
       <c r="E68" s="181"/>
-      <c r="F68" s="67"/>
+      <c r="F68" s="20"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
-      <c r="J68"/>
+      <c r="J68" s="57"/>
       <c r="L68"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="87"/>
-      <c r="O68" s="87"/>
-      <c r="P68" s="61"/>
-      <c r="Q68" s="62"/>
-      <c r="R68" s="62"/>
-      <c r="S68" s="62"/>
-      <c r="T68" s="60"/>
-      <c r="U68" s="60"/>
-    </row>
-    <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M68" s="179" t="s">
+        <v>34</v>
+      </c>
+      <c r="N68" s="180"/>
+      <c r="O68" s="46"/>
+      <c r="P68" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q68" s="46"/>
+      <c r="R68" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S68" s="46"/>
+      <c r="T68" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U68" s="46"/>
+    </row>
+    <row r="69" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69" s="95"/>
-      <c r="C69" s="25"/>
+      <c r="B69"/>
+      <c r="C69" s="95"/>
       <c r="D69" s="181"/>
       <c r="E69" s="181"/>
-      <c r="F69" s="67"/>
+      <c r="F69" s="23"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="179" t="s">
-        <v>35</v>
-      </c>
-      <c r="N69" s="187"/>
-      <c r="O69" s="187"/>
-      <c r="P69" s="187"/>
-      <c r="Q69" s="187"/>
-      <c r="R69" s="187"/>
-      <c r="S69" s="187"/>
-      <c r="T69" s="187"/>
-      <c r="U69" s="188"/>
-      <c r="V69" s="55"/>
-    </row>
-    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="58"/>
+      <c r="N69" s="59"/>
+      <c r="O69" s="74"/>
+      <c r="P69" s="23"/>
+      <c r="Q69" s="73"/>
+      <c r="R69" s="74"/>
+      <c r="S69" s="74"/>
+      <c r="T69" s="6"/>
+    </row>
+    <row r="70" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="20"/>
+      <c r="B70"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="181"/>
-      <c r="E70" s="181"/>
-      <c r="F70" s="67"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="23"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
-      <c r="L70" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M70" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N70" s="157"/>
-      <c r="O70" s="157"/>
-      <c r="P70" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q70" s="157"/>
-      <c r="R70" s="157"/>
-      <c r="S70" s="157"/>
-      <c r="T70" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U70" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V70" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W70" s="170" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="AG71" s="0"/>
-      <c r="AE71" s="0"/>
-      <c r="AA71" s="0"/>
-      <c r="X71" s="0"/>
+      <c r="L70"/>
+      <c r="M70" s="189" t="s">
+        <v>47</v>
+      </c>
+      <c r="N70" s="190"/>
+      <c r="O70" s="193"/>
+      <c r="P70" s="191"/>
+      <c r="Q70" s="192"/>
+      <c r="R70" s="189" t="s">
+        <v>37</v>
+      </c>
+      <c r="S70" s="190"/>
+      <c r="T70" s="185" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U70" s="186"/>
+    </row>
+    <row r="71" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="25"/>
-      <c r="B71" s="130"/>
+      <c r="B71"/>
       <c r="C71" s="25"/>
       <c r="D71" s="181"/>
       <c r="E71" s="181"/>
@@ -4010,215 +3926,324 @@
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
-      <c r="J71" s="23"/>
+      <c r="J71"/>
       <c r="L71"/>
-      <c r="M71" s="63"/>
-      <c r="N71" s="64"/>
-      <c r="O71" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P71" s="66"/>
-      <c r="Q71" s="65"/>
-      <c r="R71" s="178" t="s">
-        <v>6</v>
-      </c>
-      <c r="S71" s="178"/>
-      <c r="T71" s="159"/>
-      <c r="U71" s="160"/>
-      <c r="V71" s="55"/>
-    </row>
-    <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="55"/>
-      <c r="C72" s="94"/>
+      <c r="M71" s="60"/>
+      <c r="N71" s="87"/>
+      <c r="O71" s="87"/>
+      <c r="P71" s="61"/>
+      <c r="Q71" s="62"/>
+      <c r="R71" s="62"/>
+      <c r="S71" s="62"/>
+      <c r="T71" s="60"/>
+      <c r="U71" s="60"/>
+    </row>
+    <row r="72" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="25"/>
+      <c r="B72" s="95"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="181"/>
       <c r="E72" s="181"/>
       <c r="F72" s="67"/>
-      <c r="I72" s="130"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="54"/>
+      <c r="J72"/>
       <c r="L72"/>
-      <c r="M72" s="89"/>
-      <c r="N72" s="90"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="91"/>
-      <c r="Q72" s="60"/>
-      <c r="R72" s="173"/>
-      <c r="S72" s="173"/>
-      <c r="T72" s="69"/>
-      <c r="U72" s="100"/>
+      <c r="M72" s="179" t="s">
+        <v>35</v>
+      </c>
+      <c r="N72" s="187"/>
+      <c r="O72" s="187"/>
+      <c r="P72" s="187"/>
+      <c r="Q72" s="187"/>
+      <c r="R72" s="187"/>
+      <c r="S72" s="187"/>
+      <c r="T72" s="187"/>
+      <c r="U72" s="188"/>
       <c r="V72" s="55"/>
     </row>
-    <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="AE73" s="0">
-        <v>150000</v>
-      </c>
-      <c r="AA73" s="0" t="inlineStr">
+    <row r="73" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="25"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="181"/>
+      <c r="E73" s="181"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="50"/>
+      <c r="I73" s="54"/>
+      <c r="J73"/>
+      <c r="L73" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M73" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="157"/>
+      <c r="O73" s="157"/>
+      <c r="P73" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q73" s="157"/>
+      <c r="R73" s="157"/>
+      <c r="S73" s="157"/>
+      <c r="T73" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U73" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V73" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W73" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="25"/>
+      <c r="B74" s="130"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="181"/>
+      <c r="E74" s="181"/>
+      <c r="F74" s="67"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="50"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="23"/>
+      <c r="L74"/>
+      <c r="M74" s="63"/>
+      <c r="N74" s="64"/>
+      <c r="O74" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P74" s="66"/>
+      <c r="Q74" s="65"/>
+      <c r="R74" s="178" t="s">
+        <v>6</v>
+      </c>
+      <c r="S74" s="178"/>
+      <c r="T74" s="159"/>
+      <c r="U74" s="160"/>
+      <c r="V74" s="55"/>
+    </row>
+    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B75" s="55"/>
+      <c r="C75" s="94"/>
+      <c r="D75" s="181"/>
+      <c r="E75" s="181"/>
+      <c r="F75" s="67"/>
+      <c r="I75" s="130"/>
+      <c r="L75"/>
+      <c r="M75" s="89"/>
+      <c r="N75" s="90"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="91"/>
+      <c r="Q75" s="60"/>
+      <c r="R75" s="173"/>
+      <c r="S75" s="173"/>
+      <c r="T75" s="69"/>
+      <c r="U75" s="100"/>
+      <c r="V75" s="55"/>
+    </row>
+    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="53"/>
+      <c r="B76" s="94"/>
+      <c r="C76" s="94"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="67"/>
+      <c r="I76" s="130"/>
+      <c r="L76" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111</t>
+        </is>
+      </c>
+      <c r="M76" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE UNO</t>
+        </is>
+      </c>
+      <c r="N76" s="90"/>
+      <c r="O76" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P76" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
-      <c r="Z73" s="0" t="inlineStr">
+      <c r="Q76" s="60"/>
+      <c r="R76" s="173" t="s">
+        <v>10</v>
+      </c>
+      <c r="S76" s="173"/>
+      <c r="T76" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U76" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">SANTANDER</t>
         </is>
       </c>
-      <c r="X73" s="0" t="inlineStr">
+      <c r="V76" s="55"/>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="L77" s="49"/>
+      <c r="M77" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE DOS</t>
+        </is>
+      </c>
+      <c r="O77" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="P77" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F002</t>
+        </is>
+      </c>
+      <c r="T77" s="69">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="L78" s="49"/>
+      <c r="M78" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="W73" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222</t>
-        </is>
-      </c>
-      <c r="A73" s="53"/>
-      <c r="B73" s="94"/>
-      <c r="C73" s="94"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="67"/>
-      <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111</t>
-        </is>
-      </c>
-      <c r="M73" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
-      <c r="N73" s="90"/>
-      <c r="O73" s="18" t="inlineStr">
+      <c r="O78" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">SANTANDER</t>
         </is>
       </c>
-      <c r="P73" s="91" t="inlineStr">
+      <c r="P78" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="173" t="s">
-        <v>10</v>
-      </c>
-      <c r="S73" s="173"/>
-      <c r="T73" s="69">
+      <c r="T78" s="69">
         <v>150000</v>
       </c>
-      <c r="U73" s="100"/>
-      <c r="V73" s="55"/>
-    </row>
-    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L74" s="49"/>
-      <c r="M74" s="89"/>
-      <c r="N74" s="90"/>
-      <c r="O74" s="147"/>
-      <c r="P74" s="91"/>
-      <c r="Q74" s="60"/>
-      <c r="R74" s="173"/>
-      <c r="S74" s="173"/>
-      <c r="T74" s="69"/>
-      <c r="U74" s="100"/>
-      <c r="V74" s="55"/>
-    </row>
-    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L75" s="49"/>
-      <c r="M75" s="163" t="s">
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="L79" s="49"/>
+      <c r="M79" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE DOS</t>
+        </is>
+      </c>
+      <c r="O79" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="P79" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F002</t>
+        </is>
+      </c>
+      <c r="T79" s="69">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L80" s="49"/>
+      <c r="M80" s="89"/>
+      <c r="N80" s="90"/>
+      <c r="O80" s="147"/>
+      <c r="P80" s="91"/>
+      <c r="Q80" s="60"/>
+      <c r="R80" s="173"/>
+      <c r="S80" s="173"/>
+      <c r="T80" s="69"/>
+      <c r="U80" s="100"/>
+      <c r="V80" s="55"/>
+    </row>
+    <row r="81" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L81" s="49"/>
+      <c r="M81" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="N75" s="164"/>
-      <c r="O75" s="165"/>
-      <c r="P75" s="166"/>
-      <c r="Q75" s="167"/>
-      <c r="R75" s="177"/>
-      <c r="S75" s="177"/>
-      <c r="T75" s="171"/>
-      <c r="U75" s="172"/>
-      <c r="V75" s="55"/>
-    </row>
-    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L76" s="49"/>
-      <c r="M76" s="163" t="s">
+      <c r="N81" s="164"/>
+      <c r="O81" s="165"/>
+      <c r="P81" s="166"/>
+      <c r="Q81" s="167"/>
+      <c r="R81" s="177"/>
+      <c r="S81" s="177"/>
+      <c r="T81" s="171"/>
+      <c r="U81" s="172"/>
+      <c r="V81" s="55"/>
+    </row>
+    <row r="82" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L82" s="49"/>
+      <c r="M82" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="N76" s="164"/>
-      <c r="O76" s="165"/>
-      <c r="P76" s="166"/>
-      <c r="Q76" s="167"/>
-      <c r="R76" s="168"/>
-      <c r="S76" s="168"/>
-      <c r="T76" s="171"/>
-      <c r="U76" s="172"/>
-      <c r="V76" s="55"/>
-    </row>
-    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L77" s="49"/>
-      <c r="M77" s="99"/>
-      <c r="N77" s="68"/>
-      <c r="O77" s="147"/>
-      <c r="P77" s="91"/>
-      <c r="Q77" s="60"/>
-      <c r="R77" s="60"/>
-      <c r="S77" s="60"/>
-      <c r="T77" s="69"/>
-      <c r="U77" s="100"/>
-      <c r="V77" s="55"/>
-    </row>
-    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L78" s="49"/>
-      <c r="M78" s="106" t="s">
+      <c r="N82" s="164"/>
+      <c r="O82" s="165"/>
+      <c r="P82" s="166"/>
+      <c r="Q82" s="167"/>
+      <c r="R82" s="168"/>
+      <c r="S82" s="168"/>
+      <c r="T82" s="171"/>
+      <c r="U82" s="172"/>
+      <c r="V82" s="55"/>
+    </row>
+    <row r="83" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L83" s="49"/>
+      <c r="M83" s="99"/>
+      <c r="N83" s="68"/>
+      <c r="O83" s="147"/>
+      <c r="P83" s="91"/>
+      <c r="Q83" s="60"/>
+      <c r="R83" s="60"/>
+      <c r="S83" s="60"/>
+      <c r="T83" s="69"/>
+      <c r="U83" s="100"/>
+      <c r="V83" s="55"/>
+    </row>
+    <row r="84" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L84" s="49"/>
+      <c r="M84" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="N78" s="107">
-        <f>SUM(N76:N77)</f>
-        <v>0</v>
-      </c>
-      <c r="O78" s="101"/>
-      <c r="P78" s="103"/>
-      <c r="Q78" s="102"/>
-      <c r="R78" s="102"/>
-      <c r="S78" s="102"/>
-      <c r="T78" s="104"/>
-      <c r="U78" s="105"/>
-      <c r="V78" s="55"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M79"/>
-      <c r="O79" s="5"/>
-      <c r="Q79"/>
-      <c r="S79"/>
-      <c r="T79" s="6"/>
-      <c r="V79" s="55"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O80"/>
-      <c r="V80" s="55"/>
-    </row>
-    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
-      <c r="V81" s="55"/>
-    </row>
-    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V82" s="55"/>
-    </row>
-    <row r="83" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="V83" s="55"/>
-    </row>
-    <row r="84" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="N84" s="107">
+        <f>SUM(N82:N83)</f>
+        <v>0</v>
+      </c>
+      <c r="O84" s="101"/>
+      <c r="P84" s="103"/>
+      <c r="Q84" s="102"/>
+      <c r="R84" s="102"/>
+      <c r="S84" s="102"/>
+      <c r="T84" s="104"/>
+      <c r="U84" s="105"/>
       <c r="V84" s="55"/>
     </row>
-    <row r="85" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M85"/>
+      <c r="O85" s="5"/>
+      <c r="Q85"/>
+      <c r="S85"/>
+      <c r="T85" s="6"/>
       <c r="V85" s="55"/>
     </row>
-    <row r="86" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O86"/>
       <c r="V86" s="55"/>
     </row>
     <row r="87" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M87" s="23"/>
+      <c r="N87" s="23"/>
+      <c r="O87" s="23"/>
+      <c r="P87" s="23"/>
+      <c r="Q87" s="23"/>
       <c r="V87" s="55"/>
     </row>
     <row r="88" spans="13:22" x14ac:dyDescent="0.3">
@@ -4248,22 +4273,22 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
-    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V98" s="55"/>
     </row>
-    <row r="99" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V99" s="55"/>
     </row>
-    <row r="100" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V100" s="55"/>
     </row>
-    <row r="101" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V101" s="55"/>
     </row>
-    <row r="102" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V102" s="55"/>
     </row>
     <row r="103" spans="22:22" x14ac:dyDescent="0.3">
@@ -4295,6 +4320,24 @@
     </row>
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
+    </row>
+    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V113" s="55"/>
+    </row>
+    <row r="114" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V114" s="55"/>
+    </row>
+    <row r="115" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V115" s="55"/>
+    </row>
+    <row r="116" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V116" s="55"/>
+    </row>
+    <row r="117" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V117" s="55"/>
+    </row>
+    <row r="118" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V118" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="72">
@@ -4321,7 +4364,7 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:U30"/>
     <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="R35:S35"/>
     <mergeCell ref="T35:U35"/>
     <mergeCell ref="O33:P33"/>
@@ -4334,42 +4377,42 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M41:N41"/>
     <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D47:E47"/>
     <mergeCell ref="O32:P32"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="M72:U72"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="M70:O70"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D54:E54"/>
     <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D67:E67"/>
     <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="T82:U82"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="R81:S81"/>
     <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R76:S76"/>
     <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="T81:U81"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D55:E55"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -4379,7 +4422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -5138,7 +5181,11 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221"/>
+      <c r="N23" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24/06/2026</t>
+        </is>
+      </c>
       <c r="O23" s="222"/>
       <c r="P23" s="222"/>
       <c r="Q23" s="222"/>
@@ -5526,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O41)</f>
+        <f>SUM(O42)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
@@ -5554,87 +5601,85 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="20"/>
-      <c r="C38" s="32"/>
-      <c r="I38" s="134"/>
-      <c r="J38"/>
-      <c r="L38" s="114">
-        <v>2</v>
-      </c>
-      <c r="M38" s="179" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="180"/>
-      <c r="O38" s="46">
-        <v>300000</v>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M38" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/01/2026</t>
+        </is>
+      </c>
+      <c r="N38" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="O38" s="39">
+        <v>200000</v>
       </c>
       <c r="P38" s="42"/>
-      <c r="Q38" s="79"/>
+      <c r="Q38" s="72"/>
       <c r="R38" s="44"/>
       <c r="S38" s="77"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="U38" s="72"/>
+    </row>
+    <row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="20"/>
       <c r="C39" s="32"/>
       <c r="I39" s="134"/>
       <c r="J39"/>
-      <c r="K39" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L39" s="114">
-        <v>3</v>
-      </c>
-      <c r="M39" s="37"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="39"/>
+        <v>2</v>
+      </c>
+      <c r="M39" s="179" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" s="180"/>
+      <c r="O39" s="46">
+        <v>300000</v>
+      </c>
       <c r="P39" s="42"/>
-      <c r="Q39" s="72"/>
+      <c r="Q39" s="79"/>
       <c r="R39" s="44"/>
       <c r="S39" s="77"/>
       <c r="T39" s="42"/>
-      <c r="U39" s="72"/>
+      <c r="U39" s="80"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B40" s="20"/>
       <c r="C40" s="32"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="47"/>
       <c r="I40" s="134"/>
       <c r="J40"/>
-      <c r="K40" s="24"/>
+      <c r="K40" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L40" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" s="37"/>
       <c r="N40" s="38"/>
       <c r="O40" s="39"/>
       <c r="P40" s="42"/>
-      <c r="Q40" s="70"/>
+      <c r="Q40" s="72"/>
       <c r="R40" s="44"/>
-      <c r="S40" s="78"/>
+      <c r="S40" s="77"/>
       <c r="T40" s="42"/>
       <c r="U40" s="72"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="I41" s="133"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="47"/>
+      <c r="I41" s="134"/>
       <c r="J41"/>
       <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M41" s="37"/>
       <c r="N41" s="38"/>
@@ -5648,16 +5693,16 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="20"/>
-      <c r="C42" s="25"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
-      <c r="F42" s="51"/>
-      <c r="I42" s="135"/>
-      <c r="J42" s="57"/>
+      <c r="I42" s="133"/>
+      <c r="J42"/>
+      <c r="K42" s="24"/>
       <c r="L42" s="114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
@@ -5665,52 +5710,51 @@
       <c r="P42" s="42"/>
       <c r="Q42" s="70"/>
       <c r="R42" s="44"/>
-      <c r="S42" s="77"/>
+      <c r="S42" s="78"/>
       <c r="T42" s="42"/>
       <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="112"/>
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B43" s="20"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="183"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
       <c r="F43" s="51"/>
-      <c r="G43" s="8"/>
-      <c r="I43" s="136"/>
+      <c r="I43" s="135"/>
       <c r="J43" s="57"/>
-      <c r="K43" s="24" t="e">
-        <f>O38+O65</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L43" s="114">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="71"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="77"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
-    </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A44" s="112"/>
       <c r="B44" s="20"/>
-      <c r="C44" s="25"/>
+      <c r="C44" s="32"/>
       <c r="D44" s="183"/>
       <c r="E44" s="183"/>
-      <c r="F44" s="52"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="13"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="8"/>
+      <c r="I44" s="136"/>
       <c r="J44" s="57"/>
-      <c r="K44" s="24"/>
+      <c r="K44" s="24" t="e">
+        <f>O39+O66</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L44" s="114">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
@@ -5722,18 +5766,19 @@
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="43"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="25"/>
       <c r="D45" s="183"/>
       <c r="E45" s="183"/>
-      <c r="F45" s="23"/>
+      <c r="F45" s="52"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
       <c r="J45" s="57"/>
+      <c r="K45" s="24"/>
       <c r="L45" s="114">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
@@ -5741,22 +5786,22 @@
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
       <c r="R45" s="42"/>
-      <c r="S45" s="76"/>
+      <c r="S45" s="71"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="20"/>
-      <c r="B46" s="20"/>
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
       <c r="C46" s="43"/>
       <c r="D46" s="183"/>
       <c r="E46" s="183"/>
-      <c r="F46" s="53"/>
+      <c r="F46" s="23"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
       <c r="J46" s="57"/>
       <c r="L46" s="114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -5764,7 +5809,7 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="70"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="71"/>
+      <c r="S46" s="76"/>
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
@@ -5774,17 +5819,12 @@
       <c r="C47" s="43"/>
       <c r="D47" s="183"/>
       <c r="E47" s="183"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="1"/>
+      <c r="F47" s="53"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
-      <c r="K47" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L47" s="114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -5802,13 +5842,17 @@
       <c r="C48" s="43"/>
       <c r="D48" s="183"/>
       <c r="E48" s="183"/>
-      <c r="F48" s="23"/>
+      <c r="F48" s="17"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
+      <c r="K48" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L48" s="114">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -5817,10 +5861,10 @@
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
       <c r="S48" s="71"/>
-      <c r="T48" s="44"/>
+      <c r="T48" s="42"/>
       <c r="U48" s="72"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
@@ -5828,11 +5872,11 @@
       <c r="E49" s="183"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="50"/>
+      <c r="H49" s="68"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -5848,15 +5892,15 @@
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="25"/>
+      <c r="D50" s="183"/>
+      <c r="E50" s="183"/>
       <c r="F50" s="23"/>
       <c r="G50" s="1"/>
       <c r="H50" s="50"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
       <c r="L50" s="114">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -5872,20 +5916,20 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="184"/>
-      <c r="E51" s="184"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="25"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="40"/>
+      <c r="P51" s="42"/>
       <c r="Q51" s="70"/>
       <c r="R51" s="42"/>
       <c r="S51" s="71"/>
@@ -5894,17 +5938,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="55"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="182"/>
-      <c r="E52" s="182"/>
+      <c r="D52" s="184"/>
+      <c r="E52" s="184"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
-      <c r="I52" s="54"/>
+      <c r="I52" s="13"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
@@ -5917,21 +5961,23 @@
       <c r="U52" s="72"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="25"/>
+      <c r="A53" s="20"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="181"/>
-      <c r="E53" s="181"/>
+      <c r="D53" s="182"/>
+      <c r="E53" s="182"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
       <c r="I53" s="54"/>
       <c r="J53" s="57"/>
-      <c r="L53" s="18"/>
+      <c r="L53" s="114">
+        <v>16</v>
+      </c>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="42"/>
+      <c r="P53" s="40"/>
       <c r="Q53" s="70"/>
       <c r="R53" s="42"/>
       <c r="S53" s="71"/>
@@ -5939,7 +5985,7 @@
       <c r="U53" s="72"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="20"/>
+      <c r="A54" s="25"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
       <c r="D54" s="181"/>
@@ -5964,8 +6010,8 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
+      <c r="D55" s="181"/>
+      <c r="E55" s="181"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
@@ -5984,7 +6030,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
-      <c r="B56"/>
+      <c r="B56" s="55"/>
       <c r="C56" s="43"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
@@ -6071,11 +6117,11 @@
       <c r="U59" s="72"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="25"/>
+      <c r="A60" s="20"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="181"/>
-      <c r="E60" s="181"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -6096,8 +6142,8 @@
       <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
+      <c r="D61" s="181"/>
+      <c r="E61" s="181"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="50"/>
@@ -6108,9 +6154,9 @@
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
       <c r="P61" s="42"/>
-      <c r="Q61" s="161"/>
-      <c r="R61" s="93"/>
-      <c r="S61" s="92"/>
+      <c r="Q61" s="70"/>
+      <c r="R61" s="42"/>
+      <c r="S61" s="71"/>
       <c r="T61" s="44"/>
       <c r="U61" s="72"/>
     </row>
@@ -6158,12 +6204,12 @@
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
-    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="181"/>
-      <c r="E64" s="181"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -6174,116 +6220,116 @@
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
       <c r="P64" s="42"/>
-      <c r="Q64" s="88"/>
+      <c r="Q64" s="161"/>
       <c r="R64" s="93"/>
       <c r="S64" s="92"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="75"/>
-    </row>
-    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U64" s="72"/>
+    </row>
+    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
       <c r="D65" s="181"/>
       <c r="E65" s="181"/>
-      <c r="F65" s="20"/>
+      <c r="F65" s="23"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
-      <c r="L65"/>
-      <c r="M65" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="N65" s="180"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q65" s="46"/>
-      <c r="R65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S65" s="46"/>
-      <c r="T65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U65" s="46"/>
-    </row>
-    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65" s="18"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="42"/>
+      <c r="Q65" s="88"/>
+      <c r="R65" s="93"/>
+      <c r="S65" s="92"/>
+      <c r="T65" s="44"/>
+      <c r="U65" s="75"/>
+    </row>
+    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="95"/>
+      <c r="C66" s="43"/>
       <c r="D66" s="181"/>
       <c r="E66" s="181"/>
-      <c r="F66" s="23"/>
+      <c r="F66" s="20"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
-      <c r="J66"/>
+      <c r="J66" s="57"/>
       <c r="L66"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="59"/>
-      <c r="O66" s="74"/>
-      <c r="P66" s="23"/>
-      <c r="Q66" s="73"/>
-      <c r="R66" s="74"/>
-      <c r="S66" s="74"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="179" t="s">
+        <v>34</v>
+      </c>
+      <c r="N66" s="180"/>
+      <c r="O66" s="46"/>
+      <c r="P66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q66" s="46"/>
+      <c r="R66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S66" s="46"/>
+      <c r="T66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U66" s="46"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="181"/>
+      <c r="E67" s="181"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="189" t="s">
-        <v>47</v>
-      </c>
-      <c r="N67" s="190"/>
-      <c r="O67" s="193"/>
-      <c r="P67" s="191"/>
-      <c r="Q67" s="192"/>
-      <c r="R67" s="189" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" s="190"/>
-      <c r="T67" s="185" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U67" s="186"/>
-    </row>
-    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="58"/>
+      <c r="N67" s="59"/>
+      <c r="O67" s="74"/>
+      <c r="P67" s="23"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="74"/>
+      <c r="S67" s="74"/>
+      <c r="T67" s="6"/>
+    </row>
+    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="181"/>
-      <c r="E68" s="181"/>
-      <c r="F68" s="67"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="23"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
       <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="87"/>
-      <c r="O68" s="87"/>
-      <c r="P68" s="61"/>
-      <c r="Q68" s="62"/>
-      <c r="R68" s="62"/>
-      <c r="S68" s="62"/>
-      <c r="T68" s="60"/>
-      <c r="U68" s="60"/>
+      <c r="M68" s="189" t="s">
+        <v>47</v>
+      </c>
+      <c r="N68" s="190"/>
+      <c r="O68" s="193"/>
+      <c r="P68" s="191"/>
+      <c r="Q68" s="192"/>
+      <c r="R68" s="189" t="s">
+        <v>37</v>
+      </c>
+      <c r="S68" s="190"/>
+      <c r="T68" s="185" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U68" s="186"/>
     </row>
     <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69" s="95"/>
+      <c r="B69"/>
       <c r="C69" s="25"/>
       <c r="D69" s="181"/>
       <c r="E69" s="181"/>
@@ -6293,22 +6339,19 @@
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="179" t="s">
-        <v>35</v>
-      </c>
-      <c r="N69" s="187"/>
-      <c r="O69" s="187"/>
-      <c r="P69" s="187"/>
-      <c r="Q69" s="187"/>
-      <c r="R69" s="187"/>
-      <c r="S69" s="187"/>
-      <c r="T69" s="187"/>
-      <c r="U69" s="188"/>
-      <c r="V69" s="55"/>
-    </row>
-    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="60"/>
+      <c r="N69" s="87"/>
+      <c r="O69" s="87"/>
+      <c r="P69" s="61"/>
+      <c r="Q69" s="62"/>
+      <c r="R69" s="62"/>
+      <c r="S69" s="62"/>
+      <c r="T69" s="60"/>
+      <c r="U69" s="60"/>
+    </row>
+    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="20"/>
+      <c r="B70" s="95"/>
       <c r="C70" s="25"/>
       <c r="D70" s="181"/>
       <c r="E70" s="181"/>
@@ -6317,36 +6360,23 @@
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
-      <c r="L70" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M70" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N70" s="157"/>
-      <c r="O70" s="157"/>
-      <c r="P70" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q70" s="157"/>
-      <c r="R70" s="157"/>
-      <c r="S70" s="157"/>
-      <c r="T70" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U70" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V70" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W70" s="170" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L70"/>
+      <c r="M70" s="179" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" s="187"/>
+      <c r="O70" s="187"/>
+      <c r="P70" s="187"/>
+      <c r="Q70" s="187"/>
+      <c r="R70" s="187"/>
+      <c r="S70" s="187"/>
+      <c r="T70" s="187"/>
+      <c r="U70" s="188"/>
+      <c r="V70" s="55"/>
+    </row>
+    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="25"/>
-      <c r="B71" s="130"/>
+      <c r="B71" s="20"/>
       <c r="C71" s="25"/>
       <c r="D71" s="181"/>
       <c r="E71" s="181"/>
@@ -6354,182 +6384,235 @@
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
-      <c r="J71" s="23"/>
-      <c r="L71"/>
-      <c r="M71" s="63"/>
-      <c r="N71" s="64"/>
-      <c r="O71" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P71" s="66"/>
-      <c r="Q71" s="65"/>
-      <c r="R71" s="178" t="s">
-        <v>6</v>
-      </c>
-      <c r="S71" s="178"/>
-      <c r="T71" s="159"/>
-      <c r="U71" s="160"/>
-      <c r="V71" s="55"/>
+      <c r="J71"/>
+      <c r="L71" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="157"/>
+      <c r="O71" s="157"/>
+      <c r="P71" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q71" s="157"/>
+      <c r="R71" s="157"/>
+      <c r="S71" s="157"/>
+      <c r="T71" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U71" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V71" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W71" s="170" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="55"/>
-      <c r="C72" s="94"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="130"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="181"/>
       <c r="E72" s="181"/>
       <c r="F72" s="67"/>
-      <c r="I72" s="130"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="23"/>
       <c r="L72"/>
-      <c r="M72" s="89"/>
-      <c r="N72" s="90"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="91"/>
-      <c r="Q72" s="60"/>
-      <c r="R72" s="173"/>
-      <c r="S72" s="173"/>
-      <c r="T72" s="69"/>
-      <c r="U72" s="100"/>
+      <c r="M72" s="63"/>
+      <c r="N72" s="64"/>
+      <c r="O72" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P72" s="66"/>
+      <c r="Q72" s="65"/>
+      <c r="R72" s="178" t="s">
+        <v>6</v>
+      </c>
+      <c r="S72" s="178"/>
+      <c r="T72" s="159"/>
+      <c r="U72" s="160"/>
       <c r="V72" s="55"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="53"/>
-      <c r="B73" s="94"/>
+      <c r="B73" s="55"/>
       <c r="C73" s="94"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="25"/>
+      <c r="D73" s="181"/>
+      <c r="E73" s="181"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
+      <c r="L73"/>
+      <c r="M73" s="89"/>
+      <c r="N73" s="90"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="91"/>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="173"/>
+      <c r="S73" s="173"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
+      <c r="V73" s="55"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="53"/>
+      <c r="B74" s="94"/>
+      <c r="C74" s="94"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="67"/>
+      <c r="I74" s="130"/>
+      <c r="L74" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">111</t>
         </is>
       </c>
-      <c r="M73" s="89" t="inlineStr">
+      <c r="M74" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="N73" s="90"/>
-      <c r="O73" s="18" t="s">
+      <c r="N74" s="90"/>
+      <c r="O74" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91" t="inlineStr">
+      <c r="P74" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="173" t="s">
+      <c r="Q74" s="60"/>
+      <c r="R74" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="173"/>
-      <c r="T73" s="69">
+      <c r="S74" s="173"/>
+      <c r="T74" s="69">
         <v>150000</v>
       </c>
-      <c r="U73" s="100" t="inlineStr">
+      <c r="U74" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">SANTANDER</t>
         </is>
       </c>
-      <c r="V73" s="55"/>
-    </row>
-    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L74" s="49"/>
-      <c r="M74" s="89"/>
-      <c r="N74" s="90"/>
-      <c r="O74" s="147"/>
-      <c r="P74" s="91"/>
-      <c r="Q74" s="60"/>
-      <c r="R74" s="173"/>
-      <c r="S74" s="173"/>
-      <c r="T74" s="69"/>
-      <c r="U74" s="100"/>
       <c r="V74" s="55"/>
     </row>
-    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="L75" s="49"/>
-      <c r="M75" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="N75" s="164"/>
-      <c r="O75" s="165"/>
-      <c r="P75" s="166"/>
-      <c r="Q75" s="167"/>
-      <c r="R75" s="177"/>
-      <c r="S75" s="177"/>
-      <c r="T75" s="171"/>
-      <c r="U75" s="172"/>
-      <c r="V75" s="55"/>
+      <c r="M75" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE DOS</t>
+        </is>
+      </c>
+      <c r="O75" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="P75" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F002</t>
+        </is>
+      </c>
+      <c r="T75" s="69">
+        <v>250000</v>
+      </c>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="49"/>
-      <c r="M76" s="163" t="s">
+      <c r="M76" s="89"/>
+      <c r="N76" s="90"/>
+      <c r="O76" s="147"/>
+      <c r="P76" s="91"/>
+      <c r="Q76" s="60"/>
+      <c r="R76" s="173"/>
+      <c r="S76" s="173"/>
+      <c r="T76" s="69"/>
+      <c r="U76" s="100"/>
+      <c r="V76" s="55"/>
+    </row>
+    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L77" s="49"/>
+      <c r="M77" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N77" s="164"/>
+      <c r="O77" s="165"/>
+      <c r="P77" s="166"/>
+      <c r="Q77" s="167"/>
+      <c r="R77" s="177"/>
+      <c r="S77" s="177"/>
+      <c r="T77" s="171"/>
+      <c r="U77" s="172"/>
+      <c r="V77" s="55"/>
+    </row>
+    <row r="78" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L78" s="49"/>
+      <c r="M78" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="N76" s="164"/>
-      <c r="O76" s="165"/>
-      <c r="P76" s="166"/>
-      <c r="Q76" s="167"/>
-      <c r="R76" s="168"/>
-      <c r="S76" s="168"/>
-      <c r="T76" s="171"/>
-      <c r="U76" s="172"/>
-      <c r="V76" s="55"/>
-    </row>
-    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L77" s="49"/>
-      <c r="M77" s="99"/>
-      <c r="N77" s="68"/>
-      <c r="O77" s="147"/>
-      <c r="P77" s="91"/>
-      <c r="Q77" s="60"/>
-      <c r="R77" s="60"/>
-      <c r="S77" s="60"/>
-      <c r="T77" s="69"/>
-      <c r="U77" s="100"/>
-      <c r="V77" s="55"/>
-    </row>
-    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L78" s="49"/>
-      <c r="M78" s="106" t="s">
+      <c r="N78" s="164"/>
+      <c r="O78" s="165"/>
+      <c r="P78" s="166"/>
+      <c r="Q78" s="167"/>
+      <c r="R78" s="168"/>
+      <c r="S78" s="168"/>
+      <c r="T78" s="171"/>
+      <c r="U78" s="172"/>
+      <c r="V78" s="55"/>
+    </row>
+    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L79" s="49"/>
+      <c r="M79" s="99"/>
+      <c r="N79" s="68"/>
+      <c r="O79" s="147"/>
+      <c r="P79" s="91"/>
+      <c r="Q79" s="60"/>
+      <c r="R79" s="60"/>
+      <c r="S79" s="60"/>
+      <c r="T79" s="69"/>
+      <c r="U79" s="100"/>
+      <c r="V79" s="55"/>
+    </row>
+    <row r="80" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L80" s="49"/>
+      <c r="M80" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="N78" s="107">
-        <f>SUM(N76:N77)</f>
-        <v>0</v>
-      </c>
-      <c r="O78" s="101"/>
-      <c r="P78" s="103"/>
-      <c r="Q78" s="102"/>
-      <c r="R78" s="102"/>
-      <c r="S78" s="102"/>
-      <c r="T78" s="104"/>
-      <c r="U78" s="105"/>
-      <c r="V78" s="55"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M79"/>
-      <c r="O79" s="5"/>
-      <c r="Q79"/>
-      <c r="S79"/>
-      <c r="T79" s="6"/>
-      <c r="V79" s="55"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O80"/>
+      <c r="N80" s="107">
+        <f>SUM(N78:N79)</f>
+        <v>0</v>
+      </c>
+      <c r="O80" s="101"/>
+      <c r="P80" s="103"/>
+      <c r="Q80" s="102"/>
+      <c r="R80" s="102"/>
+      <c r="S80" s="102"/>
+      <c r="T80" s="104"/>
+      <c r="U80" s="105"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M81"/>
+      <c r="O81" s="5"/>
+      <c r="Q81"/>
+      <c r="S81"/>
+      <c r="T81" s="6"/>
       <c r="V81" s="55"/>
     </row>
-    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O82"/>
       <c r="V82" s="55"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M83" s="23"/>
+      <c r="N83" s="23"/>
+      <c r="O83" s="23"/>
+      <c r="P83" s="23"/>
+      <c r="Q83" s="23"/>
       <c r="V83" s="55"/>
     </row>
     <row r="84" spans="13:22" x14ac:dyDescent="0.3">
@@ -6571,10 +6654,10 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
-    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V98" s="55"/>
     </row>
     <row r="99" spans="22:22" x14ac:dyDescent="0.3">
@@ -6618,6 +6701,12 @@
     </row>
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
+    </row>
+    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V113" s="55"/>
+    </row>
+    <row r="114" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V114" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="72">
@@ -6644,7 +6733,7 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:U30"/>
     <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="R35:S35"/>
     <mergeCell ref="T35:U35"/>
     <mergeCell ref="O33:P33"/>
@@ -6657,42 +6746,42 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
     <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="O32:P32"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="M70:U70"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="P68:Q68"/>
     <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D52:E52"/>
     <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="T78:U78"/>
+    <mergeCell ref="R76:S76"/>
+    <mergeCell ref="R77:S77"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T77:U77"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
     <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -6702,7 +6791,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -7461,7 +7550,11 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221"/>
+      <c r="N23" s="221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24/06/2026</t>
+        </is>
+      </c>
       <c r="O23" s="222"/>
       <c r="P23" s="222"/>
       <c r="Q23" s="222"/>
@@ -7849,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O41)</f>
+        <f>SUM(O42)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
@@ -7877,87 +7970,85 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="20"/>
-      <c r="C38" s="32"/>
-      <c r="I38" s="134"/>
-      <c r="J38"/>
-      <c r="L38" s="114">
-        <v>2</v>
-      </c>
-      <c r="M38" s="179" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="180"/>
-      <c r="O38" s="46">
-        <v>300000</v>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M38" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02/01/2026</t>
+        </is>
+      </c>
+      <c r="N38" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="O38" s="39">
+        <v>200000</v>
       </c>
       <c r="P38" s="42"/>
-      <c r="Q38" s="79"/>
+      <c r="Q38" s="72"/>
       <c r="R38" s="44"/>
       <c r="S38" s="77"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="U38" s="72"/>
+    </row>
+    <row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="20"/>
       <c r="C39" s="32"/>
       <c r="I39" s="134"/>
       <c r="J39"/>
-      <c r="K39" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L39" s="114">
-        <v>3</v>
-      </c>
-      <c r="M39" s="37"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="39"/>
+        <v>2</v>
+      </c>
+      <c r="M39" s="179" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" s="180"/>
+      <c r="O39" s="46">
+        <v>300000</v>
+      </c>
       <c r="P39" s="42"/>
-      <c r="Q39" s="72"/>
+      <c r="Q39" s="79"/>
       <c r="R39" s="44"/>
       <c r="S39" s="77"/>
       <c r="T39" s="42"/>
-      <c r="U39" s="72"/>
+      <c r="U39" s="80"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B40" s="20"/>
       <c r="C40" s="32"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="47"/>
       <c r="I40" s="134"/>
       <c r="J40"/>
-      <c r="K40" s="24"/>
+      <c r="K40" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L40" s="114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M40" s="37"/>
       <c r="N40" s="38"/>
       <c r="O40" s="39"/>
       <c r="P40" s="42"/>
-      <c r="Q40" s="70"/>
+      <c r="Q40" s="72"/>
       <c r="R40" s="44"/>
-      <c r="S40" s="78"/>
+      <c r="S40" s="77"/>
       <c r="T40" s="42"/>
       <c r="U40" s="72"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="I41" s="133"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="47"/>
+      <c r="I41" s="134"/>
       <c r="J41"/>
       <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M41" s="37"/>
       <c r="N41" s="38"/>
@@ -7971,16 +8062,16 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="20"/>
-      <c r="C42" s="25"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
-      <c r="F42" s="51"/>
-      <c r="I42" s="135"/>
-      <c r="J42" s="57"/>
+      <c r="I42" s="133"/>
+      <c r="J42"/>
+      <c r="K42" s="24"/>
       <c r="L42" s="114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
@@ -7988,52 +8079,51 @@
       <c r="P42" s="42"/>
       <c r="Q42" s="70"/>
       <c r="R42" s="44"/>
-      <c r="S42" s="77"/>
+      <c r="S42" s="78"/>
       <c r="T42" s="42"/>
       <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="112"/>
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B43" s="20"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="183"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
       <c r="F43" s="51"/>
-      <c r="G43" s="8"/>
-      <c r="I43" s="136"/>
+      <c r="I43" s="135"/>
       <c r="J43" s="57"/>
-      <c r="K43" s="24" t="e">
-        <f>O38+O65</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L43" s="114">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="71"/>
+      <c r="R43" s="44"/>
+      <c r="S43" s="77"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
-    </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A44" s="112"/>
       <c r="B44" s="20"/>
-      <c r="C44" s="25"/>
+      <c r="C44" s="32"/>
       <c r="D44" s="183"/>
       <c r="E44" s="183"/>
-      <c r="F44" s="52"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="13"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="8"/>
+      <c r="I44" s="136"/>
       <c r="J44" s="57"/>
-      <c r="K44" s="24"/>
+      <c r="K44" s="24" t="e">
+        <f>O39+O66</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L44" s="114">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
@@ -8045,18 +8135,19 @@
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="43"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="25"/>
       <c r="D45" s="183"/>
       <c r="E45" s="183"/>
-      <c r="F45" s="23"/>
+      <c r="F45" s="52"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
       <c r="J45" s="57"/>
+      <c r="K45" s="24"/>
       <c r="L45" s="114">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
@@ -8064,22 +8155,22 @@
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
       <c r="R45" s="42"/>
-      <c r="S45" s="76"/>
+      <c r="S45" s="71"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="20"/>
-      <c r="B46" s="20"/>
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
       <c r="C46" s="43"/>
       <c r="D46" s="183"/>
       <c r="E46" s="183"/>
-      <c r="F46" s="53"/>
+      <c r="F46" s="23"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
       <c r="J46" s="57"/>
       <c r="L46" s="114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -8087,7 +8178,7 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="70"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="71"/>
+      <c r="S46" s="76"/>
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
@@ -8097,17 +8188,12 @@
       <c r="C47" s="43"/>
       <c r="D47" s="183"/>
       <c r="E47" s="183"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="1"/>
+      <c r="F47" s="53"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
-      <c r="K47" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L47" s="114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -8125,13 +8211,17 @@
       <c r="C48" s="43"/>
       <c r="D48" s="183"/>
       <c r="E48" s="183"/>
-      <c r="F48" s="23"/>
+      <c r="F48" s="17"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
+      <c r="K48" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L48" s="114">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -8140,10 +8230,10 @@
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
       <c r="S48" s="71"/>
-      <c r="T48" s="44"/>
+      <c r="T48" s="42"/>
       <c r="U48" s="72"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
@@ -8151,11 +8241,11 @@
       <c r="E49" s="183"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="50"/>
+      <c r="H49" s="68"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -8171,15 +8261,15 @@
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="25"/>
+      <c r="D50" s="183"/>
+      <c r="E50" s="183"/>
       <c r="F50" s="23"/>
       <c r="G50" s="1"/>
       <c r="H50" s="50"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
       <c r="L50" s="114">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -8195,20 +8285,20 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="184"/>
-      <c r="E51" s="184"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="25"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="40"/>
+      <c r="P51" s="42"/>
       <c r="Q51" s="70"/>
       <c r="R51" s="42"/>
       <c r="S51" s="71"/>
@@ -8217,17 +8307,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="55"/>
+      <c r="B52" s="20"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="182"/>
-      <c r="E52" s="182"/>
+      <c r="D52" s="184"/>
+      <c r="E52" s="184"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
-      <c r="I52" s="54"/>
+      <c r="I52" s="13"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
@@ -8240,21 +8330,23 @@
       <c r="U52" s="72"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="25"/>
+      <c r="A53" s="20"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="181"/>
-      <c r="E53" s="181"/>
+      <c r="D53" s="182"/>
+      <c r="E53" s="182"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
       <c r="I53" s="54"/>
       <c r="J53" s="57"/>
-      <c r="L53" s="18"/>
+      <c r="L53" s="114">
+        <v>16</v>
+      </c>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="42"/>
+      <c r="P53" s="40"/>
       <c r="Q53" s="70"/>
       <c r="R53" s="42"/>
       <c r="S53" s="71"/>
@@ -8262,7 +8354,7 @@
       <c r="U53" s="72"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="20"/>
+      <c r="A54" s="25"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
       <c r="D54" s="181"/>
@@ -8287,8 +8379,8 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
+      <c r="D55" s="181"/>
+      <c r="E55" s="181"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
@@ -8307,7 +8399,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
-      <c r="B56"/>
+      <c r="B56" s="55"/>
       <c r="C56" s="43"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
@@ -8394,11 +8486,11 @@
       <c r="U59" s="72"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="25"/>
+      <c r="A60" s="20"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="181"/>
-      <c r="E60" s="181"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -8419,8 +8511,8 @@
       <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
+      <c r="D61" s="181"/>
+      <c r="E61" s="181"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="50"/>
@@ -8431,9 +8523,9 @@
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
       <c r="P61" s="42"/>
-      <c r="Q61" s="161"/>
-      <c r="R61" s="93"/>
-      <c r="S61" s="92"/>
+      <c r="Q61" s="70"/>
+      <c r="R61" s="42"/>
+      <c r="S61" s="71"/>
       <c r="T61" s="44"/>
       <c r="U61" s="72"/>
     </row>
@@ -8481,12 +8573,12 @@
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
-    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="181"/>
-      <c r="E64" s="181"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -8497,116 +8589,116 @@
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
       <c r="P64" s="42"/>
-      <c r="Q64" s="88"/>
+      <c r="Q64" s="161"/>
       <c r="R64" s="93"/>
       <c r="S64" s="92"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="75"/>
-    </row>
-    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U64" s="72"/>
+    </row>
+    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
       <c r="D65" s="181"/>
       <c r="E65" s="181"/>
-      <c r="F65" s="20"/>
+      <c r="F65" s="23"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
-      <c r="L65"/>
-      <c r="M65" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="N65" s="180"/>
-      <c r="O65" s="46"/>
-      <c r="P65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q65" s="46"/>
-      <c r="R65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S65" s="46"/>
-      <c r="T65" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U65" s="46"/>
-    </row>
-    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65" s="18"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="39"/>
+      <c r="P65" s="42"/>
+      <c r="Q65" s="88"/>
+      <c r="R65" s="93"/>
+      <c r="S65" s="92"/>
+      <c r="T65" s="44"/>
+      <c r="U65" s="75"/>
+    </row>
+    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="95"/>
+      <c r="C66" s="43"/>
       <c r="D66" s="181"/>
       <c r="E66" s="181"/>
-      <c r="F66" s="23"/>
+      <c r="F66" s="20"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
-      <c r="J66"/>
+      <c r="J66" s="57"/>
       <c r="L66"/>
-      <c r="M66" s="58"/>
-      <c r="N66" s="59"/>
-      <c r="O66" s="74"/>
-      <c r="P66" s="23"/>
-      <c r="Q66" s="73"/>
-      <c r="R66" s="74"/>
-      <c r="S66" s="74"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="179" t="s">
+        <v>34</v>
+      </c>
+      <c r="N66" s="180"/>
+      <c r="O66" s="46"/>
+      <c r="P66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q66" s="46"/>
+      <c r="R66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S66" s="46"/>
+      <c r="T66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U66" s="46"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="181"/>
+      <c r="E67" s="181"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="189" t="s">
-        <v>47</v>
-      </c>
-      <c r="N67" s="190"/>
-      <c r="O67" s="193"/>
-      <c r="P67" s="191"/>
-      <c r="Q67" s="192"/>
-      <c r="R67" s="189" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" s="190"/>
-      <c r="T67" s="185" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U67" s="186"/>
-    </row>
-    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="58"/>
+      <c r="N67" s="59"/>
+      <c r="O67" s="74"/>
+      <c r="P67" s="23"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="74"/>
+      <c r="S67" s="74"/>
+      <c r="T67" s="6"/>
+    </row>
+    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="181"/>
-      <c r="E68" s="181"/>
-      <c r="F68" s="67"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="23"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
       <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="87"/>
-      <c r="O68" s="87"/>
-      <c r="P68" s="61"/>
-      <c r="Q68" s="62"/>
-      <c r="R68" s="62"/>
-      <c r="S68" s="62"/>
-      <c r="T68" s="60"/>
-      <c r="U68" s="60"/>
+      <c r="M68" s="189" t="s">
+        <v>47</v>
+      </c>
+      <c r="N68" s="190"/>
+      <c r="O68" s="193"/>
+      <c r="P68" s="191"/>
+      <c r="Q68" s="192"/>
+      <c r="R68" s="189" t="s">
+        <v>37</v>
+      </c>
+      <c r="S68" s="190"/>
+      <c r="T68" s="185" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U68" s="186"/>
     </row>
     <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69" s="95"/>
+      <c r="B69"/>
       <c r="C69" s="25"/>
       <c r="D69" s="181"/>
       <c r="E69" s="181"/>
@@ -8616,22 +8708,19 @@
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="179" t="s">
-        <v>35</v>
-      </c>
-      <c r="N69" s="187"/>
-      <c r="O69" s="187"/>
-      <c r="P69" s="187"/>
-      <c r="Q69" s="187"/>
-      <c r="R69" s="187"/>
-      <c r="S69" s="187"/>
-      <c r="T69" s="187"/>
-      <c r="U69" s="188"/>
-      <c r="V69" s="55"/>
-    </row>
-    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="60"/>
+      <c r="N69" s="87"/>
+      <c r="O69" s="87"/>
+      <c r="P69" s="61"/>
+      <c r="Q69" s="62"/>
+      <c r="R69" s="62"/>
+      <c r="S69" s="62"/>
+      <c r="T69" s="60"/>
+      <c r="U69" s="60"/>
+    </row>
+    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="20"/>
+      <c r="B70" s="95"/>
       <c r="C70" s="25"/>
       <c r="D70" s="181"/>
       <c r="E70" s="181"/>
@@ -8640,36 +8729,23 @@
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
-      <c r="L70" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M70" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N70" s="157"/>
-      <c r="O70" s="157"/>
-      <c r="P70" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q70" s="157"/>
-      <c r="R70" s="157"/>
-      <c r="S70" s="157"/>
-      <c r="T70" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U70" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V70" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W70" s="170" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L70"/>
+      <c r="M70" s="179" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" s="187"/>
+      <c r="O70" s="187"/>
+      <c r="P70" s="187"/>
+      <c r="Q70" s="187"/>
+      <c r="R70" s="187"/>
+      <c r="S70" s="187"/>
+      <c r="T70" s="187"/>
+      <c r="U70" s="188"/>
+      <c r="V70" s="55"/>
+    </row>
+    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="25"/>
-      <c r="B71" s="130"/>
+      <c r="B71" s="20"/>
       <c r="C71" s="25"/>
       <c r="D71" s="181"/>
       <c r="E71" s="181"/>
@@ -8677,182 +8753,235 @@
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
-      <c r="J71" s="23"/>
-      <c r="L71"/>
-      <c r="M71" s="63"/>
-      <c r="N71" s="64"/>
-      <c r="O71" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P71" s="66"/>
-      <c r="Q71" s="65"/>
-      <c r="R71" s="178" t="s">
-        <v>6</v>
-      </c>
-      <c r="S71" s="178"/>
-      <c r="T71" s="159"/>
-      <c r="U71" s="160"/>
-      <c r="V71" s="55"/>
+      <c r="J71"/>
+      <c r="L71" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="157"/>
+      <c r="O71" s="157"/>
+      <c r="P71" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q71" s="157"/>
+      <c r="R71" s="157"/>
+      <c r="S71" s="157"/>
+      <c r="T71" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U71" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V71" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W71" s="170" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="55"/>
-      <c r="C72" s="94"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="130"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="181"/>
       <c r="E72" s="181"/>
       <c r="F72" s="67"/>
-      <c r="I72" s="130"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="50"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="23"/>
       <c r="L72"/>
-      <c r="M72" s="89"/>
-      <c r="N72" s="90"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="91"/>
-      <c r="Q72" s="60"/>
-      <c r="R72" s="173"/>
-      <c r="S72" s="173"/>
-      <c r="T72" s="69"/>
-      <c r="U72" s="100"/>
+      <c r="M72" s="63"/>
+      <c r="N72" s="64"/>
+      <c r="O72" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P72" s="66"/>
+      <c r="Q72" s="65"/>
+      <c r="R72" s="178" t="s">
+        <v>6</v>
+      </c>
+      <c r="S72" s="178"/>
+      <c r="T72" s="159"/>
+      <c r="U72" s="160"/>
       <c r="V72" s="55"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="53"/>
-      <c r="B73" s="94"/>
+      <c r="B73" s="55"/>
       <c r="C73" s="94"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="25"/>
+      <c r="D73" s="181"/>
+      <c r="E73" s="181"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
+      <c r="L73"/>
+      <c r="M73" s="89"/>
+      <c r="N73" s="90"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="91"/>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="173"/>
+      <c r="S73" s="173"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
+      <c r="V73" s="55"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="53"/>
+      <c r="B74" s="94"/>
+      <c r="C74" s="94"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="67"/>
+      <c r="I74" s="130"/>
+      <c r="L74" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">222</t>
         </is>
       </c>
-      <c r="M73" s="89" t="inlineStr">
+      <c r="M74" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="N73" s="90"/>
-      <c r="O73" s="18" t="s">
+      <c r="N74" s="90"/>
+      <c r="O74" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91" t="inlineStr">
+      <c r="P74" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="173" t="s">
+      <c r="Q74" s="60"/>
+      <c r="R74" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="173"/>
-      <c r="T73" s="69">
+      <c r="S74" s="173"/>
+      <c r="T74" s="69">
         <v>150000</v>
       </c>
-      <c r="U73" s="100" t="inlineStr">
+      <c r="U74" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">SANTANDER</t>
         </is>
       </c>
-      <c r="V73" s="55"/>
-    </row>
-    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L74" s="49"/>
-      <c r="M74" s="89"/>
-      <c r="N74" s="90"/>
-      <c r="O74" s="147"/>
-      <c r="P74" s="91"/>
-      <c r="Q74" s="60"/>
-      <c r="R74" s="173"/>
-      <c r="S74" s="173"/>
-      <c r="T74" s="69"/>
-      <c r="U74" s="100"/>
       <c r="V74" s="55"/>
     </row>
-    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="L75" s="49"/>
-      <c r="M75" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="N75" s="164"/>
-      <c r="O75" s="165"/>
-      <c r="P75" s="166"/>
-      <c r="Q75" s="167"/>
-      <c r="R75" s="177"/>
-      <c r="S75" s="177"/>
-      <c r="T75" s="171"/>
-      <c r="U75" s="172"/>
-      <c r="V75" s="55"/>
+      <c r="M75" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLIENTE DOS</t>
+        </is>
+      </c>
+      <c r="O75" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BCI</t>
+        </is>
+      </c>
+      <c r="P75" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F002</t>
+        </is>
+      </c>
+      <c r="T75" s="69">
+        <v>250000</v>
+      </c>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="49"/>
-      <c r="M76" s="163" t="s">
+      <c r="M76" s="89"/>
+      <c r="N76" s="90"/>
+      <c r="O76" s="147"/>
+      <c r="P76" s="91"/>
+      <c r="Q76" s="60"/>
+      <c r="R76" s="173"/>
+      <c r="S76" s="173"/>
+      <c r="T76" s="69"/>
+      <c r="U76" s="100"/>
+      <c r="V76" s="55"/>
+    </row>
+    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L77" s="49"/>
+      <c r="M77" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N77" s="164"/>
+      <c r="O77" s="165"/>
+      <c r="P77" s="166"/>
+      <c r="Q77" s="167"/>
+      <c r="R77" s="177"/>
+      <c r="S77" s="177"/>
+      <c r="T77" s="171"/>
+      <c r="U77" s="172"/>
+      <c r="V77" s="55"/>
+    </row>
+    <row r="78" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L78" s="49"/>
+      <c r="M78" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="N76" s="164"/>
-      <c r="O76" s="165"/>
-      <c r="P76" s="166"/>
-      <c r="Q76" s="167"/>
-      <c r="R76" s="168"/>
-      <c r="S76" s="168"/>
-      <c r="T76" s="171"/>
-      <c r="U76" s="172"/>
-      <c r="V76" s="55"/>
-    </row>
-    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L77" s="49"/>
-      <c r="M77" s="99"/>
-      <c r="N77" s="68"/>
-      <c r="O77" s="147"/>
-      <c r="P77" s="91"/>
-      <c r="Q77" s="60"/>
-      <c r="R77" s="60"/>
-      <c r="S77" s="60"/>
-      <c r="T77" s="69"/>
-      <c r="U77" s="100"/>
-      <c r="V77" s="55"/>
-    </row>
-    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L78" s="49"/>
-      <c r="M78" s="106" t="s">
+      <c r="N78" s="164"/>
+      <c r="O78" s="165"/>
+      <c r="P78" s="166"/>
+      <c r="Q78" s="167"/>
+      <c r="R78" s="168"/>
+      <c r="S78" s="168"/>
+      <c r="T78" s="171"/>
+      <c r="U78" s="172"/>
+      <c r="V78" s="55"/>
+    </row>
+    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L79" s="49"/>
+      <c r="M79" s="99"/>
+      <c r="N79" s="68"/>
+      <c r="O79" s="147"/>
+      <c r="P79" s="91"/>
+      <c r="Q79" s="60"/>
+      <c r="R79" s="60"/>
+      <c r="S79" s="60"/>
+      <c r="T79" s="69"/>
+      <c r="U79" s="100"/>
+      <c r="V79" s="55"/>
+    </row>
+    <row r="80" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L80" s="49"/>
+      <c r="M80" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="N78" s="107">
-        <f>SUM(N76:N77)</f>
-        <v>0</v>
-      </c>
-      <c r="O78" s="101"/>
-      <c r="P78" s="103"/>
-      <c r="Q78" s="102"/>
-      <c r="R78" s="102"/>
-      <c r="S78" s="102"/>
-      <c r="T78" s="104"/>
-      <c r="U78" s="105"/>
-      <c r="V78" s="55"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M79"/>
-      <c r="O79" s="5"/>
-      <c r="Q79"/>
-      <c r="S79"/>
-      <c r="T79" s="6"/>
-      <c r="V79" s="55"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O80"/>
+      <c r="N80" s="107">
+        <f>SUM(N78:N79)</f>
+        <v>0</v>
+      </c>
+      <c r="O80" s="101"/>
+      <c r="P80" s="103"/>
+      <c r="Q80" s="102"/>
+      <c r="R80" s="102"/>
+      <c r="S80" s="102"/>
+      <c r="T80" s="104"/>
+      <c r="U80" s="105"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M81" s="23"/>
-      <c r="N81" s="23"/>
-      <c r="O81" s="23"/>
-      <c r="P81" s="23"/>
-      <c r="Q81" s="23"/>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M81"/>
+      <c r="O81" s="5"/>
+      <c r="Q81"/>
+      <c r="S81"/>
+      <c r="T81" s="6"/>
       <c r="V81" s="55"/>
     </row>
-    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O82"/>
       <c r="V82" s="55"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M83" s="23"/>
+      <c r="N83" s="23"/>
+      <c r="O83" s="23"/>
+      <c r="P83" s="23"/>
+      <c r="Q83" s="23"/>
       <c r="V83" s="55"/>
     </row>
     <row r="84" spans="13:22" x14ac:dyDescent="0.3">
@@ -8894,10 +9023,10 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
-    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V98" s="55"/>
     </row>
     <row r="99" spans="22:22" x14ac:dyDescent="0.3">
@@ -8941,6 +9070,12 @@
     </row>
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
+    </row>
+    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V113" s="55"/>
+    </row>
+    <row r="114" spans="22:22" x14ac:dyDescent="0.3">
+      <c r="V114" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="72">
@@ -8967,7 +9102,7 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:U30"/>
     <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="R35:S35"/>
     <mergeCell ref="T35:U35"/>
     <mergeCell ref="O33:P33"/>
@@ -8980,42 +9115,42 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
     <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
     <mergeCell ref="O32:P32"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="M70:U70"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="P68:Q68"/>
     <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D52:E52"/>
     <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="T78:U78"/>
+    <mergeCell ref="R76:S76"/>
+    <mergeCell ref="R77:S77"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T77:U77"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
     <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -1998,10 +1998,14 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARIOS</t>
+          <t xml:space="preserve">ANA</t>
         </is>
       </c>
-      <c r="C1" s="143"/>
+      <c r="C1" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOB</t>
+        </is>
+      </c>
       <c r="D1" s="143"/>
       <c r="E1" s="127"/>
       <c r="F1" s="143"/>
@@ -2029,10 +2033,14 @@
       </c>
       <c r="B2" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARIOS</t>
+          <t xml:space="preserve">AUX ANA</t>
         </is>
       </c>
-      <c r="C2" s="143"/>
+      <c r="C2" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUX BOB</t>
+        </is>
+      </c>
       <c r="D2" s="143"/>
       <c r="E2" s="127"/>
       <c r="F2" s="143"/>
@@ -2085,8 +2093,16 @@
       <c r="A4" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
+      <c r="B4" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111 · ANA</t>
+        </is>
+      </c>
+      <c r="C4" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222 · BOB</t>
+        </is>
+      </c>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
       <c r="F4" s="143"/>
@@ -2114,10 +2130,14 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">VARIOS</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
-      <c r="C5" s="154"/>
+      <c r="C5" s="154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222</t>
+        </is>
+      </c>
       <c r="D5" s="154"/>
       <c r="E5" s="154"/>
       <c r="F5" s="154"/>
@@ -2143,10 +2163,12 @@
       <c r="A6" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6"/>
+      <c r="B6" s="0">
+        <v>10</v>
+      </c>
+      <c r="C6" s="0">
+        <v>10</v>
+      </c>
       <c r="D6"/>
       <c r="E6"/>
       <c r="F6"/>
@@ -2173,9 +2195,11 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>2000000</v>
-      </c>
-      <c r="C7" s="155"/>
+        <v>1000000</v>
+      </c>
+      <c r="C7" s="155">
+        <v>1000000</v>
+      </c>
       <c r="D7" s="155"/>
       <c r="E7" s="155"/>
       <c r="F7" s="155"/>
@@ -2227,9 +2251,11 @@
         <v>3</v>
       </c>
       <c r="B9" s="227">
-        <v>900000</v>
-      </c>
-      <c r="C9" s="228"/>
+        <v>450000</v>
+      </c>
+      <c r="C9" s="228">
+        <v>450000</v>
+      </c>
       <c r="D9" s="229"/>
       <c r="E9" s="110"/>
       <c r="F9" s="119"/>
@@ -2256,9 +2282,11 @@
         <v>54</v>
       </c>
       <c r="B10" s="227">
-        <v>100000</v>
-      </c>
-      <c r="C10" s="228"/>
+        <v>50000</v>
+      </c>
+      <c r="C10" s="228">
+        <v>50000</v>
+      </c>
       <c r="D10" s="229"/>
       <c r="E10" s="110"/>
       <c r="F10" s="119"/>
@@ -2285,9 +2313,11 @@
         <v>4</v>
       </c>
       <c r="B11" s="227">
-        <v>600000</v>
-      </c>
-      <c r="C11" s="228"/>
+        <v>300000</v>
+      </c>
+      <c r="C11" s="228">
+        <v>300000</v>
+      </c>
       <c r="D11" s="229"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
@@ -2683,7 +2713,11 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTALES CONSOLIDADOS</t>
+        </is>
+      </c>
       <c r="B21" s="9"/>
       <c r="C21" s="10"/>
       <c r="D21" s="9"/>
@@ -2708,6 +2742,9 @@
       <c r="W21" s="9"/>
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="0">
+        <v>20</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="M22" s="214" t="s">
         <v>48</v>
@@ -2722,6 +2759,9 @@
       <c r="U22" s="214"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="0">
+        <v>2000000</v>
+      </c>
       <c r="D23" s="6"/>
       <c r="J23"/>
       <c r="L23"/>
@@ -2749,7 +2789,9 @@
       </c>
     </row>
     <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="2"/>
+      <c r="B24" s="2">
+        <v>900000</v>
+      </c>
       <c r="C24" s="18"/>
       <c r="J24"/>
       <c r="K24" s="15"/>
@@ -2774,7 +2816,9 @@
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
+      <c r="B25" s="2">
+        <v>100000</v>
+      </c>
       <c r="C25" s="111"/>
       <c r="D25" s="3" t="s">
         <v>15</v>
@@ -2803,6 +2847,9 @@
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B26" s="0">
+        <v>600000</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="J26"/>
       <c r="L26"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esteb\Documents\proyecto_cursor\proyectoisaqwenvisor\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703A2F14-26FE-40C5-A4C3-CF31C833DAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A7AFC3-86CF-4750-953C-1C89BFCC1343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
-    <sheet name="RUTA 111" sheetId="2" r:id="rId6"/>
-    <sheet name="RUTA 222" sheetId="3" r:id="rId7"/>
+    <sheet name="RUTA 12345" sheetId="2" r:id="rId6"/>
+    <sheet name="RUTA 67890" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="107">
   <si>
     <t>RECORRIDO</t>
   </si>
@@ -263,18 +263,9 @@
     <t>{{extraction.total_n_c_por_negocios.valor}}</t>
   </si>
   <si>
-    <t>{{extraction.auxiliar.valor}}</t>
-  </si>
-  <si>
-    <t>{{extraction.conductor.valor}}</t>
-  </si>
-  <si>
     <t>{{extraction.cant_fact.valor}}</t>
   </si>
   <si>
-    <t>{{extraction.n_recorrido.valor}}</t>
-  </si>
-  <si>
     <t>{{extraction.valor_total.valor}}</t>
   </si>
   <si>
@@ -336,6 +327,36 @@
   </si>
   <si>
     <t>{{transf_banco}}</t>
+  </si>
+  <si>
+    <t>{{chq_dia_fechas}}</t>
+  </si>
+  <si>
+    <t>{{chq_dia_bancos}}</t>
+  </si>
+  <si>
+    <t>{{chq_dia_valores}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.conductor}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.auxiliar}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.observaciones}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.sector}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.recorrido}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.n_factura}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.total_factura}}</t>
   </si>
 </sst>
 </file>
@@ -1453,6 +1474,151 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1462,172 +1628,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1662,9 +1679,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>371331</xdr:colOff>
+      <xdr:colOff>361806</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>133262</xdr:rowOff>
+      <xdr:rowOff>137072</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1969,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W118"/>
+  <dimension ref="A1:W113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -1998,12 +2015,12 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA</t>
+          <t xml:space="preserve">JUAN PEREZ</t>
         </is>
       </c>
       <c r="C1" s="143" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOB</t>
+          <t xml:space="preserve">MARIA LOPEZ</t>
         </is>
       </c>
       <c r="D1" s="143"/>
@@ -2031,16 +2048,8 @@
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUX ANA</t>
-        </is>
-      </c>
-      <c r="C2" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUX BOB</t>
-        </is>
-      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="143"/>
       <c r="D2" s="143"/>
       <c r="E2" s="127"/>
       <c r="F2" s="143"/>
@@ -2093,16 +2102,8 @@
       <c r="A4" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111 · ANA</t>
-        </is>
-      </c>
-      <c r="C4" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222 · BOB</t>
-        </is>
-      </c>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
       <c r="F4" s="143"/>
@@ -2130,12 +2131,12 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">12345</t>
         </is>
       </c>
       <c r="C5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">67890</t>
         </is>
       </c>
       <c r="D5" s="154"/>
@@ -2190,7 +2191,7 @@
       <c r="V6" s="123"/>
       <c r="W6" s="123"/>
     </row>
-    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" s="49" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="127" t="s">
         <v>2</v>
       </c>
@@ -2223,8 +2224,16 @@
     </row>
     <row r="8" spans="1:23" s="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="127"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="123"/>
+      <c r="B8" s="110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12345 · JUAN PEREZ</t>
+        </is>
+      </c>
+      <c r="C8" s="123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67890 · MARIA LOPEZ</t>
+        </is>
+      </c>
       <c r="D8" s="110"/>
       <c r="E8" s="123"/>
       <c r="F8" s="119"/>
@@ -2250,13 +2259,13 @@
       <c r="A9" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="227">
+      <c r="B9" s="171">
         <v>450000</v>
       </c>
-      <c r="C9" s="228">
+      <c r="C9" s="172">
         <v>450000</v>
       </c>
-      <c r="D9" s="229"/>
+      <c r="D9" s="173"/>
       <c r="E9" s="110"/>
       <c r="F9" s="119"/>
       <c r="G9" s="110"/>
@@ -2281,13 +2290,13 @@
       <c r="A10" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="227">
+      <c r="B10" s="171">
         <v>50000</v>
       </c>
-      <c r="C10" s="228">
+      <c r="C10" s="172">
         <v>50000</v>
       </c>
-      <c r="D10" s="229"/>
+      <c r="D10" s="173"/>
       <c r="E10" s="110"/>
       <c r="F10" s="119"/>
       <c r="G10" s="110"/>
@@ -2312,13 +2321,13 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="227">
+      <c r="B11" s="171">
         <v>300000</v>
       </c>
-      <c r="C11" s="228">
+      <c r="C11" s="172">
         <v>300000</v>
       </c>
-      <c r="D11" s="229"/>
+      <c r="D11" s="173"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
       <c r="G11" s="110"/>
@@ -2343,9 +2352,9 @@
       <c r="A12" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="227"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="229"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="173"/>
       <c r="E12" s="110"/>
       <c r="F12" s="119"/>
       <c r="G12" s="110"/>
@@ -2370,9 +2379,9 @@
       <c r="A13" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="227"/>
-      <c r="C13" s="228"/>
-      <c r="D13" s="229"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="173"/>
       <c r="E13" s="110"/>
       <c r="F13" s="119"/>
       <c r="G13" s="110"/>
@@ -2397,9 +2406,9 @@
       <c r="A14" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="227"/>
-      <c r="C14" s="228"/>
-      <c r="D14" s="229"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="173"/>
       <c r="E14" s="110"/>
       <c r="F14" s="119"/>
       <c r="G14" s="110"/>
@@ -2424,9 +2433,9 @@
       <c r="A15" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="227"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="229"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
       <c r="E15" s="110"/>
       <c r="F15" s="119"/>
       <c r="G15" s="110"/>
@@ -2451,9 +2460,9 @@
       <c r="A16" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="227"/>
-      <c r="C16" s="228"/>
-      <c r="D16" s="229"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="173"/>
       <c r="E16" s="110"/>
       <c r="F16" s="119"/>
       <c r="G16" s="110"/>
@@ -2478,9 +2487,9 @@
       <c r="A17" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="227"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="229"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
       <c r="E17" s="110"/>
       <c r="F17" s="119"/>
       <c r="G17" s="110"/>
@@ -2746,17 +2755,17 @@
         <v>20</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="M22" s="214" t="s">
+      <c r="M22" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="214"/>
-      <c r="O22" s="214"/>
-      <c r="P22" s="214"/>
-      <c r="Q22" s="214"/>
-      <c r="R22" s="214"/>
-      <c r="S22" s="214"/>
-      <c r="T22" s="214"/>
-      <c r="U22" s="214"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="0">
@@ -2768,16 +2777,16 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221" t="inlineStr">
+      <c r="N23" s="188" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/06/2026</t>
+          <t xml:space="preserve">24-06-2026</t>
         </is>
       </c>
-      <c r="O23" s="222"/>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="222"/>
-      <c r="R23" s="222"/>
-      <c r="S23" s="223"/>
+      <c r="O23" s="189"/>
+      <c r="P23" s="189"/>
+      <c r="Q23" s="189"/>
+      <c r="R23" s="189"/>
+      <c r="S23" s="190"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
@@ -2797,14 +2806,14 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="224" t="s">
+      <c r="N24" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="225"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="225"/>
-      <c r="R24" s="225"/>
-      <c r="S24" s="226"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="192"/>
+      <c r="Q24" s="192"/>
+      <c r="R24" s="192"/>
+      <c r="S24" s="193"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
@@ -2826,21 +2835,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="209" t="s">
+      <c r="M25" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="210"/>
-      <c r="O25" s="211"/>
-      <c r="P25" s="212"/>
-      <c r="Q25" s="174">
-        <v>900000</v>
-      </c>
-      <c r="R25" s="175"/>
-      <c r="S25" s="176"/>
-      <c r="T25" s="207" t="s">
+      <c r="N25" s="197"/>
+      <c r="O25" s="228"/>
+      <c r="P25" s="229"/>
+      <c r="Q25" s="171" t="s">
+        <v>94</v>
+      </c>
+      <c r="R25" s="172"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="208"/>
+      <c r="U25" s="195"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -2859,11 +2868,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="174">
-        <v>100000</v>
-      </c>
-      <c r="R26" s="175"/>
-      <c r="S26" s="176"/>
+      <c r="Q26" s="175" t="s">
+        <v>95</v>
+      </c>
+      <c r="R26" s="176"/>
+      <c r="S26" s="177"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -2881,17 +2890,17 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="199"/>
-      <c r="P27" s="200"/>
-      <c r="Q27" s="174">
-        <v>600000</v>
-      </c>
-      <c r="R27" s="175"/>
-      <c r="S27" s="176"/>
-      <c r="T27" s="219" t="s">
+      <c r="O27" s="178"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="175" t="s">
+        <v>64</v>
+      </c>
+      <c r="R27" s="176"/>
+      <c r="S27" s="177"/>
+      <c r="T27" s="186" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="220"/>
+      <c r="U27" s="187"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
         <v>2000000</v>
@@ -2907,19 +2916,21 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="194" t="s">
+      <c r="M28" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="195"/>
-      <c r="O28" s="199"/>
-      <c r="P28" s="200"/>
-      <c r="Q28" s="174"/>
-      <c r="R28" s="175"/>
-      <c r="S28" s="176"/>
-      <c r="T28" s="217" t="s">
+      <c r="N28" s="185"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="175" t="s">
+        <v>65</v>
+      </c>
+      <c r="R28" s="176"/>
+      <c r="S28" s="177"/>
+      <c r="T28" s="182" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="218"/>
+      <c r="U28" s="183"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -2934,19 +2945,21 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="194" t="s">
+      <c r="M29" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="195"/>
-      <c r="O29" s="199"/>
-      <c r="P29" s="200"/>
-      <c r="Q29" s="174"/>
-      <c r="R29" s="175"/>
-      <c r="S29" s="176"/>
-      <c r="T29" s="215" t="s">
+      <c r="N29" s="185"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="179"/>
+      <c r="Q29" s="175" t="s">
+        <v>66</v>
+      </c>
+      <c r="R29" s="176"/>
+      <c r="S29" s="177"/>
+      <c r="T29" s="180" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="216"/>
+      <c r="U29" s="181"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -2962,19 +2975,21 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="194" t="s">
+      <c r="M30" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="195"/>
-      <c r="O30" s="199"/>
-      <c r="P30" s="213"/>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="175"/>
-      <c r="S30" s="176"/>
-      <c r="T30" s="201" t="s">
+      <c r="N30" s="185"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="198"/>
+      <c r="Q30" s="175" t="s">
+        <v>67</v>
+      </c>
+      <c r="R30" s="176"/>
+      <c r="S30" s="177"/>
+      <c r="T30" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="202"/>
+      <c r="U30" s="200"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -2991,15 +3006,17 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="194" t="s">
+      <c r="M31" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="195"/>
-      <c r="O31" s="199"/>
-      <c r="P31" s="200"/>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="176"/>
+      <c r="N31" s="185"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="175" t="s">
+        <v>68</v>
+      </c>
+      <c r="R31" s="176"/>
+      <c r="S31" s="177"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -3014,15 +3031,17 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="194" t="s">
+      <c r="M32" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="195"/>
-      <c r="O32" s="199"/>
-      <c r="P32" s="200"/>
-      <c r="Q32" s="174"/>
-      <c r="R32" s="175"/>
-      <c r="S32" s="176"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="175" t="s">
+        <v>69</v>
+      </c>
+      <c r="R32" s="176"/>
+      <c r="S32" s="177"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -3044,11 +3063,13 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="199"/>
-      <c r="P33" s="200"/>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="176"/>
+      <c r="O33" s="178"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="175" t="s">
+        <v>70</v>
+      </c>
+      <c r="R33" s="176"/>
+      <c r="S33" s="177"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -3067,17 +3088,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="203" t="s">
+      <c r="M34" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="204"/>
-      <c r="O34" s="205"/>
-      <c r="P34" s="206"/>
-      <c r="Q34" s="174">
+      <c r="N34" s="205"/>
+      <c r="O34" s="206"/>
+      <c r="P34" s="207"/>
+      <c r="Q34" s="175">
         <v>2000000</v>
       </c>
-      <c r="R34" s="175"/>
-      <c r="S34" s="176"/>
+      <c r="R34" s="176"/>
+      <c r="S34" s="177"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -3095,23 +3116,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="196" t="s">
+      <c r="M35" s="217" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="189" t="s">
+      <c r="N35" s="218"/>
+      <c r="O35" s="219"/>
+      <c r="P35" s="202" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="193"/>
-      <c r="R35" s="189" t="s">
+      <c r="Q35" s="203"/>
+      <c r="R35" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="193"/>
-      <c r="T35" s="189" t="s">
+      <c r="S35" s="203"/>
+      <c r="T35" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="193"/>
+      <c r="U35" s="203"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -3167,23 +3188,13 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O44)</f>
+        <f>SUM(O42)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01/01/2026</t>
-        </is>
-      </c>
-      <c r="N37" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O37" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -3195,31 +3206,43 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M38" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02/01/2026</t>
-        </is>
-      </c>
-      <c r="N38" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="O38" s="39">
-        <v>200000</v>
-      </c>
+    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="32"/>
+      <c r="I38" s="134"/>
+      <c r="J38"/>
+      <c r="L38" s="114">
+        <v>2</v>
+      </c>
+      <c r="M38" s="208" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="226"/>
+      <c r="O38" s="227"/>
       <c r="P38" s="42"/>
-      <c r="Q38" s="72"/>
+      <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
       <c r="S38" s="77"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="72"/>
+      <c r="U38" s="80"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B39" s="20"/>
+      <c r="C39" s="32"/>
+      <c r="I39" s="134"/>
+      <c r="J39"/>
+      <c r="K39" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L39" s="114">
+        <v>3</v>
+      </c>
       <c r="M39" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">01/01/2026</t>
+          <t xml:space="preserve">01-01-2026</t>
         </is>
       </c>
       <c r="N39" s="38" t="inlineStr">
@@ -3236,86 +3259,80 @@
       <c r="S39" s="77"/>
       <c r="T39" s="42"/>
       <c r="U39" s="72"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="M40" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">02/01/2026</t>
+          <t xml:space="preserve">01-01-2026</t>
         </is>
       </c>
       <c r="N40" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">BCI</t>
+          <t xml:space="preserve">SANTANDER</t>
         </is>
       </c>
       <c r="O40" s="39">
-        <v>200000</v>
-      </c>
-      <c r="P40" s="42"/>
-      <c r="Q40" s="72"/>
-      <c r="R40" s="44"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="42"/>
-      <c r="U40" s="72"/>
-    </row>
-    <row r="41" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="47"/>
       <c r="I41" s="134"/>
       <c r="J41"/>
+      <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>2</v>
-      </c>
-      <c r="M41" s="179" t="s">
-        <v>42</v>
-      </c>
-      <c r="N41" s="180"/>
-      <c r="O41" s="46">
-        <v>600000</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="M41" s="37"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="39"/>
       <c r="P41" s="42"/>
-      <c r="Q41" s="79"/>
+      <c r="Q41" s="70"/>
       <c r="R41" s="44"/>
-      <c r="S41" s="77"/>
+      <c r="S41" s="78"/>
       <c r="T41" s="42"/>
-      <c r="U41" s="80"/>
+      <c r="U41" s="72"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="20"/>
       <c r="C42" s="32"/>
-      <c r="I42" s="134"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="I42" s="133"/>
       <c r="J42"/>
-      <c r="K42" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K42" s="24"/>
       <c r="L42" s="114">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
       <c r="O42" s="39"/>
       <c r="P42" s="42"/>
-      <c r="Q42" s="72"/>
+      <c r="Q42" s="70"/>
       <c r="R42" s="44"/>
-      <c r="S42" s="77"/>
+      <c r="S42" s="78"/>
       <c r="T42" s="42"/>
       <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B43" s="20"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="47"/>
-      <c r="I43" s="134"/>
-      <c r="J43"/>
-      <c r="K43" s="24"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="51"/>
+      <c r="I43" s="135"/>
+      <c r="J43" s="57"/>
       <c r="L43" s="114">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
@@ -3323,74 +3340,75 @@
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
       <c r="R43" s="44"/>
-      <c r="S43" s="78"/>
+      <c r="S43" s="77"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
     </row>
-    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A44" s="112"/>
       <c r="B44" s="20"/>
       <c r="C44" s="32"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="I44" s="133"/>
-      <c r="J44"/>
-      <c r="K44" s="24"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="8"/>
+      <c r="I44" s="136"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="24" t="e">
+        <f>O38+O66</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L44" s="114">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
       <c r="O44" s="39"/>
       <c r="P44" s="42"/>
       <c r="Q44" s="70"/>
-      <c r="R44" s="44"/>
-      <c r="S44" s="78"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="71"/>
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-    </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="25"/>
       <c r="B45" s="20"/>
       <c r="C45" s="25"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="51"/>
-      <c r="I45" s="135"/>
+      <c r="D45" s="201"/>
+      <c r="E45" s="201"/>
+      <c r="F45" s="52"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="13"/>
       <c r="J45" s="57"/>
+      <c r="K45" s="24"/>
       <c r="L45" s="114">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
       <c r="O45" s="39"/>
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="77"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="71"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-    </row>
-    <row r="46" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="112"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="183"/>
-      <c r="E46" s="183"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="8"/>
-      <c r="I46" s="136"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="201"/>
+      <c r="E46" s="201"/>
+      <c r="F46" s="23"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="13"/>
       <c r="J46" s="57"/>
-      <c r="K46" s="24" t="e">
-        <f>O41+O68</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L46" s="114">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -3398,23 +3416,22 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="70"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="71"/>
+      <c r="S46" s="76"/>
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
-    <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="25"/>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="20"/>
       <c r="B47" s="20"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="183"/>
-      <c r="F47" s="52"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="201"/>
+      <c r="E47" s="201"/>
+      <c r="F47" s="53"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
-      <c r="K47" s="24"/>
       <c r="L47" s="114">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -3427,17 +3444,22 @@
       <c r="U47" s="72"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="183"/>
-      <c r="E48" s="183"/>
-      <c r="F48" s="23"/>
+      <c r="D48" s="201"/>
+      <c r="E48" s="201"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
+      <c r="K48" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L48" s="114">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -3445,7 +3467,7 @@
       <c r="P48" s="42"/>
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
-      <c r="S48" s="76"/>
+      <c r="S48" s="71"/>
       <c r="T48" s="42"/>
       <c r="U48" s="72"/>
     </row>
@@ -3453,14 +3475,15 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="183"/>
-      <c r="E49" s="183"/>
-      <c r="F49" s="53"/>
+      <c r="D49" s="201"/>
+      <c r="E49" s="201"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="1"/>
       <c r="H49" s="68"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -3469,26 +3492,22 @@
       <c r="Q49" s="70"/>
       <c r="R49" s="42"/>
       <c r="S49" s="71"/>
-      <c r="T49" s="42"/>
+      <c r="T49" s="44"/>
       <c r="U49" s="72"/>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="183"/>
-      <c r="E50" s="183"/>
-      <c r="F50" s="17"/>
+      <c r="D50" s="201"/>
+      <c r="E50" s="201"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="68"/>
+      <c r="H50" s="50"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
-      <c r="K50" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L50" s="114">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -3497,22 +3516,22 @@
       <c r="Q50" s="70"/>
       <c r="R50" s="42"/>
       <c r="S50" s="71"/>
-      <c r="T50" s="42"/>
+      <c r="T50" s="44"/>
       <c r="U50" s="72"/>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="183"/>
-      <c r="E51" s="183"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="25"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="68"/>
+      <c r="H51" s="50"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
@@ -3528,20 +3547,20 @@
       <c r="A52" s="20"/>
       <c r="B52" s="20"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="183"/>
-      <c r="E52" s="183"/>
+      <c r="D52" s="213"/>
+      <c r="E52" s="213"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
       <c r="I52" s="13"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
       <c r="O52" s="39"/>
-      <c r="P52" s="42"/>
+      <c r="P52" s="40"/>
       <c r="Q52" s="70"/>
       <c r="R52" s="42"/>
       <c r="S52" s="71"/>
@@ -3550,22 +3569,22 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
+      <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="25"/>
+      <c r="D53" s="225"/>
+      <c r="E53" s="225"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
-      <c r="I53" s="13"/>
+      <c r="I53" s="54"/>
       <c r="J53" s="57"/>
       <c r="L53" s="114">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="42"/>
+      <c r="P53" s="40"/>
       <c r="Q53" s="70"/>
       <c r="R53" s="42"/>
       <c r="S53" s="71"/>
@@ -3573,23 +3592,21 @@
       <c r="U53" s="72"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
+      <c r="A54" s="25"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
+      <c r="D54" s="212"/>
+      <c r="E54" s="212"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
-      <c r="I54" s="13"/>
+      <c r="I54" s="54"/>
       <c r="J54" s="57"/>
-      <c r="L54" s="114">
-        <v>15</v>
-      </c>
+      <c r="L54" s="18"/>
       <c r="M54" s="37"/>
       <c r="N54" s="38"/>
       <c r="O54" s="39"/>
-      <c r="P54" s="40"/>
+      <c r="P54" s="42"/>
       <c r="Q54" s="70"/>
       <c r="R54" s="42"/>
       <c r="S54" s="71"/>
@@ -3600,20 +3617,18 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="182"/>
-      <c r="E55" s="182"/>
+      <c r="D55" s="212"/>
+      <c r="E55" s="212"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
       <c r="I55" s="54"/>
       <c r="J55" s="57"/>
-      <c r="L55" s="114">
-        <v>16</v>
-      </c>
+      <c r="L55" s="18"/>
       <c r="M55" s="37"/>
       <c r="N55" s="38"/>
       <c r="O55" s="39"/>
-      <c r="P55" s="40"/>
+      <c r="P55" s="42"/>
       <c r="Q55" s="70"/>
       <c r="R55" s="42"/>
       <c r="S55" s="71"/>
@@ -3621,11 +3636,11 @@
       <c r="U55" s="72"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A56" s="25"/>
+      <c r="A56" s="20"/>
       <c r="B56" s="55"/>
       <c r="C56" s="43"/>
-      <c r="D56" s="181"/>
-      <c r="E56" s="181"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="23"/>
       <c r="G56" s="1"/>
       <c r="H56" s="50"/>
@@ -3644,10 +3659,10 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="20"/>
-      <c r="B57" s="55"/>
+      <c r="B57"/>
       <c r="C57" s="43"/>
-      <c r="D57" s="181"/>
-      <c r="E57" s="181"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="23"/>
       <c r="G57" s="1"/>
       <c r="H57" s="50"/>
@@ -3666,7 +3681,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="20"/>
-      <c r="B58" s="55"/>
+      <c r="B58"/>
       <c r="C58" s="43"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
@@ -3731,11 +3746,11 @@
       <c r="U60" s="72"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A61" s="20"/>
+      <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
+      <c r="D61" s="212"/>
+      <c r="E61" s="212"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="50"/>
@@ -3753,7 +3768,7 @@
       <c r="U61" s="72"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A62" s="20"/>
+      <c r="A62" s="25"/>
       <c r="B62"/>
       <c r="C62" s="43"/>
       <c r="D62" s="22"/>
@@ -3768,9 +3783,9 @@
       <c r="N62" s="38"/>
       <c r="O62" s="39"/>
       <c r="P62" s="42"/>
-      <c r="Q62" s="70"/>
-      <c r="R62" s="42"/>
-      <c r="S62" s="71"/>
+      <c r="Q62" s="161"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="92"/>
       <c r="T62" s="44"/>
       <c r="U62" s="72"/>
     </row>
@@ -3778,8 +3793,8 @@
       <c r="A63" s="25"/>
       <c r="B63"/>
       <c r="C63" s="43"/>
-      <c r="D63" s="181"/>
-      <c r="E63" s="181"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
       <c r="F63" s="23"/>
       <c r="G63" s="1"/>
       <c r="H63" s="50"/>
@@ -3790,9 +3805,9 @@
       <c r="N63" s="38"/>
       <c r="O63" s="39"/>
       <c r="P63" s="42"/>
-      <c r="Q63" s="70"/>
-      <c r="R63" s="42"/>
-      <c r="S63" s="71"/>
+      <c r="Q63" s="161"/>
+      <c r="R63" s="93"/>
+      <c r="S63" s="92"/>
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
@@ -3818,12 +3833,12 @@
       <c r="T64" s="44"/>
       <c r="U64" s="72"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
+      <c r="D65" s="212"/>
+      <c r="E65" s="212"/>
       <c r="F65" s="23"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
@@ -3834,463 +3849,387 @@
       <c r="N65" s="38"/>
       <c r="O65" s="39"/>
       <c r="P65" s="42"/>
-      <c r="Q65" s="161"/>
+      <c r="Q65" s="88"/>
       <c r="R65" s="93"/>
       <c r="S65" s="92"/>
       <c r="T65" s="44"/>
-      <c r="U65" s="72"/>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="U65" s="75"/>
+    </row>
+    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="43"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="23"/>
+      <c r="D66" s="212"/>
+      <c r="E66" s="212"/>
+      <c r="F66" s="20"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
       <c r="J66" s="57"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="37"/>
-      <c r="N66" s="38"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="42"/>
-      <c r="Q66" s="161"/>
-      <c r="R66" s="93"/>
-      <c r="S66" s="92"/>
-      <c r="T66" s="44"/>
-      <c r="U66" s="72"/>
-    </row>
-    <row r="67" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L66"/>
+      <c r="M66" s="208" t="s">
+        <v>34</v>
+      </c>
+      <c r="N66" s="209"/>
+      <c r="O66" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="P66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q66" s="46"/>
+      <c r="R66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S66" s="46"/>
+      <c r="T66" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U66" s="46"/>
+    </row>
+    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="43"/>
-      <c r="D67" s="181"/>
-      <c r="E67" s="181"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="212"/>
+      <c r="E67" s="212"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
-      <c r="J67" s="57"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="37"/>
-      <c r="N67" s="38"/>
-      <c r="O67" s="39"/>
-      <c r="P67" s="42"/>
-      <c r="Q67" s="88"/>
-      <c r="R67" s="93"/>
-      <c r="S67" s="92"/>
-      <c r="T67" s="44"/>
-      <c r="U67" s="75"/>
-    </row>
-    <row r="68" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J67"/>
+      <c r="L67"/>
+      <c r="M67" s="58"/>
+      <c r="N67" s="59"/>
+      <c r="O67" s="74"/>
+      <c r="P67" s="23"/>
+      <c r="Q67" s="73"/>
+      <c r="R67" s="74"/>
+      <c r="S67" s="74"/>
+      <c r="T67" s="6"/>
+    </row>
+    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="181"/>
-      <c r="E68" s="181"/>
-      <c r="F68" s="20"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="23"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
-      <c r="J68" s="57"/>
+      <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="N68" s="180"/>
-      <c r="O68" s="46"/>
-      <c r="P68" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q68" s="46"/>
-      <c r="R68" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S68" s="46"/>
-      <c r="T68" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U68" s="46"/>
-    </row>
-    <row r="69" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M68" s="202" t="s">
+        <v>47</v>
+      </c>
+      <c r="N68" s="216"/>
+      <c r="O68" s="203"/>
+      <c r="P68" s="214"/>
+      <c r="Q68" s="215"/>
+      <c r="R68" s="202" t="s">
+        <v>37</v>
+      </c>
+      <c r="S68" s="216"/>
+      <c r="T68" s="210" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U68" s="211"/>
+    </row>
+    <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
       <c r="B69"/>
-      <c r="C69" s="95"/>
-      <c r="D69" s="181"/>
-      <c r="E69" s="181"/>
-      <c r="F69" s="23"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="212"/>
+      <c r="E69" s="212"/>
+      <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="58"/>
-      <c r="N69" s="59"/>
-      <c r="O69" s="74"/>
-      <c r="P69" s="23"/>
-      <c r="Q69" s="73"/>
-      <c r="R69" s="74"/>
-      <c r="S69" s="74"/>
-      <c r="T69" s="6"/>
-    </row>
-    <row r="70" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="60"/>
+      <c r="N69" s="87"/>
+      <c r="O69" s="87"/>
+      <c r="P69" s="61"/>
+      <c r="Q69" s="62"/>
+      <c r="R69" s="62"/>
+      <c r="S69" s="62"/>
+      <c r="T69" s="60"/>
+      <c r="U69" s="60"/>
+    </row>
+    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70"/>
+      <c r="B70" s="95"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="23"/>
+      <c r="D70" s="212"/>
+      <c r="E70" s="212"/>
+      <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
       <c r="L70"/>
-      <c r="M70" s="189" t="s">
-        <v>47</v>
-      </c>
-      <c r="N70" s="190"/>
-      <c r="O70" s="193"/>
-      <c r="P70" s="191"/>
-      <c r="Q70" s="192"/>
-      <c r="R70" s="189" t="s">
-        <v>37</v>
-      </c>
-      <c r="S70" s="190"/>
-      <c r="T70" s="185" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U70" s="186"/>
-    </row>
-    <row r="71" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M70" s="208" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" s="226"/>
+      <c r="O70" s="226"/>
+      <c r="P70" s="226"/>
+      <c r="Q70" s="226"/>
+      <c r="R70" s="226"/>
+      <c r="S70" s="226"/>
+      <c r="T70" s="226"/>
+      <c r="U70" s="227"/>
+      <c r="V70" s="55"/>
+    </row>
+    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="25"/>
-      <c r="B71"/>
+      <c r="B71" s="20"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="181"/>
-      <c r="E71" s="181"/>
+      <c r="D71" s="212"/>
+      <c r="E71" s="212"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
       <c r="J71"/>
-      <c r="L71"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="87"/>
-      <c r="O71" s="87"/>
-      <c r="P71" s="61"/>
-      <c r="Q71" s="62"/>
-      <c r="R71" s="62"/>
-      <c r="S71" s="62"/>
-      <c r="T71" s="60"/>
-      <c r="U71" s="60"/>
-    </row>
-    <row r="72" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L71" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M71" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="157"/>
+      <c r="O71" s="157"/>
+      <c r="P71" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q71" s="157"/>
+      <c r="R71" s="157"/>
+      <c r="S71" s="157"/>
+      <c r="T71" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U71" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V71" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W71" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="25"/>
-      <c r="B72" s="95"/>
+      <c r="B72" s="130"/>
       <c r="C72" s="25"/>
-      <c r="D72" s="181"/>
-      <c r="E72" s="181"/>
+      <c r="D72" s="212"/>
+      <c r="E72" s="212"/>
       <c r="F72" s="67"/>
       <c r="G72" s="1"/>
       <c r="H72" s="50"/>
       <c r="I72" s="54"/>
-      <c r="J72"/>
+      <c r="J72" s="23"/>
       <c r="L72"/>
-      <c r="M72" s="179" t="s">
-        <v>35</v>
-      </c>
-      <c r="N72" s="187"/>
-      <c r="O72" s="187"/>
-      <c r="P72" s="187"/>
-      <c r="Q72" s="187"/>
-      <c r="R72" s="187"/>
-      <c r="S72" s="187"/>
-      <c r="T72" s="187"/>
-      <c r="U72" s="188"/>
+      <c r="M72" s="63"/>
+      <c r="N72" s="64"/>
+      <c r="O72" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P72" s="66"/>
+      <c r="Q72" s="65"/>
+      <c r="R72" s="224" t="s">
+        <v>6</v>
+      </c>
+      <c r="S72" s="224"/>
+      <c r="T72" s="159"/>
+      <c r="U72" s="160"/>
       <c r="V72" s="55"/>
     </row>
-    <row r="73" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="25"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="181"/>
-      <c r="E73" s="181"/>
+    <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B73" s="55"/>
+      <c r="C73" s="94"/>
+      <c r="D73" s="212"/>
+      <c r="E73" s="212"/>
       <c r="F73" s="67"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="50"/>
-      <c r="I73" s="54"/>
-      <c r="J73"/>
-      <c r="L73" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M73" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N73" s="157"/>
-      <c r="O73" s="157"/>
-      <c r="P73" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q73" s="157"/>
-      <c r="R73" s="157"/>
-      <c r="S73" s="157"/>
-      <c r="T73" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U73" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V73" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W73" s="170" t="s">
-        <v>50</v>
-      </c>
+      <c r="I73" s="130"/>
+      <c r="L73"/>
+      <c r="M73" s="89"/>
+      <c r="N73" s="90"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="91"/>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="222"/>
+      <c r="S73" s="222"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
+      <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="25"/>
-      <c r="B74" s="130"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="181"/>
-      <c r="E74" s="181"/>
+      <c r="A74" s="53"/>
+      <c r="B74" s="94"/>
+      <c r="C74" s="94"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="25"/>
       <c r="F74" s="67"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="50"/>
-      <c r="I74" s="54"/>
-      <c r="J74" s="23"/>
-      <c r="L74"/>
-      <c r="M74" s="63"/>
-      <c r="N74" s="64"/>
-      <c r="O74" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P74" s="66"/>
-      <c r="Q74" s="65"/>
-      <c r="R74" s="178" t="s">
-        <v>6</v>
-      </c>
-      <c r="S74" s="178"/>
-      <c r="T74" s="159"/>
-      <c r="U74" s="160"/>
-      <c r="V74" s="55"/>
-    </row>
-    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B75" s="55"/>
-      <c r="C75" s="94"/>
-      <c r="D75" s="181"/>
-      <c r="E75" s="181"/>
-      <c r="F75" s="67"/>
-      <c r="I75" s="130"/>
-      <c r="L75"/>
-      <c r="M75" s="89"/>
-      <c r="N75" s="90"/>
-      <c r="O75" s="18"/>
-      <c r="P75" s="91"/>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="173"/>
-      <c r="S75" s="173"/>
-      <c r="T75" s="69"/>
-      <c r="U75" s="100"/>
-      <c r="V75" s="55"/>
-    </row>
-    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="53"/>
-      <c r="B76" s="94"/>
-      <c r="C76" s="94"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="67"/>
-      <c r="I76" s="130"/>
-      <c r="L76" s="49" t="inlineStr">
+      <c r="I74" s="130"/>
+      <c r="L74" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">12345</t>
         </is>
       </c>
-      <c r="M76" s="89" t="inlineStr">
+      <c r="M74" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="N76" s="90"/>
-      <c r="O76" s="18" t="s">
+      <c r="N74" s="90"/>
+      <c r="O74" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P76" s="91" t="inlineStr">
+      <c r="P74" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
-      <c r="Q76" s="60"/>
-      <c r="R76" s="173" t="s">
+      <c r="Q74" s="60"/>
+      <c r="R74" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="S76" s="173"/>
-      <c r="T76" s="69">
+      <c r="S74" s="222"/>
+      <c r="T74" s="69">
         <v>150000</v>
       </c>
-      <c r="U76" s="100" t="inlineStr">
+      <c r="U74" s="100" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTANDER</t>
+          <t xml:space="preserve">Banco Santander</t>
         </is>
       </c>
-      <c r="V76" s="55"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="L77" s="49"/>
-      <c r="M77" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE DOS</t>
-        </is>
-      </c>
-      <c r="O77" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="P77" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F002</t>
-        </is>
-      </c>
-      <c r="T77" s="69">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="L78" s="49"/>
-      <c r="M78" s="89" t="inlineStr">
+      <c r="V74" s="55"/>
+    </row>
+    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L75" s="49"/>
+      <c r="M75" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="O78" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="P78" s="91" t="inlineStr">
+      <c r="N75" s="90"/>
+      <c r="O75" s="147"/>
+      <c r="P75" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
-      <c r="T78" s="69">
+      <c r="Q75" s="60"/>
+      <c r="R75" s="222"/>
+      <c r="S75" s="222"/>
+      <c r="T75" s="69">
         <v>150000</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="U75" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banco Santander</t>
+        </is>
+      </c>
+      <c r="V75" s="55"/>
+    </row>
+    <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L76" s="49"/>
+      <c r="M76" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N76" s="164"/>
+      <c r="O76" s="165"/>
+      <c r="P76" s="166"/>
+      <c r="Q76" s="167"/>
+      <c r="R76" s="223"/>
+      <c r="S76" s="223"/>
+      <c r="T76" s="220"/>
+      <c r="U76" s="221"/>
+      <c r="V76" s="55"/>
+    </row>
+    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L77" s="49"/>
+      <c r="M77" s="163" t="s">
+        <v>62</v>
+      </c>
+      <c r="N77" s="164"/>
+      <c r="O77" s="165"/>
+      <c r="P77" s="166"/>
+      <c r="Q77" s="167"/>
+      <c r="R77" s="168"/>
+      <c r="S77" s="168"/>
+      <c r="T77" s="220"/>
+      <c r="U77" s="221"/>
+      <c r="V77" s="55"/>
+    </row>
+    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L78" s="49"/>
+      <c r="M78" s="99"/>
+      <c r="N78" s="68"/>
+      <c r="O78" s="147"/>
+      <c r="P78" s="91"/>
+      <c r="Q78" s="60"/>
+      <c r="R78" s="60"/>
+      <c r="S78" s="60"/>
+      <c r="T78" s="69"/>
+      <c r="U78" s="100"/>
+      <c r="V78" s="55"/>
+    </row>
+    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L79" s="49"/>
-      <c r="M79" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE DOS</t>
-        </is>
-      </c>
-      <c r="O79" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="P79" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F002</t>
-        </is>
-      </c>
-      <c r="T79" s="69">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L80" s="49"/>
-      <c r="M80" s="89"/>
-      <c r="N80" s="90"/>
-      <c r="O80" s="147"/>
-      <c r="P80" s="91"/>
-      <c r="Q80" s="60"/>
-      <c r="R80" s="173"/>
-      <c r="S80" s="173"/>
-      <c r="T80" s="69"/>
-      <c r="U80" s="100"/>
+      <c r="M79" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N79" s="107">
+        <f>SUM(N77:N78)</f>
+        <v>0</v>
+      </c>
+      <c r="O79" s="101"/>
+      <c r="P79" s="103"/>
+      <c r="Q79" s="102"/>
+      <c r="R79" s="102"/>
+      <c r="S79" s="102"/>
+      <c r="T79" s="104"/>
+      <c r="U79" s="105"/>
+      <c r="V79" s="55"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M80"/>
+      <c r="O80" s="5"/>
+      <c r="Q80"/>
+      <c r="S80"/>
+      <c r="T80" s="6"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L81" s="49"/>
-      <c r="M81" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="N81" s="164"/>
-      <c r="O81" s="165"/>
-      <c r="P81" s="166"/>
-      <c r="Q81" s="167"/>
-      <c r="R81" s="177"/>
-      <c r="S81" s="177"/>
-      <c r="T81" s="171"/>
-      <c r="U81" s="172"/>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O81"/>
       <c r="V81" s="55"/>
     </row>
-    <row r="82" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L82" s="49"/>
-      <c r="M82" s="163" t="s">
-        <v>62</v>
-      </c>
-      <c r="N82" s="164"/>
-      <c r="O82" s="165"/>
-      <c r="P82" s="166"/>
-      <c r="Q82" s="167"/>
-      <c r="R82" s="168"/>
-      <c r="S82" s="168"/>
-      <c r="T82" s="171"/>
-      <c r="U82" s="172"/>
+    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M82" s="23"/>
+      <c r="N82" s="23"/>
+      <c r="O82" s="23"/>
+      <c r="P82" s="23"/>
+      <c r="Q82" s="23"/>
       <c r="V82" s="55"/>
     </row>
-    <row r="83" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L83" s="49"/>
-      <c r="M83" s="99"/>
-      <c r="N83" s="68"/>
-      <c r="O83" s="147"/>
-      <c r="P83" s="91"/>
-      <c r="Q83" s="60"/>
-      <c r="R83" s="60"/>
-      <c r="S83" s="60"/>
-      <c r="T83" s="69"/>
-      <c r="U83" s="100"/>
+    <row r="83" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V83" s="55"/>
     </row>
-    <row r="84" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L84" s="49"/>
-      <c r="M84" s="106" t="s">
-        <v>11</v>
-      </c>
-      <c r="N84" s="107">
-        <f>SUM(N82:N83)</f>
-        <v>0</v>
-      </c>
-      <c r="O84" s="101"/>
-      <c r="P84" s="103"/>
-      <c r="Q84" s="102"/>
-      <c r="R84" s="102"/>
-      <c r="S84" s="102"/>
-      <c r="T84" s="104"/>
-      <c r="U84" s="105"/>
+    <row r="84" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V84" s="55"/>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M85"/>
-      <c r="O85" s="5"/>
-      <c r="Q85"/>
-      <c r="S85"/>
-      <c r="T85" s="6"/>
+    <row r="85" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V85" s="55"/>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O86"/>
+    <row r="86" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V86" s="55"/>
     </row>
     <row r="87" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M87" s="23"/>
-      <c r="N87" s="23"/>
-      <c r="O87" s="23"/>
-      <c r="P87" s="23"/>
-      <c r="Q87" s="23"/>
       <c r="V87" s="55"/>
     </row>
     <row r="88" spans="13:22" x14ac:dyDescent="0.3">
@@ -4323,19 +4262,19 @@
     <row r="97" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
-    <row r="98" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V98" s="55"/>
     </row>
-    <row r="99" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V99" s="55"/>
     </row>
-    <row r="100" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V100" s="55"/>
     </row>
-    <row r="101" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V101" s="55"/>
     </row>
-    <row r="102" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V102" s="55"/>
     </row>
     <row r="103" spans="22:22" x14ac:dyDescent="0.3">
@@ -4371,23 +4310,62 @@
     <row r="113" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V113" s="55"/>
     </row>
-    <row r="114" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V114" s="55"/>
-    </row>
-    <row r="115" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V115" s="55"/>
-    </row>
-    <row r="116" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V116" s="55"/>
-    </row>
-    <row r="117" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V117" s="55"/>
-    </row>
-    <row r="118" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V118" s="55"/>
-    </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="70">
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="M70:U70"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="T77:U77"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R76:S76"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="O29:P29"/>
@@ -4404,62 +4382,6 @@
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
     <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="M72:U72"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="M70:O70"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="T82:U82"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="T81:U81"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D55:E55"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -4469,7 +4391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W114"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -4498,7 +4420,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA</t>
+          <t xml:space="preserve">JUAN PEREZ</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -4527,10 +4449,8 @@
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUX ANA</t>
-        </is>
+      <c r="B2" s="127" t="s">
+        <v>101</v>
       </c>
       <c r="C2" s="143"/>
       <c r="D2" s="143"/>
@@ -4558,7 +4478,9 @@
       <c r="A3" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="143"/>
+      <c r="B3" s="143" t="s">
+        <v>102</v>
+      </c>
       <c r="C3" s="143"/>
       <c r="D3" s="143"/>
       <c r="E3" s="143"/>
@@ -4585,7 +4507,9 @@
       <c r="A4" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="143"/>
+      <c r="B4" s="143" t="s">
+        <v>103</v>
+      </c>
       <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
@@ -4614,7 +4538,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">12345</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -4668,7 +4592,7 @@
       <c r="V6" s="123"/>
       <c r="W6" s="123"/>
     </row>
-    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" s="49" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="127" t="s">
         <v>2</v>
       </c>
@@ -4726,11 +4650,11 @@
       <c r="A9" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="227">
+      <c r="B9" s="171">
         <v>450000</v>
       </c>
-      <c r="C9" s="228"/>
-      <c r="D9" s="229"/>
+      <c r="C9" s="172"/>
+      <c r="D9" s="173"/>
       <c r="E9" s="110"/>
       <c r="F9" s="119"/>
       <c r="G9" s="110"/>
@@ -4755,11 +4679,11 @@
       <c r="A10" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="227">
+      <c r="B10" s="171">
         <v>50000</v>
       </c>
-      <c r="C10" s="228"/>
-      <c r="D10" s="229"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="173"/>
       <c r="E10" s="110"/>
       <c r="F10" s="119"/>
       <c r="G10" s="110"/>
@@ -4784,11 +4708,11 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="227">
+      <c r="B11" s="171">
         <v>300000</v>
       </c>
-      <c r="C11" s="228"/>
-      <c r="D11" s="229"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="173"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
       <c r="G11" s="110"/>
@@ -4813,9 +4737,9 @@
       <c r="A12" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="227"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="229"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="173"/>
       <c r="E12" s="110"/>
       <c r="F12" s="119"/>
       <c r="G12" s="110"/>
@@ -4840,9 +4764,9 @@
       <c r="A13" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="227"/>
-      <c r="C13" s="228"/>
-      <c r="D13" s="229"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="173"/>
       <c r="E13" s="110"/>
       <c r="F13" s="119"/>
       <c r="G13" s="110"/>
@@ -4867,9 +4791,9 @@
       <c r="A14" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="227"/>
-      <c r="C14" s="228"/>
-      <c r="D14" s="229"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="173"/>
       <c r="E14" s="110"/>
       <c r="F14" s="119"/>
       <c r="G14" s="110"/>
@@ -4894,9 +4818,9 @@
       <c r="A15" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="227"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="229"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
       <c r="E15" s="110"/>
       <c r="F15" s="119"/>
       <c r="G15" s="110"/>
@@ -4921,9 +4845,9 @@
       <c r="A16" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="227"/>
-      <c r="C16" s="228"/>
-      <c r="D16" s="229"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="173"/>
       <c r="E16" s="110"/>
       <c r="F16" s="119"/>
       <c r="G16" s="110"/>
@@ -4948,9 +4872,9 @@
       <c r="A17" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="227"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="229"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
       <c r="E17" s="110"/>
       <c r="F17" s="119"/>
       <c r="G17" s="110"/>
@@ -5209,17 +5133,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="214" t="s">
+      <c r="M22" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="214"/>
-      <c r="O22" s="214"/>
-      <c r="P22" s="214"/>
-      <c r="Q22" s="214"/>
-      <c r="R22" s="214"/>
-      <c r="S22" s="214"/>
-      <c r="T22" s="214"/>
-      <c r="U22" s="214"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -5228,16 +5152,16 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221" t="inlineStr">
+      <c r="N23" s="188" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/06/2026</t>
+          <t xml:space="preserve">24-06-2026</t>
         </is>
       </c>
-      <c r="O23" s="222"/>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="222"/>
-      <c r="R23" s="222"/>
-      <c r="S23" s="223"/>
+      <c r="O23" s="189"/>
+      <c r="P23" s="189"/>
+      <c r="Q23" s="189"/>
+      <c r="R23" s="189"/>
+      <c r="S23" s="190"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
@@ -5255,14 +5179,14 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="224" t="s">
+      <c r="N24" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="225"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="225"/>
-      <c r="R24" s="225"/>
-      <c r="S24" s="226"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="192"/>
+      <c r="Q24" s="192"/>
+      <c r="R24" s="192"/>
+      <c r="S24" s="193"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
@@ -5282,21 +5206,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="209" t="s">
+      <c r="M25" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="210"/>
-      <c r="O25" s="211"/>
-      <c r="P25" s="212"/>
-      <c r="Q25" s="174">
+      <c r="N25" s="197"/>
+      <c r="O25" s="228"/>
+      <c r="P25" s="229"/>
+      <c r="Q25" s="171">
         <v>450000</v>
       </c>
-      <c r="R25" s="175"/>
-      <c r="S25" s="176"/>
-      <c r="T25" s="207" t="s">
+      <c r="R25" s="172"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="208"/>
+      <c r="U25" s="195"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -5312,11 +5236,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="174">
+      <c r="Q26" s="175">
         <v>50000</v>
       </c>
-      <c r="R26" s="175"/>
-      <c r="S26" s="176"/>
+      <c r="R26" s="176"/>
+      <c r="S26" s="177"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -5334,17 +5258,17 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="199"/>
-      <c r="P27" s="200"/>
-      <c r="Q27" s="174">
+      <c r="O27" s="178"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="175">
         <v>300000</v>
       </c>
-      <c r="R27" s="175"/>
-      <c r="S27" s="176"/>
-      <c r="T27" s="219" t="s">
+      <c r="R27" s="176"/>
+      <c r="S27" s="177"/>
+      <c r="T27" s="186" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="220"/>
+      <c r="U27" s="187"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
         <v>1000000</v>
@@ -5360,19 +5284,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="194" t="s">
+      <c r="M28" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="195"/>
-      <c r="O28" s="199"/>
-      <c r="P28" s="200"/>
-      <c r="Q28" s="174"/>
-      <c r="R28" s="175"/>
-      <c r="S28" s="176"/>
-      <c r="T28" s="217" t="s">
+      <c r="N28" s="185"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="175"/>
+      <c r="R28" s="176"/>
+      <c r="S28" s="177"/>
+      <c r="T28" s="182" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="218"/>
+      <c r="U28" s="183"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -5387,19 +5311,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="194" t="s">
+      <c r="M29" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="195"/>
-      <c r="O29" s="199"/>
-      <c r="P29" s="200"/>
-      <c r="Q29" s="174"/>
-      <c r="R29" s="175"/>
-      <c r="S29" s="176"/>
-      <c r="T29" s="215" t="s">
+      <c r="N29" s="185"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="179"/>
+      <c r="Q29" s="175"/>
+      <c r="R29" s="176"/>
+      <c r="S29" s="177"/>
+      <c r="T29" s="180" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="216"/>
+      <c r="U29" s="181"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -5415,19 +5339,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="194" t="s">
+      <c r="M30" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="195"/>
-      <c r="O30" s="199"/>
-      <c r="P30" s="213"/>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="175"/>
-      <c r="S30" s="176"/>
-      <c r="T30" s="201" t="s">
+      <c r="N30" s="185"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="198"/>
+      <c r="Q30" s="175"/>
+      <c r="R30" s="176"/>
+      <c r="S30" s="177"/>
+      <c r="T30" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="202"/>
+      <c r="U30" s="200"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -5444,15 +5368,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="194" t="s">
+      <c r="M31" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="195"/>
-      <c r="O31" s="199"/>
-      <c r="P31" s="200"/>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="176"/>
+      <c r="N31" s="185"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="175"/>
+      <c r="R31" s="176"/>
+      <c r="S31" s="177"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -5467,15 +5391,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="194" t="s">
+      <c r="M32" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="195"/>
-      <c r="O32" s="199"/>
-      <c r="P32" s="200"/>
-      <c r="Q32" s="174"/>
-      <c r="R32" s="175"/>
-      <c r="S32" s="176"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="175"/>
+      <c r="R32" s="176"/>
+      <c r="S32" s="177"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -5497,11 +5421,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="199"/>
-      <c r="P33" s="200"/>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="176"/>
+      <c r="O33" s="178"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="175"/>
+      <c r="R33" s="176"/>
+      <c r="S33" s="177"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -5520,17 +5444,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="203" t="s">
+      <c r="M34" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="204"/>
-      <c r="O34" s="205"/>
-      <c r="P34" s="206"/>
-      <c r="Q34" s="174">
+      <c r="N34" s="205"/>
+      <c r="O34" s="206"/>
+      <c r="P34" s="207"/>
+      <c r="Q34" s="175">
         <v>1000000</v>
       </c>
-      <c r="R34" s="175"/>
-      <c r="S34" s="176"/>
+      <c r="R34" s="176"/>
+      <c r="S34" s="177"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -5548,23 +5472,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="196" t="s">
+      <c r="M35" s="217" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="189" t="s">
+      <c r="N35" s="218"/>
+      <c r="O35" s="219"/>
+      <c r="P35" s="202" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="193"/>
-      <c r="R35" s="189" t="s">
+      <c r="Q35" s="203"/>
+      <c r="R35" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="193"/>
-      <c r="T35" s="189" t="s">
+      <c r="S35" s="203"/>
+      <c r="T35" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="193"/>
+      <c r="U35" s="203"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -5620,23 +5544,13 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O42)</f>
+        <f>SUM(O41)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01/01/2026</t>
-        </is>
-      </c>
-      <c r="N37" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O37" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -5648,85 +5562,95 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M38" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02/01/2026</t>
-        </is>
-      </c>
-      <c r="N38" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="O38" s="39">
-        <v>200000</v>
-      </c>
+    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="32"/>
+      <c r="I38" s="134"/>
+      <c r="J38"/>
+      <c r="L38" s="114">
+        <v>2</v>
+      </c>
+      <c r="M38" s="208" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="226"/>
+      <c r="O38" s="227"/>
       <c r="P38" s="42"/>
-      <c r="Q38" s="72"/>
+      <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
       <c r="S38" s="77"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="72"/>
-    </row>
-    <row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U38" s="80"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B39" s="20"/>
       <c r="C39" s="32"/>
       <c r="I39" s="134"/>
       <c r="J39"/>
+      <c r="K39" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L39" s="114">
-        <v>2</v>
-      </c>
-      <c r="M39" s="179" t="s">
-        <v>42</v>
-      </c>
-      <c r="N39" s="180"/>
-      <c r="O39" s="46">
-        <v>300000</v>
+        <v>3</v>
+      </c>
+      <c r="M39" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01-01-2026</t>
+        </is>
+      </c>
+      <c r="N39" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O39" s="39">
+        <v>100000</v>
       </c>
       <c r="P39" s="42"/>
-      <c r="Q39" s="79"/>
+      <c r="Q39" s="72"/>
       <c r="R39" s="44"/>
       <c r="S39" s="77"/>
       <c r="T39" s="42"/>
-      <c r="U39" s="80"/>
+      <c r="U39" s="72"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="20"/>
       <c r="C40" s="32"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="47"/>
       <c r="I40" s="134"/>
       <c r="J40"/>
-      <c r="K40" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K40" s="24"/>
       <c r="L40" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="37"/>
       <c r="N40" s="38"/>
       <c r="O40" s="39"/>
       <c r="P40" s="42"/>
-      <c r="Q40" s="72"/>
+      <c r="Q40" s="70"/>
       <c r="R40" s="44"/>
-      <c r="S40" s="77"/>
+      <c r="S40" s="78"/>
       <c r="T40" s="42"/>
       <c r="U40" s="72"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="47"/>
-      <c r="I41" s="134"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="I41" s="133"/>
       <c r="J41"/>
       <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" s="37"/>
       <c r="N41" s="38"/>
@@ -5740,16 +5664,16 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B42" s="20"/>
-      <c r="C42" s="32"/>
+      <c r="C42" s="25"/>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
-      <c r="I42" s="133"/>
-      <c r="J42"/>
-      <c r="K42" s="24"/>
+      <c r="F42" s="51"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="57"/>
       <c r="L42" s="114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
@@ -5757,51 +5681,52 @@
       <c r="P42" s="42"/>
       <c r="Q42" s="70"/>
       <c r="R42" s="44"/>
-      <c r="S42" s="78"/>
+      <c r="S42" s="77"/>
       <c r="T42" s="42"/>
       <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="112"/>
       <c r="B43" s="20"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="201"/>
+      <c r="E43" s="201"/>
       <c r="F43" s="51"/>
-      <c r="I43" s="135"/>
+      <c r="G43" s="8"/>
+      <c r="I43" s="136"/>
       <c r="J43" s="57"/>
+      <c r="K43" s="24" t="e">
+        <f>O38+O65</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L43" s="114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="77"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="71"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="112"/>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25"/>
       <c r="B44" s="20"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="183"/>
-      <c r="E44" s="183"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="8"/>
-      <c r="I44" s="136"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="52"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="13"/>
       <c r="J44" s="57"/>
-      <c r="K44" s="24" t="e">
-        <f>O39+O66</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K44" s="24"/>
       <c r="L44" s="114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
@@ -5813,19 +5738,18 @@
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="183"/>
-      <c r="F45" s="52"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="201"/>
+      <c r="E45" s="201"/>
+      <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
       <c r="J45" s="57"/>
-      <c r="K45" s="24"/>
       <c r="L45" s="114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
@@ -5833,22 +5757,22 @@
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
       <c r="R45" s="42"/>
-      <c r="S45" s="71"/>
+      <c r="S45" s="76"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="183"/>
-      <c r="E46" s="183"/>
-      <c r="F46" s="23"/>
+      <c r="D46" s="201"/>
+      <c r="E46" s="201"/>
+      <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
       <c r="J46" s="57"/>
       <c r="L46" s="114">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -5856,7 +5780,7 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="70"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="76"/>
+      <c r="S46" s="71"/>
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
@@ -5864,14 +5788,19 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="183"/>
-      <c r="F47" s="53"/>
+      <c r="D47" s="201"/>
+      <c r="E47" s="201"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="1"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
+      <c r="K47" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L47" s="114">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -5887,19 +5816,15 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="183"/>
-      <c r="E48" s="183"/>
-      <c r="F48" s="17"/>
+      <c r="D48" s="201"/>
+      <c r="E48" s="201"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
-      <c r="K48" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L48" s="114">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -5908,22 +5833,22 @@
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
       <c r="S48" s="71"/>
-      <c r="T48" s="42"/>
+      <c r="T48" s="44"/>
       <c r="U48" s="72"/>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="183"/>
-      <c r="E49" s="183"/>
+      <c r="D49" s="201"/>
+      <c r="E49" s="201"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="68"/>
+      <c r="H49" s="50"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -5939,15 +5864,15 @@
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="183"/>
-      <c r="E50" s="183"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="25"/>
       <c r="F50" s="23"/>
       <c r="G50" s="1"/>
       <c r="H50" s="50"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
       <c r="L50" s="114">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -5963,20 +5888,20 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="25"/>
+      <c r="D51" s="213"/>
+      <c r="E51" s="213"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="42"/>
+      <c r="P51" s="40"/>
       <c r="Q51" s="70"/>
       <c r="R51" s="42"/>
       <c r="S51" s="71"/>
@@ -5985,17 +5910,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
+      <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="184"/>
-      <c r="E52" s="184"/>
+      <c r="D52" s="225"/>
+      <c r="E52" s="225"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
-      <c r="I52" s="13"/>
+      <c r="I52" s="54"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
@@ -6008,23 +5933,21 @@
       <c r="U52" s="72"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="20"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="182"/>
-      <c r="E53" s="182"/>
+      <c r="D53" s="212"/>
+      <c r="E53" s="212"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
       <c r="I53" s="54"/>
       <c r="J53" s="57"/>
-      <c r="L53" s="114">
-        <v>16</v>
-      </c>
+      <c r="L53" s="18"/>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="40"/>
+      <c r="P53" s="42"/>
       <c r="Q53" s="70"/>
       <c r="R53" s="42"/>
       <c r="S53" s="71"/>
@@ -6032,11 +5955,11 @@
       <c r="U53" s="72"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="25"/>
+      <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="181"/>
-      <c r="E54" s="181"/>
+      <c r="D54" s="212"/>
+      <c r="E54" s="212"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -6057,8 +5980,8 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="181"/>
-      <c r="E55" s="181"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
@@ -6077,7 +6000,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
-      <c r="B56" s="55"/>
+      <c r="B56"/>
       <c r="C56" s="43"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
@@ -6164,11 +6087,11 @@
       <c r="U59" s="72"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="20"/>
+      <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
+      <c r="D60" s="212"/>
+      <c r="E60" s="212"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -6189,8 +6112,8 @@
       <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="181"/>
-      <c r="E61" s="181"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="50"/>
@@ -6201,9 +6124,9 @@
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
       <c r="P61" s="42"/>
-      <c r="Q61" s="70"/>
-      <c r="R61" s="42"/>
-      <c r="S61" s="71"/>
+      <c r="Q61" s="161"/>
+      <c r="R61" s="93"/>
+      <c r="S61" s="92"/>
       <c r="T61" s="44"/>
       <c r="U61" s="72"/>
     </row>
@@ -6251,12 +6174,12 @@
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
+      <c r="D64" s="212"/>
+      <c r="E64" s="212"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -6267,399 +6190,362 @@
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
       <c r="P64" s="42"/>
-      <c r="Q64" s="161"/>
+      <c r="Q64" s="88"/>
       <c r="R64" s="93"/>
       <c r="S64" s="92"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="72"/>
-    </row>
-    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U64" s="75"/>
+    </row>
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="181"/>
-      <c r="E65" s="181"/>
-      <c r="F65" s="23"/>
+      <c r="D65" s="212"/>
+      <c r="E65" s="212"/>
+      <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="37"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="42"/>
-      <c r="Q65" s="88"/>
-      <c r="R65" s="93"/>
-      <c r="S65" s="92"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="75"/>
-    </row>
-    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65"/>
+      <c r="M65" s="208" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="209"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="46"/>
+      <c r="R65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S65" s="46"/>
+      <c r="T65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="46"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="181"/>
-      <c r="E66" s="181"/>
-      <c r="F66" s="20"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="212"/>
+      <c r="E66" s="212"/>
+      <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
-      <c r="J66" s="57"/>
+      <c r="J66"/>
       <c r="L66"/>
-      <c r="M66" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="N66" s="180"/>
-      <c r="O66" s="46"/>
-      <c r="P66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q66" s="46"/>
-      <c r="R66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S66" s="46"/>
-      <c r="T66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U66" s="46"/>
-    </row>
-    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="58"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="23"/>
+      <c r="Q66" s="73"/>
+      <c r="R66" s="74"/>
+      <c r="S66" s="74"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="95"/>
-      <c r="D67" s="181"/>
-      <c r="E67" s="181"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="58"/>
-      <c r="N67" s="59"/>
-      <c r="O67" s="74"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="73"/>
-      <c r="R67" s="74"/>
-      <c r="S67" s="74"/>
-      <c r="T67" s="6"/>
-    </row>
-    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="202" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="216"/>
+      <c r="O67" s="203"/>
+      <c r="P67" s="214"/>
+      <c r="Q67" s="215"/>
+      <c r="R67" s="202" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="216"/>
+      <c r="T67" s="210" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U67" s="211"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="23"/>
+      <c r="D68" s="212"/>
+      <c r="E68" s="212"/>
+      <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
       <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="189" t="s">
-        <v>47</v>
-      </c>
-      <c r="N68" s="190"/>
-      <c r="O68" s="193"/>
-      <c r="P68" s="191"/>
-      <c r="Q68" s="192"/>
-      <c r="R68" s="189" t="s">
-        <v>37</v>
-      </c>
-      <c r="S68" s="190"/>
-      <c r="T68" s="185" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U68" s="186"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="87"/>
+      <c r="O68" s="87"/>
+      <c r="P68" s="61"/>
+      <c r="Q68" s="62"/>
+      <c r="R68" s="62"/>
+      <c r="S68" s="62"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
     </row>
     <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69"/>
+      <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="181"/>
-      <c r="E69" s="181"/>
+      <c r="D69" s="212"/>
+      <c r="E69" s="212"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="87"/>
-      <c r="O69" s="87"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="62"/>
-      <c r="R69" s="62"/>
-      <c r="S69" s="62"/>
-      <c r="T69" s="60"/>
-      <c r="U69" s="60"/>
-    </row>
-    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="208" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="226"/>
+      <c r="O69" s="226"/>
+      <c r="P69" s="226"/>
+      <c r="Q69" s="226"/>
+      <c r="R69" s="226"/>
+      <c r="S69" s="226"/>
+      <c r="T69" s="226"/>
+      <c r="U69" s="227"/>
+      <c r="V69" s="55"/>
+    </row>
+    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="95"/>
+      <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="181"/>
-      <c r="E70" s="181"/>
+      <c r="D70" s="212"/>
+      <c r="E70" s="212"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
-      <c r="L70"/>
-      <c r="M70" s="179" t="s">
-        <v>35</v>
-      </c>
-      <c r="N70" s="187"/>
-      <c r="O70" s="187"/>
-      <c r="P70" s="187"/>
-      <c r="Q70" s="187"/>
-      <c r="R70" s="187"/>
-      <c r="S70" s="187"/>
-      <c r="T70" s="187"/>
-      <c r="U70" s="188"/>
-      <c r="V70" s="55"/>
-    </row>
-    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L70" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="157"/>
+      <c r="O70" s="157"/>
+      <c r="P70" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q70" s="157"/>
+      <c r="R70" s="157"/>
+      <c r="S70" s="157"/>
+      <c r="T70" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U70" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V70" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W70" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="25"/>
-      <c r="B71" s="20"/>
+      <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="181"/>
-      <c r="E71" s="181"/>
+      <c r="D71" s="212"/>
+      <c r="E71" s="212"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
-      <c r="J71"/>
-      <c r="L71" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M71" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N71" s="157"/>
-      <c r="O71" s="157"/>
-      <c r="P71" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q71" s="157"/>
-      <c r="R71" s="157"/>
-      <c r="S71" s="157"/>
-      <c r="T71" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U71" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V71" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W71" s="170" t="s">
-        <v>50</v>
-      </c>
+      <c r="J71" s="23"/>
+      <c r="L71"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="64"/>
+      <c r="O71" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="65"/>
+      <c r="R71" s="224" t="s">
+        <v>6</v>
+      </c>
+      <c r="S71" s="224"/>
+      <c r="T71" s="159"/>
+      <c r="U71" s="160"/>
+      <c r="V71" s="55"/>
     </row>
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="25"/>
-      <c r="B72" s="130"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="181"/>
-      <c r="E72" s="181"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="212"/>
+      <c r="E72" s="212"/>
       <c r="F72" s="67"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="23"/>
+      <c r="I72" s="130"/>
       <c r="L72"/>
-      <c r="M72" s="63"/>
-      <c r="N72" s="64"/>
-      <c r="O72" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P72" s="66"/>
-      <c r="Q72" s="65"/>
-      <c r="R72" s="178" t="s">
-        <v>6</v>
-      </c>
-      <c r="S72" s="178"/>
-      <c r="T72" s="159"/>
-      <c r="U72" s="160"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="91"/>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="222"/>
+      <c r="S72" s="222"/>
+      <c r="T72" s="69"/>
+      <c r="U72" s="100"/>
       <c r="V72" s="55"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B73" s="55"/>
+      <c r="A73" s="53"/>
+      <c r="B73" s="94"/>
       <c r="C73" s="94"/>
-      <c r="D73" s="181"/>
-      <c r="E73" s="181"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73"/>
-      <c r="M73" s="89"/>
-      <c r="N73" s="90"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="91"/>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="173"/>
-      <c r="S73" s="173"/>
-      <c r="T73" s="69"/>
-      <c r="U73" s="100"/>
-      <c r="V73" s="55"/>
-    </row>
-    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="53"/>
-      <c r="B74" s="94"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="67"/>
-      <c r="I74" s="130"/>
-      <c r="L74" s="49" t="inlineStr">
+      <c r="L73" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">12345</t>
         </is>
       </c>
-      <c r="M74" s="89" t="inlineStr">
+      <c r="M73" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="N74" s="90"/>
-      <c r="O74" s="18" t="s">
+      <c r="N73" s="90"/>
+      <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P74" s="91" t="inlineStr">
+      <c r="P73" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="222" t="s">
+        <v>10</v>
+      </c>
+      <c r="S73" s="222"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U73" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banco Santander</t>
+        </is>
+      </c>
+      <c r="V73" s="55"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L74" s="49"/>
+      <c r="M74" s="89"/>
+      <c r="N74" s="90"/>
+      <c r="O74" s="147"/>
+      <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="173" t="s">
-        <v>10</v>
-      </c>
-      <c r="S74" s="173"/>
-      <c r="T74" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U74" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
+      <c r="R74" s="222"/>
+      <c r="S74" s="222"/>
+      <c r="T74" s="69"/>
+      <c r="U74" s="100"/>
       <c r="V74" s="55"/>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L75" s="49"/>
-      <c r="M75" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE DOS</t>
-        </is>
-      </c>
-      <c r="O75" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="P75" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F002</t>
-        </is>
-      </c>
-      <c r="T75" s="69">
-        <v>250000</v>
-      </c>
+      <c r="M75" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="165"/>
+      <c r="P75" s="166"/>
+      <c r="Q75" s="167"/>
+      <c r="R75" s="223"/>
+      <c r="S75" s="223"/>
+      <c r="T75" s="220"/>
+      <c r="U75" s="221"/>
+      <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="49"/>
-      <c r="M76" s="89"/>
-      <c r="N76" s="90"/>
-      <c r="O76" s="147"/>
-      <c r="P76" s="91"/>
-      <c r="Q76" s="60"/>
-      <c r="R76" s="173"/>
-      <c r="S76" s="173"/>
-      <c r="T76" s="69"/>
-      <c r="U76" s="100"/>
+      <c r="M76" s="163" t="s">
+        <v>62</v>
+      </c>
+      <c r="N76" s="164"/>
+      <c r="O76" s="165"/>
+      <c r="P76" s="166"/>
+      <c r="Q76" s="167"/>
+      <c r="R76" s="168"/>
+      <c r="S76" s="168"/>
+      <c r="T76" s="220"/>
+      <c r="U76" s="221"/>
       <c r="V76" s="55"/>
     </row>
-    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L77" s="49"/>
-      <c r="M77" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="N77" s="164"/>
-      <c r="O77" s="165"/>
-      <c r="P77" s="166"/>
-      <c r="Q77" s="167"/>
-      <c r="R77" s="177"/>
-      <c r="S77" s="177"/>
-      <c r="T77" s="171"/>
-      <c r="U77" s="172"/>
+      <c r="M77" s="99"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="147"/>
+      <c r="P77" s="91"/>
+      <c r="Q77" s="60"/>
+      <c r="R77" s="60"/>
+      <c r="S77" s="60"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="100"/>
       <c r="V77" s="55"/>
     </row>
-    <row r="78" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L78" s="49"/>
-      <c r="M78" s="163" t="s">
-        <v>62</v>
-      </c>
-      <c r="N78" s="164"/>
-      <c r="O78" s="165"/>
-      <c r="P78" s="166"/>
-      <c r="Q78" s="167"/>
-      <c r="R78" s="168"/>
-      <c r="S78" s="168"/>
-      <c r="T78" s="171"/>
-      <c r="U78" s="172"/>
+      <c r="M78" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="107">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="101"/>
+      <c r="P78" s="103"/>
+      <c r="Q78" s="102"/>
+      <c r="R78" s="102"/>
+      <c r="S78" s="102"/>
+      <c r="T78" s="104"/>
+      <c r="U78" s="105"/>
       <c r="V78" s="55"/>
     </row>
-    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L79" s="49"/>
-      <c r="M79" s="99"/>
-      <c r="N79" s="68"/>
-      <c r="O79" s="147"/>
-      <c r="P79" s="91"/>
-      <c r="Q79" s="60"/>
-      <c r="R79" s="60"/>
-      <c r="S79" s="60"/>
-      <c r="T79" s="69"/>
-      <c r="U79" s="100"/>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
       <c r="V79" s="55"/>
     </row>
-    <row r="80" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L80" s="49"/>
-      <c r="M80" s="106" t="s">
-        <v>11</v>
-      </c>
-      <c r="N80" s="107">
-        <f>SUM(N78:N79)</f>
-        <v>0</v>
-      </c>
-      <c r="O80" s="101"/>
-      <c r="P80" s="103"/>
-      <c r="Q80" s="102"/>
-      <c r="R80" s="102"/>
-      <c r="S80" s="102"/>
-      <c r="T80" s="104"/>
-      <c r="U80" s="105"/>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O80"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M81"/>
-      <c r="O81" s="5"/>
-      <c r="Q81"/>
-      <c r="S81"/>
-      <c r="T81" s="6"/>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
       <c r="V81" s="55"/>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O82"/>
+    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V82" s="55"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M83" s="23"/>
-      <c r="N83" s="23"/>
-      <c r="O83" s="23"/>
-      <c r="P83" s="23"/>
-      <c r="Q83" s="23"/>
       <c r="V83" s="55"/>
     </row>
     <row r="84" spans="13:22" x14ac:dyDescent="0.3">
@@ -6701,10 +6587,10 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
-    <row r="98" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V98" s="55"/>
     </row>
     <row r="99" spans="22:22" x14ac:dyDescent="0.3">
@@ -6749,14 +6635,62 @@
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
     </row>
-    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V113" s="55"/>
-    </row>
-    <row r="114" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V114" s="55"/>
-    </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="70">
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="O29:P29"/>
@@ -6773,62 +6707,6 @@
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
     <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="M70:U70"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="M68:O68"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="T78:U78"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R77:S77"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T77:U77"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D53:E53"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -6838,7 +6716,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W114"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -6867,7 +6745,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOB</t>
+          <t xml:space="preserve">MARIA LOPEZ</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -6896,10 +6774,8 @@
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUX BOB</t>
-        </is>
+      <c r="B2" s="127" t="s">
+        <v>101</v>
       </c>
       <c r="C2" s="143"/>
       <c r="D2" s="143"/>
@@ -6927,7 +6803,9 @@
       <c r="A3" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="143"/>
+      <c r="B3" s="143" t="s">
+        <v>102</v>
+      </c>
       <c r="C3" s="143"/>
       <c r="D3" s="143"/>
       <c r="E3" s="143"/>
@@ -6954,7 +6832,9 @@
       <c r="A4" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="143"/>
+      <c r="B4" s="143" t="s">
+        <v>103</v>
+      </c>
       <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
@@ -6983,7 +6863,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">67890</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -7037,7 +6917,7 @@
       <c r="V6" s="123"/>
       <c r="W6" s="123"/>
     </row>
-    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" s="49" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="127" t="s">
         <v>2</v>
       </c>
@@ -7095,11 +6975,11 @@
       <c r="A9" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="227">
+      <c r="B9" s="171">
         <v>450000</v>
       </c>
-      <c r="C9" s="228"/>
-      <c r="D9" s="229"/>
+      <c r="C9" s="172"/>
+      <c r="D9" s="173"/>
       <c r="E9" s="110"/>
       <c r="F9" s="119"/>
       <c r="G9" s="110"/>
@@ -7124,11 +7004,11 @@
       <c r="A10" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="227">
+      <c r="B10" s="171">
         <v>50000</v>
       </c>
-      <c r="C10" s="228"/>
-      <c r="D10" s="229"/>
+      <c r="C10" s="172"/>
+      <c r="D10" s="173"/>
       <c r="E10" s="110"/>
       <c r="F10" s="119"/>
       <c r="G10" s="110"/>
@@ -7153,11 +7033,11 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="227">
+      <c r="B11" s="171">
         <v>300000</v>
       </c>
-      <c r="C11" s="228"/>
-      <c r="D11" s="229"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="173"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
       <c r="G11" s="110"/>
@@ -7182,9 +7062,9 @@
       <c r="A12" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="227"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="229"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="172"/>
+      <c r="D12" s="173"/>
       <c r="E12" s="110"/>
       <c r="F12" s="119"/>
       <c r="G12" s="110"/>
@@ -7209,9 +7089,9 @@
       <c r="A13" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="227"/>
-      <c r="C13" s="228"/>
-      <c r="D13" s="229"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="173"/>
       <c r="E13" s="110"/>
       <c r="F13" s="119"/>
       <c r="G13" s="110"/>
@@ -7236,9 +7116,9 @@
       <c r="A14" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="227"/>
-      <c r="C14" s="228"/>
-      <c r="D14" s="229"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="173"/>
       <c r="E14" s="110"/>
       <c r="F14" s="119"/>
       <c r="G14" s="110"/>
@@ -7263,9 +7143,9 @@
       <c r="A15" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="227"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="229"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="173"/>
       <c r="E15" s="110"/>
       <c r="F15" s="119"/>
       <c r="G15" s="110"/>
@@ -7290,9 +7170,9 @@
       <c r="A16" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="227"/>
-      <c r="C16" s="228"/>
-      <c r="D16" s="229"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="173"/>
       <c r="E16" s="110"/>
       <c r="F16" s="119"/>
       <c r="G16" s="110"/>
@@ -7317,9 +7197,9 @@
       <c r="A17" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="227"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="229"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="173"/>
       <c r="E17" s="110"/>
       <c r="F17" s="119"/>
       <c r="G17" s="110"/>
@@ -7578,17 +7458,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="214" t="s">
+      <c r="M22" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="214"/>
-      <c r="O22" s="214"/>
-      <c r="P22" s="214"/>
-      <c r="Q22" s="214"/>
-      <c r="R22" s="214"/>
-      <c r="S22" s="214"/>
-      <c r="T22" s="214"/>
-      <c r="U22" s="214"/>
+      <c r="N22" s="174"/>
+      <c r="O22" s="174"/>
+      <c r="P22" s="174"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -7597,16 +7477,16 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="221" t="inlineStr">
+      <c r="N23" s="188" t="inlineStr">
         <is>
-          <t xml:space="preserve">24/06/2026</t>
+          <t xml:space="preserve">24-06-2026</t>
         </is>
       </c>
-      <c r="O23" s="222"/>
-      <c r="P23" s="222"/>
-      <c r="Q23" s="222"/>
-      <c r="R23" s="222"/>
-      <c r="S23" s="223"/>
+      <c r="O23" s="189"/>
+      <c r="P23" s="189"/>
+      <c r="Q23" s="189"/>
+      <c r="R23" s="189"/>
+      <c r="S23" s="190"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
@@ -7624,14 +7504,14 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="224" t="s">
+      <c r="N24" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="225"/>
-      <c r="P24" s="225"/>
-      <c r="Q24" s="225"/>
-      <c r="R24" s="225"/>
-      <c r="S24" s="226"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="192"/>
+      <c r="Q24" s="192"/>
+      <c r="R24" s="192"/>
+      <c r="S24" s="193"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
@@ -7651,21 +7531,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="209" t="s">
+      <c r="M25" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="210"/>
-      <c r="O25" s="211"/>
-      <c r="P25" s="212"/>
-      <c r="Q25" s="174">
+      <c r="N25" s="197"/>
+      <c r="O25" s="228"/>
+      <c r="P25" s="229"/>
+      <c r="Q25" s="171">
         <v>450000</v>
       </c>
-      <c r="R25" s="175"/>
-      <c r="S25" s="176"/>
-      <c r="T25" s="207" t="s">
+      <c r="R25" s="172"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="194" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="208"/>
+      <c r="U25" s="195"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -7681,11 +7561,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="174">
+      <c r="Q26" s="175">
         <v>50000</v>
       </c>
-      <c r="R26" s="175"/>
-      <c r="S26" s="176"/>
+      <c r="R26" s="176"/>
+      <c r="S26" s="177"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -7703,17 +7583,17 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="199"/>
-      <c r="P27" s="200"/>
-      <c r="Q27" s="174">
+      <c r="O27" s="178"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="175">
         <v>300000</v>
       </c>
-      <c r="R27" s="175"/>
-      <c r="S27" s="176"/>
-      <c r="T27" s="219" t="s">
+      <c r="R27" s="176"/>
+      <c r="S27" s="177"/>
+      <c r="T27" s="186" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="220"/>
+      <c r="U27" s="187"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
         <v>1000000</v>
@@ -7729,19 +7609,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="194" t="s">
+      <c r="M28" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="195"/>
-      <c r="O28" s="199"/>
-      <c r="P28" s="200"/>
-      <c r="Q28" s="174"/>
-      <c r="R28" s="175"/>
-      <c r="S28" s="176"/>
-      <c r="T28" s="217" t="s">
+      <c r="N28" s="185"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="175"/>
+      <c r="R28" s="176"/>
+      <c r="S28" s="177"/>
+      <c r="T28" s="182" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="218"/>
+      <c r="U28" s="183"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -7756,19 +7636,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="194" t="s">
+      <c r="M29" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="195"/>
-      <c r="O29" s="199"/>
-      <c r="P29" s="200"/>
-      <c r="Q29" s="174"/>
-      <c r="R29" s="175"/>
-      <c r="S29" s="176"/>
-      <c r="T29" s="215" t="s">
+      <c r="N29" s="185"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="179"/>
+      <c r="Q29" s="175"/>
+      <c r="R29" s="176"/>
+      <c r="S29" s="177"/>
+      <c r="T29" s="180" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="216"/>
+      <c r="U29" s="181"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -7784,19 +7664,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="194" t="s">
+      <c r="M30" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="195"/>
-      <c r="O30" s="199"/>
-      <c r="P30" s="213"/>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="175"/>
-      <c r="S30" s="176"/>
-      <c r="T30" s="201" t="s">
+      <c r="N30" s="185"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="198"/>
+      <c r="Q30" s="175"/>
+      <c r="R30" s="176"/>
+      <c r="S30" s="177"/>
+      <c r="T30" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="202"/>
+      <c r="U30" s="200"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -7813,15 +7693,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="194" t="s">
+      <c r="M31" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="195"/>
-      <c r="O31" s="199"/>
-      <c r="P31" s="200"/>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="176"/>
+      <c r="N31" s="185"/>
+      <c r="O31" s="178"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="175"/>
+      <c r="R31" s="176"/>
+      <c r="S31" s="177"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -7836,15 +7716,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="194" t="s">
+      <c r="M32" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="195"/>
-      <c r="O32" s="199"/>
-      <c r="P32" s="200"/>
-      <c r="Q32" s="174"/>
-      <c r="R32" s="175"/>
-      <c r="S32" s="176"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="178"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="175"/>
+      <c r="R32" s="176"/>
+      <c r="S32" s="177"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -7866,11 +7746,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="199"/>
-      <c r="P33" s="200"/>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="176"/>
+      <c r="O33" s="178"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="175"/>
+      <c r="R33" s="176"/>
+      <c r="S33" s="177"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -7889,17 +7769,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="203" t="s">
+      <c r="M34" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="204"/>
-      <c r="O34" s="205"/>
-      <c r="P34" s="206"/>
-      <c r="Q34" s="174">
+      <c r="N34" s="205"/>
+      <c r="O34" s="206"/>
+      <c r="P34" s="207"/>
+      <c r="Q34" s="175">
         <v>1000000</v>
       </c>
-      <c r="R34" s="175"/>
-      <c r="S34" s="176"/>
+      <c r="R34" s="176"/>
+      <c r="S34" s="177"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -7917,23 +7797,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="196" t="s">
+      <c r="M35" s="217" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="197"/>
-      <c r="O35" s="198"/>
-      <c r="P35" s="189" t="s">
+      <c r="N35" s="218"/>
+      <c r="O35" s="219"/>
+      <c r="P35" s="202" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="193"/>
-      <c r="R35" s="189" t="s">
+      <c r="Q35" s="203"/>
+      <c r="R35" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="193"/>
-      <c r="T35" s="189" t="s">
+      <c r="S35" s="203"/>
+      <c r="T35" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="193"/>
+      <c r="U35" s="203"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -7989,23 +7869,13 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O42)</f>
+        <f>SUM(O41)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01/01/2026</t>
-        </is>
-      </c>
-      <c r="N37" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O37" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="81"/>
       <c r="R37" s="41"/>
@@ -8017,85 +7887,95 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M38" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02/01/2026</t>
-        </is>
-      </c>
-      <c r="N38" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="O38" s="39">
-        <v>200000</v>
-      </c>
+    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="32"/>
+      <c r="I38" s="134"/>
+      <c r="J38"/>
+      <c r="L38" s="114">
+        <v>2</v>
+      </c>
+      <c r="M38" s="208" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="226"/>
+      <c r="O38" s="227"/>
       <c r="P38" s="42"/>
-      <c r="Q38" s="72"/>
+      <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
       <c r="S38" s="77"/>
       <c r="T38" s="42"/>
-      <c r="U38" s="72"/>
-    </row>
-    <row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U38" s="80"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B39" s="20"/>
       <c r="C39" s="32"/>
       <c r="I39" s="134"/>
       <c r="J39"/>
+      <c r="K39" s="24" t="e">
+        <f>Q27+Q28</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L39" s="114">
-        <v>2</v>
-      </c>
-      <c r="M39" s="179" t="s">
-        <v>42</v>
-      </c>
-      <c r="N39" s="180"/>
-      <c r="O39" s="46">
-        <v>300000</v>
+        <v>3</v>
+      </c>
+      <c r="M39" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01-01-2026</t>
+        </is>
+      </c>
+      <c r="N39" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTANDER</t>
+        </is>
+      </c>
+      <c r="O39" s="39">
+        <v>100000</v>
       </c>
       <c r="P39" s="42"/>
-      <c r="Q39" s="79"/>
+      <c r="Q39" s="72"/>
       <c r="R39" s="44"/>
       <c r="S39" s="77"/>
       <c r="T39" s="42"/>
-      <c r="U39" s="80"/>
+      <c r="U39" s="72"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="20"/>
       <c r="C40" s="32"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="47"/>
       <c r="I40" s="134"/>
       <c r="J40"/>
-      <c r="K40" s="24" t="e">
-        <f>Q27+Q28</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K40" s="24"/>
       <c r="L40" s="114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="37"/>
       <c r="N40" s="38"/>
       <c r="O40" s="39"/>
       <c r="P40" s="42"/>
-      <c r="Q40" s="72"/>
+      <c r="Q40" s="70"/>
       <c r="R40" s="44"/>
-      <c r="S40" s="77"/>
+      <c r="S40" s="78"/>
       <c r="T40" s="42"/>
       <c r="U40" s="72"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="47"/>
-      <c r="I41" s="134"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="I41" s="133"/>
       <c r="J41"/>
       <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" s="37"/>
       <c r="N41" s="38"/>
@@ -8109,16 +7989,16 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B42" s="20"/>
-      <c r="C42" s="32"/>
+      <c r="C42" s="25"/>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
-      <c r="I42" s="133"/>
-      <c r="J42"/>
-      <c r="K42" s="24"/>
+      <c r="F42" s="51"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="57"/>
       <c r="L42" s="114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
@@ -8126,51 +8006,52 @@
       <c r="P42" s="42"/>
       <c r="Q42" s="70"/>
       <c r="R42" s="44"/>
-      <c r="S42" s="78"/>
+      <c r="S42" s="77"/>
       <c r="T42" s="42"/>
       <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="112"/>
       <c r="B43" s="20"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="201"/>
+      <c r="E43" s="201"/>
       <c r="F43" s="51"/>
-      <c r="I43" s="135"/>
+      <c r="G43" s="8"/>
+      <c r="I43" s="136"/>
       <c r="J43" s="57"/>
+      <c r="K43" s="24" t="e">
+        <f>O38+O65</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L43" s="114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="77"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="71"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="112"/>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25"/>
       <c r="B44" s="20"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="183"/>
-      <c r="E44" s="183"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="8"/>
-      <c r="I44" s="136"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="201"/>
+      <c r="E44" s="201"/>
+      <c r="F44" s="52"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="13"/>
       <c r="J44" s="57"/>
-      <c r="K44" s="24" t="e">
-        <f>O39+O66</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K44" s="24"/>
       <c r="L44" s="114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
@@ -8182,19 +8063,18 @@
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="183"/>
-      <c r="F45" s="52"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="201"/>
+      <c r="E45" s="201"/>
+      <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
       <c r="J45" s="57"/>
-      <c r="K45" s="24"/>
       <c r="L45" s="114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
@@ -8202,22 +8082,22 @@
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
       <c r="R45" s="42"/>
-      <c r="S45" s="71"/>
+      <c r="S45" s="76"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="183"/>
-      <c r="E46" s="183"/>
-      <c r="F46" s="23"/>
+      <c r="D46" s="201"/>
+      <c r="E46" s="201"/>
+      <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
       <c r="J46" s="57"/>
       <c r="L46" s="114">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -8225,7 +8105,7 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="70"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="76"/>
+      <c r="S46" s="71"/>
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
@@ -8233,14 +8113,19 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="183"/>
-      <c r="F47" s="53"/>
+      <c r="D47" s="201"/>
+      <c r="E47" s="201"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="1"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
+      <c r="K47" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L47" s="114">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -8256,19 +8141,15 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="183"/>
-      <c r="E48" s="183"/>
-      <c r="F48" s="17"/>
+      <c r="D48" s="201"/>
+      <c r="E48" s="201"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
-      <c r="K48" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L48" s="114">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -8277,22 +8158,22 @@
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
       <c r="S48" s="71"/>
-      <c r="T48" s="42"/>
+      <c r="T48" s="44"/>
       <c r="U48" s="72"/>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="183"/>
-      <c r="E49" s="183"/>
+      <c r="D49" s="201"/>
+      <c r="E49" s="201"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="68"/>
+      <c r="H49" s="50"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -8308,15 +8189,15 @@
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="183"/>
-      <c r="E50" s="183"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="25"/>
       <c r="F50" s="23"/>
       <c r="G50" s="1"/>
       <c r="H50" s="50"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
       <c r="L50" s="114">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -8332,20 +8213,20 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="25"/>
+      <c r="D51" s="213"/>
+      <c r="E51" s="213"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="42"/>
+      <c r="P51" s="40"/>
       <c r="Q51" s="70"/>
       <c r="R51" s="42"/>
       <c r="S51" s="71"/>
@@ -8354,17 +8235,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
+      <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="184"/>
-      <c r="E52" s="184"/>
+      <c r="D52" s="225"/>
+      <c r="E52" s="225"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
-      <c r="I52" s="13"/>
+      <c r="I52" s="54"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
@@ -8377,23 +8258,21 @@
       <c r="U52" s="72"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="20"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="182"/>
-      <c r="E53" s="182"/>
+      <c r="D53" s="212"/>
+      <c r="E53" s="212"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
       <c r="I53" s="54"/>
       <c r="J53" s="57"/>
-      <c r="L53" s="114">
-        <v>16</v>
-      </c>
+      <c r="L53" s="18"/>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="40"/>
+      <c r="P53" s="42"/>
       <c r="Q53" s="70"/>
       <c r="R53" s="42"/>
       <c r="S53" s="71"/>
@@ -8401,11 +8280,11 @@
       <c r="U53" s="72"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="25"/>
+      <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="181"/>
-      <c r="E54" s="181"/>
+      <c r="D54" s="212"/>
+      <c r="E54" s="212"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -8426,8 +8305,8 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="181"/>
-      <c r="E55" s="181"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
@@ -8446,7 +8325,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
-      <c r="B56" s="55"/>
+      <c r="B56"/>
       <c r="C56" s="43"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
@@ -8533,11 +8412,11 @@
       <c r="U59" s="72"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="20"/>
+      <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
+      <c r="D60" s="212"/>
+      <c r="E60" s="212"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -8558,8 +8437,8 @@
       <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="181"/>
-      <c r="E61" s="181"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="50"/>
@@ -8570,9 +8449,9 @@
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
       <c r="P61" s="42"/>
-      <c r="Q61" s="70"/>
-      <c r="R61" s="42"/>
-      <c r="S61" s="71"/>
+      <c r="Q61" s="161"/>
+      <c r="R61" s="93"/>
+      <c r="S61" s="92"/>
       <c r="T61" s="44"/>
       <c r="U61" s="72"/>
     </row>
@@ -8620,12 +8499,12 @@
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
+      <c r="D64" s="212"/>
+      <c r="E64" s="212"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -8636,399 +8515,362 @@
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
       <c r="P64" s="42"/>
-      <c r="Q64" s="161"/>
+      <c r="Q64" s="88"/>
       <c r="R64" s="93"/>
       <c r="S64" s="92"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="72"/>
-    </row>
-    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U64" s="75"/>
+    </row>
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="181"/>
-      <c r="E65" s="181"/>
-      <c r="F65" s="23"/>
+      <c r="D65" s="212"/>
+      <c r="E65" s="212"/>
+      <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="37"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="42"/>
-      <c r="Q65" s="88"/>
-      <c r="R65" s="93"/>
-      <c r="S65" s="92"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="75"/>
-    </row>
-    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65"/>
+      <c r="M65" s="208" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="209"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="46"/>
+      <c r="R65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S65" s="46"/>
+      <c r="T65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="46"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="181"/>
-      <c r="E66" s="181"/>
-      <c r="F66" s="20"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="212"/>
+      <c r="E66" s="212"/>
+      <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
-      <c r="J66" s="57"/>
+      <c r="J66"/>
       <c r="L66"/>
-      <c r="M66" s="179" t="s">
-        <v>34</v>
-      </c>
-      <c r="N66" s="180"/>
-      <c r="O66" s="46"/>
-      <c r="P66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q66" s="46"/>
-      <c r="R66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S66" s="46"/>
-      <c r="T66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U66" s="46"/>
-    </row>
-    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="58"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="23"/>
+      <c r="Q66" s="73"/>
+      <c r="R66" s="74"/>
+      <c r="S66" s="74"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="95"/>
-      <c r="D67" s="181"/>
-      <c r="E67" s="181"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="58"/>
-      <c r="N67" s="59"/>
-      <c r="O67" s="74"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="73"/>
-      <c r="R67" s="74"/>
-      <c r="S67" s="74"/>
-      <c r="T67" s="6"/>
-    </row>
-    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="202" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="216"/>
+      <c r="O67" s="203"/>
+      <c r="P67" s="214"/>
+      <c r="Q67" s="215"/>
+      <c r="R67" s="202" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="216"/>
+      <c r="T67" s="210" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U67" s="211"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="23"/>
+      <c r="D68" s="212"/>
+      <c r="E68" s="212"/>
+      <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
       <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="189" t="s">
-        <v>47</v>
-      </c>
-      <c r="N68" s="190"/>
-      <c r="O68" s="193"/>
-      <c r="P68" s="191"/>
-      <c r="Q68" s="192"/>
-      <c r="R68" s="189" t="s">
-        <v>37</v>
-      </c>
-      <c r="S68" s="190"/>
-      <c r="T68" s="185" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U68" s="186"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="87"/>
+      <c r="O68" s="87"/>
+      <c r="P68" s="61"/>
+      <c r="Q68" s="62"/>
+      <c r="R68" s="62"/>
+      <c r="S68" s="62"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
     </row>
     <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69"/>
+      <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="181"/>
-      <c r="E69" s="181"/>
+      <c r="D69" s="212"/>
+      <c r="E69" s="212"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="87"/>
-      <c r="O69" s="87"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="62"/>
-      <c r="R69" s="62"/>
-      <c r="S69" s="62"/>
-      <c r="T69" s="60"/>
-      <c r="U69" s="60"/>
-    </row>
-    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="208" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="226"/>
+      <c r="O69" s="226"/>
+      <c r="P69" s="226"/>
+      <c r="Q69" s="226"/>
+      <c r="R69" s="226"/>
+      <c r="S69" s="226"/>
+      <c r="T69" s="226"/>
+      <c r="U69" s="227"/>
+      <c r="V69" s="55"/>
+    </row>
+    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="95"/>
+      <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="181"/>
-      <c r="E70" s="181"/>
+      <c r="D70" s="212"/>
+      <c r="E70" s="212"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
-      <c r="L70"/>
-      <c r="M70" s="179" t="s">
-        <v>35</v>
-      </c>
-      <c r="N70" s="187"/>
-      <c r="O70" s="187"/>
-      <c r="P70" s="187"/>
-      <c r="Q70" s="187"/>
-      <c r="R70" s="187"/>
-      <c r="S70" s="187"/>
-      <c r="T70" s="187"/>
-      <c r="U70" s="188"/>
-      <c r="V70" s="55"/>
-    </row>
-    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L70" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="157"/>
+      <c r="O70" s="157"/>
+      <c r="P70" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q70" s="157"/>
+      <c r="R70" s="157"/>
+      <c r="S70" s="157"/>
+      <c r="T70" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U70" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V70" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W70" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="25"/>
-      <c r="B71" s="20"/>
+      <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="181"/>
-      <c r="E71" s="181"/>
+      <c r="D71" s="212"/>
+      <c r="E71" s="212"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
-      <c r="J71"/>
-      <c r="L71" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M71" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N71" s="157"/>
-      <c r="O71" s="157"/>
-      <c r="P71" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q71" s="157"/>
-      <c r="R71" s="157"/>
-      <c r="S71" s="157"/>
-      <c r="T71" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U71" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V71" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W71" s="170" t="s">
-        <v>50</v>
-      </c>
+      <c r="J71" s="23"/>
+      <c r="L71"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="64"/>
+      <c r="O71" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="65"/>
+      <c r="R71" s="224" t="s">
+        <v>6</v>
+      </c>
+      <c r="S71" s="224"/>
+      <c r="T71" s="159"/>
+      <c r="U71" s="160"/>
+      <c r="V71" s="55"/>
     </row>
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="25"/>
-      <c r="B72" s="130"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="181"/>
-      <c r="E72" s="181"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="212"/>
+      <c r="E72" s="212"/>
       <c r="F72" s="67"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="23"/>
+      <c r="I72" s="130"/>
       <c r="L72"/>
-      <c r="M72" s="63"/>
-      <c r="N72" s="64"/>
-      <c r="O72" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P72" s="66"/>
-      <c r="Q72" s="65"/>
-      <c r="R72" s="178" t="s">
-        <v>6</v>
-      </c>
-      <c r="S72" s="178"/>
-      <c r="T72" s="159"/>
-      <c r="U72" s="160"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="91"/>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="222"/>
+      <c r="S72" s="222"/>
+      <c r="T72" s="69"/>
+      <c r="U72" s="100"/>
       <c r="V72" s="55"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B73" s="55"/>
+      <c r="A73" s="53"/>
+      <c r="B73" s="94"/>
       <c r="C73" s="94"/>
-      <c r="D73" s="181"/>
-      <c r="E73" s="181"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73"/>
-      <c r="M73" s="89"/>
-      <c r="N73" s="90"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="91"/>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="173"/>
-      <c r="S73" s="173"/>
-      <c r="T73" s="69"/>
-      <c r="U73" s="100"/>
-      <c r="V73" s="55"/>
-    </row>
-    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="53"/>
-      <c r="B74" s="94"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="67"/>
-      <c r="I74" s="130"/>
-      <c r="L74" s="49" t="inlineStr">
+      <c r="L73" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">67890</t>
         </is>
       </c>
-      <c r="M74" s="89" t="inlineStr">
+      <c r="M73" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE UNO</t>
         </is>
       </c>
-      <c r="N74" s="90"/>
-      <c r="O74" s="18" t="s">
+      <c r="N73" s="90"/>
+      <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P74" s="91" t="inlineStr">
+      <c r="P73" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F001</t>
         </is>
       </c>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="222" t="s">
+        <v>10</v>
+      </c>
+      <c r="S73" s="222"/>
+      <c r="T73" s="69">
+        <v>150000</v>
+      </c>
+      <c r="U73" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banco Santander</t>
+        </is>
+      </c>
+      <c r="V73" s="55"/>
+    </row>
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L74" s="49"/>
+      <c r="M74" s="89"/>
+      <c r="N74" s="90"/>
+      <c r="O74" s="147"/>
+      <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="173" t="s">
-        <v>10</v>
-      </c>
-      <c r="S74" s="173"/>
-      <c r="T74" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U74" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
+      <c r="R74" s="222"/>
+      <c r="S74" s="222"/>
+      <c r="T74" s="69"/>
+      <c r="U74" s="100"/>
       <c r="V74" s="55"/>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L75" s="49"/>
-      <c r="M75" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE DOS</t>
-        </is>
-      </c>
-      <c r="O75" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
-      <c r="P75" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F002</t>
-        </is>
-      </c>
-      <c r="T75" s="69">
-        <v>250000</v>
-      </c>
+      <c r="M75" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="165"/>
+      <c r="P75" s="166"/>
+      <c r="Q75" s="167"/>
+      <c r="R75" s="223"/>
+      <c r="S75" s="223"/>
+      <c r="T75" s="220"/>
+      <c r="U75" s="221"/>
+      <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="49"/>
-      <c r="M76" s="89"/>
-      <c r="N76" s="90"/>
-      <c r="O76" s="147"/>
-      <c r="P76" s="91"/>
-      <c r="Q76" s="60"/>
-      <c r="R76" s="173"/>
-      <c r="S76" s="173"/>
-      <c r="T76" s="69"/>
-      <c r="U76" s="100"/>
+      <c r="M76" s="163" t="s">
+        <v>62</v>
+      </c>
+      <c r="N76" s="164"/>
+      <c r="O76" s="165"/>
+      <c r="P76" s="166"/>
+      <c r="Q76" s="167"/>
+      <c r="R76" s="168"/>
+      <c r="S76" s="168"/>
+      <c r="T76" s="220"/>
+      <c r="U76" s="221"/>
       <c r="V76" s="55"/>
     </row>
-    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L77" s="49"/>
-      <c r="M77" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="N77" s="164"/>
-      <c r="O77" s="165"/>
-      <c r="P77" s="166"/>
-      <c r="Q77" s="167"/>
-      <c r="R77" s="177"/>
-      <c r="S77" s="177"/>
-      <c r="T77" s="171"/>
-      <c r="U77" s="172"/>
+      <c r="M77" s="99"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="147"/>
+      <c r="P77" s="91"/>
+      <c r="Q77" s="60"/>
+      <c r="R77" s="60"/>
+      <c r="S77" s="60"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="100"/>
       <c r="V77" s="55"/>
     </row>
-    <row r="78" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L78" s="49"/>
-      <c r="M78" s="163" t="s">
-        <v>62</v>
-      </c>
-      <c r="N78" s="164"/>
-      <c r="O78" s="165"/>
-      <c r="P78" s="166"/>
-      <c r="Q78" s="167"/>
-      <c r="R78" s="168"/>
-      <c r="S78" s="168"/>
-      <c r="T78" s="171"/>
-      <c r="U78" s="172"/>
+      <c r="M78" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="107">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="101"/>
+      <c r="P78" s="103"/>
+      <c r="Q78" s="102"/>
+      <c r="R78" s="102"/>
+      <c r="S78" s="102"/>
+      <c r="T78" s="104"/>
+      <c r="U78" s="105"/>
       <c r="V78" s="55"/>
     </row>
-    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L79" s="49"/>
-      <c r="M79" s="99"/>
-      <c r="N79" s="68"/>
-      <c r="O79" s="147"/>
-      <c r="P79" s="91"/>
-      <c r="Q79" s="60"/>
-      <c r="R79" s="60"/>
-      <c r="S79" s="60"/>
-      <c r="T79" s="69"/>
-      <c r="U79" s="100"/>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
       <c r="V79" s="55"/>
     </row>
-    <row r="80" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L80" s="49"/>
-      <c r="M80" s="106" t="s">
-        <v>11</v>
-      </c>
-      <c r="N80" s="107">
-        <f>SUM(N78:N79)</f>
-        <v>0</v>
-      </c>
-      <c r="O80" s="101"/>
-      <c r="P80" s="103"/>
-      <c r="Q80" s="102"/>
-      <c r="R80" s="102"/>
-      <c r="S80" s="102"/>
-      <c r="T80" s="104"/>
-      <c r="U80" s="105"/>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="O80"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M81"/>
-      <c r="O81" s="5"/>
-      <c r="Q81"/>
-      <c r="S81"/>
-      <c r="T81" s="6"/>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
       <c r="V81" s="55"/>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O82"/>
+    <row r="82" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V82" s="55"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M83" s="23"/>
-      <c r="N83" s="23"/>
-      <c r="O83" s="23"/>
-      <c r="P83" s="23"/>
-      <c r="Q83" s="23"/>
       <c r="V83" s="55"/>
     </row>
     <row r="84" spans="13:22" x14ac:dyDescent="0.3">
@@ -9070,10 +8912,10 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
-    <row r="98" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V98" s="55"/>
     </row>
     <row r="99" spans="22:22" x14ac:dyDescent="0.3">
@@ -9118,14 +8960,62 @@
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
     </row>
-    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V113" s="55"/>
-    </row>
-    <row r="114" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V114" s="55"/>
-    </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="70">
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="O29:P29"/>
@@ -9142,62 +9032,6 @@
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
     <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="M70:U70"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="M68:O68"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="T78:U78"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R77:S77"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T77:U77"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D53:E53"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esteb\Documents\proyecto_cursor\proyectoisaqwenvisor\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A7AFC3-86CF-4750-953C-1C89BFCC1343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695E1391-83E3-46CC-9DD5-F4B9257BEDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
-    <sheet name="RUTA 12345" sheetId="2" r:id="rId6"/>
-    <sheet name="RUTA 67890" sheetId="3" r:id="rId7"/>
+    <sheet name="RUTA 111" sheetId="2" r:id="rId6"/>
+    <sheet name="RUTA 222" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="107">
   <si>
     <t>RECORRIDO</t>
   </si>
@@ -1034,7 +1034,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1483,24 +1483,126 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1513,12 +1615,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1549,102 +1645,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1986,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W113"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -2015,12 +2018,12 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PEREZ</t>
+          <t xml:space="preserve">ANA</t>
         </is>
       </c>
       <c r="C1" s="143" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA LOPEZ</t>
+          <t xml:space="preserve">BOB</t>
         </is>
       </c>
       <c r="D1" s="143"/>
@@ -2131,12 +2134,12 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">12345</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="C5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">67890</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="D5" s="154"/>
@@ -2165,10 +2168,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -2196,10 +2199,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C7" s="155">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="D7" s="155"/>
       <c r="E7" s="155"/>
@@ -2226,12 +2229,12 @@
       <c r="A8" s="127"/>
       <c r="B8" s="110" t="inlineStr">
         <is>
-          <t xml:space="preserve">12345 · JUAN PEREZ</t>
+          <t xml:space="preserve">111 · ANA</t>
         </is>
       </c>
       <c r="C8" s="123" t="inlineStr">
         <is>
-          <t xml:space="preserve">67890 · MARIA LOPEZ</t>
+          <t xml:space="preserve">222 · BOB</t>
         </is>
       </c>
       <c r="D8" s="110"/>
@@ -2260,10 +2263,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="171">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="C9" s="172">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="D9" s="173"/>
       <c r="E9" s="110"/>
@@ -2291,10 +2294,10 @@
         <v>54</v>
       </c>
       <c r="B10" s="171">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="C10" s="172">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="D10" s="173"/>
       <c r="E10" s="110"/>
@@ -2321,12 +2324,8 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="171">
-        <v>300000</v>
-      </c>
-      <c r="C11" s="172">
-        <v>300000</v>
-      </c>
+      <c r="B11" s="171"/>
+      <c r="C11" s="172"/>
       <c r="D11" s="173"/>
       <c r="E11" s="110"/>
       <c r="F11" s="119"/>
@@ -2752,24 +2751,24 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="M22" s="174" t="s">
+      <c r="M22" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
+      <c r="N22" s="215"/>
+      <c r="O22" s="215"/>
+      <c r="P22" s="215"/>
+      <c r="Q22" s="215"/>
+      <c r="R22" s="215"/>
+      <c r="S22" s="215"/>
+      <c r="T22" s="215"/>
+      <c r="U22" s="215"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="0">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="D23" s="6"/>
       <c r="J23"/>
@@ -2777,21 +2776,17 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-06-2026</t>
-        </is>
-      </c>
-      <c r="O23" s="189"/>
-      <c r="P23" s="189"/>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="190"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="223"/>
+      <c r="P23" s="223"/>
+      <c r="Q23" s="223"/>
+      <c r="R23" s="223"/>
+      <c r="S23" s="224"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -2799,34 +2794,34 @@
     </row>
     <row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
-        <v>900000</v>
+        <v>180000</v>
       </c>
       <c r="C24" s="18"/>
       <c r="J24"/>
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="191" t="s">
+      <c r="N24" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="192"/>
-      <c r="P24" s="192"/>
-      <c r="Q24" s="192"/>
-      <c r="R24" s="192"/>
-      <c r="S24" s="193"/>
+      <c r="O24" s="226"/>
+      <c r="P24" s="226"/>
+      <c r="Q24" s="226"/>
+      <c r="R24" s="226"/>
+      <c r="S24" s="227"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="W24" s="141">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="C25" s="111"/>
       <c r="D25" s="3" t="s">
@@ -2835,30 +2830,27 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="196" t="s">
+      <c r="M25" s="212" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="197"/>
-      <c r="O25" s="228"/>
-      <c r="P25" s="229"/>
-      <c r="Q25" s="171" t="s">
-        <v>94</v>
+      <c r="N25" s="213"/>
+      <c r="O25" s="174"/>
+      <c r="P25" s="175"/>
+      <c r="Q25" s="171">
+        <v>180000</v>
       </c>
       <c r="R25" s="172"/>
       <c r="S25" s="173"/>
-      <c r="T25" s="194" t="s">
+      <c r="T25" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="195"/>
+      <c r="U25" s="229"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B26" s="0">
-        <v>600000</v>
-      </c>
       <c r="E26" s="4"/>
       <c r="J26"/>
       <c r="L26"/>
@@ -2868,11 +2860,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="175" t="s">
-        <v>95</v>
-      </c>
-      <c r="R26" s="176"/>
-      <c r="S26" s="177"/>
+      <c r="Q26" s="203">
+        <v>20000</v>
+      </c>
+      <c r="R26" s="204"/>
+      <c r="S26" s="205"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -2890,20 +2882,18 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="179"/>
-      <c r="Q27" s="175" t="s">
-        <v>64</v>
-      </c>
-      <c r="R27" s="176"/>
-      <c r="S27" s="177"/>
-      <c r="T27" s="186" t="s">
+      <c r="O27" s="194"/>
+      <c r="P27" s="195"/>
+      <c r="Q27" s="203"/>
+      <c r="R27" s="204"/>
+      <c r="S27" s="205"/>
+      <c r="T27" s="220" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="187"/>
+      <c r="U27" s="221"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -2916,21 +2906,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="184" t="s">
+      <c r="M28" s="210" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="185"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="175" t="s">
-        <v>65</v>
-      </c>
-      <c r="R28" s="176"/>
-      <c r="S28" s="177"/>
-      <c r="T28" s="182" t="s">
+      <c r="N28" s="211"/>
+      <c r="O28" s="194"/>
+      <c r="P28" s="195"/>
+      <c r="Q28" s="203"/>
+      <c r="R28" s="204"/>
+      <c r="S28" s="205"/>
+      <c r="T28" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="183"/>
+      <c r="U28" s="219"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -2945,21 +2933,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="184" t="s">
+      <c r="M29" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="185"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179"/>
-      <c r="Q29" s="175" t="s">
-        <v>66</v>
-      </c>
-      <c r="R29" s="176"/>
-      <c r="S29" s="177"/>
-      <c r="T29" s="180" t="s">
+      <c r="N29" s="211"/>
+      <c r="O29" s="194"/>
+      <c r="P29" s="195"/>
+      <c r="Q29" s="203"/>
+      <c r="R29" s="204"/>
+      <c r="S29" s="205"/>
+      <c r="T29" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="181"/>
+      <c r="U29" s="217"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -2975,21 +2961,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="184" t="s">
+      <c r="M30" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="185"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="198"/>
-      <c r="Q30" s="175" t="s">
-        <v>67</v>
-      </c>
-      <c r="R30" s="176"/>
-      <c r="S30" s="177"/>
-      <c r="T30" s="199" t="s">
+      <c r="N30" s="211"/>
+      <c r="O30" s="194"/>
+      <c r="P30" s="214"/>
+      <c r="Q30" s="203"/>
+      <c r="R30" s="204"/>
+      <c r="S30" s="205"/>
+      <c r="T30" s="201" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="200"/>
+      <c r="U30" s="202"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -3006,17 +2990,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="184" t="s">
+      <c r="M31" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="185"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="175" t="s">
-        <v>68</v>
-      </c>
-      <c r="R31" s="176"/>
-      <c r="S31" s="177"/>
+      <c r="N31" s="211"/>
+      <c r="O31" s="194"/>
+      <c r="P31" s="195"/>
+      <c r="Q31" s="203"/>
+      <c r="R31" s="204"/>
+      <c r="S31" s="205"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -3031,17 +3013,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="184" t="s">
+      <c r="M32" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="185"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="175" t="s">
-        <v>69</v>
-      </c>
-      <c r="R32" s="176"/>
-      <c r="S32" s="177"/>
+      <c r="N32" s="211"/>
+      <c r="O32" s="194"/>
+      <c r="P32" s="195"/>
+      <c r="Q32" s="203"/>
+      <c r="R32" s="204"/>
+      <c r="S32" s="205"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -3063,13 +3043,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="178"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="175" t="s">
-        <v>70</v>
-      </c>
-      <c r="R33" s="176"/>
-      <c r="S33" s="177"/>
+      <c r="O33" s="194"/>
+      <c r="P33" s="195"/>
+      <c r="Q33" s="203"/>
+      <c r="R33" s="204"/>
+      <c r="S33" s="205"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -3088,17 +3066,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="204" t="s">
+      <c r="M34" s="206" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="205"/>
-      <c r="O34" s="206"/>
-      <c r="P34" s="207"/>
-      <c r="Q34" s="175">
-        <v>2000000</v>
-      </c>
-      <c r="R34" s="176"/>
-      <c r="S34" s="177"/>
+      <c r="N34" s="207"/>
+      <c r="O34" s="208"/>
+      <c r="P34" s="209"/>
+      <c r="Q34" s="203">
+        <v>1000000</v>
+      </c>
+      <c r="R34" s="204"/>
+      <c r="S34" s="205"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -3116,23 +3094,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="217" t="s">
+      <c r="M35" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="218"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="202" t="s">
+      <c r="N35" s="190"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="203"/>
-      <c r="R35" s="202" t="s">
+      <c r="Q35" s="188"/>
+      <c r="R35" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="203"/>
-      <c r="T35" s="202" t="s">
+      <c r="S35" s="188"/>
+      <c r="T35" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="203"/>
+      <c r="U35" s="188"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -3188,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="148">
-        <f>SUM(O42)</f>
+        <f>SUM(O41)</f>
         <v>0</v>
       </c>
       <c r="L37"/>
@@ -3214,11 +3192,11 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="208" t="s">
+      <c r="M38" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="226"/>
-      <c r="O38" s="227"/>
+      <c r="N38" s="179"/>
+      <c r="O38" s="230"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -3240,19 +3218,9 @@
       <c r="L39" s="114">
         <v>3</v>
       </c>
-      <c r="M39" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-01-2026</t>
-        </is>
-      </c>
-      <c r="N39" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O39" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M39" s="37"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="39"/>
       <c r="P39" s="42"/>
       <c r="Q39" s="72"/>
       <c r="R39" s="44"/>
@@ -3262,31 +3230,39 @@
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M40" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-01-2026</t>
-        </is>
-      </c>
-      <c r="N40" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O40" s="39">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="20"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="47"/>
+      <c r="I40" s="134"/>
+      <c r="J40"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="114">
+        <v>4</v>
+      </c>
+      <c r="M40" s="37"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="44"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="20"/>
       <c r="C41" s="32"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="47"/>
-      <c r="I41" s="134"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="I41" s="133"/>
       <c r="J41"/>
       <c r="K41" s="24"/>
       <c r="L41" s="114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" s="37"/>
       <c r="N41" s="38"/>
@@ -3300,16 +3276,16 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B42" s="20"/>
-      <c r="C42" s="32"/>
+      <c r="C42" s="25"/>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
-      <c r="I42" s="133"/>
-      <c r="J42"/>
-      <c r="K42" s="24"/>
+      <c r="F42" s="51"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="57"/>
       <c r="L42" s="114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
@@ -3317,51 +3293,52 @@
       <c r="P42" s="42"/>
       <c r="Q42" s="70"/>
       <c r="R42" s="44"/>
-      <c r="S42" s="78"/>
+      <c r="S42" s="77"/>
       <c r="T42" s="42"/>
       <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="112"/>
       <c r="B43" s="20"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="192"/>
       <c r="F43" s="51"/>
-      <c r="I43" s="135"/>
+      <c r="G43" s="8"/>
+      <c r="I43" s="136"/>
       <c r="J43" s="57"/>
+      <c r="K43" s="24" t="e">
+        <f>O38+O65</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L43" s="114">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="70"/>
-      <c r="R43" s="44"/>
-      <c r="S43" s="77"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="71"/>
       <c r="T43" s="42"/>
       <c r="U43" s="72"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A44" s="112"/>
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25"/>
       <c r="B44" s="20"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="201"/>
-      <c r="E44" s="201"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="8"/>
-      <c r="I44" s="136"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="192"/>
+      <c r="E44" s="192"/>
+      <c r="F44" s="52"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="13"/>
       <c r="J44" s="57"/>
-      <c r="K44" s="24" t="e">
-        <f>O38+O66</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="K44" s="24"/>
       <c r="L44" s="114">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
@@ -3373,19 +3350,18 @@
       <c r="T44" s="42"/>
       <c r="U44" s="72"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" s="25"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="201"/>
-      <c r="E45" s="201"/>
-      <c r="F45" s="52"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="192"/>
+      <c r="E45" s="192"/>
+      <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
       <c r="J45" s="57"/>
-      <c r="K45" s="24"/>
       <c r="L45" s="114">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
@@ -3393,22 +3369,22 @@
       <c r="P45" s="42"/>
       <c r="Q45" s="70"/>
       <c r="R45" s="42"/>
-      <c r="S45" s="71"/>
+      <c r="S45" s="76"/>
       <c r="T45" s="42"/>
       <c r="U45" s="72"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="201"/>
-      <c r="E46" s="201"/>
-      <c r="F46" s="23"/>
+      <c r="D46" s="192"/>
+      <c r="E46" s="192"/>
+      <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
       <c r="J46" s="57"/>
       <c r="L46" s="114">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
@@ -3416,7 +3392,7 @@
       <c r="P46" s="42"/>
       <c r="Q46" s="70"/>
       <c r="R46" s="42"/>
-      <c r="S46" s="76"/>
+      <c r="S46" s="71"/>
       <c r="T46" s="42"/>
       <c r="U46" s="72"/>
     </row>
@@ -3424,14 +3400,19 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="201"/>
-      <c r="E47" s="201"/>
-      <c r="F47" s="53"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="1"/>
       <c r="H47" s="68"/>
       <c r="I47" s="13"/>
       <c r="J47" s="57"/>
+      <c r="K47" s="24" t="e">
+        <f>Q34-U24</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="L47" s="114">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
@@ -3447,19 +3428,15 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="201"/>
-      <c r="E48" s="201"/>
-      <c r="F48" s="17"/>
+      <c r="D48" s="192"/>
+      <c r="E48" s="192"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
       <c r="I48" s="13"/>
       <c r="J48" s="57"/>
-      <c r="K48" s="24" t="e">
-        <f>Q34-U24</f>
-        <v>#VALUE!</v>
-      </c>
       <c r="L48" s="114">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
@@ -3468,22 +3445,22 @@
       <c r="Q48" s="70"/>
       <c r="R48" s="42"/>
       <c r="S48" s="71"/>
-      <c r="T48" s="42"/>
+      <c r="T48" s="44"/>
       <c r="U48" s="72"/>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="201"/>
-      <c r="E49" s="201"/>
+      <c r="D49" s="192"/>
+      <c r="E49" s="192"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="68"/>
+      <c r="H49" s="50"/>
       <c r="I49" s="13"/>
       <c r="J49" s="57"/>
       <c r="L49" s="114">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
@@ -3499,15 +3476,15 @@
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="43"/>
-      <c r="D50" s="201"/>
-      <c r="E50" s="201"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="25"/>
       <c r="F50" s="23"/>
       <c r="G50" s="1"/>
       <c r="H50" s="50"/>
       <c r="I50" s="13"/>
       <c r="J50" s="57"/>
       <c r="L50" s="114">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
@@ -3523,20 +3500,20 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="25"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
       <c r="I51" s="13"/>
       <c r="J51" s="57"/>
       <c r="L51" s="114">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="42"/>
+      <c r="P51" s="40"/>
       <c r="Q51" s="70"/>
       <c r="R51" s="42"/>
       <c r="S51" s="71"/>
@@ -3545,17 +3522,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
+      <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="213"/>
-      <c r="E52" s="213"/>
+      <c r="D52" s="177"/>
+      <c r="E52" s="177"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
-      <c r="I52" s="13"/>
+      <c r="I52" s="54"/>
       <c r="J52" s="57"/>
       <c r="L52" s="114">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
@@ -3568,23 +3545,21 @@
       <c r="U52" s="72"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="20"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="225"/>
-      <c r="E53" s="225"/>
+      <c r="D53" s="176"/>
+      <c r="E53" s="176"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
       <c r="I53" s="54"/>
       <c r="J53" s="57"/>
-      <c r="L53" s="114">
-        <v>16</v>
-      </c>
+      <c r="L53" s="18"/>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="40"/>
+      <c r="P53" s="42"/>
       <c r="Q53" s="70"/>
       <c r="R53" s="42"/>
       <c r="S53" s="71"/>
@@ -3592,11 +3567,11 @@
       <c r="U53" s="72"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="25"/>
+      <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="212"/>
-      <c r="E54" s="212"/>
+      <c r="D54" s="176"/>
+      <c r="E54" s="176"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -3617,8 +3592,8 @@
       <c r="A55" s="20"/>
       <c r="B55" s="55"/>
       <c r="C55" s="43"/>
-      <c r="D55" s="212"/>
-      <c r="E55" s="212"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="50"/>
@@ -3637,7 +3612,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
-      <c r="B56" s="55"/>
+      <c r="B56"/>
       <c r="C56" s="43"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
@@ -3724,11 +3699,11 @@
       <c r="U59" s="72"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="20"/>
+      <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
+      <c r="D60" s="176"/>
+      <c r="E60" s="176"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -3749,8 +3724,8 @@
       <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="43"/>
-      <c r="D61" s="212"/>
-      <c r="E61" s="212"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="50"/>
@@ -3761,9 +3736,9 @@
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
       <c r="P61" s="42"/>
-      <c r="Q61" s="70"/>
-      <c r="R61" s="42"/>
-      <c r="S61" s="71"/>
+      <c r="Q61" s="161"/>
+      <c r="R61" s="93"/>
+      <c r="S61" s="92"/>
       <c r="T61" s="44"/>
       <c r="U61" s="72"/>
     </row>
@@ -3811,12 +3786,12 @@
       <c r="T63" s="44"/>
       <c r="U63" s="72"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
+      <c r="D64" s="176"/>
+      <c r="E64" s="176"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -3827,394 +3802,341 @@
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
       <c r="P64" s="42"/>
-      <c r="Q64" s="161"/>
+      <c r="Q64" s="88"/>
       <c r="R64" s="93"/>
       <c r="S64" s="92"/>
       <c r="T64" s="44"/>
-      <c r="U64" s="72"/>
-    </row>
-    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U64" s="75"/>
+    </row>
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
-      <c r="F65" s="23"/>
+      <c r="D65" s="176"/>
+      <c r="E65" s="176"/>
+      <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="37"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="42"/>
-      <c r="Q65" s="88"/>
-      <c r="R65" s="93"/>
-      <c r="S65" s="92"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="75"/>
-    </row>
-    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65"/>
+      <c r="M65" s="178" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="193"/>
+      <c r="O65" s="46"/>
+      <c r="P65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="46"/>
+      <c r="R65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="S65" s="46"/>
+      <c r="T65" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="46"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="212"/>
-      <c r="E66" s="212"/>
-      <c r="F66" s="20"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="176"/>
+      <c r="E66" s="176"/>
+      <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
       <c r="I66" s="54"/>
-      <c r="J66" s="57"/>
+      <c r="J66"/>
       <c r="L66"/>
-      <c r="M66" s="208" t="s">
-        <v>34</v>
-      </c>
-      <c r="N66" s="209"/>
-      <c r="O66" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="P66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q66" s="46"/>
-      <c r="R66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="S66" s="46"/>
-      <c r="T66" s="56" t="s">
-        <v>11</v>
-      </c>
-      <c r="U66" s="46"/>
-    </row>
-    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="58"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="74"/>
+      <c r="P66" s="23"/>
+      <c r="Q66" s="73"/>
+      <c r="R66" s="74"/>
+      <c r="S66" s="74"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="95"/>
-      <c r="D67" s="212"/>
-      <c r="E67" s="212"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="50"/>
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="58"/>
-      <c r="N67" s="59"/>
-      <c r="O67" s="74"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="73"/>
-      <c r="R67" s="74"/>
-      <c r="S67" s="74"/>
-      <c r="T67" s="6"/>
-    </row>
-    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="181" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="182"/>
+      <c r="O67" s="188"/>
+      <c r="P67" s="199"/>
+      <c r="Q67" s="200"/>
+      <c r="R67" s="181" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="182"/>
+      <c r="T67" s="196" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U67" s="197"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="23"/>
+      <c r="D68" s="176"/>
+      <c r="E68" s="176"/>
+      <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
       <c r="I68" s="54"/>
       <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="202" t="s">
-        <v>47</v>
-      </c>
-      <c r="N68" s="216"/>
-      <c r="O68" s="203"/>
-      <c r="P68" s="214"/>
-      <c r="Q68" s="215"/>
-      <c r="R68" s="202" t="s">
-        <v>37</v>
-      </c>
-      <c r="S68" s="216"/>
-      <c r="T68" s="210" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U68" s="211"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="87"/>
+      <c r="O68" s="87"/>
+      <c r="P68" s="61"/>
+      <c r="Q68" s="62"/>
+      <c r="R68" s="62"/>
+      <c r="S68" s="62"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
     </row>
     <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69"/>
+      <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="212"/>
-      <c r="E69" s="212"/>
+      <c r="D69" s="176"/>
+      <c r="E69" s="176"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="87"/>
-      <c r="O69" s="87"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="62"/>
-      <c r="R69" s="62"/>
-      <c r="S69" s="62"/>
-      <c r="T69" s="60"/>
-      <c r="U69" s="60"/>
-    </row>
-    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="178" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
+      <c r="R69" s="179"/>
+      <c r="S69" s="179"/>
+      <c r="T69" s="179"/>
+      <c r="U69" s="180"/>
+      <c r="V69" s="55"/>
+    </row>
+    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="95"/>
+      <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="212"/>
-      <c r="E70" s="212"/>
+      <c r="D70" s="176"/>
+      <c r="E70" s="176"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
       <c r="I70" s="54"/>
       <c r="J70"/>
-      <c r="L70"/>
-      <c r="M70" s="208" t="s">
-        <v>35</v>
-      </c>
-      <c r="N70" s="226"/>
-      <c r="O70" s="226"/>
-      <c r="P70" s="226"/>
-      <c r="Q70" s="226"/>
-      <c r="R70" s="226"/>
-      <c r="S70" s="226"/>
-      <c r="T70" s="226"/>
-      <c r="U70" s="227"/>
-      <c r="V70" s="55"/>
-    </row>
-    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L70" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="157"/>
+      <c r="O70" s="157"/>
+      <c r="P70" s="157" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q70" s="157"/>
+      <c r="R70" s="157"/>
+      <c r="S70" s="157"/>
+      <c r="T70" s="157" t="s">
+        <v>57</v>
+      </c>
+      <c r="U70" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="V70" s="170" t="s">
+        <v>58</v>
+      </c>
+      <c r="W70" s="170" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="25"/>
-      <c r="B71" s="20"/>
+      <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="212"/>
-      <c r="E71" s="212"/>
+      <c r="D71" s="176"/>
+      <c r="E71" s="176"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
       <c r="I71" s="54"/>
-      <c r="J71"/>
-      <c r="L71" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="M71" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="N71" s="157"/>
-      <c r="O71" s="157"/>
-      <c r="P71" s="157" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q71" s="157"/>
-      <c r="R71" s="157"/>
-      <c r="S71" s="157"/>
-      <c r="T71" s="157" t="s">
-        <v>57</v>
-      </c>
-      <c r="U71" s="158" t="s">
-        <v>60</v>
-      </c>
-      <c r="V71" s="170" t="s">
-        <v>58</v>
-      </c>
-      <c r="W71" s="170" t="s">
-        <v>50</v>
-      </c>
+      <c r="J71" s="23"/>
+      <c r="L71"/>
+      <c r="M71" s="63"/>
+      <c r="N71" s="64"/>
+      <c r="O71" s="169" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="66"/>
+      <c r="Q71" s="65"/>
+      <c r="R71" s="187" t="s">
+        <v>6</v>
+      </c>
+      <c r="S71" s="187"/>
+      <c r="T71" s="159"/>
+      <c r="U71" s="160"/>
+      <c r="V71" s="55"/>
     </row>
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="25"/>
-      <c r="B72" s="130"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="212"/>
-      <c r="E72" s="212"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="94"/>
+      <c r="D72" s="176"/>
+      <c r="E72" s="176"/>
       <c r="F72" s="67"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="50"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="23"/>
+      <c r="I72" s="130"/>
       <c r="L72"/>
-      <c r="M72" s="63"/>
-      <c r="N72" s="64"/>
-      <c r="O72" s="169" t="s">
-        <v>43</v>
-      </c>
-      <c r="P72" s="66"/>
-      <c r="Q72" s="65"/>
-      <c r="R72" s="224" t="s">
-        <v>6</v>
-      </c>
-      <c r="S72" s="224"/>
-      <c r="T72" s="159"/>
-      <c r="U72" s="160"/>
+      <c r="M72" s="89"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="91"/>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="185"/>
+      <c r="S72" s="185"/>
+      <c r="T72" s="69"/>
+      <c r="U72" s="100"/>
       <c r="V72" s="55"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B73" s="55"/>
+      <c r="A73" s="53"/>
+      <c r="B73" s="94"/>
       <c r="C73" s="94"/>
-      <c r="D73" s="212"/>
-      <c r="E73" s="212"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73"/>
+      <c r="L73" s="49"/>
       <c r="M73" s="89"/>
       <c r="N73" s="90"/>
-      <c r="O73" s="18"/>
+      <c r="O73" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="P73" s="91"/>
       <c r="Q73" s="60"/>
-      <c r="R73" s="222"/>
-      <c r="S73" s="222"/>
+      <c r="R73" s="185" t="s">
+        <v>10</v>
+      </c>
+      <c r="S73" s="185"/>
       <c r="T73" s="69"/>
       <c r="U73" s="100"/>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="53"/>
-      <c r="B74" s="94"/>
-      <c r="C74" s="94"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="67"/>
-      <c r="I74" s="130"/>
-      <c r="L74" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12345</t>
-        </is>
-      </c>
-      <c r="M74" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
+      <c r="L74" s="49"/>
+      <c r="M74" s="89"/>
       <c r="N74" s="90"/>
-      <c r="O74" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P74" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
+      <c r="O74" s="147"/>
+      <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="222" t="s">
-        <v>10</v>
-      </c>
-      <c r="S74" s="222"/>
-      <c r="T74" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U74" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Banco Santander</t>
-        </is>
-      </c>
+      <c r="R74" s="185"/>
+      <c r="S74" s="185"/>
+      <c r="T74" s="69"/>
+      <c r="U74" s="100"/>
       <c r="V74" s="55"/>
     </row>
     <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L75" s="49"/>
-      <c r="M75" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
-      <c r="N75" s="90"/>
-      <c r="O75" s="147"/>
-      <c r="P75" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="222"/>
-      <c r="S75" s="222"/>
-      <c r="T75" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U75" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Banco Santander</t>
-        </is>
-      </c>
+      <c r="M75" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="165"/>
+      <c r="P75" s="166"/>
+      <c r="Q75" s="167"/>
+      <c r="R75" s="186"/>
+      <c r="S75" s="186"/>
+      <c r="T75" s="183"/>
+      <c r="U75" s="184"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="49"/>
       <c r="M76" s="163" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N76" s="164"/>
       <c r="O76" s="165"/>
       <c r="P76" s="166"/>
       <c r="Q76" s="167"/>
-      <c r="R76" s="223"/>
-      <c r="S76" s="223"/>
-      <c r="T76" s="220"/>
-      <c r="U76" s="221"/>
+      <c r="R76" s="168"/>
+      <c r="S76" s="168"/>
+      <c r="T76" s="183"/>
+      <c r="U76" s="184"/>
       <c r="V76" s="55"/>
     </row>
-    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L77" s="49"/>
-      <c r="M77" s="163" t="s">
-        <v>62</v>
-      </c>
-      <c r="N77" s="164"/>
-      <c r="O77" s="165"/>
-      <c r="P77" s="166"/>
-      <c r="Q77" s="167"/>
-      <c r="R77" s="168"/>
-      <c r="S77" s="168"/>
-      <c r="T77" s="220"/>
-      <c r="U77" s="221"/>
+      <c r="M77" s="99"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="147"/>
+      <c r="P77" s="91"/>
+      <c r="Q77" s="60"/>
+      <c r="R77" s="60"/>
+      <c r="S77" s="60"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="100"/>
       <c r="V77" s="55"/>
     </row>
     <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L78" s="49"/>
-      <c r="M78" s="99"/>
-      <c r="N78" s="68"/>
-      <c r="O78" s="147"/>
-      <c r="P78" s="91"/>
-      <c r="Q78" s="60"/>
-      <c r="R78" s="60"/>
-      <c r="S78" s="60"/>
-      <c r="T78" s="69"/>
-      <c r="U78" s="100"/>
+      <c r="M78" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="107">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="101"/>
+      <c r="P78" s="103"/>
+      <c r="Q78" s="102"/>
+      <c r="R78" s="102"/>
+      <c r="S78" s="102"/>
+      <c r="T78" s="104"/>
+      <c r="U78" s="105"/>
       <c r="V78" s="55"/>
     </row>
-    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L79" s="49"/>
-      <c r="M79" s="106" t="s">
-        <v>11</v>
-      </c>
-      <c r="N79" s="107">
-        <f>SUM(N77:N78)</f>
-        <v>0</v>
-      </c>
-      <c r="O79" s="101"/>
-      <c r="P79" s="103"/>
-      <c r="Q79" s="102"/>
-      <c r="R79" s="102"/>
-      <c r="S79" s="102"/>
-      <c r="T79" s="104"/>
-      <c r="U79" s="105"/>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
       <c r="V79" s="55"/>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M80"/>
-      <c r="O80" s="5"/>
-      <c r="Q80"/>
-      <c r="S80"/>
-      <c r="T80" s="6"/>
+      <c r="O80"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O81"/>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
       <c r="V81" s="55"/>
     </row>
     <row r="82" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M82" s="23"/>
-      <c r="N82" s="23"/>
-      <c r="O82" s="23"/>
-      <c r="P82" s="23"/>
-      <c r="Q82" s="23"/>
       <c r="V82" s="55"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
@@ -4259,7 +4181,7 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
     <row r="98" spans="22:22" x14ac:dyDescent="0.3">
@@ -4307,62 +4229,12 @@
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
     </row>
-    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V113" s="55"/>
-    </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="M70:U70"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="T77:U77"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="M68:O68"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M38:N38"/>
     <mergeCell ref="M25:N25"/>
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="Q30:S30"/>
@@ -4379,9 +4251,56 @@
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="T27:U27"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -4420,7 +4339,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PEREZ</t>
+          <t xml:space="preserve">ANA</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -4538,7 +4457,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">12345</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -4568,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -4597,7 +4516,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -4651,7 +4570,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="171">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="C9" s="172"/>
       <c r="D9" s="173"/>
@@ -4680,7 +4599,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="171">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="C10" s="172"/>
       <c r="D10" s="173"/>
@@ -4708,9 +4627,7 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="171">
-        <v>300000</v>
-      </c>
+      <c r="B11" s="171"/>
       <c r="C11" s="172"/>
       <c r="D11" s="173"/>
       <c r="E11" s="110"/>
@@ -5133,17 +5050,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="174" t="s">
+      <c r="M22" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
+      <c r="N22" s="215"/>
+      <c r="O22" s="215"/>
+      <c r="P22" s="215"/>
+      <c r="Q22" s="215"/>
+      <c r="R22" s="215"/>
+      <c r="S22" s="215"/>
+      <c r="T22" s="215"/>
+      <c r="U22" s="215"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -5152,21 +5069,17 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-06-2026</t>
-        </is>
-      </c>
-      <c r="O23" s="189"/>
-      <c r="P23" s="189"/>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="190"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="223"/>
+      <c r="P23" s="223"/>
+      <c r="Q23" s="223"/>
+      <c r="R23" s="223"/>
+      <c r="S23" s="224"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -5179,22 +5092,22 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="191" t="s">
+      <c r="N24" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="192"/>
-      <c r="P24" s="192"/>
-      <c r="Q24" s="192"/>
-      <c r="R24" s="192"/>
-      <c r="S24" s="193"/>
+      <c r="O24" s="226"/>
+      <c r="P24" s="226"/>
+      <c r="Q24" s="226"/>
+      <c r="R24" s="226"/>
+      <c r="S24" s="227"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="W24" s="141">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -5206,21 +5119,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="196" t="s">
+      <c r="M25" s="212" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="197"/>
-      <c r="O25" s="228"/>
-      <c r="P25" s="229"/>
+      <c r="N25" s="213"/>
+      <c r="O25" s="174"/>
+      <c r="P25" s="175"/>
       <c r="Q25" s="171">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="R25" s="172"/>
       <c r="S25" s="173"/>
-      <c r="T25" s="194" t="s">
+      <c r="T25" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="195"/>
+      <c r="U25" s="229"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -5236,11 +5149,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="175">
-        <v>50000</v>
-      </c>
-      <c r="R26" s="176"/>
-      <c r="S26" s="177"/>
+      <c r="Q26" s="203">
+        <v>10000</v>
+      </c>
+      <c r="R26" s="204"/>
+      <c r="S26" s="205"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -5258,20 +5171,18 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="179"/>
-      <c r="Q27" s="175">
-        <v>300000</v>
-      </c>
-      <c r="R27" s="176"/>
-      <c r="S27" s="177"/>
-      <c r="T27" s="186" t="s">
+      <c r="O27" s="194"/>
+      <c r="P27" s="195"/>
+      <c r="Q27" s="203"/>
+      <c r="R27" s="204"/>
+      <c r="S27" s="205"/>
+      <c r="T27" s="220" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="187"/>
+      <c r="U27" s="221"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -5284,19 +5195,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="184" t="s">
+      <c r="M28" s="210" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="185"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="175"/>
-      <c r="R28" s="176"/>
-      <c r="S28" s="177"/>
-      <c r="T28" s="182" t="s">
+      <c r="N28" s="211"/>
+      <c r="O28" s="194"/>
+      <c r="P28" s="195"/>
+      <c r="Q28" s="203"/>
+      <c r="R28" s="204"/>
+      <c r="S28" s="205"/>
+      <c r="T28" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="183"/>
+      <c r="U28" s="219"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -5311,19 +5222,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="184" t="s">
+      <c r="M29" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="185"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179"/>
-      <c r="Q29" s="175"/>
-      <c r="R29" s="176"/>
-      <c r="S29" s="177"/>
-      <c r="T29" s="180" t="s">
+      <c r="N29" s="211"/>
+      <c r="O29" s="194"/>
+      <c r="P29" s="195"/>
+      <c r="Q29" s="203"/>
+      <c r="R29" s="204"/>
+      <c r="S29" s="205"/>
+      <c r="T29" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="181"/>
+      <c r="U29" s="217"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -5339,19 +5250,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="184" t="s">
+      <c r="M30" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="185"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="198"/>
-      <c r="Q30" s="175"/>
-      <c r="R30" s="176"/>
-      <c r="S30" s="177"/>
-      <c r="T30" s="199" t="s">
+      <c r="N30" s="211"/>
+      <c r="O30" s="194"/>
+      <c r="P30" s="214"/>
+      <c r="Q30" s="203"/>
+      <c r="R30" s="204"/>
+      <c r="S30" s="205"/>
+      <c r="T30" s="201" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="200"/>
+      <c r="U30" s="202"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -5368,15 +5279,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="184" t="s">
+      <c r="M31" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="185"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="175"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="177"/>
+      <c r="N31" s="211"/>
+      <c r="O31" s="194"/>
+      <c r="P31" s="195"/>
+      <c r="Q31" s="203"/>
+      <c r="R31" s="204"/>
+      <c r="S31" s="205"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -5391,15 +5302,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="184" t="s">
+      <c r="M32" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="185"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="175"/>
-      <c r="R32" s="176"/>
-      <c r="S32" s="177"/>
+      <c r="N32" s="211"/>
+      <c r="O32" s="194"/>
+      <c r="P32" s="195"/>
+      <c r="Q32" s="203"/>
+      <c r="R32" s="204"/>
+      <c r="S32" s="205"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -5421,11 +5332,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="178"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="175"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="177"/>
+      <c r="O33" s="194"/>
+      <c r="P33" s="195"/>
+      <c r="Q33" s="203"/>
+      <c r="R33" s="204"/>
+      <c r="S33" s="205"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -5444,17 +5355,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="204" t="s">
+      <c r="M34" s="206" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="205"/>
-      <c r="O34" s="206"/>
-      <c r="P34" s="207"/>
-      <c r="Q34" s="175">
-        <v>1000000</v>
-      </c>
-      <c r="R34" s="176"/>
-      <c r="S34" s="177"/>
+      <c r="N34" s="207"/>
+      <c r="O34" s="208"/>
+      <c r="P34" s="209"/>
+      <c r="Q34" s="203">
+        <v>500000</v>
+      </c>
+      <c r="R34" s="204"/>
+      <c r="S34" s="205"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -5472,23 +5383,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="217" t="s">
+      <c r="M35" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="218"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="202" t="s">
+      <c r="N35" s="190"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="203"/>
-      <c r="R35" s="202" t="s">
+      <c r="Q35" s="188"/>
+      <c r="R35" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="203"/>
-      <c r="T35" s="202" t="s">
+      <c r="S35" s="188"/>
+      <c r="T35" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="203"/>
+      <c r="U35" s="188"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -5570,11 +5481,11 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="208" t="s">
+      <c r="M38" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="226"/>
-      <c r="O38" s="227"/>
+      <c r="N38" s="179"/>
+      <c r="O38" s="230"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -5596,19 +5507,9 @@
       <c r="L39" s="114">
         <v>3</v>
       </c>
-      <c r="M39" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-01-2026</t>
-        </is>
-      </c>
-      <c r="N39" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O39" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M39" s="37"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="39"/>
       <c r="P39" s="42"/>
       <c r="Q39" s="72"/>
       <c r="R39" s="44"/>
@@ -5691,8 +5592,8 @@
       <c r="A43" s="112"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="201"/>
-      <c r="E43" s="201"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="192"/>
       <c r="F43" s="51"/>
       <c r="G43" s="8"/>
       <c r="I43" s="136"/>
@@ -5718,8 +5619,8 @@
       <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="201"/>
-      <c r="E44" s="201"/>
+      <c r="D44" s="192"/>
+      <c r="E44" s="192"/>
       <c r="F44" s="52"/>
       <c r="H44" s="68"/>
       <c r="I44" s="13"/>
@@ -5742,8 +5643,8 @@
       <c r="A45" s="25"/>
       <c r="B45" s="25"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="201"/>
-      <c r="E45" s="201"/>
+      <c r="D45" s="192"/>
+      <c r="E45" s="192"/>
       <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
@@ -5765,8 +5666,8 @@
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="201"/>
-      <c r="E46" s="201"/>
+      <c r="D46" s="192"/>
+      <c r="E46" s="192"/>
       <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
@@ -5788,8 +5689,8 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="201"/>
-      <c r="E47" s="201"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
       <c r="H47" s="68"/>
@@ -5816,8 +5717,8 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="201"/>
-      <c r="E48" s="201"/>
+      <c r="D48" s="192"/>
+      <c r="E48" s="192"/>
       <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
@@ -5840,8 +5741,8 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="201"/>
-      <c r="E49" s="201"/>
+      <c r="D49" s="192"/>
+      <c r="E49" s="192"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
       <c r="H49" s="50"/>
@@ -5888,8 +5789,8 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="213"/>
-      <c r="E51" s="213"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
@@ -5912,8 +5813,8 @@
       <c r="A52" s="20"/>
       <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="225"/>
-      <c r="E52" s="225"/>
+      <c r="D52" s="177"/>
+      <c r="E52" s="177"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
@@ -5936,8 +5837,8 @@
       <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="212"/>
-      <c r="E53" s="212"/>
+      <c r="D53" s="176"/>
+      <c r="E53" s="176"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
@@ -5958,8 +5859,8 @@
       <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="212"/>
-      <c r="E54" s="212"/>
+      <c r="D54" s="176"/>
+      <c r="E54" s="176"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -6090,8 +5991,8 @@
       <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="212"/>
-      <c r="E60" s="212"/>
+      <c r="D60" s="176"/>
+      <c r="E60" s="176"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -6178,8 +6079,8 @@
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
+      <c r="D64" s="176"/>
+      <c r="E64" s="176"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -6200,18 +6101,18 @@
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
+      <c r="D65" s="176"/>
+      <c r="E65" s="176"/>
       <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
       <c r="L65"/>
-      <c r="M65" s="208" t="s">
+      <c r="M65" s="178" t="s">
         <v>34</v>
       </c>
-      <c r="N65" s="209"/>
+      <c r="N65" s="193"/>
       <c r="O65" s="46"/>
       <c r="P65" s="56" t="s">
         <v>11</v>
@@ -6230,8 +6131,8 @@
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="95"/>
-      <c r="D66" s="212"/>
-      <c r="E66" s="212"/>
+      <c r="D66" s="176"/>
+      <c r="E66" s="176"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
@@ -6259,28 +6160,28 @@
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="202" t="s">
+      <c r="M67" s="181" t="s">
         <v>47</v>
       </c>
-      <c r="N67" s="216"/>
-      <c r="O67" s="203"/>
-      <c r="P67" s="214"/>
-      <c r="Q67" s="215"/>
-      <c r="R67" s="202" t="s">
+      <c r="N67" s="182"/>
+      <c r="O67" s="188"/>
+      <c r="P67" s="199"/>
+      <c r="Q67" s="200"/>
+      <c r="R67" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="216"/>
-      <c r="T67" s="210" t="str">
+      <c r="S67" s="182"/>
+      <c r="T67" s="196" t="str">
         <f>Q25</f>
       </c>
-      <c r="U67" s="211"/>
+      <c r="U67" s="197"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
+      <c r="D68" s="176"/>
+      <c r="E68" s="176"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
@@ -6301,33 +6202,33 @@
       <c r="A69" s="25"/>
       <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="212"/>
-      <c r="E69" s="212"/>
+      <c r="D69" s="176"/>
+      <c r="E69" s="176"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="208" t="s">
+      <c r="M69" s="178" t="s">
         <v>35</v>
       </c>
-      <c r="N69" s="226"/>
-      <c r="O69" s="226"/>
-      <c r="P69" s="226"/>
-      <c r="Q69" s="226"/>
-      <c r="R69" s="226"/>
-      <c r="S69" s="226"/>
-      <c r="T69" s="226"/>
-      <c r="U69" s="227"/>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
+      <c r="R69" s="179"/>
+      <c r="S69" s="179"/>
+      <c r="T69" s="179"/>
+      <c r="U69" s="180"/>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
       <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="212"/>
-      <c r="E70" s="212"/>
+      <c r="D70" s="176"/>
+      <c r="E70" s="176"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
@@ -6364,8 +6265,8 @@
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="212"/>
-      <c r="E71" s="212"/>
+      <c r="D71" s="176"/>
+      <c r="E71" s="176"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
@@ -6379,10 +6280,10 @@
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="65"/>
-      <c r="R71" s="224" t="s">
+      <c r="R71" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="S71" s="224"/>
+      <c r="S71" s="187"/>
       <c r="T71" s="159"/>
       <c r="U71" s="160"/>
       <c r="V71" s="55"/>
@@ -6390,8 +6291,8 @@
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" s="55"/>
       <c r="C72" s="94"/>
-      <c r="D72" s="212"/>
-      <c r="E72" s="212"/>
+      <c r="D72" s="176"/>
+      <c r="E72" s="176"/>
       <c r="F72" s="67"/>
       <c r="I72" s="130"/>
       <c r="L72"/>
@@ -6400,8 +6301,8 @@
       <c r="O72" s="18"/>
       <c r="P72" s="91"/>
       <c r="Q72" s="60"/>
-      <c r="R72" s="222"/>
-      <c r="S72" s="222"/>
+      <c r="R72" s="185"/>
+      <c r="S72" s="185"/>
       <c r="T72" s="69"/>
       <c r="U72" s="100"/>
       <c r="V72" s="55"/>
@@ -6414,38 +6315,20 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12345</t>
-        </is>
-      </c>
-      <c r="M73" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
+      <c r="L73" s="49"/>
+      <c r="M73" s="89"/>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
+      <c r="P73" s="91"/>
       <c r="Q73" s="60"/>
-      <c r="R73" s="222" t="s">
+      <c r="R73" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="222"/>
-      <c r="T73" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U73" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Banco Santander</t>
-        </is>
-      </c>
+      <c r="S73" s="185"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -6455,8 +6338,8 @@
       <c r="O74" s="147"/>
       <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="222"/>
-      <c r="S74" s="222"/>
+      <c r="R74" s="185"/>
+      <c r="S74" s="185"/>
       <c r="T74" s="69"/>
       <c r="U74" s="100"/>
       <c r="V74" s="55"/>
@@ -6470,10 +6353,10 @@
       <c r="O75" s="165"/>
       <c r="P75" s="166"/>
       <c r="Q75" s="167"/>
-      <c r="R75" s="223"/>
-      <c r="S75" s="223"/>
-      <c r="T75" s="220"/>
-      <c r="U75" s="221"/>
+      <c r="R75" s="186"/>
+      <c r="S75" s="186"/>
+      <c r="T75" s="183"/>
+      <c r="U75" s="184"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -6487,8 +6370,8 @@
       <c r="Q76" s="167"/>
       <c r="R76" s="168"/>
       <c r="S76" s="168"/>
-      <c r="T76" s="220"/>
-      <c r="U76" s="221"/>
+      <c r="T76" s="183"/>
+      <c r="U76" s="184"/>
       <c r="V76" s="55"/>
     </row>
     <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -6637,57 +6520,10 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M38:N38"/>
     <mergeCell ref="M25:N25"/>
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="Q30:S30"/>
@@ -6704,9 +6540,56 @@
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="T27:U27"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -6745,7 +6628,7 @@
       </c>
       <c r="B1" s="127" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA LOPEZ</t>
+          <t xml:space="preserve">BOB</t>
         </is>
       </c>
       <c r="C1" s="143"/>
@@ -6863,7 +6746,7 @@
       </c>
       <c r="B5" s="154" t="inlineStr">
         <is>
-          <t xml:space="preserve">67890</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="C5" s="154"/>
@@ -6893,7 +6776,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -6922,7 +6805,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="155">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
@@ -6976,7 +6859,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="171">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="C9" s="172"/>
       <c r="D9" s="173"/>
@@ -7005,7 +6888,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="171">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="C10" s="172"/>
       <c r="D10" s="173"/>
@@ -7033,9 +6916,7 @@
       <c r="A11" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="171">
-        <v>300000</v>
-      </c>
+      <c r="B11" s="171"/>
       <c r="C11" s="172"/>
       <c r="D11" s="173"/>
       <c r="E11" s="110"/>
@@ -7458,17 +7339,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="174" t="s">
+      <c r="M22" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
+      <c r="N22" s="215"/>
+      <c r="O22" s="215"/>
+      <c r="P22" s="215"/>
+      <c r="Q22" s="215"/>
+      <c r="R22" s="215"/>
+      <c r="S22" s="215"/>
+      <c r="T22" s="215"/>
+      <c r="U22" s="215"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -7477,21 +7358,17 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-06-2026</t>
-        </is>
-      </c>
-      <c r="O23" s="189"/>
-      <c r="P23" s="189"/>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="189"/>
-      <c r="S23" s="190"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="223"/>
+      <c r="P23" s="223"/>
+      <c r="Q23" s="223"/>
+      <c r="R23" s="223"/>
+      <c r="S23" s="224"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="115">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W23" s="96" t="s">
         <v>44</v>
@@ -7504,22 +7381,22 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="191" t="s">
+      <c r="N24" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="192"/>
-      <c r="P24" s="192"/>
-      <c r="Q24" s="192"/>
-      <c r="R24" s="192"/>
-      <c r="S24" s="193"/>
+      <c r="O24" s="226"/>
+      <c r="P24" s="226"/>
+      <c r="Q24" s="226"/>
+      <c r="R24" s="226"/>
+      <c r="S24" s="227"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="W24" s="141">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -7531,21 +7408,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="196" t="s">
+      <c r="M25" s="212" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="197"/>
-      <c r="O25" s="228"/>
-      <c r="P25" s="229"/>
+      <c r="N25" s="213"/>
+      <c r="O25" s="174"/>
+      <c r="P25" s="175"/>
       <c r="Q25" s="171">
-        <v>450000</v>
+        <v>90000</v>
       </c>
       <c r="R25" s="172"/>
       <c r="S25" s="173"/>
-      <c r="T25" s="194" t="s">
+      <c r="T25" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="195"/>
+      <c r="U25" s="229"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -7561,11 +7438,11 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="175">
-        <v>50000</v>
-      </c>
-      <c r="R26" s="176"/>
-      <c r="S26" s="177"/>
+      <c r="Q26" s="203">
+        <v>10000</v>
+      </c>
+      <c r="R26" s="204"/>
+      <c r="S26" s="205"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -7583,20 +7460,18 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="179"/>
-      <c r="Q27" s="175">
-        <v>300000</v>
-      </c>
-      <c r="R27" s="176"/>
-      <c r="S27" s="177"/>
-      <c r="T27" s="186" t="s">
+      <c r="O27" s="194"/>
+      <c r="P27" s="195"/>
+      <c r="Q27" s="203"/>
+      <c r="R27" s="204"/>
+      <c r="S27" s="205"/>
+      <c r="T27" s="220" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="187"/>
+      <c r="U27" s="221"/>
       <c r="V27" s="19"/>
       <c r="W27" s="97">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -7609,19 +7484,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="184" t="s">
+      <c r="M28" s="210" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="185"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="175"/>
-      <c r="R28" s="176"/>
-      <c r="S28" s="177"/>
-      <c r="T28" s="182" t="s">
+      <c r="N28" s="211"/>
+      <c r="O28" s="194"/>
+      <c r="P28" s="195"/>
+      <c r="Q28" s="203"/>
+      <c r="R28" s="204"/>
+      <c r="S28" s="205"/>
+      <c r="T28" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="183"/>
+      <c r="U28" s="219"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -7636,19 +7511,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="184" t="s">
+      <c r="M29" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="185"/>
-      <c r="O29" s="178"/>
-      <c r="P29" s="179"/>
-      <c r="Q29" s="175"/>
-      <c r="R29" s="176"/>
-      <c r="S29" s="177"/>
-      <c r="T29" s="180" t="s">
+      <c r="N29" s="211"/>
+      <c r="O29" s="194"/>
+      <c r="P29" s="195"/>
+      <c r="Q29" s="203"/>
+      <c r="R29" s="204"/>
+      <c r="S29" s="205"/>
+      <c r="T29" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="181"/>
+      <c r="U29" s="217"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -7664,19 +7539,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="184" t="s">
+      <c r="M30" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="185"/>
-      <c r="O30" s="178"/>
-      <c r="P30" s="198"/>
-      <c r="Q30" s="175"/>
-      <c r="R30" s="176"/>
-      <c r="S30" s="177"/>
-      <c r="T30" s="199" t="s">
+      <c r="N30" s="211"/>
+      <c r="O30" s="194"/>
+      <c r="P30" s="214"/>
+      <c r="Q30" s="203"/>
+      <c r="R30" s="204"/>
+      <c r="S30" s="205"/>
+      <c r="T30" s="201" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="200"/>
+      <c r="U30" s="202"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -7693,15 +7568,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="184" t="s">
+      <c r="M31" s="210" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="185"/>
-      <c r="O31" s="178"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="175"/>
-      <c r="R31" s="176"/>
-      <c r="S31" s="177"/>
+      <c r="N31" s="211"/>
+      <c r="O31" s="194"/>
+      <c r="P31" s="195"/>
+      <c r="Q31" s="203"/>
+      <c r="R31" s="204"/>
+      <c r="S31" s="205"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -7716,15 +7591,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="184" t="s">
+      <c r="M32" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="185"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="175"/>
-      <c r="R32" s="176"/>
-      <c r="S32" s="177"/>
+      <c r="N32" s="211"/>
+      <c r="O32" s="194"/>
+      <c r="P32" s="195"/>
+      <c r="Q32" s="203"/>
+      <c r="R32" s="204"/>
+      <c r="S32" s="205"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -7746,11 +7621,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="178"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="175"/>
-      <c r="R33" s="176"/>
-      <c r="S33" s="177"/>
+      <c r="O33" s="194"/>
+      <c r="P33" s="195"/>
+      <c r="Q33" s="203"/>
+      <c r="R33" s="204"/>
+      <c r="S33" s="205"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -7769,17 +7644,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="204" t="s">
+      <c r="M34" s="206" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="205"/>
-      <c r="O34" s="206"/>
-      <c r="P34" s="207"/>
-      <c r="Q34" s="175">
-        <v>1000000</v>
-      </c>
-      <c r="R34" s="176"/>
-      <c r="S34" s="177"/>
+      <c r="N34" s="207"/>
+      <c r="O34" s="208"/>
+      <c r="P34" s="209"/>
+      <c r="Q34" s="203">
+        <v>500000</v>
+      </c>
+      <c r="R34" s="204"/>
+      <c r="S34" s="205"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -7797,23 +7672,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="217" t="s">
+      <c r="M35" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="218"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="202" t="s">
+      <c r="N35" s="190"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="203"/>
-      <c r="R35" s="202" t="s">
+      <c r="Q35" s="188"/>
+      <c r="R35" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="203"/>
-      <c r="T35" s="202" t="s">
+      <c r="S35" s="188"/>
+      <c r="T35" s="181" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="203"/>
+      <c r="U35" s="188"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -7895,11 +7770,11 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="208" t="s">
+      <c r="M38" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="226"/>
-      <c r="O38" s="227"/>
+      <c r="N38" s="179"/>
+      <c r="O38" s="230"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="44"/>
@@ -7921,19 +7796,9 @@
       <c r="L39" s="114">
         <v>3</v>
       </c>
-      <c r="M39" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-01-2026</t>
-        </is>
-      </c>
-      <c r="N39" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O39" s="39">
-        <v>100000</v>
-      </c>
+      <c r="M39" s="37"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="39"/>
       <c r="P39" s="42"/>
       <c r="Q39" s="72"/>
       <c r="R39" s="44"/>
@@ -8016,8 +7881,8 @@
       <c r="A43" s="112"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="201"/>
-      <c r="E43" s="201"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="192"/>
       <c r="F43" s="51"/>
       <c r="G43" s="8"/>
       <c r="I43" s="136"/>
@@ -8043,8 +7908,8 @@
       <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="201"/>
-      <c r="E44" s="201"/>
+      <c r="D44" s="192"/>
+      <c r="E44" s="192"/>
       <c r="F44" s="52"/>
       <c r="H44" s="68"/>
       <c r="I44" s="13"/>
@@ -8067,8 +7932,8 @@
       <c r="A45" s="25"/>
       <c r="B45" s="25"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="201"/>
-      <c r="E45" s="201"/>
+      <c r="D45" s="192"/>
+      <c r="E45" s="192"/>
       <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
@@ -8090,8 +7955,8 @@
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="201"/>
-      <c r="E46" s="201"/>
+      <c r="D46" s="192"/>
+      <c r="E46" s="192"/>
       <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
@@ -8113,8 +7978,8 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="201"/>
-      <c r="E47" s="201"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="192"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
       <c r="H47" s="68"/>
@@ -8141,8 +8006,8 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="201"/>
-      <c r="E48" s="201"/>
+      <c r="D48" s="192"/>
+      <c r="E48" s="192"/>
       <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
@@ -8165,8 +8030,8 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="201"/>
-      <c r="E49" s="201"/>
+      <c r="D49" s="192"/>
+      <c r="E49" s="192"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
       <c r="H49" s="50"/>
@@ -8213,8 +8078,8 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="213"/>
-      <c r="E51" s="213"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
@@ -8237,8 +8102,8 @@
       <c r="A52" s="20"/>
       <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="225"/>
-      <c r="E52" s="225"/>
+      <c r="D52" s="177"/>
+      <c r="E52" s="177"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
@@ -8261,8 +8126,8 @@
       <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="212"/>
-      <c r="E53" s="212"/>
+      <c r="D53" s="176"/>
+      <c r="E53" s="176"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
@@ -8283,8 +8148,8 @@
       <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="212"/>
-      <c r="E54" s="212"/>
+      <c r="D54" s="176"/>
+      <c r="E54" s="176"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -8415,8 +8280,8 @@
       <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="212"/>
-      <c r="E60" s="212"/>
+      <c r="D60" s="176"/>
+      <c r="E60" s="176"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -8503,8 +8368,8 @@
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="212"/>
-      <c r="E64" s="212"/>
+      <c r="D64" s="176"/>
+      <c r="E64" s="176"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -8525,18 +8390,18 @@
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="212"/>
-      <c r="E65" s="212"/>
+      <c r="D65" s="176"/>
+      <c r="E65" s="176"/>
       <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
       <c r="L65"/>
-      <c r="M65" s="208" t="s">
+      <c r="M65" s="178" t="s">
         <v>34</v>
       </c>
-      <c r="N65" s="209"/>
+      <c r="N65" s="193"/>
       <c r="O65" s="46"/>
       <c r="P65" s="56" t="s">
         <v>11</v>
@@ -8555,8 +8420,8 @@
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="95"/>
-      <c r="D66" s="212"/>
-      <c r="E66" s="212"/>
+      <c r="D66" s="176"/>
+      <c r="E66" s="176"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
@@ -8584,28 +8449,28 @@
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="202" t="s">
+      <c r="M67" s="181" t="s">
         <v>47</v>
       </c>
-      <c r="N67" s="216"/>
-      <c r="O67" s="203"/>
-      <c r="P67" s="214"/>
-      <c r="Q67" s="215"/>
-      <c r="R67" s="202" t="s">
+      <c r="N67" s="182"/>
+      <c r="O67" s="188"/>
+      <c r="P67" s="199"/>
+      <c r="Q67" s="200"/>
+      <c r="R67" s="181" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="216"/>
-      <c r="T67" s="210" t="str">
+      <c r="S67" s="182"/>
+      <c r="T67" s="196" t="str">
         <f>Q25</f>
       </c>
-      <c r="U67" s="211"/>
+      <c r="U67" s="197"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="212"/>
-      <c r="E68" s="212"/>
+      <c r="D68" s="176"/>
+      <c r="E68" s="176"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
@@ -8626,33 +8491,33 @@
       <c r="A69" s="25"/>
       <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="212"/>
-      <c r="E69" s="212"/>
+      <c r="D69" s="176"/>
+      <c r="E69" s="176"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="208" t="s">
+      <c r="M69" s="178" t="s">
         <v>35</v>
       </c>
-      <c r="N69" s="226"/>
-      <c r="O69" s="226"/>
-      <c r="P69" s="226"/>
-      <c r="Q69" s="226"/>
-      <c r="R69" s="226"/>
-      <c r="S69" s="226"/>
-      <c r="T69" s="226"/>
-      <c r="U69" s="227"/>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
+      <c r="R69" s="179"/>
+      <c r="S69" s="179"/>
+      <c r="T69" s="179"/>
+      <c r="U69" s="180"/>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
       <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="212"/>
-      <c r="E70" s="212"/>
+      <c r="D70" s="176"/>
+      <c r="E70" s="176"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
@@ -8689,8 +8554,8 @@
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="212"/>
-      <c r="E71" s="212"/>
+      <c r="D71" s="176"/>
+      <c r="E71" s="176"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
@@ -8704,10 +8569,10 @@
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="65"/>
-      <c r="R71" s="224" t="s">
+      <c r="R71" s="187" t="s">
         <v>6</v>
       </c>
-      <c r="S71" s="224"/>
+      <c r="S71" s="187"/>
       <c r="T71" s="159"/>
       <c r="U71" s="160"/>
       <c r="V71" s="55"/>
@@ -8715,8 +8580,8 @@
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" s="55"/>
       <c r="C72" s="94"/>
-      <c r="D72" s="212"/>
-      <c r="E72" s="212"/>
+      <c r="D72" s="176"/>
+      <c r="E72" s="176"/>
       <c r="F72" s="67"/>
       <c r="I72" s="130"/>
       <c r="L72"/>
@@ -8725,8 +8590,8 @@
       <c r="O72" s="18"/>
       <c r="P72" s="91"/>
       <c r="Q72" s="60"/>
-      <c r="R72" s="222"/>
-      <c r="S72" s="222"/>
+      <c r="R72" s="185"/>
+      <c r="S72" s="185"/>
       <c r="T72" s="69"/>
       <c r="U72" s="100"/>
       <c r="V72" s="55"/>
@@ -8739,38 +8604,20 @@
       <c r="E73" s="25"/>
       <c r="F73" s="67"/>
       <c r="I73" s="130"/>
-      <c r="L73" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67890</t>
-        </is>
-      </c>
-      <c r="M73" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
+      <c r="L73" s="49"/>
+      <c r="M73" s="89"/>
       <c r="N73" s="90"/>
       <c r="O73" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="P73" s="91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
+      <c r="P73" s="91"/>
       <c r="Q73" s="60"/>
-      <c r="R73" s="222" t="s">
+      <c r="R73" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="222"/>
-      <c r="T73" s="69">
-        <v>150000</v>
-      </c>
-      <c r="U73" s="100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Banco Santander</t>
-        </is>
-      </c>
+      <c r="S73" s="185"/>
+      <c r="T73" s="69"/>
+      <c r="U73" s="100"/>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -8780,8 +8627,8 @@
       <c r="O74" s="147"/>
       <c r="P74" s="91"/>
       <c r="Q74" s="60"/>
-      <c r="R74" s="222"/>
-      <c r="S74" s="222"/>
+      <c r="R74" s="185"/>
+      <c r="S74" s="185"/>
       <c r="T74" s="69"/>
       <c r="U74" s="100"/>
       <c r="V74" s="55"/>
@@ -8795,10 +8642,10 @@
       <c r="O75" s="165"/>
       <c r="P75" s="166"/>
       <c r="Q75" s="167"/>
-      <c r="R75" s="223"/>
-      <c r="S75" s="223"/>
-      <c r="T75" s="220"/>
-      <c r="U75" s="221"/>
+      <c r="R75" s="186"/>
+      <c r="S75" s="186"/>
+      <c r="T75" s="183"/>
+      <c r="U75" s="184"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -8812,8 +8659,8 @@
       <c r="Q76" s="167"/>
       <c r="R76" s="168"/>
       <c r="S76" s="168"/>
-      <c r="T76" s="220"/>
-      <c r="U76" s="221"/>
+      <c r="T76" s="183"/>
+      <c r="U76" s="184"/>
       <c r="V76" s="55"/>
     </row>
     <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8962,57 +8809,10 @@
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T75:U75"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="N23:S23"/>
+    <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M38:N38"/>
     <mergeCell ref="M25:N25"/>
     <mergeCell ref="O30:P30"/>
     <mergeCell ref="Q30:S30"/>
@@ -9029,9 +8829,56 @@
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="T27:U27"/>
-    <mergeCell ref="N23:S23"/>
-    <mergeCell ref="N24:S24"/>
-    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esteb\Documents\proyecto_cursor\proyectoisaqwenvisor\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121944EB-68AE-4CE1-8C80-B49289578493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49775DE-810D-4758-A059-F713516FBF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen" sheetId="1" r:id="rId1"/>
@@ -1021,7 +1021,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1409,166 +1409,6 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="4" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1584,41 +1424,20 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1630,6 +1449,166 @@
     </xf>
     <xf numFmtId="42" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="4" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1972,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W113"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -2001,12 +1980,12 @@
       </c>
       <c r="B1" s="112" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PEREZ</t>
+          <t xml:space="preserve">ANA</t>
         </is>
       </c>
       <c r="C1" s="120" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA LOPEZ</t>
+          <t xml:space="preserve">BOB</t>
         </is>
       </c>
       <c r="D1" s="120"/>
@@ -2081,7 +2060,7 @@
       <c r="S3" s="120"/>
       <c r="T3" s="120"/>
       <c r="U3" s="110"/>
-      <c r="V3" s="224"/>
+      <c r="V3" s="163"/>
       <c r="W3" s="116"/>
     </row>
     <row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2108,7 +2087,7 @@
       <c r="S4" s="120"/>
       <c r="T4" s="120"/>
       <c r="U4" s="110"/>
-      <c r="V4" s="224"/>
+      <c r="V4" s="163"/>
       <c r="W4" s="116"/>
     </row>
     <row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2117,12 +2096,12 @@
       </c>
       <c r="B5" s="129" t="inlineStr">
         <is>
-          <t xml:space="preserve">12345</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="C5" s="129" t="inlineStr">
         <is>
-          <t xml:space="preserve">67890</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="D5" s="129"/>
@@ -2151,10 +2130,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="120">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="120">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" s="120"/>
       <c r="E6" s="120"/>
@@ -2177,436 +2156,432 @@
       <c r="V6" s="111"/>
       <c r="W6" s="111"/>
     </row>
-    <row r="7" spans="1:23" s="213" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="225">
-        <v>1000000</v>
-      </c>
-      <c r="C7" s="225">
-        <v>1000000</v>
-      </c>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="225"/>
-      <c r="J7" s="225"/>
-      <c r="K7" s="225"/>
-      <c r="L7" s="225"/>
-      <c r="M7" s="225"/>
-      <c r="N7" s="225"/>
-      <c r="O7" s="225"/>
-      <c r="P7" s="225"/>
-      <c r="Q7" s="225"/>
-      <c r="R7" s="211"/>
-      <c r="S7" s="211"/>
-      <c r="T7" s="211"/>
-      <c r="U7" s="212"/>
-      <c r="V7" s="212"/>
-      <c r="W7" s="212"/>
-    </row>
-    <row r="8" spans="1:23" s="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="210"/>
-      <c r="B8" s="212"/>
-      <c r="C8" s="214"/>
-      <c r="D8" s="212"/>
-      <c r="E8" s="214"/>
-      <c r="F8" s="215"/>
-      <c r="G8" s="214"/>
-      <c r="H8" s="212"/>
-      <c r="I8" s="214"/>
-      <c r="J8" s="212"/>
-      <c r="K8" s="214"/>
-      <c r="L8" s="215"/>
-      <c r="M8" s="214"/>
-      <c r="N8" s="215"/>
-      <c r="O8" s="214"/>
-      <c r="P8" s="216"/>
-      <c r="Q8" s="214"/>
-      <c r="R8" s="216"/>
-      <c r="S8" s="214"/>
-      <c r="T8" s="216"/>
-      <c r="U8" s="214"/>
-      <c r="V8" s="215"/>
-      <c r="W8" s="214"/>
-    </row>
-    <row r="9" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="217" t="s">
+      <c r="B7" s="164">
+        <v>500000</v>
+      </c>
+      <c r="C7" s="164">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="164"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="164"/>
+      <c r="M7" s="164"/>
+      <c r="N7" s="164"/>
+      <c r="O7" s="164"/>
+      <c r="P7" s="164"/>
+      <c r="Q7" s="164"/>
+      <c r="R7" s="156"/>
+      <c r="S7" s="156"/>
+      <c r="T7" s="156"/>
+      <c r="U7" s="157"/>
+      <c r="V7" s="157"/>
+      <c r="W7" s="157"/>
+    </row>
+    <row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="112"/>
+      <c r="B8" s="157"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="157"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="157"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="157"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="158"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="158"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="158"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="110"/>
+      <c r="W8" s="111"/>
+    </row>
+    <row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="226">
-        <v>450000</v>
-      </c>
-      <c r="C9" s="226">
-        <v>450000</v>
-      </c>
-      <c r="D9" s="226"/>
-      <c r="E9" s="212"/>
-      <c r="F9" s="215"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="215"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="215"/>
-      <c r="K9" s="212"/>
-      <c r="L9" s="215"/>
-      <c r="M9" s="212"/>
-      <c r="N9" s="215"/>
-      <c r="O9" s="212"/>
-      <c r="P9" s="216"/>
-      <c r="Q9" s="212"/>
-      <c r="R9" s="216"/>
-      <c r="S9" s="218"/>
-      <c r="T9" s="218"/>
-      <c r="U9" s="212"/>
-      <c r="V9" s="215"/>
-      <c r="W9" s="212"/>
-    </row>
-    <row r="10" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="217" t="s">
+      <c r="B9" s="165">
+        <v>90000</v>
+      </c>
+      <c r="C9" s="165">
+        <v>90000</v>
+      </c>
+      <c r="D9" s="165"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="157"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="157"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="157"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="157"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="157"/>
+      <c r="P9" s="158"/>
+      <c r="Q9" s="157"/>
+      <c r="R9" s="158"/>
+      <c r="S9" s="159"/>
+      <c r="T9" s="159"/>
+      <c r="U9" s="157"/>
+      <c r="V9" s="110"/>
+      <c r="W9" s="157"/>
+    </row>
+    <row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="226">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="226">
-        <v>50000</v>
-      </c>
-      <c r="D10" s="226"/>
-      <c r="E10" s="212"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="215"/>
-      <c r="I10" s="212"/>
-      <c r="J10" s="215"/>
-      <c r="K10" s="212"/>
-      <c r="L10" s="215"/>
-      <c r="M10" s="212"/>
-      <c r="N10" s="215"/>
-      <c r="O10" s="212"/>
-      <c r="P10" s="216"/>
-      <c r="Q10" s="212"/>
-      <c r="R10" s="216"/>
-      <c r="S10" s="218"/>
-      <c r="T10" s="218"/>
-      <c r="U10" s="212"/>
-      <c r="V10" s="215"/>
-      <c r="W10" s="212"/>
-    </row>
-    <row r="11" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="217" t="s">
+      <c r="B10" s="165">
+        <v>10000</v>
+      </c>
+      <c r="C10" s="165">
+        <v>10000</v>
+      </c>
+      <c r="D10" s="165"/>
+      <c r="E10" s="157"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="157"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="157"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="157"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="157"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="157"/>
+      <c r="P10" s="158"/>
+      <c r="Q10" s="157"/>
+      <c r="R10" s="158"/>
+      <c r="S10" s="159"/>
+      <c r="T10" s="159"/>
+      <c r="U10" s="157"/>
+      <c r="V10" s="110"/>
+      <c r="W10" s="157"/>
+    </row>
+    <row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="226">
-        <v>300000</v>
-      </c>
-      <c r="C11" s="226">
-        <v>300000</v>
-      </c>
-      <c r="D11" s="226"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="215"/>
-      <c r="G11" s="212"/>
-      <c r="H11" s="215"/>
-      <c r="I11" s="212"/>
-      <c r="J11" s="215"/>
-      <c r="K11" s="212"/>
-      <c r="L11" s="215"/>
-      <c r="M11" s="212"/>
-      <c r="N11" s="215"/>
-      <c r="O11" s="212"/>
-      <c r="P11" s="216"/>
-      <c r="Q11" s="212"/>
-      <c r="R11" s="216"/>
-      <c r="S11" s="218"/>
-      <c r="T11" s="218"/>
-      <c r="U11" s="212"/>
-      <c r="V11" s="215"/>
-      <c r="W11" s="212"/>
-    </row>
-    <row r="12" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="217" t="s">
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="110"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="158"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="158"/>
+      <c r="S11" s="159"/>
+      <c r="T11" s="159"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="110"/>
+      <c r="W11" s="157"/>
+    </row>
+    <row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="226"/>
-      <c r="C12" s="226"/>
-      <c r="D12" s="226"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="215"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="215"/>
-      <c r="I12" s="212"/>
-      <c r="J12" s="215"/>
-      <c r="K12" s="212"/>
-      <c r="L12" s="215"/>
-      <c r="M12" s="212"/>
-      <c r="N12" s="215"/>
-      <c r="O12" s="212"/>
-      <c r="P12" s="216"/>
-      <c r="Q12" s="212"/>
-      <c r="R12" s="216"/>
-      <c r="S12" s="218"/>
-      <c r="T12" s="218"/>
-      <c r="U12" s="212"/>
-      <c r="V12" s="215"/>
-      <c r="W12" s="212"/>
-    </row>
-    <row r="13" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="217" t="s">
+      <c r="B12" s="165"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="157"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="157"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="157"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="157"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="157"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="158"/>
+      <c r="Q12" s="157"/>
+      <c r="R12" s="158"/>
+      <c r="S12" s="159"/>
+      <c r="T12" s="159"/>
+      <c r="U12" s="157"/>
+      <c r="V12" s="110"/>
+      <c r="W12" s="157"/>
+    </row>
+    <row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="226"/>
-      <c r="C13" s="226"/>
-      <c r="D13" s="226"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="215"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="215"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="215"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="215"/>
-      <c r="M13" s="212"/>
-      <c r="N13" s="215"/>
-      <c r="O13" s="212"/>
-      <c r="P13" s="216"/>
-      <c r="Q13" s="212"/>
-      <c r="R13" s="216"/>
-      <c r="S13" s="218"/>
-      <c r="T13" s="218"/>
-      <c r="U13" s="212"/>
-      <c r="V13" s="215"/>
-      <c r="W13" s="212"/>
-    </row>
-    <row r="14" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="217" t="s">
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="157"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="157"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="157"/>
+      <c r="L13" s="110"/>
+      <c r="M13" s="157"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="157"/>
+      <c r="P13" s="158"/>
+      <c r="Q13" s="157"/>
+      <c r="R13" s="158"/>
+      <c r="S13" s="159"/>
+      <c r="T13" s="159"/>
+      <c r="U13" s="157"/>
+      <c r="V13" s="110"/>
+      <c r="W13" s="157"/>
+    </row>
+    <row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="226"/>
-      <c r="C14" s="226"/>
-      <c r="D14" s="226"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="215"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="215"/>
-      <c r="I14" s="212"/>
-      <c r="J14" s="215"/>
-      <c r="K14" s="212"/>
-      <c r="L14" s="215"/>
-      <c r="M14" s="212"/>
-      <c r="N14" s="215"/>
-      <c r="O14" s="212"/>
-      <c r="P14" s="216"/>
-      <c r="Q14" s="212"/>
-      <c r="R14" s="216"/>
-      <c r="S14" s="218"/>
-      <c r="T14" s="218"/>
-      <c r="U14" s="212"/>
-      <c r="V14" s="215"/>
-      <c r="W14" s="212"/>
-    </row>
-    <row r="15" spans="1:23" s="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217" t="s">
+      <c r="B14" s="165"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="165"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="157"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="157"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="157"/>
+      <c r="L14" s="110"/>
+      <c r="M14" s="157"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="157"/>
+      <c r="P14" s="158"/>
+      <c r="Q14" s="157"/>
+      <c r="R14" s="158"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="159"/>
+      <c r="U14" s="157"/>
+      <c r="V14" s="110"/>
+      <c r="W14" s="157"/>
+    </row>
+    <row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="226"/>
-      <c r="C15" s="226"/>
-      <c r="D15" s="226"/>
-      <c r="E15" s="212"/>
-      <c r="F15" s="215"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="215"/>
-      <c r="I15" s="212"/>
-      <c r="J15" s="215"/>
-      <c r="K15" s="212"/>
-      <c r="L15" s="215"/>
-      <c r="M15" s="212"/>
-      <c r="N15" s="215"/>
-      <c r="O15" s="212"/>
-      <c r="P15" s="216"/>
-      <c r="Q15" s="212"/>
-      <c r="R15" s="216"/>
-      <c r="S15" s="218"/>
-      <c r="T15" s="218"/>
-      <c r="U15" s="212"/>
-      <c r="V15" s="215"/>
-      <c r="W15" s="212"/>
-    </row>
-    <row r="16" spans="1:23" s="222" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="217" t="s">
+      <c r="B15" s="165"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="165"/>
+      <c r="E15" s="157"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="157"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="157"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="157"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="157"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="157"/>
+      <c r="P15" s="158"/>
+      <c r="Q15" s="157"/>
+      <c r="R15" s="158"/>
+      <c r="S15" s="159"/>
+      <c r="T15" s="159"/>
+      <c r="U15" s="157"/>
+      <c r="V15" s="110"/>
+      <c r="W15" s="157"/>
+    </row>
+    <row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="226"/>
-      <c r="C16" s="226"/>
-      <c r="D16" s="226"/>
-      <c r="E16" s="212"/>
-      <c r="F16" s="215"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="215"/>
-      <c r="I16" s="219"/>
-      <c r="J16" s="215"/>
-      <c r="K16" s="219"/>
-      <c r="L16" s="215"/>
-      <c r="M16" s="212"/>
-      <c r="N16" s="215"/>
-      <c r="O16" s="212"/>
-      <c r="P16" s="216"/>
-      <c r="Q16" s="212"/>
-      <c r="R16" s="216"/>
-      <c r="S16" s="218"/>
-      <c r="T16" s="218"/>
-      <c r="U16" s="212"/>
-      <c r="V16" s="215"/>
-      <c r="W16" s="212"/>
-    </row>
-    <row r="17" spans="1:23" s="222" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="217" t="s">
+      <c r="B16" s="165"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="165"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="160"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="160"/>
+      <c r="L16" s="110"/>
+      <c r="M16" s="157"/>
+      <c r="N16" s="110"/>
+      <c r="O16" s="157"/>
+      <c r="P16" s="158"/>
+      <c r="Q16" s="157"/>
+      <c r="R16" s="158"/>
+      <c r="S16" s="159"/>
+      <c r="T16" s="159"/>
+      <c r="U16" s="157"/>
+      <c r="V16" s="110"/>
+      <c r="W16" s="157"/>
+    </row>
+    <row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="226"/>
-      <c r="C17" s="226"/>
-      <c r="D17" s="226"/>
-      <c r="E17" s="212"/>
-      <c r="F17" s="215"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="215"/>
-      <c r="I17" s="219"/>
-      <c r="J17" s="215"/>
-      <c r="K17" s="212"/>
-      <c r="L17" s="215"/>
-      <c r="M17" s="212"/>
-      <c r="N17" s="215"/>
-      <c r="O17" s="212"/>
-      <c r="P17" s="216"/>
-      <c r="Q17" s="212"/>
-      <c r="R17" s="216"/>
-      <c r="S17" s="218"/>
-      <c r="T17" s="218"/>
-      <c r="U17" s="212"/>
-      <c r="V17" s="215"/>
-      <c r="W17" s="212"/>
-    </row>
-    <row r="18" spans="1:23" s="222" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217" t="s">
+      <c r="B17" s="165"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="160"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="110"/>
+      <c r="O17" s="157"/>
+      <c r="P17" s="158"/>
+      <c r="Q17" s="157"/>
+      <c r="R17" s="158"/>
+      <c r="S17" s="159"/>
+      <c r="T17" s="159"/>
+      <c r="U17" s="157"/>
+      <c r="V17" s="110"/>
+      <c r="W17" s="157"/>
+    </row>
+    <row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="215">
+      <c r="B18" s="110">
         <f>SUM(B9:B17)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="215">
+      <c r="C18" s="110">
         <f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="215">
+      <c r="D18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="215">
+      <c r="E18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="215">
+      <c r="F18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="215">
+      <c r="G18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="215">
+      <c r="H18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="215">
+      <c r="J18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="215">
+      <c r="K18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M18" s="215">
+      <c r="M18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O18" s="215">
+      <c r="O18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="110">
         <f t="shared" ref="P18" si="1">SUM(P9:P17)</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="215">
+      <c r="Q18" s="110">
         <f>SUM(Q9:Q17)</f>
         <v>0</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="110">
         <f>SUM(R9:R17)</f>
         <v>0</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="116">
         <f>SUM(S9:S17)</f>
         <v>0</v>
       </c>
-      <c r="T18" s="220">
+      <c r="T18" s="116">
         <f>SUM(T9:T17)</f>
         <v>0</v>
       </c>
-      <c r="U18" s="215">
+      <c r="U18" s="110">
         <f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f>
         <v>0</v>
       </c>
-      <c r="V18" s="215">
+      <c r="V18" s="110">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W18" s="215">
+      <c r="W18" s="110">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="222" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
-      <c r="B19" s="215"/>
-      <c r="C19" s="215"/>
-      <c r="D19" s="215"/>
-      <c r="E19" s="215"/>
-      <c r="F19" s="212"/>
-      <c r="G19" s="215"/>
-      <c r="H19" s="215"/>
-      <c r="I19" s="215"/>
-      <c r="J19" s="215"/>
-      <c r="K19" s="215"/>
-      <c r="L19" s="215"/>
-      <c r="M19" s="215"/>
-      <c r="N19" s="215"/>
-      <c r="O19" s="215"/>
-      <c r="P19" s="215"/>
-      <c r="Q19" s="215"/>
-      <c r="R19" s="215"/>
-      <c r="S19" s="220"/>
-      <c r="T19" s="220"/>
-      <c r="U19" s="215"/>
-      <c r="V19" s="215"/>
-      <c r="W19" s="215"/>
-    </row>
-    <row r="20" spans="1:23" s="223" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="113"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="110"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="116"/>
+      <c r="T19" s="116"/>
+      <c r="U19" s="110"/>
+      <c r="V19" s="110"/>
+      <c r="W19" s="110"/>
+    </row>
+    <row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="113" t="s">
         <v>12</v>
       </c>
@@ -2726,17 +2701,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="168" t="s">
+      <c r="M22" s="198" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="168"/>
-      <c r="O22" s="168"/>
-      <c r="P22" s="168"/>
-      <c r="Q22" s="168"/>
-      <c r="R22" s="168"/>
-      <c r="S22" s="168"/>
-      <c r="T22" s="168"/>
-      <c r="U22" s="168"/>
+      <c r="N22" s="198"/>
+      <c r="O22" s="198"/>
+      <c r="P22" s="198"/>
+      <c r="Q22" s="198"/>
+      <c r="R22" s="198"/>
+      <c r="S22" s="198"/>
+      <c r="T22" s="198"/>
+      <c r="U22" s="198"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -2745,21 +2720,17 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-06-2026</t>
-        </is>
-      </c>
-      <c r="O23" s="152"/>
-      <c r="P23" s="152"/>
-      <c r="Q23" s="152"/>
-      <c r="R23" s="152"/>
-      <c r="S23" s="153"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="208"/>
+      <c r="P23" s="208"/>
+      <c r="Q23" s="208"/>
+      <c r="R23" s="208"/>
+      <c r="S23" s="209"/>
       <c r="T23" s="119" t="s">
         <v>38</v>
       </c>
       <c r="U23" s="106">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W23" s="91" t="s">
         <v>44</v>
@@ -2772,22 +2743,22 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="154" t="s">
+      <c r="N24" s="210" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="155"/>
-      <c r="P24" s="155"/>
-      <c r="Q24" s="155"/>
-      <c r="R24" s="155"/>
-      <c r="S24" s="156"/>
+      <c r="O24" s="211"/>
+      <c r="P24" s="211"/>
+      <c r="Q24" s="211"/>
+      <c r="R24" s="211"/>
+      <c r="S24" s="212"/>
       <c r="T24" s="108" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="107">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="W24" s="118">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -2799,21 +2770,21 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="161" t="s">
+      <c r="M25" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="162"/>
+      <c r="N25" s="216"/>
       <c r="O25" s="148"/>
       <c r="P25" s="149"/>
       <c r="Q25" s="145">
-        <v>900000</v>
+        <v>180000</v>
       </c>
       <c r="R25" s="146"/>
       <c r="S25" s="147"/>
-      <c r="T25" s="157" t="s">
+      <c r="T25" s="213" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="158"/>
+      <c r="U25" s="214"/>
       <c r="V25" s="13"/>
       <c r="W25" s="82" t="s">
         <v>45</v>
@@ -2829,11 +2800,11 @@
       <c r="N26" s="80"/>
       <c r="O26" s="126"/>
       <c r="P26" s="127"/>
-      <c r="Q26" s="165">
-        <v>100000</v>
-      </c>
-      <c r="R26" s="166"/>
-      <c r="S26" s="167"/>
+      <c r="Q26" s="188">
+        <v>20000</v>
+      </c>
+      <c r="R26" s="189"/>
+      <c r="S26" s="190"/>
       <c r="T26" s="124"/>
       <c r="U26" s="125"/>
       <c r="V26" s="13"/>
@@ -2851,20 +2822,18 @@
         <v>18</v>
       </c>
       <c r="N27" s="80"/>
-      <c r="O27" s="163"/>
-      <c r="P27" s="169"/>
-      <c r="Q27" s="165" t="s">
-        <v>64</v>
-      </c>
-      <c r="R27" s="166"/>
-      <c r="S27" s="167"/>
-      <c r="T27" s="176" t="s">
+      <c r="O27" s="186"/>
+      <c r="P27" s="187"/>
+      <c r="Q27" s="188"/>
+      <c r="R27" s="189"/>
+      <c r="S27" s="190"/>
+      <c r="T27" s="205" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="177"/>
+      <c r="U27" s="206"/>
       <c r="V27" s="19"/>
       <c r="W27" s="92">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -2877,19 +2846,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="174" t="s">
+      <c r="M28" s="203" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="175"/>
-      <c r="O28" s="163"/>
-      <c r="P28" s="169"/>
-      <c r="Q28" s="165"/>
-      <c r="R28" s="166"/>
-      <c r="S28" s="167"/>
-      <c r="T28" s="172" t="s">
+      <c r="N28" s="204"/>
+      <c r="O28" s="186"/>
+      <c r="P28" s="187"/>
+      <c r="Q28" s="188"/>
+      <c r="R28" s="189"/>
+      <c r="S28" s="190"/>
+      <c r="T28" s="201" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="173"/>
+      <c r="U28" s="202"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -2904,19 +2873,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="174" t="s">
+      <c r="M29" s="203" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="175"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="169"/>
-      <c r="Q29" s="165"/>
-      <c r="R29" s="166"/>
-      <c r="S29" s="167"/>
-      <c r="T29" s="170" t="s">
+      <c r="N29" s="204"/>
+      <c r="O29" s="186"/>
+      <c r="P29" s="187"/>
+      <c r="Q29" s="188"/>
+      <c r="R29" s="189"/>
+      <c r="S29" s="190"/>
+      <c r="T29" s="199" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="171"/>
+      <c r="U29" s="200"/>
       <c r="W29" s="93" t="str">
         <f>U23</f>
       </c>
@@ -2932,19 +2901,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="174" t="s">
+      <c r="M30" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="175"/>
-      <c r="O30" s="163"/>
-      <c r="P30" s="164"/>
-      <c r="Q30" s="165"/>
-      <c r="R30" s="166"/>
-      <c r="S30" s="167"/>
-      <c r="T30" s="178" t="s">
+      <c r="N30" s="204"/>
+      <c r="O30" s="186"/>
+      <c r="P30" s="217"/>
+      <c r="Q30" s="188"/>
+      <c r="R30" s="189"/>
+      <c r="S30" s="190"/>
+      <c r="T30" s="218" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="179"/>
+      <c r="U30" s="219"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -2961,15 +2930,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="174" t="s">
+      <c r="M31" s="203" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="175"/>
-      <c r="O31" s="163"/>
-      <c r="P31" s="169"/>
-      <c r="Q31" s="165"/>
-      <c r="R31" s="166"/>
-      <c r="S31" s="167"/>
+      <c r="N31" s="204"/>
+      <c r="O31" s="186"/>
+      <c r="P31" s="187"/>
+      <c r="Q31" s="188"/>
+      <c r="R31" s="189"/>
+      <c r="S31" s="190"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -2984,15 +2953,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="174" t="s">
+      <c r="M32" s="203" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="175"/>
-      <c r="O32" s="163"/>
-      <c r="P32" s="169"/>
-      <c r="Q32" s="165"/>
-      <c r="R32" s="166"/>
-      <c r="S32" s="167"/>
+      <c r="N32" s="204"/>
+      <c r="O32" s="186"/>
+      <c r="P32" s="187"/>
+      <c r="Q32" s="188"/>
+      <c r="R32" s="189"/>
+      <c r="S32" s="190"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="82" t="s">
@@ -3014,11 +2983,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="81"/>
-      <c r="O33" s="163"/>
-      <c r="P33" s="169"/>
-      <c r="Q33" s="165"/>
-      <c r="R33" s="166"/>
-      <c r="S33" s="167"/>
+      <c r="O33" s="186"/>
+      <c r="P33" s="187"/>
+      <c r="Q33" s="188"/>
+      <c r="R33" s="189"/>
+      <c r="S33" s="190"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="117" t="e">
@@ -3037,17 +3006,17 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="183" t="s">
+      <c r="M34" s="191" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="184"/>
-      <c r="O34" s="185"/>
-      <c r="P34" s="186"/>
-      <c r="Q34" s="165">
-        <v>2000000</v>
-      </c>
-      <c r="R34" s="166"/>
-      <c r="S34" s="167"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="193"/>
+      <c r="P34" s="194"/>
+      <c r="Q34" s="188">
+        <v>1000000</v>
+      </c>
+      <c r="R34" s="189"/>
+      <c r="S34" s="190"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -3065,23 +3034,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="193" t="s">
+      <c r="M35" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="194"/>
-      <c r="O35" s="195"/>
-      <c r="P35" s="181" t="s">
+      <c r="N35" s="196"/>
+      <c r="O35" s="197"/>
+      <c r="P35" s="167" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="182"/>
-      <c r="R35" s="181" t="s">
+      <c r="Q35" s="169"/>
+      <c r="R35" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="182"/>
-      <c r="T35" s="181" t="s">
+      <c r="S35" s="169"/>
+      <c r="T35" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="182"/>
+      <c r="U35" s="169"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -3138,169 +3107,131 @@
       </c>
       <c r="K37" s="24"/>
       <c r="L37"/>
-      <c r="M37" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-01-2026</t>
-        </is>
-      </c>
-      <c r="N37" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O37" s="39">
-        <v>100000</v>
-      </c>
-      <c r="P37" s="205"/>
+      <c r="M37" s="37"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="39"/>
+      <c r="P37" s="151"/>
       <c r="Q37" s="77"/>
-      <c r="R37" s="207"/>
+      <c r="R37" s="153"/>
       <c r="S37" s="78"/>
-      <c r="T37" s="206"/>
+      <c r="T37" s="152"/>
       <c r="U37" s="74"/>
       <c r="V37" s="1"/>
       <c r="W37" s="18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
+    <row r="38" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="32"/>
       <c r="I38" s="41">
-        <f>
-          L
-          <row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-            <c r="A37" s="1"/>
-            <c r="I37" s="41">
-              <f>L$1</f>
-              <v>0</v>
-            </c>
-            <c r="J37" s="27">
-              <f>L9</f>
-              <v>0</v>
-            </c>
-            <c r="K37" s="24"/>
-            <c r="L37"/>
-            <c r="M37" s="37" t="inlineStr">
-              <is>
-                <t xml:space="preserve">01-01-2026</t>
-              </is>
-            </c>
-            <c r="N37" s="38" t="inlineStr">
-              <is>
-                <t xml:space="preserve">SANTANDER</t>
-              </is>
-            </c>
-            <c r="O37" s="39">
-              <v>100000</v>
-            </c>
-            <c r="P37" s="205"/>
-            <c r="Q37" s="77"/>
-            <c r="R37" s="207"/>
-            <c r="S37" s="78"/>
-            <c r="T37" s="206"/>
-            <c r="U37" s="74"/>
-            <c r="V37" s="1"/>
-            <c r="W37" s="18" t="s">
-              <v>14</v>
-            </c>
-          </row>
-        </f>
+        <f t="shared" ref="I38:I45" si="6">L$1</f>
         <v>0</v>
       </c>
       <c r="J38" s="27">
-        <f>L9</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="24"/>
-      <c r="L38"/>
-      <c r="M38" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01-01-2026</t>
-        </is>
-      </c>
-      <c r="N38" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTANDER</t>
-        </is>
-      </c>
-      <c r="O38" s="39">
-        <v>100000</v>
-      </c>
-      <c r="P38" s="205"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="207"/>
-      <c r="S38" s="78"/>
-      <c r="T38" s="206"/>
-      <c r="U38" s="74"/>
+        <f t="shared" ref="J38:J45" si="7">L10</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="105"/>
+      <c r="M38" s="171" t="s">
+        <v>42</v>
+      </c>
+      <c r="N38" s="179"/>
+      <c r="O38" s="150"/>
+      <c r="P38" s="152"/>
+      <c r="Q38" s="75"/>
+      <c r="R38" s="154"/>
+      <c r="S38" s="73"/>
+      <c r="T38" s="152"/>
+      <c r="U38" s="76"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="18"/>
-    </row>
-    <row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="W38" s="1"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B39" s="20"/>
       <c r="C39" s="32"/>
       <c r="I39" s="41">
-        <f t="shared" ref="I39:I46" si="6">L$1</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J39" s="27">
-        <f t="shared" ref="J39:J46" si="7">L10</f>
-        <v>0</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="24"/>
       <c r="L39" s="105"/>
-      <c r="M39" s="159" t="s">
-        <v>42</v>
-      </c>
-      <c r="N39" s="160"/>
-      <c r="O39" s="150">
-        <f>SUMA(O37:O38)</f>
-      </c>
-      <c r="P39" s="206"/>
-      <c r="Q39" s="75"/>
-      <c r="R39" s="208"/>
+      <c r="M39" s="37"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="39"/>
+      <c r="P39" s="152"/>
+      <c r="Q39" s="68"/>
+      <c r="R39" s="154"/>
       <c r="S39" s="73"/>
-      <c r="T39" s="206"/>
-      <c r="U39" s="76"/>
+      <c r="T39" s="152"/>
+      <c r="U39" s="68"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O40" s="0"/>
-      <c r="N40" s="0"/>
-      <c r="M40" s="0"/>
+    <row r="40" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="20"/>
       <c r="C40" s="32"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="43"/>
       <c r="I40" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="J40" s="27">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="24"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="37"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="152"/>
+      <c r="Q40" s="66"/>
+      <c r="R40" s="154"/>
+      <c r="S40" s="74"/>
+      <c r="T40" s="152"/>
+      <c r="U40" s="68"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+    </row>
+    <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="20"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="I41" s="41">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="J41" s="27">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K41" s="24"/>
       <c r="L41" s="105"/>
-      <c r="M41" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="N41" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="O41" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="P41" s="206"/>
-      <c r="Q41" s="68"/>
-      <c r="R41" s="208"/>
-      <c r="S41" s="73"/>
-      <c r="T41" s="206"/>
+      <c r="M41" s="37"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="152"/>
+      <c r="Q41" s="66"/>
+      <c r="R41" s="154"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="152"/>
       <c r="U41" s="68"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
-    <row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B42" s="20"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="43"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="47"/>
       <c r="I42" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -3309,25 +3240,27 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K42" s="24"/>
       <c r="L42" s="105"/>
       <c r="M42" s="37"/>
       <c r="N42" s="38"/>
       <c r="O42" s="39"/>
-      <c r="P42" s="206"/>
+      <c r="P42" s="152"/>
       <c r="Q42" s="66"/>
-      <c r="R42" s="208"/>
-      <c r="S42" s="74"/>
-      <c r="T42" s="206"/>
+      <c r="R42" s="154"/>
+      <c r="S42" s="73"/>
+      <c r="T42" s="152"/>
       <c r="U42" s="68"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
-    <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="104"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="D43" s="170"/>
+      <c r="E43" s="170"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="8"/>
       <c r="I43" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -3341,21 +3274,21 @@
       <c r="M43" s="37"/>
       <c r="N43" s="38"/>
       <c r="O43" s="39"/>
-      <c r="P43" s="206"/>
+      <c r="P43" s="152"/>
       <c r="Q43" s="66"/>
-      <c r="R43" s="208"/>
-      <c r="S43" s="74"/>
-      <c r="T43" s="206"/>
+      <c r="R43" s="152"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="152"/>
       <c r="U43" s="68"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-    </row>
-    <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="47"/>
+      <c r="D44" s="170"/>
+      <c r="E44" s="170"/>
+      <c r="F44" s="48"/>
+      <c r="H44" s="64"/>
       <c r="I44" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -3364,27 +3297,26 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="K44" s="24"/>
       <c r="L44" s="105"/>
       <c r="M44" s="37"/>
       <c r="N44" s="38"/>
       <c r="O44" s="39"/>
-      <c r="P44" s="206"/>
+      <c r="P44" s="152"/>
       <c r="Q44" s="66"/>
-      <c r="R44" s="208"/>
-      <c r="S44" s="73"/>
-      <c r="T44" s="206"/>
+      <c r="R44" s="152"/>
+      <c r="S44" s="67"/>
+      <c r="T44" s="152"/>
       <c r="U44" s="68"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-    </row>
-    <row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="104"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="180"/>
-      <c r="E45" s="180"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="8"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="170"/>
+      <c r="E45" s="170"/>
+      <c r="F45" s="23"/>
+      <c r="H45" s="64"/>
       <c r="I45" s="41">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -3393,148 +3325,114 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K45" s="24"/>
       <c r="L45" s="105"/>
       <c r="M45" s="37"/>
       <c r="N45" s="38"/>
       <c r="O45" s="39"/>
-      <c r="P45" s="206"/>
+      <c r="P45" s="152"/>
       <c r="Q45" s="66"/>
-      <c r="R45" s="206"/>
-      <c r="S45" s="67"/>
-      <c r="T45" s="206"/>
+      <c r="R45" s="152"/>
+      <c r="S45" s="72"/>
+      <c r="T45" s="152"/>
       <c r="U45" s="68"/>
     </row>
-    <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A46" s="20"/>
       <c r="B46" s="20"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="180"/>
-      <c r="E46" s="180"/>
-      <c r="F46" s="48"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="170"/>
+      <c r="E46" s="170"/>
+      <c r="F46" s="49"/>
       <c r="H46" s="64"/>
-      <c r="I46" s="41">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="27">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="24"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="53">
+        <f>SUM(J28:J45)</f>
+        <v>0</v>
+      </c>
       <c r="L46" s="105"/>
       <c r="M46" s="37"/>
       <c r="N46" s="38"/>
       <c r="O46" s="39"/>
-      <c r="P46" s="206"/>
+      <c r="P46" s="152"/>
       <c r="Q46" s="66"/>
-      <c r="R46" s="206"/>
+      <c r="R46" s="152"/>
       <c r="S46" s="67"/>
-      <c r="T46" s="206"/>
+      <c r="T46" s="152"/>
       <c r="U46" s="68"/>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="180"/>
-      <c r="E47" s="180"/>
-      <c r="F47" s="23"/>
+      <c r="D47" s="170"/>
+      <c r="E47" s="170"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="1"/>
       <c r="H47" s="64"/>
-      <c r="I47" s="41">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J47" s="27">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="I47" s="13"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="24"/>
       <c r="L47" s="105"/>
       <c r="M47" s="37"/>
       <c r="N47" s="38"/>
       <c r="O47" s="39"/>
-      <c r="P47" s="206"/>
+      <c r="P47" s="152"/>
       <c r="Q47" s="66"/>
-      <c r="R47" s="206"/>
-      <c r="S47" s="72"/>
-      <c r="T47" s="206"/>
-      <c r="U47" s="68"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="180"/>
-      <c r="E48" s="180"/>
-      <c r="F48" s="49"/>
-      <c r="H48" s="64"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="53">
-        <f>SUM(J28:J46)</f>
-        <v>0</v>
-      </c>
-      <c r="L47" s="105"/>
-      <c r="M47" s="37"/>
-      <c r="N47" s="38"/>
-      <c r="O47" s="39"/>
-      <c r="P47" s="206"/>
-      <c r="Q47" s="66"/>
-      <c r="R47" s="206"/>
+      <c r="R47" s="152"/>
       <c r="S47" s="67"/>
-      <c r="T47" s="206"/>
+      <c r="T47" s="152"/>
       <c r="U47" s="68"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="180"/>
-      <c r="E48" s="180"/>
-      <c r="F48" s="17"/>
+      <c r="D48" s="170"/>
+      <c r="E48" s="170"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="64"/>
       <c r="I48" s="13"/>
       <c r="J48" s="53"/>
-      <c r="K48" s="24"/>
       <c r="L48" s="105"/>
       <c r="M48" s="37"/>
       <c r="N48" s="38"/>
       <c r="O48" s="39"/>
-      <c r="P48" s="206"/>
+      <c r="P48" s="152"/>
       <c r="Q48" s="66"/>
-      <c r="R48" s="206"/>
+      <c r="R48" s="152"/>
       <c r="S48" s="67"/>
-      <c r="T48" s="206"/>
+      <c r="T48" s="154"/>
       <c r="U48" s="68"/>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="180"/>
-      <c r="E49" s="180"/>
+      <c r="D49" s="170"/>
+      <c r="E49" s="170"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="64"/>
+      <c r="H49" s="46"/>
       <c r="I49" s="13"/>
       <c r="J49" s="53"/>
       <c r="L49" s="105"/>
       <c r="M49" s="37"/>
       <c r="N49" s="38"/>
       <c r="O49" s="39"/>
-      <c r="P49" s="206"/>
+      <c r="P49" s="152"/>
       <c r="Q49" s="66"/>
-      <c r="R49" s="206"/>
+      <c r="R49" s="152"/>
       <c r="S49" s="67"/>
-      <c r="T49" s="208"/>
+      <c r="T49" s="154"/>
       <c r="U49" s="68"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="20"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="180"/>
-      <c r="E50" s="180"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="25"/>
       <c r="F50" s="23"/>
       <c r="G50" s="1"/>
       <c r="H50" s="46"/>
@@ -3544,19 +3442,19 @@
       <c r="M50" s="37"/>
       <c r="N50" s="38"/>
       <c r="O50" s="39"/>
-      <c r="P50" s="206"/>
+      <c r="P50" s="152"/>
       <c r="Q50" s="66"/>
-      <c r="R50" s="206"/>
+      <c r="R50" s="152"/>
       <c r="S50" s="67"/>
-      <c r="T50" s="208"/>
+      <c r="T50" s="154"/>
       <c r="U50" s="68"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="25"/>
+      <c r="D51" s="185"/>
+      <c r="E51" s="185"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="46"/>
@@ -3566,63 +3464,63 @@
       <c r="M51" s="37"/>
       <c r="N51" s="38"/>
       <c r="O51" s="39"/>
-      <c r="P51" s="206"/>
+      <c r="P51" s="151"/>
       <c r="Q51" s="66"/>
-      <c r="R51" s="206"/>
+      <c r="R51" s="152"/>
       <c r="S51" s="67"/>
-      <c r="T51" s="208"/>
+      <c r="T51" s="154"/>
       <c r="U51" s="68"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
+      <c r="B52" s="51"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="190"/>
-      <c r="E52" s="190"/>
+      <c r="D52" s="178"/>
+      <c r="E52" s="178"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="46"/>
-      <c r="I52" s="13"/>
+      <c r="I52" s="50"/>
       <c r="J52" s="53"/>
       <c r="L52" s="105"/>
       <c r="M52" s="37"/>
       <c r="N52" s="38"/>
       <c r="O52" s="39"/>
-      <c r="P52" s="205"/>
+      <c r="P52" s="151"/>
       <c r="Q52" s="66"/>
-      <c r="R52" s="206"/>
+      <c r="R52" s="152"/>
       <c r="S52" s="67"/>
-      <c r="T52" s="208"/>
+      <c r="T52" s="154"/>
       <c r="U52" s="68"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="20"/>
+      <c r="A53" s="25"/>
       <c r="B53" s="51"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="202"/>
-      <c r="E53" s="202"/>
+      <c r="D53" s="166"/>
+      <c r="E53" s="166"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="46"/>
       <c r="I53" s="50"/>
       <c r="J53" s="53"/>
-      <c r="L53" s="105"/>
+      <c r="L53" s="18"/>
       <c r="M53" s="37"/>
       <c r="N53" s="38"/>
       <c r="O53" s="39"/>
-      <c r="P53" s="205"/>
+      <c r="P53" s="152"/>
       <c r="Q53" s="66"/>
-      <c r="R53" s="206"/>
+      <c r="R53" s="152"/>
       <c r="S53" s="67"/>
-      <c r="T53" s="208"/>
+      <c r="T53" s="154"/>
       <c r="U53" s="68"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="25"/>
+      <c r="A54" s="20"/>
       <c r="B54" s="51"/>
       <c r="C54" s="40"/>
-      <c r="D54" s="189"/>
-      <c r="E54" s="189"/>
+      <c r="D54" s="166"/>
+      <c r="E54" s="166"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="46"/>
@@ -3632,19 +3530,19 @@
       <c r="M54" s="37"/>
       <c r="N54" s="38"/>
       <c r="O54" s="39"/>
-      <c r="P54" s="206"/>
+      <c r="P54" s="152"/>
       <c r="Q54" s="66"/>
-      <c r="R54" s="206"/>
+      <c r="R54" s="152"/>
       <c r="S54" s="67"/>
-      <c r="T54" s="208"/>
+      <c r="T54" s="154"/>
       <c r="U54" s="68"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="20"/>
       <c r="B55" s="51"/>
       <c r="C55" s="40"/>
-      <c r="D55" s="189"/>
-      <c r="E55" s="189"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="23"/>
       <c r="G55" s="1"/>
       <c r="H55" s="46"/>
@@ -3654,16 +3552,16 @@
       <c r="M55" s="37"/>
       <c r="N55" s="38"/>
       <c r="O55" s="39"/>
-      <c r="P55" s="206"/>
+      <c r="P55" s="152"/>
       <c r="Q55" s="66"/>
-      <c r="R55" s="206"/>
+      <c r="R55" s="152"/>
       <c r="S55" s="67"/>
-      <c r="T55" s="208"/>
+      <c r="T55" s="154"/>
       <c r="U55" s="68"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
-      <c r="B56" s="51"/>
+      <c r="B56"/>
       <c r="C56" s="40"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
@@ -3676,11 +3574,11 @@
       <c r="M56" s="37"/>
       <c r="N56" s="38"/>
       <c r="O56" s="39"/>
-      <c r="P56" s="206"/>
+      <c r="P56" s="152"/>
       <c r="Q56" s="66"/>
-      <c r="R56" s="206"/>
+      <c r="R56" s="152"/>
       <c r="S56" s="67"/>
-      <c r="T56" s="208"/>
+      <c r="T56" s="154"/>
       <c r="U56" s="68"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
@@ -3698,11 +3596,11 @@
       <c r="M57" s="37"/>
       <c r="N57" s="38"/>
       <c r="O57" s="39"/>
-      <c r="P57" s="206"/>
+      <c r="P57" s="152"/>
       <c r="Q57" s="66"/>
-      <c r="R57" s="206"/>
+      <c r="R57" s="152"/>
       <c r="S57" s="67"/>
-      <c r="T57" s="208"/>
+      <c r="T57" s="154"/>
       <c r="U57" s="68"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
@@ -3720,11 +3618,11 @@
       <c r="M58" s="37"/>
       <c r="N58" s="38"/>
       <c r="O58" s="39"/>
-      <c r="P58" s="206"/>
+      <c r="P58" s="152"/>
       <c r="Q58" s="66"/>
-      <c r="R58" s="206"/>
+      <c r="R58" s="152"/>
       <c r="S58" s="67"/>
-      <c r="T58" s="208"/>
+      <c r="T58" s="154"/>
       <c r="U58" s="68"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.3">
@@ -3742,19 +3640,19 @@
       <c r="M59" s="37"/>
       <c r="N59" s="38"/>
       <c r="O59" s="39"/>
-      <c r="P59" s="206"/>
+      <c r="P59" s="152"/>
       <c r="Q59" s="66"/>
-      <c r="R59" s="206"/>
+      <c r="R59" s="152"/>
       <c r="S59" s="67"/>
-      <c r="T59" s="208"/>
+      <c r="T59" s="154"/>
       <c r="U59" s="68"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A60" s="20"/>
+      <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="40"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
+      <c r="D60" s="166"/>
+      <c r="E60" s="166"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="46"/>
@@ -3764,19 +3662,19 @@
       <c r="M60" s="37"/>
       <c r="N60" s="38"/>
       <c r="O60" s="39"/>
-      <c r="P60" s="206"/>
+      <c r="P60" s="152"/>
       <c r="Q60" s="66"/>
-      <c r="R60" s="206"/>
+      <c r="R60" s="152"/>
       <c r="S60" s="67"/>
-      <c r="T60" s="208"/>
+      <c r="T60" s="154"/>
       <c r="U60" s="68"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="25"/>
       <c r="B61"/>
       <c r="C61" s="40"/>
-      <c r="D61" s="189"/>
-      <c r="E61" s="189"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="23"/>
       <c r="G61" s="1"/>
       <c r="H61" s="46"/>
@@ -3786,11 +3684,11 @@
       <c r="M61" s="37"/>
       <c r="N61" s="38"/>
       <c r="O61" s="39"/>
-      <c r="P61" s="206"/>
-      <c r="Q61" s="66"/>
-      <c r="R61" s="206"/>
-      <c r="S61" s="67"/>
-      <c r="T61" s="208"/>
+      <c r="P61" s="152"/>
+      <c r="Q61" s="135"/>
+      <c r="R61" s="155"/>
+      <c r="S61" s="88"/>
+      <c r="T61" s="154"/>
       <c r="U61" s="68"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
@@ -3808,11 +3706,11 @@
       <c r="M62" s="37"/>
       <c r="N62" s="38"/>
       <c r="O62" s="39"/>
-      <c r="P62" s="206"/>
+      <c r="P62" s="152"/>
       <c r="Q62" s="135"/>
-      <c r="R62" s="209"/>
+      <c r="R62" s="155"/>
       <c r="S62" s="88"/>
-      <c r="T62" s="208"/>
+      <c r="T62" s="154"/>
       <c r="U62" s="68"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
@@ -3830,19 +3728,19 @@
       <c r="M63" s="37"/>
       <c r="N63" s="38"/>
       <c r="O63" s="39"/>
-      <c r="P63" s="206"/>
+      <c r="P63" s="152"/>
       <c r="Q63" s="135"/>
-      <c r="R63" s="209"/>
+      <c r="R63" s="155"/>
       <c r="S63" s="88"/>
-      <c r="T63" s="208"/>
+      <c r="T63" s="154"/>
       <c r="U63" s="68"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="40"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
+      <c r="D64" s="166"/>
+      <c r="E64" s="166"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="46"/>
@@ -3852,403 +3750,342 @@
       <c r="M64" s="37"/>
       <c r="N64" s="38"/>
       <c r="O64" s="39"/>
-      <c r="P64" s="206"/>
-      <c r="Q64" s="135"/>
-      <c r="R64" s="209"/>
+      <c r="P64" s="152"/>
+      <c r="Q64" s="84"/>
+      <c r="R64" s="155"/>
       <c r="S64" s="88"/>
-      <c r="T64" s="208"/>
-      <c r="U64" s="68"/>
-    </row>
-    <row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="T64" s="154"/>
+      <c r="U64" s="71"/>
+    </row>
+    <row r="65" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="40"/>
-      <c r="D65" s="189"/>
-      <c r="E65" s="189"/>
-      <c r="F65" s="23"/>
+      <c r="D65" s="166"/>
+      <c r="E65" s="166"/>
+      <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="46"/>
       <c r="I65" s="50"/>
       <c r="J65" s="53"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="37"/>
-      <c r="N65" s="38"/>
-      <c r="O65" s="39"/>
-      <c r="P65" s="206"/>
-      <c r="Q65" s="84"/>
-      <c r="R65" s="209"/>
-      <c r="S65" s="88"/>
-      <c r="T65" s="208"/>
-      <c r="U65" s="71"/>
-    </row>
-    <row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65"/>
+      <c r="M65" s="171" t="s">
+        <v>34</v>
+      </c>
+      <c r="N65" s="172"/>
+      <c r="O65" s="42"/>
+      <c r="P65" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="42"/>
+      <c r="R65" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="S65" s="42"/>
+      <c r="T65" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="42"/>
+    </row>
+    <row r="66" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="25"/>
       <c r="B66"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="189"/>
-      <c r="E66" s="189"/>
-      <c r="F66" s="20"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="166"/>
+      <c r="E66" s="166"/>
+      <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="46"/>
       <c r="I66" s="50"/>
-      <c r="J66" s="53"/>
+      <c r="J66"/>
       <c r="L66"/>
-      <c r="M66" s="159" t="s">
-        <v>34</v>
-      </c>
-      <c r="N66" s="196"/>
-      <c r="O66" s="42"/>
-      <c r="P66" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q66" s="42">
-        <f>SUMA(Q37:Q38)</f>
-      </c>
-      <c r="R66" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="S66" s="42">
-        <f>SUMA(S37:S38)</f>
-      </c>
-      <c r="T66" s="52" t="s">
-        <v>11</v>
-      </c>
-      <c r="U66" s="42">
-        <f>SUMA(U37:U38)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M66" s="54"/>
+      <c r="N66" s="55"/>
+      <c r="O66" s="70"/>
+      <c r="P66" s="23"/>
+      <c r="Q66" s="69"/>
+      <c r="R66" s="70"/>
+      <c r="S66" s="70"/>
+      <c r="T66" s="6"/>
+    </row>
+    <row r="67" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="25"/>
       <c r="B67"/>
-      <c r="C67" s="90"/>
-      <c r="D67" s="189"/>
-      <c r="E67" s="189"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
       <c r="F67" s="23"/>
       <c r="G67" s="1"/>
       <c r="H67" s="46"/>
       <c r="I67" s="50"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="54"/>
-      <c r="N67" s="55"/>
-      <c r="O67" s="70"/>
-      <c r="P67" s="23"/>
-      <c r="Q67" s="69"/>
-      <c r="R67" s="70"/>
-      <c r="S67" s="70"/>
-      <c r="T67" s="6"/>
-    </row>
-    <row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="167" t="s">
+        <v>47</v>
+      </c>
+      <c r="N67" s="168"/>
+      <c r="O67" s="169"/>
+      <c r="P67" s="181"/>
+      <c r="Q67" s="182"/>
+      <c r="R67" s="167" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="168"/>
+      <c r="T67" s="183" t="str">
+        <f>Q25</f>
+      </c>
+      <c r="U67" s="184"/>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="23"/>
+      <c r="D68" s="166"/>
+      <c r="E68" s="166"/>
+      <c r="F68" s="63"/>
       <c r="G68" s="1"/>
       <c r="H68" s="46"/>
       <c r="I68" s="50"/>
       <c r="J68"/>
       <c r="L68"/>
-      <c r="M68" s="181" t="s">
-        <v>47</v>
-      </c>
-      <c r="N68" s="204"/>
-      <c r="O68" s="182"/>
-      <c r="P68" s="191"/>
-      <c r="Q68" s="192"/>
-      <c r="R68" s="181" t="s">
-        <v>37</v>
-      </c>
-      <c r="S68" s="204"/>
-      <c r="T68" s="187" t="str">
-        <f>Q25</f>
-      </c>
-      <c r="U68" s="188"/>
+      <c r="M68" s="56"/>
+      <c r="N68" s="83"/>
+      <c r="O68" s="83"/>
+      <c r="P68" s="57"/>
+      <c r="Q68" s="58"/>
+      <c r="R68" s="58"/>
+      <c r="S68" s="58"/>
+      <c r="T68" s="56"/>
+      <c r="U68" s="56"/>
     </row>
     <row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="25"/>
-      <c r="B69"/>
+      <c r="B69" s="90"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="189"/>
-      <c r="E69" s="189"/>
+      <c r="D69" s="166"/>
+      <c r="E69" s="166"/>
       <c r="F69" s="63"/>
       <c r="G69" s="1"/>
       <c r="H69" s="46"/>
       <c r="I69" s="50"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="56"/>
-      <c r="N69" s="83"/>
-      <c r="O69" s="83"/>
-      <c r="P69" s="57"/>
-      <c r="Q69" s="58"/>
-      <c r="R69" s="58"/>
-      <c r="S69" s="58"/>
-      <c r="T69" s="56"/>
-      <c r="U69" s="56"/>
-    </row>
-    <row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M69" s="171" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
+      <c r="R69" s="179"/>
+      <c r="S69" s="179"/>
+      <c r="T69" s="179"/>
+      <c r="U69" s="180"/>
+      <c r="V69" s="51"/>
+    </row>
+    <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
-      <c r="B70" s="90"/>
+      <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="189"/>
-      <c r="E70" s="189"/>
+      <c r="D70" s="166"/>
+      <c r="E70" s="166"/>
       <c r="F70" s="63"/>
       <c r="G70" s="1"/>
       <c r="H70" s="46"/>
       <c r="I70" s="50"/>
       <c r="J70"/>
-      <c r="L70"/>
-      <c r="M70" s="159" t="s">
-        <v>35</v>
-      </c>
-      <c r="N70" s="160"/>
-      <c r="O70" s="160"/>
-      <c r="P70" s="160"/>
-      <c r="Q70" s="160"/>
-      <c r="R70" s="160"/>
-      <c r="S70" s="160"/>
-      <c r="T70" s="160"/>
-      <c r="U70" s="203"/>
-      <c r="V70" s="51"/>
-    </row>
-    <row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L70" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="M70" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="131"/>
+      <c r="O70" s="131"/>
+      <c r="P70" s="131" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q70" s="131"/>
+      <c r="R70" s="131"/>
+      <c r="S70" s="131"/>
+      <c r="T70" s="131" t="s">
+        <v>57</v>
+      </c>
+      <c r="U70" s="132" t="s">
+        <v>60</v>
+      </c>
+      <c r="V70" s="144" t="s">
+        <v>58</v>
+      </c>
+      <c r="W70" s="144" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="25"/>
-      <c r="B71" s="20"/>
+      <c r="B71" s="115"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="189"/>
-      <c r="E71" s="189"/>
+      <c r="D71" s="166"/>
+      <c r="E71" s="166"/>
       <c r="F71" s="63"/>
       <c r="G71" s="1"/>
       <c r="H71" s="46"/>
       <c r="I71" s="50"/>
-      <c r="J71"/>
-      <c r="L71" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="M71" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="N71" s="131"/>
-      <c r="O71" s="131"/>
-      <c r="P71" s="131" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q71" s="131"/>
-      <c r="R71" s="131"/>
-      <c r="S71" s="131"/>
-      <c r="T71" s="131" t="s">
-        <v>57</v>
-      </c>
-      <c r="U71" s="132" t="s">
-        <v>60</v>
-      </c>
-      <c r="V71" s="144" t="s">
-        <v>58</v>
-      </c>
-      <c r="W71" s="144" t="s">
-        <v>50</v>
-      </c>
+      <c r="J71" s="23"/>
+      <c r="L71" s="0"/>
+      <c r="M71" s="59"/>
+      <c r="N71" s="60"/>
+      <c r="O71" s="143" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="62"/>
+      <c r="Q71" s="61"/>
+      <c r="R71" s="177" t="s">
+        <v>6</v>
+      </c>
+      <c r="S71" s="177"/>
+      <c r="T71" s="133"/>
+      <c r="U71" s="134"/>
+      <c r="V71" s="51"/>
     </row>
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="25"/>
-      <c r="B72" s="115"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="189"/>
-      <c r="E72" s="189"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="89"/>
+      <c r="D72" s="166"/>
+      <c r="E72" s="166"/>
       <c r="F72" s="63"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="50"/>
-      <c r="J72" s="23"/>
-      <c r="L72" s="0"/>
-      <c r="M72" s="59"/>
-      <c r="N72" s="60"/>
-      <c r="O72" s="143" t="s">
-        <v>43</v>
-      </c>
-      <c r="P72" s="62"/>
-      <c r="Q72" s="61"/>
-      <c r="R72" s="201" t="s">
-        <v>6</v>
-      </c>
-      <c r="S72" s="201"/>
-      <c r="T72" s="133"/>
-      <c r="U72" s="134"/>
+      <c r="I72" s="115"/>
+      <c r="L72"/>
+      <c r="M72" s="85"/>
+      <c r="N72" s="86"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="87"/>
+      <c r="Q72" s="56"/>
+      <c r="R72" s="175"/>
+      <c r="S72" s="175"/>
+      <c r="T72" s="65"/>
+      <c r="U72" s="95"/>
       <c r="V72" s="51"/>
     </row>
     <row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B73" s="51"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="89"/>
       <c r="C73" s="89"/>
-      <c r="D73" s="189"/>
-      <c r="E73" s="189"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="25"/>
       <c r="F73" s="63"/>
       <c r="I73" s="115"/>
-      <c r="L73"/>
+      <c r="L73" s="45"/>
       <c r="M73" s="85"/>
       <c r="N73" s="86"/>
-      <c r="O73" s="18"/>
+      <c r="O73" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="P73" s="87"/>
       <c r="Q73" s="56"/>
-      <c r="R73" s="199"/>
-      <c r="S73" s="199"/>
+      <c r="R73" s="175" t="s">
+        <v>10</v>
+      </c>
+      <c r="S73" s="175"/>
       <c r="T73" s="65"/>
       <c r="U73" s="95"/>
       <c r="V73" s="51"/>
     </row>
     <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="49"/>
-      <c r="B74" s="89"/>
-      <c r="C74" s="89"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="25"/>
-      <c r="F74" s="63"/>
-      <c r="I74" s="115"/>
-      <c r="L74" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12345</t>
-        </is>
-      </c>
-      <c r="M74" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
+      <c r="L74" s="45"/>
+      <c r="M74" s="85"/>
       <c r="N74" s="86"/>
-      <c r="O74" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="P74" s="87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
+      <c r="O74" s="123"/>
+      <c r="P74" s="87"/>
       <c r="Q74" s="56"/>
-      <c r="R74" s="199" t="s">
-        <v>10</v>
-      </c>
-      <c r="S74" s="199"/>
-      <c r="T74" s="65">
-        <v>150000</v>
-      </c>
-      <c r="U74" s="95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Banco Santander</t>
-        </is>
-      </c>
+      <c r="R74" s="175"/>
+      <c r="S74" s="175"/>
+      <c r="T74" s="65"/>
+      <c r="U74" s="95"/>
       <c r="V74" s="51"/>
     </row>
     <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="L75" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67890</t>
-        </is>
-      </c>
-      <c r="M75" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLIENTE UNO</t>
-        </is>
-      </c>
-      <c r="N75" s="86"/>
-      <c r="O75" s="123"/>
-      <c r="P75" s="87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F001</t>
-        </is>
-      </c>
-      <c r="Q75" s="56"/>
-      <c r="R75" s="199"/>
-      <c r="S75" s="199"/>
-      <c r="T75" s="65">
-        <v>150000</v>
-      </c>
-      <c r="U75" s="95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Banco Santander</t>
-        </is>
-      </c>
+      <c r="L75" s="45"/>
+      <c r="M75" s="137" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="138"/>
+      <c r="O75" s="139"/>
+      <c r="P75" s="140"/>
+      <c r="Q75" s="141"/>
+      <c r="R75" s="176"/>
+      <c r="S75" s="176"/>
+      <c r="T75" s="173"/>
+      <c r="U75" s="174"/>
       <c r="V75" s="51"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="45"/>
       <c r="M76" s="137" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N76" s="138"/>
       <c r="O76" s="139"/>
       <c r="P76" s="140"/>
       <c r="Q76" s="141"/>
-      <c r="R76" s="200"/>
-      <c r="S76" s="200"/>
-      <c r="T76" s="197"/>
-      <c r="U76" s="198"/>
+      <c r="R76" s="142"/>
+      <c r="S76" s="142"/>
+      <c r="T76" s="173"/>
+      <c r="U76" s="174"/>
       <c r="V76" s="51"/>
     </row>
-    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L77" s="45"/>
-      <c r="M77" s="137" t="s">
-        <v>62</v>
-      </c>
-      <c r="N77" s="138"/>
-      <c r="O77" s="139"/>
-      <c r="P77" s="140"/>
-      <c r="Q77" s="141"/>
-      <c r="R77" s="142"/>
-      <c r="S77" s="142"/>
-      <c r="T77" s="197"/>
-      <c r="U77" s="198"/>
+      <c r="M77" s="94"/>
+      <c r="N77" s="64"/>
+      <c r="O77" s="123"/>
+      <c r="P77" s="87"/>
+      <c r="Q77" s="56"/>
+      <c r="R77" s="56"/>
+      <c r="S77" s="56"/>
+      <c r="T77" s="65"/>
+      <c r="U77" s="95"/>
       <c r="V77" s="51"/>
     </row>
     <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L78" s="45"/>
-      <c r="M78" s="94"/>
-      <c r="N78" s="64"/>
-      <c r="O78" s="123"/>
-      <c r="P78" s="87"/>
-      <c r="Q78" s="56"/>
-      <c r="R78" s="56"/>
-      <c r="S78" s="56"/>
-      <c r="T78" s="65"/>
-      <c r="U78" s="95"/>
+      <c r="M78" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="102">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="96"/>
+      <c r="P78" s="98"/>
+      <c r="Q78" s="97"/>
+      <c r="R78" s="97"/>
+      <c r="S78" s="97"/>
+      <c r="T78" s="99"/>
+      <c r="U78" s="100"/>
       <c r="V78" s="51"/>
     </row>
-    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L79" s="45"/>
-      <c r="M79" s="101" t="s">
-        <v>11</v>
-      </c>
-      <c r="N79" s="102">
-        <f>SUM(N77:N78)</f>
-        <v>0</v>
-      </c>
-      <c r="O79" s="96"/>
-      <c r="P79" s="98"/>
-      <c r="Q79" s="97"/>
-      <c r="R79" s="97"/>
-      <c r="S79" s="97"/>
-      <c r="T79" s="99"/>
-      <c r="U79" s="100"/>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
       <c r="V79" s="51"/>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M80"/>
-      <c r="O80" s="5"/>
-      <c r="Q80"/>
-      <c r="S80"/>
-      <c r="T80" s="6"/>
+      <c r="O80"/>
       <c r="V80" s="51"/>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O81"/>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
       <c r="V81" s="51"/>
     </row>
     <row r="82" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M82" s="23"/>
-      <c r="N82" s="23"/>
-      <c r="O82" s="23"/>
-      <c r="P82" s="23"/>
-      <c r="Q82" s="23"/>
       <c r="V82" s="51"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
@@ -4293,7 +4130,7 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="51"/>
     </row>
-    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V97" s="51"/>
     </row>
     <row r="98" spans="22:22" x14ac:dyDescent="0.3">
@@ -4341,53 +4178,19 @@
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="51"/>
     </row>
-    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V113" s="51"/>
-    </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="M68:O68"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="T77:U77"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="M70:U70"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="O29:P29"/>
@@ -4404,18 +4207,49 @@
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
     <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D51:E51"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -1950,5 +1950,5 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}"><dimension ref="A1:W113"/><sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/><cols><col min="1" max="1" width="17.33203125" customWidth="1"/><col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/><col min="3" max="3" width="12.6640625" customWidth="1"/><col min="4" max="4" width="12.6640625" style="3" customWidth="1"/><col min="5" max="5" width="12.6640625" customWidth="1"/><col min="6" max="6" width="12.6640625" style="3" customWidth="1"/><col min="7" max="9" width="12.6640625" customWidth="1"/><col min="10" max="10" width="12.6640625" style="3" customWidth="1"/><col min="11" max="11" width="12.6640625" customWidth="1"/><col min="12" max="12" width="12.6640625" style="3" customWidth="1"/><col min="13" max="13" width="11.5546875" style="3" customWidth="1"/><col min="14" max="14" width="11" bestFit="1" customWidth="1"/><col min="15" max="15" width="11.6640625" style="4" customWidth="1"/><col min="16" max="19" width="11.6640625" style="3" customWidth="1"/><col min="20" max="20" width="13.88671875" customWidth="1"/><col min="21" max="21" width="14" customWidth="1"/><col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/><col min="23" max="23" width="16" customWidth="1"/></cols><sheetData><row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A1" s="7" t="s"><v>50</v></c><c r="B1" s="112" t="inlineStr"><is><t xml:space="preserve">JUAN PEREZ</t></is></c><c r="C1" s="120" t="inlineStr"><is><t xml:space="preserve">MARIA LOPEZ</t></is></c><c r="D1" s="120"/><c r="E1" s="112"/><c r="F1" s="120"/><c r="G1" s="120"/><c r="H1" s="112"/><c r="I1" s="112"/><c r="J1" s="120"/><c r="K1" s="120"/><c r="L1" s="112"/><c r="M1" s="112"/><c r="N1" s="112"/><c r="O1" s="112"/><c r="P1" s="112"/><c r="Q1" s="112"/><c r="R1" s="121"/><c r="S1" s="120"/><c r="T1" s="120"/><c r="U1" s="7"/><c r="V1" s="7"/><c r="W1" s="114"/></row><row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A2" s="7" t="s"><v>51</v></c><c r="B2" s="112"/><c r="C2" s="120"/><c r="D2" s="120"/><c r="E2" s="112"/><c r="F2" s="120"/><c r="G2" s="128"/><c r="H2" s="112"/><c r="I2" s="112"/><c r="J2" s="120"/><c r="K2" s="120"/><c r="L2" s="112"/><c r="M2" s="112"/><c r="N2" s="112"/><c r="O2" s="112"/><c r="P2" s="112"/><c r="Q2" s="112"/><c r="R2" s="121"/><c r="S2" s="120"/><c r="T2" s="120"/><c r="U2" s="7"/><c r="V2" s="7"/><c r="W2" s="114"/></row><row r="3" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A3" s="122" t="s"><v>35</v></c><c r="B3" s="120"/><c r="C3" s="120"/><c r="D3" s="120"/><c r="E3" s="120"/><c r="F3" s="120"/><c r="G3" s="120"/><c r="H3" s="120"/><c r="I3" s="120"/><c r="J3" s="120"/><c r="K3" s="120"/><c r="L3" s="120"/><c r="M3" s="120"/><c r="N3" s="120"/><c r="O3" s="120"/><c r="P3" s="120"/><c r="Q3" s="120"/><c r="R3" s="120"/><c r="S3" s="120"/><c r="T3" s="120"/><c r="U3" s="110"/><c r="V3" s="163"/><c r="W3" s="116"/></row><row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A4" s="122" t="s"><v>52</v></c><c r="B4" s="120"/><c r="C4" s="120"/><c r="D4" s="120"/><c r="E4" s="120"/><c r="F4" s="120"/><c r="G4" s="120"/><c r="H4" s="120"/><c r="I4" s="120"/><c r="J4" s="120"/><c r="K4" s="120"/><c r="L4" s="120"/><c r="M4" s="120"/><c r="N4" s="120"/><c r="O4" s="120"/><c r="P4" s="120"/><c r="Q4" s="120"/><c r="R4" s="120"/><c r="S4" s="120"/><c r="T4" s="120"/><c r="U4" s="110"/><c r="V4" s="163"/><c r="W4" s="116"/></row><row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A5" s="122" t="s"><v>0</v></c><c r="B5" s="129" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="C5" s="129" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="D5" s="129"/><c r="E5" s="129"/><c r="F5" s="129"/><c r="G5" s="129"/><c r="H5" s="129"/><c r="I5" s="129"/><c r="J5" s="129"/><c r="K5" s="129"/><c r="L5" s="129"/><c r="M5" s="129"/><c r="N5" s="129"/><c r="O5" s="129"/><c r="P5" s="129"/><c r="Q5" s="129"/><c r="R5" s="120"/><c r="S5" s="120"/><c r="T5" s="120"/><c r="U5" s="111"/><c r="V5" s="111"/><c r="W5" s="111"/></row><row r="6" spans="1:23" s="45" customFormat="1" x14ac:dyDescent="0.3"><c r="A6" s="122" t="s"><v>1</v></c><c r="B6" s="120"><v>10</v></c><c r="C6" s="120"><v>10</v></c><c r="D6" s="120"/><c r="E6" s="120"/><c r="F6" s="120"/><c r="G6" s="120"/><c r="H6" s="120"/><c r="I6" s="120"/><c r="J6" s="120"/><c r="K6" s="120"/><c r="L6" s="120"/><c r="M6" s="111"/><c r="N6" s="111"/><c r="O6" s="111"/><c r="P6" s="111"/><c r="Q6" s="111"/><c r="R6" s="120"/><c r="S6" s="120"/><c r="T6" s="120"/><c r="U6" s="111"/><c r="V6" s="111"/><c r="W6" s="111"/></row><row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3"><c r="A7" s="122" t="s"><v>2</v></c><c r="B7" s="164"><v>1000000</v></c><c r="C7" s="164"><v>1000000</v></c><c r="D7" s="164"/><c r="E7" s="164"/><c r="F7" s="164"/><c r="G7" s="164"/><c r="H7" s="164"/><c r="I7" s="164"/><c r="J7" s="164"/><c r="K7" s="164"/><c r="L7" s="164"/><c r="M7" s="164"/><c r="N7" s="164"/><c r="O7" s="164"/><c r="P7" s="164"/><c r="Q7" s="164"/><c r="R7" s="156"/><c r="S7" s="156"/><c r="T7" s="156"/><c r="U7" s="157"/><c r="V7" s="157"/><c r="W7" s="157"/></row><row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A8" s="112"/><c r="B8" s="157"/><c r="C8" s="111"/><c r="D8" s="157"/><c r="E8" s="111"/><c r="F8" s="110"/><c r="G8" s="111"/><c r="H8" s="157"/><c r="I8" s="111"/><c r="J8" s="157"/><c r="K8" s="111"/><c r="L8" s="110"/><c r="M8" s="111"/><c r="N8" s="110"/><c r="O8" s="111"/><c r="P8" s="158"/><c r="Q8" s="111"/><c r="R8" s="158"/><c r="S8" s="111"/><c r="T8" s="158"/><c r="U8" s="111"/><c r="V8" s="110"/><c r="W8" s="111"/></row><row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A9" s="113" t="s"><v>3</v></c><c r="B9" s="165"><v>450000</v></c><c r="C9" s="165"><v>450000</v></c><c r="D9" s="165"/><c r="E9" s="157"/><c r="F9" s="110"/><c r="G9" s="157"/><c r="H9" s="110"/><c r="I9" s="157"/><c r="J9" s="110"/><c r="K9" s="157"/><c r="L9" s="110"/><c r="M9" s="157"/><c r="N9" s="110"/><c r="O9" s="157"/><c r="P9" s="158"/><c r="Q9" s="157"/><c r="R9" s="158"/><c r="S9" s="159"/><c r="T9" s="159"/><c r="U9" s="157"/><c r="V9" s="110"/><c r="W9" s="157"/></row><row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A10" s="113" t="s"><v>54</v></c><c r="B10" s="165"><v>50000</v></c><c r="C10" s="165"><v>50000</v></c><c r="D10" s="165"/><c r="E10" s="157"/><c r="F10" s="110"/><c r="G10" s="157"/><c r="H10" s="110"/><c r="I10" s="157"/><c r="J10" s="110"/><c r="K10" s="157"/><c r="L10" s="110"/><c r="M10" s="157"/><c r="N10" s="110"/><c r="O10" s="157"/><c r="P10" s="158"/><c r="Q10" s="157"/><c r="R10" s="158"/><c r="S10" s="159"/><c r="T10" s="159"/><c r="U10" s="157"/><c r="V10" s="110"/><c r="W10" s="157"/></row><row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A11" s="113" t="s"><v>4</v></c><c r="B11" s="165"><v>300000</v></c><c r="C11" s="165"><v>300000</v></c><c r="D11" s="165"/><c r="E11" s="157"/><c r="F11" s="110"/><c r="G11" s="157"/><c r="H11" s="110"/><c r="I11" s="157"/><c r="J11" s="110"/><c r="K11" s="157"/><c r="L11" s="110"/><c r="M11" s="157"/><c r="N11" s="110"/><c r="O11" s="157"/><c r="P11" s="158"/><c r="Q11" s="157"/><c r="R11" s="158"/><c r="S11" s="159"/><c r="T11" s="159"/><c r="U11" s="157"/><c r="V11" s="110"/><c r="W11" s="157"/></row><row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A12" s="113" t="s"><v>5</v></c><c r="B12" s="165"/><c r="C12" s="165"/><c r="D12" s="165"/><c r="E12" s="157"/><c r="F12" s="110"/><c r="G12" s="157"/><c r="H12" s="110"/><c r="I12" s="157"/><c r="J12" s="110"/><c r="K12" s="157"/><c r="L12" s="110"/><c r="M12" s="157"/><c r="N12" s="110"/><c r="O12" s="157"/><c r="P12" s="158"/><c r="Q12" s="157"/><c r="R12" s="158"/><c r="S12" s="159"/><c r="T12" s="159"/><c r="U12" s="157"/><c r="V12" s="110"/><c r="W12" s="157"/></row><row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A13" s="113" t="s"><v>6</v></c><c r="B13" s="165"/><c r="C13" s="165"/><c r="D13" s="165"/><c r="E13" s="157"/><c r="F13" s="110"/><c r="G13" s="157"/><c r="H13" s="110"/><c r="I13" s="157"/><c r="J13" s="110"/><c r="K13" s="157"/><c r="L13" s="110"/><c r="M13" s="157"/><c r="N13" s="110"/><c r="O13" s="157"/><c r="P13" s="158"/><c r="Q13" s="157"/><c r="R13" s="158"/><c r="S13" s="159"/><c r="T13" s="159"/><c r="U13" s="157"/><c r="V13" s="110"/><c r="W13" s="157"/></row><row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A14" s="113" t="s"><v>7</v></c><c r="B14" s="165"/><c r="C14" s="165"/><c r="D14" s="165"/><c r="E14" s="157"/><c r="F14" s="110"/><c r="G14" s="157"/><c r="H14" s="110"/><c r="I14" s="157"/><c r="J14" s="110"/><c r="K14" s="157"/><c r="L14" s="110"/><c r="M14" s="157"/><c r="N14" s="110"/><c r="O14" s="157"/><c r="P14" s="158"/><c r="Q14" s="157"/><c r="R14" s="158"/><c r="S14" s="159"/><c r="T14" s="159"/><c r="U14" s="157"/><c r="V14" s="110"/><c r="W14" s="157"/></row><row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A15" s="113" t="s"><v>8</v></c><c r="B15" s="165"/><c r="C15" s="165"/><c r="D15" s="165"/><c r="E15" s="157"/><c r="F15" s="110"/><c r="G15" s="157"/><c r="H15" s="110"/><c r="I15" s="157"/><c r="J15" s="110"/><c r="K15" s="157"/><c r="L15" s="110"/><c r="M15" s="157"/><c r="N15" s="110"/><c r="O15" s="157"/><c r="P15" s="158"/><c r="Q15" s="157"/><c r="R15" s="158"/><c r="S15" s="159"/><c r="T15" s="159"/><c r="U15" s="157"/><c r="V15" s="110"/><c r="W15" s="157"/></row><row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A16" s="113" t="s"><v>9</v></c><c r="B16" s="165"/><c r="C16" s="165"/><c r="D16" s="165"/><c r="E16" s="157"/><c r="F16" s="110"/><c r="G16" s="157"/><c r="H16" s="110"/><c r="I16" s="160"/><c r="J16" s="110"/><c r="K16" s="160"/><c r="L16" s="110"/><c r="M16" s="157"/><c r="N16" s="110"/><c r="O16" s="157"/><c r="P16" s="158"/><c r="Q16" s="157"/><c r="R16" s="158"/><c r="S16" s="159"/><c r="T16" s="159"/><c r="U16" s="157"/><c r="V16" s="110"/><c r="W16" s="157"/></row><row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A17" s="113" t="s"><v>10</v></c><c r="B17" s="165"/><c r="C17" s="165"/><c r="D17" s="165"/><c r="E17" s="157"/><c r="F17" s="110"/><c r="G17" s="157"/><c r="H17" s="110"/><c r="I17" s="160"/><c r="J17" s="110"/><c r="K17" s="157"/><c r="L17" s="110"/><c r="M17" s="157"/><c r="N17" s="110"/><c r="O17" s="157"/><c r="P17" s="158"/><c r="Q17" s="157"/><c r="R17" s="158"/><c r="S17" s="159"/><c r="T17" s="159"/><c r="U17" s="157"/><c r="V17" s="110"/><c r="W17" s="157"/></row><row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A18" s="113" t="s"><v>11</v></c><c r="B18" s="110"><f>SUM(B9:B17)</f><v>0</v></c><c r="C18" s="110"><f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f><v>0</v></c><c r="D18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="E18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="F18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="G18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="H18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="I18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="J18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="K18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="L18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="M18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="N18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="O18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="P18" s="110"><f t="shared" ref="P18" si="1">SUM(P9:P17)</f><v>0</v></c><c r="Q18" s="110"><f>SUM(Q9:Q17)</f><v>0</v></c><c r="R18" s="110"><f>SUM(R9:R17)</f><v>0</v></c><c r="S18" s="116"><f>SUM(S9:S17)</f><v>0</v></c><c r="T18" s="116"><f>SUM(T9:T17)</f><v>0</v></c><c r="U18" s="110"><f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f><v>0</v></c><c r="V18" s="110"><f t="shared" si="2"/><v>0</v></c><c r="W18" s="110"><f t="shared" si="2"/><v>0</v></c></row><row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A19" s="113"/><c r="B19" s="110"/><c r="C19" s="110"/><c r="D19" s="110"/><c r="E19" s="110"/><c r="F19" s="157"/><c r="G19" s="110"/><c r="H19" s="110"/><c r="I19" s="110"/><c r="J19" s="110"/><c r="K19" s="110"/><c r="L19" s="110"/><c r="M19" s="110"/><c r="N19" s="110"/><c r="O19" s="110"/><c r="P19" s="110"/><c r="Q19" s="110"/><c r="R19" s="110"/><c r="S19" s="116"/><c r="T19" s="116"/><c r="U19" s="110"/><c r="V19" s="110"/><c r="W19" s="110"/></row><row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3"><c r="A20" s="113" t="s"><v>12</v></c><c r="B20" s="110" t="e"><f t="shared" ref="B20:O20" si="3">B18-B7</f><v>#VALUE!</v></c><c r="C20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="D20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="E20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="F20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="G20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="H20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="I20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="J20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="K20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="L20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="M20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="N20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="O20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="P20" s="110"><f t="shared" ref="P20" si="4">P18-P7</f><v>0</v></c><c r="Q20" s="110"><f>Q18-Q7</f><v>0</v></c><c r="R20" s="110"><f>R18-R7</f><v>0</v></c><c r="S20" s="110"><f>S18-S7</f><v>0</v></c><c r="T20" s="110"><f>T18-T7</f><v>0</v></c><c r="U20" s="110"><f t="shared" ref="U20:W20" si="5">U18-U7</f><v>0</v></c><c r="V20" s="110"><f t="shared" si="5"/><v>0</v></c><c r="W20" s="110"><f t="shared" si="5"/><v>0</v></c></row><row r="21" spans="1:23" x14ac:dyDescent="0.3"><c r="A21" s="1"/><c r="B21" s="9"/><c r="C21" s="10"/><c r="D21" s="9"/><c r="E21" s="10"/><c r="F21" s="11"/><c r="G21" s="10"/><c r="H21" s="11"/><c r="I21" s="9"/><c r="J21" s="9"/><c r="K21" s="10"/><c r="L21" s="12"/><c r="M21" s="12"/><c r="N21" s="10"/><c r="O21" s="9"/><c r="P21" s="9"/><c r="Q21" s="10"/><c r="R21" s="12"/><c r="S21" s="12"/><c r="T21" s="9"/><c r="U21" s="9"/><c r="V21" s="9"/><c r="W21" s="9"/></row><row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35"><c r="D22" s="2"/><c r="M22" s="198" t="s"><v>48</v></c><c r="N22" s="198"/><c r="O22" s="198"/><c r="P22" s="198"/><c r="Q22" s="198"/><c r="R22" s="198"/><c r="S22" s="198"/><c r="T22" s="198"/><c r="U22" s="198"/></row><row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="D23" s="6"/><c r="J23"/><c r="L23"/><c r="M23" s="14" t="s"><v>13</v></c><c r="N23" s="207" t="inlineStr"><is><t xml:space="preserve">24-06-2026</t></is></c><c r="O23" s="208"/><c r="P23" s="208"/><c r="Q23" s="208"/><c r="R23" s="208"/><c r="S23" s="209"/><c r="T23" s="119" t="s"><v>38</v></c><c r="U23" s="106"><v>20</v></c><c r="W23" s="91" t="s"><v>44</v></c></row><row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="B24" s="2"/><c r="C24" s="18"/><c r="J24"/><c r="K24" s="15"/><c r="L24"/><c r="M24" s="16"/><c r="N24" s="210" t="s"><v>49</v></c><c r="O24" s="211"/><c r="P24" s="211"/><c r="Q24" s="211"/><c r="R24" s="211"/><c r="S24" s="212"/><c r="T24" s="108" t="s"><v>11</v></c><c r="U24" s="107"><v>2000000</v></c><c r="W24" s="118"><v>20</v></c></row><row r="25" spans="1:23" x14ac:dyDescent="0.3"><c r="B25" s="2"/><c r="C25" s="103"/><c r="D25" s="3" t="s"><v>15</v></c><c r="E25" s="4"/><c r="J25"/><c r="L25"/><c r="M25" s="215" t="s"><v>16</v></c><c r="N25" s="216"/><c r="O25" s="148"/><c r="P25" s="149"/><c r="Q25" s="145"><v>900000</v></c><c r="R25" s="146"/><c r="S25" s="147"/><c r="T25" s="213" t="s"><v>17</v></c><c r="U25" s="214"/><c r="V25" s="13"/><c r="W25" s="82" t="s"><v>45</v></c></row><row r="26" spans="1:23" x14ac:dyDescent="0.3"><c r="E26" s="4"/><c r="J26"/><c r="L26"/><c r="M26" s="79" t="s"><v>53</v></c><c r="N26" s="80"/><c r="O26" s="126"/><c r="P26" s="127"/><c r="Q26" s="188"><v>100000</v></c><c r="R26" s="189"/><c r="S26" s="190"/><c r="T26" s="124"/><c r="U26" s="125"/><c r="V26" s="13"/><c r="W26" s="82"/></row><row r="27" spans="1:23" x14ac:dyDescent="0.3"><c r="I27" s="109" t="str"><f>B1</f></c><c r="J27" s="136" t="str"><f>B9</f></c><c r="L27"/><c r="M27" s="79" t="s"><v>18</v></c><c r="N27" s="80"/><c r="O27" s="186"/><c r="P27" s="187"/><c r="Q27" s="188"><v>600000</v></c><c r="R27" s="189"/><c r="S27" s="190"/><c r="T27" s="205" t="s"><v>19</v></c><c r="U27" s="206"/><c r="V27" s="19"/><c r="W27" s="92"><v>2000000</v></c></row><row r="28" spans="1:23" x14ac:dyDescent="0.3"><c r="I28" s="109"><f>C1</f><v>0</v></c><c r="J28" s="136"><f>C9</f><v>0</v></c><c r="L28"/><c r="M28" s="203" t="s"><v>20</v></c><c r="N28" s="204"/><c r="O28" s="186"/><c r="P28" s="187"/><c r="Q28" s="188"/><c r="R28" s="189"/><c r="S28" s="190"/><c r="T28" s="201" t="s"><v>39</v></c><c r="U28" s="202"/><c r="V28" s="21"/><c r="W28" s="13"/></row><row r="29" spans="1:23" x14ac:dyDescent="0.3"><c r="I29" s="109"><f>D1</f><v>0</v></c><c r="J29" s="136"><f>D9</f><v>0</v></c><c r="K29" s="24"/><c r="L29"/><c r="M29" s="203" t="s"><v>21</v></c><c r="N29" s="204"/><c r="O29" s="186"/><c r="P29" s="187"/><c r="Q29" s="188"/><c r="R29" s="189"/><c r="S29" s="190"/><c r="T29" s="199" t="s"><v>40</v></c><c r="U29" s="200"/><c r="W29" s="93" t="str"><f>U23</f></c></row><row r="30" spans="1:23" x14ac:dyDescent="0.3"><c r="A30" s="1"/><c r="I30" s="109"><f>E1</f><v>0</v></c><c r="J30" s="136"><f>E9</f><v>0</v></c><c r="L30"/><c r="M30" s="203" t="s"><v>22</v></c><c r="N30" s="204"/><c r="O30" s="186"/><c r="P30" s="217"/><c r="Q30" s="188"/><c r="R30" s="189"/><c r="S30" s="190"/><c r="T30" s="218" t="s"><v>41</v></c><c r="U30" s="219"/><c r="V30" s="24"/><c r="W30" s="21" t="str"><f>Q34</f></c></row><row r="31" spans="1:23" x14ac:dyDescent="0.3"><c r="A31" s="1"/><c r="I31" s="109"><f>F1</f><v>0</v></c><c r="J31" s="136"><f>F9</f><v>0</v></c><c r="L31"/><c r="M31" s="203" t="s"><v>23</v></c><c r="N31" s="204"/><c r="O31" s="186"/><c r="P31" s="187"/><c r="Q31" s="188"/><c r="R31" s="189"/><c r="S31" s="190"/><c r="T31" s="28"/><c r="U31" s="26"/></row><row r="32" spans="1:23" x14ac:dyDescent="0.3"><c r="A32" s="1"/><c r="I32" s="109"><f>G1</f><v>0</v></c><c r="J32" s="136"><f>G9</f><v>0</v></c><c r="L32"/><c r="M32" s="203" t="s"><v>24</v></c><c r="N32" s="204"/><c r="O32" s="186"/><c r="P32" s="187"/><c r="Q32" s="188"/><c r="R32" s="189"/><c r="S32" s="190"/><c r="T32" s="28"/><c r="U32" s="26"/><c r="W32" s="82" t="s"><v>46</v></c></row><row r="33" spans="1:23" x14ac:dyDescent="0.3"><c r="A33" s="1"/><c r="I33" s="109"><f>H1</f><v>0</v></c><c r="J33" s="136"><f>H9</f><v>0</v></c><c r="L33"/><c r="M33" s="79" t="s"><v>25</v></c><c r="N33" s="81"/><c r="O33" s="186"/><c r="P33" s="187"/><c r="Q33" s="188"/><c r="R33" s="189"/><c r="S33" s="190"/><c r="T33" s="28"/><c r="U33" s="26"/><c r="W33" s="117" t="e"><f>W30-W27</f><v>#VALUE!</v></c></row><row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A34" s="1"/><c r="I34" s="109"><f>I1</f><v>0</v></c><c r="J34" s="136"><f>I9</f><v>0</v></c><c r="L34" s="8"/><c r="M34" s="191" t="s"><v>26</v></c><c r="N34" s="192"/><c r="O34" s="193"/><c r="P34" s="194"/><c r="Q34" s="188"><v>2000000</v></c><c r="R34" s="189"/><c r="S34" s="190"/><c r="T34" s="30"/><c r="U34" s="29"/><c r="V34" s="1"/><c r="W34" s="24"/></row><row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A35" s="1"/><c r="D35" s="31"/><c r="I35" s="41"><f>J1</f><v>0</v></c><c r="J35" s="27"><f>J9</f><v>0</v></c><c r="L35"/><c r="M35" s="195" t="s"><v>27</v></c><c r="N35" s="196"/><c r="O35" s="197"/><c r="P35" s="167" t="s"><v>28</v></c><c r="Q35" s="169"/><c r="R35" s="167" t="s"><v>29</v></c><c r="S35" s="169"/><c r="T35" s="167" t="s"><v>30</v></c><c r="U35" s="169"/><c r="V35" s="1"/><c r="W35" s="1"/></row><row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B36" s="9"/><c r="I36" s="41"><f>K1</f><v>0</v></c><c r="J36" s="27"><f>K9</f><v>0</v></c><c r="L36"/><c r="M36" s="33" t="s"><v>13</v></c><c r="N36" s="34" t="s"><v>31</v></c><c r="O36" s="35" t="s"><v>32</v></c><c r="P36" s="36" t="s"><v>33</v></c><c r="Q36" s="35" t="s"><v>32</v></c><c r="R36" s="36" t="s"><v>33</v></c><c r="S36" s="35" t="s"><v>32</v></c><c r="T36" s="36" t="s"><v>33</v></c><c r="U36" s="35" t="s"><v>32</v></c><c r="V36" s="1"/><c r="W36" s="1"/></row><row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A37" s="1"/><c r="I37" s="41"><f>L$1</f><v>0</v></c><c r="J37" s="27"><f>L9</f><v>0</v></c><c r="K37" s="24"/><c r="L37"/><c r="M37" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N37" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O37" s="39"><v>100000</v></c><c r="P37" s="151"/><c r="Q37" s="77"/><c r="R37" s="153"/><c r="S37" s="78"/><c r="T37" s="152"/><c r="U37" s="74"/><c r="V37" s="1"/><c r="W37" s="18" t="s"><v>14</v></c></row><row r="38"  x14ac:dyDescent="0.3" spans="1:23" x14ac:dyDescent="0.3"><c r="A38" s="1"/><c r="I38" s="41"><f>L$1</f><v>0</v></c><c r="J38" s="27"><f>L9</f><v>0</v></c><c r="K38" s="24"/><c r="L38"/><c r="M38" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N38" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O38" s="39"><v>100000</v></c><c r="P38" s="42"/><c r="Q38" s="72"/><c r="R38" s="44"/><c r="S38" s="77"/><c r="T38" s="42"/><c r="U38" s="72"/><c r="V38" s="1"/><c r="W38" s="18" t="s"><v>14</v></c></row><row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B39" s="20"/><c r="C39" s="32"/><c r="I39" s="41"><f t="shared" ref="I39:I39" si="6">L$1</f><v>0</v></c><c r="J39" s="27"><f t="shared" ref="J39:J39" si="7">L10</f><v>0</v></c><c r="L39" s="105"/><c r="M39" s="171" t="s"><v>42</v></c><c r="N39" s="179"/><c r="O39" s="150"><v>600000</v></c><c r="P39" s="152"/><c r="Q39" s="75"/><c r="R39" s="154"/><c r="S39" s="73"/><c r="T39" s="152"/><c r="U39" s="76"/><c r="V39" s="1"/><c r="W39" s="1"/></row><row r="40" spans="1:23" x14ac:dyDescent="0.3"><c r="O40" s="39"/><c r="N40" s="38"/><c r="M40" s="37"/><c r="B40" s="20"/><c r="C40" s="32"/><c r="I40" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J40" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K40" s="24"/><c r="L40" s="105"/><c r="M40" s="37"/><c r="N40" s="38"/><c r="O40" s="39"/><c r="P40" s="152"/><c r="Q40" s="68"/><c r="R40" s="154"/><c r="S40" s="73"/><c r="T40" s="152"/><c r="U40" s="68"/><c r="V40" s="1"/><c r="W40" s="1"/></row><row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"><c r="B41" s="20"/><c r="C41" s="32"/><c r="D41" s="44"/><c r="E41" s="43"/><c r="I41" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J41" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K41" s="24"/><c r="L41" s="105"/><c r="M41" s="37"/><c r="N41" s="38"/><c r="O41" s="39"/><c r="P41" s="152"/><c r="Q41" s="66"/><c r="R41" s="154"/><c r="S41" s="74"/><c r="T41" s="152"/><c r="U41" s="68"/><c r="V41" s="1"/><c r="W41" s="1"/></row><row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="B42" s="20"/><c r="C42" s="32"/><c r="D42" s="23"/><c r="E42" s="23"/><c r="I42" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J42" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K42" s="24"/><c r="L42" s="105"/><c r="M42" s="37"/><c r="N42" s="38"/><c r="O42" s="39"/><c r="P42" s="152"/><c r="Q42" s="66"/><c r="R42" s="154"/><c r="S42" s="74"/><c r="T42" s="152"/><c r="U42" s="68"/><c r="V42" s="1"/><c r="W42" s="1"/></row><row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6"><c r="B43" s="20"/><c r="C43" s="25"/><c r="D43" s="23"/><c r="E43" s="23"/><c r="F43" s="47"/><c r="I43" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J43" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L43" s="105"/><c r="M43" s="37"/><c r="N43" s="38"/><c r="O43" s="39"/><c r="P43" s="152"/><c r="Q43" s="66"/><c r="R43" s="154"/><c r="S43" s="73"/><c r="T43" s="152"/><c r="U43" s="68"/><c r="V43" s="1"/><c r="W43" s="1"/></row><row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6"><c r="A44" s="104"/><c r="B44" s="20"/><c r="C44" s="32"/><c r="D44" s="170"/><c r="E44" s="170"/><c r="F44" s="47"/><c r="G44" s="8"/><c r="I44" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J44" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K44" s="24"/><c r="L44" s="105"/><c r="M44" s="37"/><c r="N44" s="38"/><c r="O44" s="39"/><c r="P44" s="152"/><c r="Q44" s="66"/><c r="R44" s="152"/><c r="S44" s="67"/><c r="T44" s="152"/><c r="U44" s="68"/></row><row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A45" s="25"/><c r="B45" s="20"/><c r="C45" s="25"/><c r="D45" s="170"/><c r="E45" s="170"/><c r="F45" s="48"/><c r="H45" s="64"/><c r="I45" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J45" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K45" s="24"/><c r="L45" s="105"/><c r="M45" s="37"/><c r="N45" s="38"/><c r="O45" s="39"/><c r="P45" s="152"/><c r="Q45" s="66"/><c r="R45" s="152"/><c r="S45" s="67"/><c r="T45" s="152"/><c r="U45" s="68"/></row><row r="46" spans="1:23" x14ac:dyDescent="0.3"><c r="A46" s="25"/><c r="B46" s="25"/><c r="C46" s="40"/><c r="D46" s="170"/><c r="E46" s="170"/><c r="F46" s="23"/><c r="H46" s="64"/><c r="I46" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J46" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L46" s="105"/><c r="M46" s="37"/><c r="N46" s="38"/><c r="O46" s="39"/><c r="P46" s="152"/><c r="Q46" s="66"/><c r="R46" s="152"/><c r="S46" s="72"/><c r="T46" s="152"/><c r="U46" s="68"/></row><row r="47" spans="1:23" x14ac:dyDescent="0.3"><c r="A47" s="20"/><c r="B47" s="20"/><c r="C47" s="40"/><c r="D47" s="170"/><c r="E47" s="170"/><c r="F47" s="49"/><c r="H47" s="64"/><c r="I47" s="13"/><c r="J47" s="53"><f>SUM(J28:J46)</f><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="67"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="48" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="17"/><c r="G48" s="1"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"/><c r="K48" s="24"/><c r="L48" s="105"/><c r="M48" s="37"/><c r="N48" s="38"/><c r="O48" s="39"/><c r="P48" s="152"/><c r="Q48" s="66"/><c r="R48" s="152"/><c r="S48" s="67"/><c r="T48" s="152"/><c r="U48" s="68"/></row><row r="49" spans="1:23" x14ac:dyDescent="0.3"><c r="A49" s="20"/><c r="B49" s="20"/><c r="C49" s="40"/><c r="D49" s="170"/><c r="E49" s="170"/><c r="F49" s="23"/><c r="G49" s="1"/><c r="H49" s="64"/><c r="I49" s="13"/><c r="J49" s="53"/><c r="L49" s="105"/><c r="M49" s="37"/><c r="N49" s="38"/><c r="O49" s="39"/><c r="P49" s="152"/><c r="Q49" s="66"/><c r="R49" s="152"/><c r="S49" s="67"/><c r="T49" s="154"/><c r="U49" s="68"/></row><row r="50" spans="1:21" x14ac:dyDescent="0.3"><c r="A50" s="20"/><c r="B50" s="20"/><c r="C50" s="40"/><c r="D50" s="170"/><c r="E50" s="170"/><c r="F50" s="23"/><c r="G50" s="1"/><c r="H50" s="46"/><c r="I50" s="13"/><c r="J50" s="53"/><c r="L50" s="105"/><c r="M50" s="37"/><c r="N50" s="38"/><c r="O50" s="39"/><c r="P50" s="152"/><c r="Q50" s="66"/><c r="R50" s="152"/><c r="S50" s="67"/><c r="T50" s="154"/><c r="U50" s="68"/></row><row r="51" spans="1:21" x14ac:dyDescent="0.3"><c r="A51" s="20"/><c r="B51" s="20"/><c r="C51" s="40"/><c r="D51" s="23"/><c r="E51" s="25"/><c r="F51" s="23"/><c r="G51" s="1"/><c r="H51" s="46"/><c r="I51" s="13"/><c r="J51" s="53"/><c r="L51" s="105"/><c r="M51" s="37"/><c r="N51" s="38"/><c r="O51" s="39"/><c r="P51" s="152"/><c r="Q51" s="66"/><c r="R51" s="152"/><c r="S51" s="67"/><c r="T51" s="154"/><c r="U51" s="68"/></row><row r="52" spans="1:21" x14ac:dyDescent="0.3"><c r="A52" s="20"/><c r="B52" s="20"/><c r="C52" s="40"/><c r="D52" s="185"/><c r="E52" s="185"/><c r="F52" s="23"/><c r="G52" s="1"/><c r="H52" s="46"/><c r="I52" s="13"/><c r="J52" s="53"/><c r="L52" s="105"/><c r="M52" s="37"/><c r="N52" s="38"/><c r="O52" s="39"/><c r="P52" s="151"/><c r="Q52" s="66"/><c r="R52" s="152"/><c r="S52" s="67"/><c r="T52" s="154"/><c r="U52" s="68"/></row><row r="53" spans="1:21" x14ac:dyDescent="0.3"><c r="A53" s="20"/><c r="B53" s="51"/><c r="C53" s="40"/><c r="D53" s="178"/><c r="E53" s="178"/><c r="F53" s="23"/><c r="G53" s="1"/><c r="H53" s="46"/><c r="I53" s="50"/><c r="J53" s="53"/><c r="L53" s="105"/><c r="M53" s="37"/><c r="N53" s="38"/><c r="O53" s="39"/><c r="P53" s="151"/><c r="Q53" s="66"/><c r="R53" s="152"/><c r="S53" s="67"/><c r="T53" s="154"/><c r="U53" s="68"/></row><row r="54" spans="1:21" x14ac:dyDescent="0.3"><c r="A54" s="25"/><c r="B54" s="51"/><c r="C54" s="40"/><c r="D54" s="166"/><c r="E54" s="166"/><c r="F54" s="23"/><c r="G54" s="1"/><c r="H54" s="46"/><c r="I54" s="50"/><c r="J54" s="53"/><c r="L54" s="18"/><c r="M54" s="37"/><c r="N54" s="38"/><c r="O54" s="39"/><c r="P54" s="152"/><c r="Q54" s="66"/><c r="R54" s="152"/><c r="S54" s="67"/><c r="T54" s="154"/><c r="U54" s="68"/></row><row r="55" spans="1:21" x14ac:dyDescent="0.3"><c r="A55" s="20"/><c r="B55" s="51"/><c r="C55" s="40"/><c r="D55" s="166"/><c r="E55" s="166"/><c r="F55" s="23"/><c r="G55" s="1"/><c r="H55" s="46"/><c r="I55" s="50"/><c r="J55" s="53"/><c r="L55" s="18"/><c r="M55" s="37"/><c r="N55" s="38"/><c r="O55" s="39"/><c r="P55" s="152"/><c r="Q55" s="66"/><c r="R55" s="152"/><c r="S55" s="67"/><c r="T55" s="154"/><c r="U55" s="68"/></row><row r="56" spans="1:21" x14ac:dyDescent="0.3"><c r="A56" s="20"/><c r="B56" s="51"/><c r="C56" s="40"/><c r="D56" s="22"/><c r="E56" s="22"/><c r="F56" s="23"/><c r="G56" s="1"/><c r="H56" s="46"/><c r="I56" s="50"/><c r="J56" s="53"/><c r="L56" s="18"/><c r="M56" s="37"/><c r="N56" s="38"/><c r="O56" s="39"/><c r="P56" s="152"/><c r="Q56" s="66"/><c r="R56" s="152"/><c r="S56" s="67"/><c r="T56" s="154"/><c r="U56" s="68"/></row><row r="57" spans="1:21" x14ac:dyDescent="0.3"><c r="A57" s="20"/><c r="B57"/><c r="C57" s="40"/><c r="D57" s="22"/><c r="E57" s="22"/><c r="F57" s="23"/><c r="G57" s="1"/><c r="H57" s="46"/><c r="I57" s="50"/><c r="J57" s="53"/><c r="L57" s="18"/><c r="M57" s="37"/><c r="N57" s="38"/><c r="O57" s="39"/><c r="P57" s="152"/><c r="Q57" s="66"/><c r="R57" s="152"/><c r="S57" s="67"/><c r="T57" s="154"/><c r="U57" s="68"/></row><row r="58" spans="1:21" x14ac:dyDescent="0.3"><c r="A58" s="20"/><c r="B58"/><c r="C58" s="40"/><c r="D58" s="22"/><c r="E58" s="22"/><c r="F58" s="23"/><c r="G58" s="1"/><c r="H58" s="46"/><c r="I58" s="50"/><c r="J58" s="53"/><c r="L58" s="18"/><c r="M58" s="37"/><c r="N58" s="38"/><c r="O58" s="39"/><c r="P58" s="152"/><c r="Q58" s="66"/><c r="R58" s="152"/><c r="S58" s="67"/><c r="T58" s="154"/><c r="U58" s="68"/></row><row r="59" spans="1:21" x14ac:dyDescent="0.3"><c r="A59" s="20"/><c r="B59"/><c r="C59" s="40"/><c r="D59" s="22"/><c r="E59" s="22"/><c r="F59" s="23"/><c r="G59" s="1"/><c r="H59" s="46"/><c r="I59" s="50"/><c r="J59" s="53"/><c r="L59" s="18"/><c r="M59" s="37"/><c r="N59" s="38"/><c r="O59" s="39"/><c r="P59" s="152"/><c r="Q59" s="66"/><c r="R59" s="152"/><c r="S59" s="67"/><c r="T59" s="154"/><c r="U59" s="68"/></row><row r="60" spans="1:21" x14ac:dyDescent="0.3"><c r="A60" s="20"/><c r="B60"/><c r="C60" s="40"/><c r="D60" s="22"/><c r="E60" s="22"/><c r="F60" s="23"/><c r="G60" s="1"/><c r="H60" s="46"/><c r="I60" s="50"/><c r="J60" s="53"/><c r="L60" s="18"/><c r="M60" s="37"/><c r="N60" s="38"/><c r="O60" s="39"/><c r="P60" s="152"/><c r="Q60" s="66"/><c r="R60" s="152"/><c r="S60" s="67"/><c r="T60" s="154"/><c r="U60" s="68"/></row><row r="61" spans="1:21" x14ac:dyDescent="0.3"><c r="A61" s="25"/><c r="B61"/><c r="C61" s="40"/><c r="D61" s="166"/><c r="E61" s="166"/><c r="F61" s="23"/><c r="G61" s="1"/><c r="H61" s="46"/><c r="I61" s="50"/><c r="J61" s="53"/><c r="L61" s="18"/><c r="M61" s="37"/><c r="N61" s="38"/><c r="O61" s="39"/><c r="P61" s="152"/><c r="Q61" s="66"/><c r="R61" s="152"/><c r="S61" s="67"/><c r="T61" s="154"/><c r="U61" s="68"/></row><row r="62" spans="1:21" x14ac:dyDescent="0.3"><c r="A62" s="25"/><c r="B62"/><c r="C62" s="40"/><c r="D62" s="22"/><c r="E62" s="22"/><c r="F62" s="23"/><c r="G62" s="1"/><c r="H62" s="46"/><c r="I62" s="50"/><c r="J62" s="53"/><c r="L62" s="18"/><c r="M62" s="37"/><c r="N62" s="38"/><c r="O62" s="39"/><c r="P62" s="152"/><c r="Q62" s="135"/><c r="R62" s="155"/><c r="S62" s="88"/><c r="T62" s="154"/><c r="U62" s="68"/></row><row r="63" spans="1:21" x14ac:dyDescent="0.3"><c r="A63" s="25"/><c r="B63"/><c r="C63" s="40"/><c r="D63" s="22"/><c r="E63" s="22"/><c r="F63" s="23"/><c r="G63" s="1"/><c r="H63" s="46"/><c r="I63" s="50"/><c r="J63" s="53"/><c r="L63" s="18"/><c r="M63" s="37"/><c r="N63" s="38"/><c r="O63" s="39"/><c r="P63" s="152"/><c r="Q63" s="135"/><c r="R63" s="155"/><c r="S63" s="88"/><c r="T63" s="154"/><c r="U63" s="68"/></row><row r="64" spans="1:21" x14ac:dyDescent="0.3"><c r="A64" s="25"/><c r="B64"/><c r="C64" s="40"/><c r="D64" s="22"/><c r="E64" s="22"/><c r="F64" s="23"/><c r="G64" s="1"/><c r="H64" s="46"/><c r="I64" s="50"/><c r="J64" s="53"/><c r="L64" s="18"/><c r="M64" s="37"/><c r="N64" s="38"/><c r="O64" s="39"/><c r="P64" s="152"/><c r="Q64" s="135"/><c r="R64" s="155"/><c r="S64" s="88"/><c r="T64" s="154"/><c r="U64" s="68"/></row><row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A65" s="25"/><c r="B65"/><c r="C65" s="40"/><c r="D65" s="166"/><c r="E65" s="166"/><c r="F65" s="23"/><c r="G65" s="1"/><c r="H65" s="46"/><c r="I65" s="50"/><c r="J65" s="53"/><c r="L65" s="18"/><c r="M65" s="37"/><c r="N65" s="38"/><c r="O65" s="39"/><c r="P65" s="152"/><c r="Q65" s="84"/><c r="R65" s="155"/><c r="S65" s="88"/><c r="T65" s="154"/><c r="U65" s="71"/></row><row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A66" s="25"/><c r="B66"/><c r="C66" s="40"/><c r="D66" s="166"/><c r="E66" s="166"/><c r="F66" s="20"/><c r="G66" s="1"/><c r="H66" s="46"/><c r="I66" s="50"/><c r="J66" s="53"/><c r="L66"/><c r="M66" s="171" t="s"><v>34</v></c><c r="N66" s="172"/><c r="O66" s="42"/><c r="P66" s="52" t="s"><v>11</v></c><c r="Q66" s="42"/><c r="R66" s="52" t="s"><v>11</v></c><c r="S66" s="42"/><c r="T66" s="52" t="s"><v>11</v></c><c r="U66" s="42"/></row><row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A67" s="25"/><c r="B67"/><c r="C67" s="90"/><c r="D67" s="166"/><c r="E67" s="166"/><c r="F67" s="23"/><c r="G67" s="1"/><c r="H67" s="46"/><c r="I67" s="50"/><c r="J67"/><c r="L67"/><c r="M67" s="54"/><c r="N67" s="55"/><c r="O67" s="70"/><c r="P67" s="23"/><c r="Q67" s="69"/><c r="R67" s="70"/><c r="S67" s="70"/><c r="T67" s="6"/></row><row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="A68" s="25"/><c r="B68"/><c r="C68" s="25"/><c r="D68" s="22"/><c r="E68" s="22"/><c r="F68" s="23"/><c r="G68" s="1"/><c r="H68" s="46"/><c r="I68" s="50"/><c r="J68"/><c r="L68"/><c r="M68" s="167" t="s"><v>47</v></c><c r="N68" s="168"/><c r="O68" s="169"/><c r="P68" s="181"/><c r="Q68" s="182"/><c r="R68" s="167" t="s"><v>37</v></c><c r="S68" s="168"/><c r="T68" s="183" t="str"><f>Q25</f></c><c r="U68" s="184"/></row><row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A69" s="25"/><c r="B69"/><c r="C69" s="25"/><c r="D69" s="166"/><c r="E69" s="166"/><c r="F69" s="63"/><c r="G69" s="1"/><c r="H69" s="46"/><c r="I69" s="50"/><c r="J69"/><c r="L69"/><c r="M69" s="56"/><c r="N69" s="83"/><c r="O69" s="83"/><c r="P69" s="57"/><c r="Q69" s="58"/><c r="R69" s="58"/><c r="S69" s="58"/><c r="T69" s="56"/><c r="U69" s="56"/></row><row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A70" s="25"/><c r="B70" s="90"/><c r="C70" s="25"/><c r="D70" s="166"/><c r="E70" s="166"/><c r="F70" s="63"/><c r="G70" s="1"/><c r="H70" s="46"/><c r="I70" s="50"/><c r="J70"/><c r="L70"/><c r="M70" s="171" t="s"><v>35</v></c><c r="N70" s="179"/><c r="O70" s="179"/><c r="P70" s="179"/><c r="Q70" s="179"/><c r="R70" s="179"/><c r="S70" s="179"/><c r="T70" s="179"/><c r="U70" s="180"/><c r="V70" s="51"/></row><row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A71" s="25"/><c r="B71" s="20"/><c r="C71" s="25"/><c r="D71" s="166"/><c r="E71" s="166"/><c r="F71" s="63"/><c r="G71" s="1"/><c r="H71" s="46"/><c r="I71" s="50"/><c r="J71"/><c r="L71" s="49" t="s"><v>59</v></c><c r="M71" s="130" t="s"><v>55</v></c><c r="N71" s="131"/><c r="O71" s="131"/><c r="P71" s="131" t="s"><v>56</v></c><c r="Q71" s="131"/><c r="R71" s="131"/><c r="S71" s="131"/><c r="T71" s="131" t="s"><v>57</v></c><c r="U71" s="132" t="s"><v>60</v></c><c r="V71" s="144" t="s"><v>58</v></c><c r="W71" s="144" t="s"><v>50</v></c></row><row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A72" s="25"/><c r="B72" s="115"/><c r="C72" s="25"/><c r="D72" s="166"/><c r="E72" s="166"/><c r="F72" s="63"/><c r="G72" s="1"/><c r="H72" s="46"/><c r="I72" s="50"/><c r="J72" s="23"/><c r="L72" s="0"/><c r="M72" s="59"/><c r="N72" s="60"/><c r="O72" s="143" t="s"><v>43</v></c><c r="P72" s="62"/><c r="Q72" s="61"/><c r="R72" s="177" t="s"><v>6</v></c><c r="S72" s="177"/><c r="T72" s="133"/><c r="U72" s="134"/><c r="V72" s="51"/></row><row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="B73" s="51"/><c r="C73" s="89"/><c r="D73" s="166"/><c r="E73" s="166"/><c r="F73" s="63"/><c r="I73" s="115"/><c r="L73"/><c r="M73" s="85"/><c r="N73" s="86"/><c r="O73" s="18"/><c r="P73" s="87"/><c r="Q73" s="56"/><c r="R73" s="175"/><c r="S73" s="175"/><c r="T73" s="65"/><c r="U73" s="95"/><c r="V73" s="51"/></row><row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A74" s="49"/><c r="B74" s="89"/><c r="C74" s="89"/><c r="D74" s="23"/><c r="E74" s="25"/><c r="F74" s="63"/><c r="I74" s="115"/><c r="L74" s="45" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="M74" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N74" s="86"/><c r="O74" s="18" t="s"><v>43</v></c><c r="P74" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q74" s="56"/><c r="R74" s="175" t="s"><v>10</v></c><c r="S74" s="175"/><c r="T74" s="65"><v>150000</v></c><c r="U74" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V74" s="51"/></row><row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L75" s="45" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="M75" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N75" s="86"/><c r="O75" s="123"/><c r="P75" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q75" s="56"/><c r="R75" s="175"/><c r="S75" s="175"/><c r="T75" s="65"><v>150000</v></c><c r="U75" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V75" s="51"/></row><row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L76" s="45"/><c r="M76" s="137" t="s"><v>61</v></c><c r="N76" s="138"/><c r="O76" s="139"/><c r="P76" s="140"/><c r="Q76" s="141"/><c r="R76" s="176"/><c r="S76" s="176"/><c r="T76" s="173"/><c r="U76" s="174"/><c r="V76" s="51"/></row><row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L77" s="45"/><c r="M77" s="137" t="s"><v>62</v></c><c r="N77" s="138"/><c r="O77" s="139"/><c r="P77" s="140"/><c r="Q77" s="141"/><c r="R77" s="142"/><c r="S77" s="142"/><c r="T77" s="173"/><c r="U77" s="174"/><c r="V77" s="51"/></row><row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L78" s="45"/><c r="M78" s="94"/><c r="N78" s="64"/><c r="O78" s="123"/><c r="P78" s="87"/><c r="Q78" s="56"/><c r="R78" s="56"/><c r="S78" s="56"/><c r="T78" s="65"/><c r="U78" s="95"/><c r="V78" s="51"/></row><row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L79" s="45"/><c r="M79" s="101" t="s"><v>11</v></c><c r="N79" s="102"><f>SUM(N77:N78)</f><v>0</v></c><c r="O79" s="96"/><c r="P79" s="98"/><c r="Q79" s="97"/><c r="R79" s="97"/><c r="S79" s="97"/><c r="T79" s="99"/><c r="U79" s="100"/><c r="V79" s="51"/></row><row r="80" spans="1:23" x14ac:dyDescent="0.3"><c r="M80"/><c r="O80" s="5"/><c r="Q80"/><c r="S80"/><c r="T80" s="6"/><c r="V80" s="51"/></row><row r="81" spans="1:23" x14ac:dyDescent="0.3"><c r="O81"/><c r="V81" s="51"/></row><row r="82" spans="13:22" x14ac:dyDescent="0.3"><c r="M82" s="23"/><c r="N82" s="23"/><c r="O82" s="23"/><c r="P82" s="23"/><c r="Q82" s="23"/><c r="V82" s="51"/></row><row r="83" spans="13:22" x14ac:dyDescent="0.3"><c r="V83" s="51"/></row><row r="84" spans="13:22" x14ac:dyDescent="0.3"><c r="V84" s="51"/></row><row r="85" spans="13:22" x14ac:dyDescent="0.3"><c r="V85" s="51"/></row><row r="86" spans="13:22" x14ac:dyDescent="0.3"><c r="V86" s="51"/></row><row r="87" spans="13:22" x14ac:dyDescent="0.3"><c r="V87" s="51"/></row><row r="88" spans="13:22" x14ac:dyDescent="0.3"><c r="V88" s="51"/></row><row r="89" spans="13:22" x14ac:dyDescent="0.3"><c r="V89" s="51"/></row><row r="90" spans="13:22" x14ac:dyDescent="0.3"><c r="V90" s="51"/></row><row r="91" spans="13:22" x14ac:dyDescent="0.3"><c r="V91" s="51"/></row><row r="92" spans="13:22" x14ac:dyDescent="0.3"><c r="V92" s="51"/></row><row r="93" spans="13:22" x14ac:dyDescent="0.3"><c r="V93" s="51"/></row><row r="94" spans="13:22" x14ac:dyDescent="0.3"><c r="V94" s="51"/></row><row r="95" spans="13:22" x14ac:dyDescent="0.3"><c r="V95" s="51"/></row><row r="96" spans="13:22" x14ac:dyDescent="0.3"><c r="V96" s="51"/></row><row r="97" spans="13:22" x14ac:dyDescent="0.3"><c r="V97" s="51"/></row><row r="98" spans="22:22" x14ac:dyDescent="0.3"><c r="V98" s="51"/></row><row r="99" spans="22:22" x14ac:dyDescent="0.3"><c r="V99" s="51"/></row><row r="100" spans="22:22" x14ac:dyDescent="0.3"><c r="V100" s="51"/></row><row r="101" spans="22:22" x14ac:dyDescent="0.3"><c r="V101" s="51"/></row><row r="102" spans="22:22" x14ac:dyDescent="0.3"><c r="V102" s="51"/></row><row r="103" spans="22:22" x14ac:dyDescent="0.3"><c r="V103" s="51"/></row><row r="104" spans="22:22" x14ac:dyDescent="0.3"><c r="V104" s="51"/></row><row r="105" spans="22:22" x14ac:dyDescent="0.3"><c r="V105" s="51"/></row><row r="106" spans="22:22" x14ac:dyDescent="0.3"><c r="V106" s="51"/></row><row r="107" spans="22:22" x14ac:dyDescent="0.3"><c r="V107" s="51"/></row><row r="108" spans="22:22" x14ac:dyDescent="0.3"><c r="V108" s="51"/></row><row r="109" spans="22:22" x14ac:dyDescent="0.3"><c r="V109" s="51"/></row><row r="110" spans="22:22" x14ac:dyDescent="0.3"><c r="V110" s="51"/></row><row r="111" spans="22:22" x14ac:dyDescent="0.3"><c r="V111" s="51"/></row><row r="112" spans="22:22" x14ac:dyDescent="0.3"><c r="V112" s="51"/></row><row r="113" spans="22:22" x14ac:dyDescent="0.3"><c r="V113" s="51"/></row></sheetData><mergeCells count="70"><mergeCell ref="M25:N25"/><mergeCell ref="O30:P30"/><mergeCell ref="Q30:S30"/><mergeCell ref="T30:U30"/><mergeCell ref="Q32:S32"/><mergeCell ref="M31:N31"/><mergeCell ref="O31:P31"/><mergeCell ref="Q31:S31"/><mergeCell ref="M30:N30"/><mergeCell ref="M32:N32"/><mergeCell ref="O32:P32"/><mergeCell ref="M22:U22"/><mergeCell ref="Q26:S26"/><mergeCell ref="O29:P29"/><mergeCell ref="Q29:S29"/><mergeCell ref="T29:U29"/><mergeCell ref="T28:U28"/><mergeCell ref="O28:P28"/><mergeCell ref="Q28:S28"/><mergeCell ref="M28:N28"/><mergeCell ref="M29:N29"/><mergeCell ref="O27:P27"/><mergeCell ref="Q27:S27"/><mergeCell ref="T27:U27"/><mergeCell ref="N23:S23"/><mergeCell ref="N24:S24"/><mergeCell ref="T25:U25"/><mergeCell ref="D44:E44"/><mergeCell ref="R35:S35"/><mergeCell ref="T35:U35"/><mergeCell ref="O33:P33"/><mergeCell ref="Q33:S33"/><mergeCell ref="M34:N34"/><mergeCell ref="O34:P34"/><mergeCell ref="Q34:S34"/><mergeCell ref="P35:Q35"/><mergeCell ref="M35:O35"/><mergeCell ref="M39:N39"/><mergeCell ref="D72:E72"/><mergeCell ref="D73:E73"/><mergeCell ref="D53:E53"/><mergeCell ref="M70:U70"/><mergeCell ref="R68:S68"/><mergeCell ref="D69:E69"/><mergeCell ref="P68:Q68"/><mergeCell ref="T68:U68"/><mergeCell ref="D61:E61"/><mergeCell ref="D67:E67"/><mergeCell ref="D54:E54"/><mergeCell ref="D66:E66"/><mergeCell ref="D55:E55"/><mergeCell ref="D65:E65"/><mergeCell ref="T77:U77"/><mergeCell ref="R75:S75"/><mergeCell ref="R76:S76"/><mergeCell ref="R72:S72"/><mergeCell ref="R74:S74"/><mergeCell ref="R73:S73"/><mergeCell ref="T76:U76"/><mergeCell ref="D71:E71"/><mergeCell ref="D70:E70"/><mergeCell ref="M68:O68"/><mergeCell ref="D45:E45"/><mergeCell ref="D47:E47"/><mergeCell ref="M66:N66"/><mergeCell ref="D49:E49"/><mergeCell ref="D50:E50"/><mergeCell ref="D48:E48"/><mergeCell ref="D46:E46"/><mergeCell ref="D52:E52"/></mergeCells><pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/><pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/><drawing r:id="rId2"/></worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}"><dimension ref="A1:W113"/><sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/><cols><col min="1" max="1" width="17.33203125" customWidth="1"/><col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/><col min="3" max="3" width="12.6640625" customWidth="1"/><col min="4" max="4" width="12.6640625" style="3" customWidth="1"/><col min="5" max="5" width="12.6640625" customWidth="1"/><col min="6" max="6" width="12.6640625" style="3" customWidth="1"/><col min="7" max="9" width="12.6640625" customWidth="1"/><col min="10" max="10" width="12.6640625" style="3" customWidth="1"/><col min="11" max="11" width="12.6640625" customWidth="1"/><col min="12" max="12" width="12.6640625" style="3" customWidth="1"/><col min="13" max="13" width="11.5546875" style="3" customWidth="1"/><col min="14" max="14" width="11" bestFit="1" customWidth="1"/><col min="15" max="15" width="11.6640625" style="4" customWidth="1"/><col min="16" max="19" width="11.6640625" style="3" customWidth="1"/><col min="20" max="20" width="13.88671875" customWidth="1"/><col min="21" max="21" width="14" customWidth="1"/><col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/><col min="23" max="23" width="16" customWidth="1"/></cols><sheetData><row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A1" s="7" t="s"><v>50</v></c><c r="B1" s="112" t="inlineStr"><is><t xml:space="preserve">JUAN PEREZ</t></is></c><c r="C1" s="120" t="inlineStr"><is><t xml:space="preserve">MARIA LOPEZ</t></is></c><c r="D1" s="120"/><c r="E1" s="112"/><c r="F1" s="120"/><c r="G1" s="120"/><c r="H1" s="112"/><c r="I1" s="112"/><c r="J1" s="120"/><c r="K1" s="120"/><c r="L1" s="112"/><c r="M1" s="112"/><c r="N1" s="112"/><c r="O1" s="112"/><c r="P1" s="112"/><c r="Q1" s="112"/><c r="R1" s="121"/><c r="S1" s="120"/><c r="T1" s="120"/><c r="U1" s="7"/><c r="V1" s="7"/><c r="W1" s="114"/></row><row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A2" s="7" t="s"><v>51</v></c><c r="B2" s="112"/><c r="C2" s="120"/><c r="D2" s="120"/><c r="E2" s="112"/><c r="F2" s="120"/><c r="G2" s="128"/><c r="H2" s="112"/><c r="I2" s="112"/><c r="J2" s="120"/><c r="K2" s="120"/><c r="L2" s="112"/><c r="M2" s="112"/><c r="N2" s="112"/><c r="O2" s="112"/><c r="P2" s="112"/><c r="Q2" s="112"/><c r="R2" s="121"/><c r="S2" s="120"/><c r="T2" s="120"/><c r="U2" s="7"/><c r="V2" s="7"/><c r="W2" s="114"/></row><row r="3" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A3" s="122" t="s"><v>35</v></c><c r="B3" s="120"/><c r="C3" s="120"/><c r="D3" s="120"/><c r="E3" s="120"/><c r="F3" s="120"/><c r="G3" s="120"/><c r="H3" s="120"/><c r="I3" s="120"/><c r="J3" s="120"/><c r="K3" s="120"/><c r="L3" s="120"/><c r="M3" s="120"/><c r="N3" s="120"/><c r="O3" s="120"/><c r="P3" s="120"/><c r="Q3" s="120"/><c r="R3" s="120"/><c r="S3" s="120"/><c r="T3" s="120"/><c r="U3" s="110"/><c r="V3" s="163"/><c r="W3" s="116"/></row><row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A4" s="122" t="s"><v>52</v></c><c r="B4" s="120"/><c r="C4" s="120"/><c r="D4" s="120"/><c r="E4" s="120"/><c r="F4" s="120"/><c r="G4" s="120"/><c r="H4" s="120"/><c r="I4" s="120"/><c r="J4" s="120"/><c r="K4" s="120"/><c r="L4" s="120"/><c r="M4" s="120"/><c r="N4" s="120"/><c r="O4" s="120"/><c r="P4" s="120"/><c r="Q4" s="120"/><c r="R4" s="120"/><c r="S4" s="120"/><c r="T4" s="120"/><c r="U4" s="110"/><c r="V4" s="163"/><c r="W4" s="116"/></row><row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A5" s="122" t="s"><v>0</v></c><c r="B5" s="129" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="C5" s="129" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="D5" s="129"/><c r="E5" s="129"/><c r="F5" s="129"/><c r="G5" s="129"/><c r="H5" s="129"/><c r="I5" s="129"/><c r="J5" s="129"/><c r="K5" s="129"/><c r="L5" s="129"/><c r="M5" s="129"/><c r="N5" s="129"/><c r="O5" s="129"/><c r="P5" s="129"/><c r="Q5" s="129"/><c r="R5" s="120"/><c r="S5" s="120"/><c r="T5" s="120"/><c r="U5" s="111"/><c r="V5" s="111"/><c r="W5" s="111"/></row><row r="6" spans="1:23" s="45" customFormat="1" x14ac:dyDescent="0.3"><c r="A6" s="122" t="s"><v>1</v></c><c r="B6" s="120"><v>10</v></c><c r="C6" s="120"><v>10</v></c><c r="D6" s="120"/><c r="E6" s="120"/><c r="F6" s="120"/><c r="G6" s="120"/><c r="H6" s="120"/><c r="I6" s="120"/><c r="J6" s="120"/><c r="K6" s="120"/><c r="L6" s="120"/><c r="M6" s="111"/><c r="N6" s="111"/><c r="O6" s="111"/><c r="P6" s="111"/><c r="Q6" s="111"/><c r="R6" s="120"/><c r="S6" s="120"/><c r="T6" s="120"/><c r="U6" s="111"/><c r="V6" s="111"/><c r="W6" s="111"/></row><row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3"><c r="A7" s="122" t="s"><v>2</v></c><c r="B7" s="164"><v>1000000</v></c><c r="C7" s="164"><v>1000000</v></c><c r="D7" s="164"/><c r="E7" s="164"/><c r="F7" s="164"/><c r="G7" s="164"/><c r="H7" s="164"/><c r="I7" s="164"/><c r="J7" s="164"/><c r="K7" s="164"/><c r="L7" s="164"/><c r="M7" s="164"/><c r="N7" s="164"/><c r="O7" s="164"/><c r="P7" s="164"/><c r="Q7" s="164"/><c r="R7" s="156"/><c r="S7" s="156"/><c r="T7" s="156"/><c r="U7" s="157"/><c r="V7" s="157"/><c r="W7" s="157"/></row><row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A8" s="112"/><c r="B8" s="157"/><c r="C8" s="111"/><c r="D8" s="157"/><c r="E8" s="111"/><c r="F8" s="110"/><c r="G8" s="111"/><c r="H8" s="157"/><c r="I8" s="111"/><c r="J8" s="157"/><c r="K8" s="111"/><c r="L8" s="110"/><c r="M8" s="111"/><c r="N8" s="110"/><c r="O8" s="111"/><c r="P8" s="158"/><c r="Q8" s="111"/><c r="R8" s="158"/><c r="S8" s="111"/><c r="T8" s="158"/><c r="U8" s="111"/><c r="V8" s="110"/><c r="W8" s="111"/></row><row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A9" s="113" t="s"><v>3</v></c><c r="B9" s="165"><v>450000</v></c><c r="C9" s="165"><v>450000</v></c><c r="D9" s="165"/><c r="E9" s="157"/><c r="F9" s="110"/><c r="G9" s="157"/><c r="H9" s="110"/><c r="I9" s="157"/><c r="J9" s="110"/><c r="K9" s="157"/><c r="L9" s="110"/><c r="M9" s="157"/><c r="N9" s="110"/><c r="O9" s="157"/><c r="P9" s="158"/><c r="Q9" s="157"/><c r="R9" s="158"/><c r="S9" s="159"/><c r="T9" s="159"/><c r="U9" s="157"/><c r="V9" s="110"/><c r="W9" s="157"/></row><row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A10" s="113" t="s"><v>54</v></c><c r="B10" s="165"><v>50000</v></c><c r="C10" s="165"><v>50000</v></c><c r="D10" s="165"/><c r="E10" s="157"/><c r="F10" s="110"/><c r="G10" s="157"/><c r="H10" s="110"/><c r="I10" s="157"/><c r="J10" s="110"/><c r="K10" s="157"/><c r="L10" s="110"/><c r="M10" s="157"/><c r="N10" s="110"/><c r="O10" s="157"/><c r="P10" s="158"/><c r="Q10" s="157"/><c r="R10" s="158"/><c r="S10" s="159"/><c r="T10" s="159"/><c r="U10" s="157"/><c r="V10" s="110"/><c r="W10" s="157"/></row><row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A11" s="113" t="s"><v>4</v></c><c r="B11" s="165"><v>300000</v></c><c r="C11" s="165"><v>300000</v></c><c r="D11" s="165"/><c r="E11" s="157"/><c r="F11" s="110"/><c r="G11" s="157"/><c r="H11" s="110"/><c r="I11" s="157"/><c r="J11" s="110"/><c r="K11" s="157"/><c r="L11" s="110"/><c r="M11" s="157"/><c r="N11" s="110"/><c r="O11" s="157"/><c r="P11" s="158"/><c r="Q11" s="157"/><c r="R11" s="158"/><c r="S11" s="159"/><c r="T11" s="159"/><c r="U11" s="157"/><c r="V11" s="110"/><c r="W11" s="157"/></row><row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A12" s="113" t="s"><v>5</v></c><c r="B12" s="165"/><c r="C12" s="165"/><c r="D12" s="165"/><c r="E12" s="157"/><c r="F12" s="110"/><c r="G12" s="157"/><c r="H12" s="110"/><c r="I12" s="157"/><c r="J12" s="110"/><c r="K12" s="157"/><c r="L12" s="110"/><c r="M12" s="157"/><c r="N12" s="110"/><c r="O12" s="157"/><c r="P12" s="158"/><c r="Q12" s="157"/><c r="R12" s="158"/><c r="S12" s="159"/><c r="T12" s="159"/><c r="U12" s="157"/><c r="V12" s="110"/><c r="W12" s="157"/></row><row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A13" s="113" t="s"><v>6</v></c><c r="B13" s="165"/><c r="C13" s="165"/><c r="D13" s="165"/><c r="E13" s="157"/><c r="F13" s="110"/><c r="G13" s="157"/><c r="H13" s="110"/><c r="I13" s="157"/><c r="J13" s="110"/><c r="K13" s="157"/><c r="L13" s="110"/><c r="M13" s="157"/><c r="N13" s="110"/><c r="O13" s="157"/><c r="P13" s="158"/><c r="Q13" s="157"/><c r="R13" s="158"/><c r="S13" s="159"/><c r="T13" s="159"/><c r="U13" s="157"/><c r="V13" s="110"/><c r="W13" s="157"/></row><row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A14" s="113" t="s"><v>7</v></c><c r="B14" s="165"/><c r="C14" s="165"/><c r="D14" s="165"/><c r="E14" s="157"/><c r="F14" s="110"/><c r="G14" s="157"/><c r="H14" s="110"/><c r="I14" s="157"/><c r="J14" s="110"/><c r="K14" s="157"/><c r="L14" s="110"/><c r="M14" s="157"/><c r="N14" s="110"/><c r="O14" s="157"/><c r="P14" s="158"/><c r="Q14" s="157"/><c r="R14" s="158"/><c r="S14" s="159"/><c r="T14" s="159"/><c r="U14" s="157"/><c r="V14" s="110"/><c r="W14" s="157"/></row><row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A15" s="113" t="s"><v>8</v></c><c r="B15" s="165"/><c r="C15" s="165"/><c r="D15" s="165"/><c r="E15" s="157"/><c r="F15" s="110"/><c r="G15" s="157"/><c r="H15" s="110"/><c r="I15" s="157"/><c r="J15" s="110"/><c r="K15" s="157"/><c r="L15" s="110"/><c r="M15" s="157"/><c r="N15" s="110"/><c r="O15" s="157"/><c r="P15" s="158"/><c r="Q15" s="157"/><c r="R15" s="158"/><c r="S15" s="159"/><c r="T15" s="159"/><c r="U15" s="157"/><c r="V15" s="110"/><c r="W15" s="157"/></row><row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A16" s="113" t="s"><v>9</v></c><c r="B16" s="165"/><c r="C16" s="165"/><c r="D16" s="165"/><c r="E16" s="157"/><c r="F16" s="110"/><c r="G16" s="157"/><c r="H16" s="110"/><c r="I16" s="160"/><c r="J16" s="110"/><c r="K16" s="160"/><c r="L16" s="110"/><c r="M16" s="157"/><c r="N16" s="110"/><c r="O16" s="157"/><c r="P16" s="158"/><c r="Q16" s="157"/><c r="R16" s="158"/><c r="S16" s="159"/><c r="T16" s="159"/><c r="U16" s="157"/><c r="V16" s="110"/><c r="W16" s="157"/></row><row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A17" s="113" t="s"><v>10</v></c><c r="B17" s="165"/><c r="C17" s="165"/><c r="D17" s="165"/><c r="E17" s="157"/><c r="F17" s="110"/><c r="G17" s="157"/><c r="H17" s="110"/><c r="I17" s="160"/><c r="J17" s="110"/><c r="K17" s="157"/><c r="L17" s="110"/><c r="M17" s="157"/><c r="N17" s="110"/><c r="O17" s="157"/><c r="P17" s="158"/><c r="Q17" s="157"/><c r="R17" s="158"/><c r="S17" s="159"/><c r="T17" s="159"/><c r="U17" s="157"/><c r="V17" s="110"/><c r="W17" s="157"/></row><row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A18" s="113" t="s"><v>11</v></c><c r="B18" s="110"><f>SUM(B9:B17)</f><v>0</v></c><c r="C18" s="110"><f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f><v>0</v></c><c r="D18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="E18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="F18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="G18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="H18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="I18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="J18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="K18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="L18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="M18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="N18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="O18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="P18" s="110"><f t="shared" ref="P18" si="1">SUM(P9:P17)</f><v>0</v></c><c r="Q18" s="110"><f>SUM(Q9:Q17)</f><v>0</v></c><c r="R18" s="110"><f>SUM(R9:R17)</f><v>0</v></c><c r="S18" s="116"><f>SUM(S9:S17)</f><v>0</v></c><c r="T18" s="116"><f>SUM(T9:T17)</f><v>0</v></c><c r="U18" s="110"><f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f><v>0</v></c><c r="V18" s="110"><f t="shared" si="2"/><v>0</v></c><c r="W18" s="110"><f t="shared" si="2"/><v>0</v></c></row><row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A19" s="113"/><c r="B19" s="110"/><c r="C19" s="110"/><c r="D19" s="110"/><c r="E19" s="110"/><c r="F19" s="157"/><c r="G19" s="110"/><c r="H19" s="110"/><c r="I19" s="110"/><c r="J19" s="110"/><c r="K19" s="110"/><c r="L19" s="110"/><c r="M19" s="110"/><c r="N19" s="110"/><c r="O19" s="110"/><c r="P19" s="110"/><c r="Q19" s="110"/><c r="R19" s="110"/><c r="S19" s="116"/><c r="T19" s="116"/><c r="U19" s="110"/><c r="V19" s="110"/><c r="W19" s="110"/></row><row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3"><c r="A20" s="113" t="s"><v>12</v></c><c r="B20" s="110" t="e"><f t="shared" ref="B20:O20" si="3">B18-B7</f><v>#VALUE!</v></c><c r="C20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="D20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="E20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="F20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="G20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="H20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="I20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="J20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="K20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="L20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="M20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="N20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="O20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="P20" s="110"><f t="shared" ref="P20" si="4">P18-P7</f><v>0</v></c><c r="Q20" s="110"><f>Q18-Q7</f><v>0</v></c><c r="R20" s="110"><f>R18-R7</f><v>0</v></c><c r="S20" s="110"><f>S18-S7</f><v>0</v></c><c r="T20" s="110"><f>T18-T7</f><v>0</v></c><c r="U20" s="110"><f t="shared" ref="U20:W20" si="5">U18-U7</f><v>0</v></c><c r="V20" s="110"><f t="shared" si="5"/><v>0</v></c><c r="W20" s="110"><f t="shared" si="5"/><v>0</v></c></row><row r="21" spans="1:23" x14ac:dyDescent="0.3"><c r="A21" s="1"/><c r="B21" s="9"/><c r="C21" s="10"/><c r="D21" s="9"/><c r="E21" s="10"/><c r="F21" s="11"/><c r="G21" s="10"/><c r="H21" s="11"/><c r="I21" s="9"/><c r="J21" s="9"/><c r="K21" s="10"/><c r="L21" s="12"/><c r="M21" s="12"/><c r="N21" s="10"/><c r="O21" s="9"/><c r="P21" s="9"/><c r="Q21" s="10"/><c r="R21" s="12"/><c r="S21" s="12"/><c r="T21" s="9"/><c r="U21" s="9"/><c r="V21" s="9"/><c r="W21" s="9"/></row><row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35"><c r="D22" s="2"/><c r="M22" s="198" t="s"><v>48</v></c><c r="N22" s="198"/><c r="O22" s="198"/><c r="P22" s="198"/><c r="Q22" s="198"/><c r="R22" s="198"/><c r="S22" s="198"/><c r="T22" s="198"/><c r="U22" s="198"/></row><row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="D23" s="6"/><c r="J23"/><c r="L23"/><c r="M23" s="14" t="s"><v>13</v></c><c r="N23" s="207" t="inlineStr"><is><t xml:space="preserve">24-06-2026</t></is></c><c r="O23" s="208"/><c r="P23" s="208"/><c r="Q23" s="208"/><c r="R23" s="208"/><c r="S23" s="209"/><c r="T23" s="119" t="s"><v>38</v></c><c r="U23" s="106"><v>20</v></c><c r="W23" s="91" t="s"><v>44</v></c></row><row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="B24" s="2"/><c r="C24" s="18"/><c r="J24"/><c r="K24" s="15"/><c r="L24"/><c r="M24" s="16"/><c r="N24" s="210" t="s"><v>49</v></c><c r="O24" s="211"/><c r="P24" s="211"/><c r="Q24" s="211"/><c r="R24" s="211"/><c r="S24" s="212"/><c r="T24" s="108" t="s"><v>11</v></c><c r="U24" s="107"><v>2000000</v></c><c r="W24" s="118"><v>20</v></c></row><row r="25" spans="1:23" x14ac:dyDescent="0.3"><c r="B25" s="2"/><c r="C25" s="103"/><c r="D25" s="3" t="s"><v>15</v></c><c r="E25" s="4"/><c r="J25"/><c r="L25"/><c r="M25" s="215" t="s"><v>16</v></c><c r="N25" s="216"/><c r="O25" s="148"/><c r="P25" s="149"/><c r="Q25" s="145"><v>900000</v></c><c r="R25" s="146"/><c r="S25" s="147"/><c r="T25" s="213" t="s"><v>17</v></c><c r="U25" s="214"/><c r="V25" s="13"/><c r="W25" s="82" t="s"><v>45</v></c></row><row r="26" spans="1:23" x14ac:dyDescent="0.3"><c r="E26" s="4"/><c r="J26"/><c r="L26"/><c r="M26" s="79" t="s"><v>53</v></c><c r="N26" s="80"/><c r="O26" s="126"/><c r="P26" s="127"/><c r="Q26" s="188"><v>100000</v></c><c r="R26" s="189"/><c r="S26" s="190"/><c r="T26" s="124"/><c r="U26" s="125"/><c r="V26" s="13"/><c r="W26" s="82"/></row><row r="27" spans="1:23" x14ac:dyDescent="0.3"><c r="I27" s="109" t="str"><f>B1</f></c><c r="J27" s="136" t="str"><f>B9</f></c><c r="L27"/><c r="M27" s="79" t="s"><v>18</v></c><c r="N27" s="80"/><c r="O27" s="186"/><c r="P27" s="187"/><c r="Q27" s="188"><v>600000</v></c><c r="R27" s="189"/><c r="S27" s="190"/><c r="T27" s="205" t="s"><v>19</v></c><c r="U27" s="206"/><c r="V27" s="19"/><c r="W27" s="92"><v>2000000</v></c></row><row r="28" spans="1:23" x14ac:dyDescent="0.3"><c r="I28" s="109"><f>C1</f><v>0</v></c><c r="J28" s="136"><f>C9</f><v>0</v></c><c r="L28"/><c r="M28" s="203" t="s"><v>20</v></c><c r="N28" s="204"/><c r="O28" s="186"/><c r="P28" s="187"/><c r="Q28" s="188"/><c r="R28" s="189"/><c r="S28" s="190"/><c r="T28" s="201" t="s"><v>39</v></c><c r="U28" s="202"/><c r="V28" s="21"/><c r="W28" s="13"/></row><row r="29" spans="1:23" x14ac:dyDescent="0.3"><c r="I29" s="109"><f>D1</f><v>0</v></c><c r="J29" s="136"><f>D9</f><v>0</v></c><c r="K29" s="24"/><c r="L29"/><c r="M29" s="203" t="s"><v>21</v></c><c r="N29" s="204"/><c r="O29" s="186"/><c r="P29" s="187"/><c r="Q29" s="188"/><c r="R29" s="189"/><c r="S29" s="190"/><c r="T29" s="199" t="s"><v>40</v></c><c r="U29" s="200"/><c r="W29" s="93" t="str"><f>U23</f></c></row><row r="30" spans="1:23" x14ac:dyDescent="0.3"><c r="A30" s="1"/><c r="I30" s="109"><f>E1</f><v>0</v></c><c r="J30" s="136"><f>E9</f><v>0</v></c><c r="L30"/><c r="M30" s="203" t="s"><v>22</v></c><c r="N30" s="204"/><c r="O30" s="186"/><c r="P30" s="217"/><c r="Q30" s="188"/><c r="R30" s="189"/><c r="S30" s="190"/><c r="T30" s="218" t="s"><v>41</v></c><c r="U30" s="219"/><c r="V30" s="24"/><c r="W30" s="21" t="str"><f>Q34</f></c></row><row r="31" spans="1:23" x14ac:dyDescent="0.3"><c r="A31" s="1"/><c r="I31" s="109"><f>F1</f><v>0</v></c><c r="J31" s="136"><f>F9</f><v>0</v></c><c r="L31"/><c r="M31" s="203" t="s"><v>23</v></c><c r="N31" s="204"/><c r="O31" s="186"/><c r="P31" s="187"/><c r="Q31" s="188"/><c r="R31" s="189"/><c r="S31" s="190"/><c r="T31" s="28"/><c r="U31" s="26"/></row><row r="32" spans="1:23" x14ac:dyDescent="0.3"><c r="A32" s="1"/><c r="I32" s="109"><f>G1</f><v>0</v></c><c r="J32" s="136"><f>G9</f><v>0</v></c><c r="L32"/><c r="M32" s="203" t="s"><v>24</v></c><c r="N32" s="204"/><c r="O32" s="186"/><c r="P32" s="187"/><c r="Q32" s="188"/><c r="R32" s="189"/><c r="S32" s="190"/><c r="T32" s="28"/><c r="U32" s="26"/><c r="W32" s="82" t="s"><v>46</v></c></row><row r="33" spans="1:23" x14ac:dyDescent="0.3"><c r="A33" s="1"/><c r="I33" s="109"><f>H1</f><v>0</v></c><c r="J33" s="136"><f>H9</f><v>0</v></c><c r="L33"/><c r="M33" s="79" t="s"><v>25</v></c><c r="N33" s="81"/><c r="O33" s="186"/><c r="P33" s="187"/><c r="Q33" s="188"/><c r="R33" s="189"/><c r="S33" s="190"/><c r="T33" s="28"/><c r="U33" s="26"/><c r="W33" s="117" t="e"><f>W30-W27</f><v>#VALUE!</v></c></row><row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A34" s="1"/><c r="I34" s="109"><f>I1</f><v>0</v></c><c r="J34" s="136"><f>I9</f><v>0</v></c><c r="L34" s="8"/><c r="M34" s="191" t="s"><v>26</v></c><c r="N34" s="192"/><c r="O34" s="193"/><c r="P34" s="194"/><c r="Q34" s="188"><v>2000000</v></c><c r="R34" s="189"/><c r="S34" s="190"/><c r="T34" s="30"/><c r="U34" s="29"/><c r="V34" s="1"/><c r="W34" s="24"/></row><row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A35" s="1"/><c r="D35" s="31"/><c r="I35" s="41"><f>J1</f><v>0</v></c><c r="J35" s="27"><f>J9</f><v>0</v></c><c r="L35"/><c r="M35" s="195" t="s"><v>27</v></c><c r="N35" s="196"/><c r="O35" s="197"/><c r="P35" s="167" t="s"><v>28</v></c><c r="Q35" s="169"/><c r="R35" s="167" t="s"><v>29</v></c><c r="S35" s="169"/><c r="T35" s="167" t="s"><v>30</v></c><c r="U35" s="169"/><c r="V35" s="1"/><c r="W35" s="1"/></row><row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B36" s="9"/><c r="I36" s="41"><f>K1</f><v>0</v></c><c r="J36" s="27"><f>K9</f><v>0</v></c><c r="L36"/><c r="M36" s="33" t="s"><v>13</v></c><c r="N36" s="34" t="s"><v>31</v></c><c r="O36" s="35" t="s"><v>32</v></c><c r="P36" s="36" t="s"><v>33</v></c><c r="Q36" s="35" t="s"><v>32</v></c><c r="R36" s="36" t="s"><v>33</v></c><c r="S36" s="35" t="s"><v>32</v></c><c r="T36" s="36" t="s"><v>33</v></c><c r="U36" s="35" t="s"><v>32</v></c><c r="V36" s="1"/><c r="W36" s="1"/></row><row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A37" s="1"/><c r="I37" s="41"><f>L$1</f><v>0</v></c><c r="J37" s="27"><f>L9</f><v>0</v></c><c r="K37" s="24"/><c r="L37"/><c r="M37" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N37" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O37" s="39"><v>100000</v></c><c r="P37" s="151"/><c r="Q37" s="77"/><c r="R37" s="153"/><c r="S37" s="78"/><c r="T37" s="152"/><c r="U37" s="74"/><c r="V37" s="1"/><c r="W37" s="18" t="s"><v>14</v></c></row><row r="38"  x14ac:dyDescent="0.3" spans="1:23" x14ac:dyDescent="0.3"><c r="A38" s="1"/><c r="I38" s="41"><f>L$1</f><v>0</v></c><c r="J38" s="27"><f>L9</f><v>0</v></c><c r="K38" s="24"/><c r="L38"/><c r="M38" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N38" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O38" s="39"><v>100000</v></c><c r="P38" s="42"/><c r="Q38" s="72"/><c r="R38" s="44"/><c r="S38" s="77"/><c r="T38" s="42"/><c r="U38" s="72"/><c r="V38" s="1"/><c r="W38" s="18" t="s"><v>14</v></c></row><row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B39" s="20"/><c r="C39" s="32"/><c r="I39" s="41"><f t="shared" ref="I39:I46" si="6">L$1</f><v>0</v></c><c r="J39" s="27"><f t="shared" ref="J39:J46" si="7">L10</f><v>0</v></c><c r="L39" s="105"/><c r="M39" s="171" t="s"><v>42</v></c><c r="N39" s="179"/><c r="O39" s="150"><v>600000</v></c><c r="P39" s="152"/><c r="Q39" s="75"/><c r="R39" s="154"/><c r="S39" s="73"/><c r="T39" s="152"/><c r="U39" s="76"/><c r="V39" s="1"/><c r="W39" s="1"/></row><row r="40" spans="1:23" x14ac:dyDescent="0.3"><c r="O40" s="39"/><c r="N40" s="38"/><c r="M40" s="37"/><c r="B40" s="20"/><c r="C40" s="32"/><c r="I40" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J40" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K40" s="24"/><c r="L40" s="105"/><c r="M40" s="37"/><c r="N40" s="38"/><c r="O40" s="39"/><c r="P40" s="152"/><c r="Q40" s="68"/><c r="R40" s="154"/><c r="S40" s="73"/><c r="T40" s="152"/><c r="U40" s="68"/><c r="V40" s="1"/><c r="W40" s="1"/></row><row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"><c r="B41" s="20"/><c r="C41" s="32"/><c r="D41" s="44"/><c r="E41" s="43"/><c r="I41" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J41" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K41" s="24"/><c r="L41" s="105"/><c r="M41" s="37"/><c r="N41" s="38"/><c r="O41" s="39"/><c r="P41" s="152"/><c r="Q41" s="66"/><c r="R41" s="154"/><c r="S41" s="74"/><c r="T41" s="152"/><c r="U41" s="68"/><c r="V41" s="1"/><c r="W41" s="1"/></row><row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="B42" s="20"/><c r="C42" s="32"/><c r="D42" s="23"/><c r="E42" s="23"/><c r="I42" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J42" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K42" s="24"/><c r="L42" s="105"/><c r="M42" s="37"/><c r="N42" s="38"/><c r="O42" s="39"/><c r="P42" s="152"/><c r="Q42" s="66"/><c r="R42" s="154"/><c r="S42" s="74"/><c r="T42" s="152"/><c r="U42" s="68"/><c r="V42" s="1"/><c r="W42" s="1"/></row><row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6"><c r="B43" s="20"/><c r="C43" s="25"/><c r="D43" s="23"/><c r="E43" s="23"/><c r="F43" s="47"/><c r="I43" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J43" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L43" s="105"/><c r="M43" s="37"/><c r="N43" s="38"/><c r="O43" s="39"/><c r="P43" s="152"/><c r="Q43" s="66"/><c r="R43" s="154"/><c r="S43" s="73"/><c r="T43" s="152"/><c r="U43" s="68"/><c r="V43" s="1"/><c r="W43" s="1"/></row><row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6"><c r="A44" s="104"/><c r="B44" s="20"/><c r="C44" s="32"/><c r="D44" s="170"/><c r="E44" s="170"/><c r="F44" s="47"/><c r="G44" s="8"/><c r="I44" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J44" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K44" s="24"/><c r="L44" s="105"/><c r="M44" s="37"/><c r="N44" s="38"/><c r="O44" s="39"/><c r="P44" s="152"/><c r="Q44" s="66"/><c r="R44" s="152"/><c r="S44" s="67"/><c r="T44" s="152"/><c r="U44" s="68"/></row><row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A45" s="25"/><c r="B45" s="20"/><c r="C45" s="25"/><c r="D45" s="170"/><c r="E45" s="170"/><c r="F45" s="48"/><c r="H45" s="64"/><c r="I45" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J45" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K45" s="24"/><c r="L45" s="105"/><c r="M45" s="37"/><c r="N45" s="38"/><c r="O45" s="39"/><c r="P45" s="152"/><c r="Q45" s="66"/><c r="R45" s="152"/><c r="S45" s="67"/><c r="T45" s="152"/><c r="U45" s="68"/></row><row r="46" spans="1:23" x14ac:dyDescent="0.3"><c r="A46" s="25"/><c r="B46" s="25"/><c r="C46" s="40"/><c r="D46" s="170"/><c r="E46" s="170"/><c r="F46" s="23"/><c r="H46" s="64"/><c r="I46" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J46" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L46" s="105"/><c r="M46" s="37"/><c r="N46" s="38"/><c r="O46" s="39"/><c r="P46" s="152"/><c r="Q46" s="66"/><c r="R46" s="152"/><c r="S46" s="72"/><c r="T46" s="152"/><c r="U46" s="68"/></row><row r="47" spans="1:23" x14ac:dyDescent="0.3"><c r="A47" s="20"/><c r="B47" s="20"/><c r="C47" s="40"/><c r="D47" s="170"/><c r="E47" s="170"/><c r="F47" s="49"/><c r="H47" s="64"/><c r="I47" s="13"/><c r="J47" s="53"><f>SUM(J28:J46)</f><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="67"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="48" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="17"/><c r="G48" s="1"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"/><c r="K48" s="24"/><c r="L48" s="105"/><c r="M48" s="37"/><c r="N48" s="38"/><c r="O48" s="39"/><c r="P48" s="152"/><c r="Q48" s="66"/><c r="R48" s="152"/><c r="S48" s="67"/><c r="T48" s="152"/><c r="U48" s="68"/></row><row r="49" spans="1:23" x14ac:dyDescent="0.3"><c r="A49" s="20"/><c r="B49" s="20"/><c r="C49" s="40"/><c r="D49" s="170"/><c r="E49" s="170"/><c r="F49" s="23"/><c r="G49" s="1"/><c r="H49" s="64"/><c r="I49" s="13"/><c r="J49" s="53"/><c r="L49" s="105"/><c r="M49" s="37"/><c r="N49" s="38"/><c r="O49" s="39"/><c r="P49" s="152"/><c r="Q49" s="66"/><c r="R49" s="152"/><c r="S49" s="67"/><c r="T49" s="154"/><c r="U49" s="68"/></row><row r="50" spans="1:21" x14ac:dyDescent="0.3"><c r="A50" s="20"/><c r="B50" s="20"/><c r="C50" s="40"/><c r="D50" s="170"/><c r="E50" s="170"/><c r="F50" s="23"/><c r="G50" s="1"/><c r="H50" s="46"/><c r="I50" s="13"/><c r="J50" s="53"/><c r="L50" s="105"/><c r="M50" s="37"/><c r="N50" s="38"/><c r="O50" s="39"/><c r="P50" s="152"/><c r="Q50" s="66"/><c r="R50" s="152"/><c r="S50" s="67"/><c r="T50" s="154"/><c r="U50" s="68"/></row><row r="51" spans="1:21" x14ac:dyDescent="0.3"><c r="A51" s="20"/><c r="B51" s="20"/><c r="C51" s="40"/><c r="D51" s="23"/><c r="E51" s="25"/><c r="F51" s="23"/><c r="G51" s="1"/><c r="H51" s="46"/><c r="I51" s="13"/><c r="J51" s="53"/><c r="L51" s="105"/><c r="M51" s="37"/><c r="N51" s="38"/><c r="O51" s="39"/><c r="P51" s="152"/><c r="Q51" s="66"/><c r="R51" s="152"/><c r="S51" s="67"/><c r="T51" s="154"/><c r="U51" s="68"/></row><row r="52" spans="1:21" x14ac:dyDescent="0.3"><c r="A52" s="20"/><c r="B52" s="20"/><c r="C52" s="40"/><c r="D52" s="185"/><c r="E52" s="185"/><c r="F52" s="23"/><c r="G52" s="1"/><c r="H52" s="46"/><c r="I52" s="13"/><c r="J52" s="53"/><c r="L52" s="105"/><c r="M52" s="37"/><c r="N52" s="38"/><c r="O52" s="39"/><c r="P52" s="151"/><c r="Q52" s="66"/><c r="R52" s="152"/><c r="S52" s="67"/><c r="T52" s="154"/><c r="U52" s="68"/></row><row r="53" spans="1:21" x14ac:dyDescent="0.3"><c r="A53" s="20"/><c r="B53" s="51"/><c r="C53" s="40"/><c r="D53" s="178"/><c r="E53" s="178"/><c r="F53" s="23"/><c r="G53" s="1"/><c r="H53" s="46"/><c r="I53" s="50"/><c r="J53" s="53"/><c r="L53" s="105"/><c r="M53" s="37"/><c r="N53" s="38"/><c r="O53" s="39"/><c r="P53" s="151"/><c r="Q53" s="66"/><c r="R53" s="152"/><c r="S53" s="67"/><c r="T53" s="154"/><c r="U53" s="68"/></row><row r="54" spans="1:21" x14ac:dyDescent="0.3"><c r="A54" s="25"/><c r="B54" s="51"/><c r="C54" s="40"/><c r="D54" s="166"/><c r="E54" s="166"/><c r="F54" s="23"/><c r="G54" s="1"/><c r="H54" s="46"/><c r="I54" s="50"/><c r="J54" s="53"/><c r="L54" s="18"/><c r="M54" s="37"/><c r="N54" s="38"/><c r="O54" s="39"/><c r="P54" s="152"/><c r="Q54" s="66"/><c r="R54" s="152"/><c r="S54" s="67"/><c r="T54" s="154"/><c r="U54" s="68"/></row><row r="55" spans="1:21" x14ac:dyDescent="0.3"><c r="A55" s="20"/><c r="B55" s="51"/><c r="C55" s="40"/><c r="D55" s="166"/><c r="E55" s="166"/><c r="F55" s="23"/><c r="G55" s="1"/><c r="H55" s="46"/><c r="I55" s="50"/><c r="J55" s="53"/><c r="L55" s="18"/><c r="M55" s="37"/><c r="N55" s="38"/><c r="O55" s="39"/><c r="P55" s="152"/><c r="Q55" s="66"/><c r="R55" s="152"/><c r="S55" s="67"/><c r="T55" s="154"/><c r="U55" s="68"/></row><row r="56" spans="1:21" x14ac:dyDescent="0.3"><c r="A56" s="20"/><c r="B56" s="51"/><c r="C56" s="40"/><c r="D56" s="22"/><c r="E56" s="22"/><c r="F56" s="23"/><c r="G56" s="1"/><c r="H56" s="46"/><c r="I56" s="50"/><c r="J56" s="53"/><c r="L56" s="18"/><c r="M56" s="37"/><c r="N56" s="38"/><c r="O56" s="39"/><c r="P56" s="152"/><c r="Q56" s="66"/><c r="R56" s="152"/><c r="S56" s="67"/><c r="T56" s="154"/><c r="U56" s="68"/></row><row r="57" spans="1:21" x14ac:dyDescent="0.3"><c r="A57" s="20"/><c r="B57"/><c r="C57" s="40"/><c r="D57" s="22"/><c r="E57" s="22"/><c r="F57" s="23"/><c r="G57" s="1"/><c r="H57" s="46"/><c r="I57" s="50"/><c r="J57" s="53"/><c r="L57" s="18"/><c r="M57" s="37"/><c r="N57" s="38"/><c r="O57" s="39"/><c r="P57" s="152"/><c r="Q57" s="66"/><c r="R57" s="152"/><c r="S57" s="67"/><c r="T57" s="154"/><c r="U57" s="68"/></row><row r="58" spans="1:21" x14ac:dyDescent="0.3"><c r="A58" s="20"/><c r="B58"/><c r="C58" s="40"/><c r="D58" s="22"/><c r="E58" s="22"/><c r="F58" s="23"/><c r="G58" s="1"/><c r="H58" s="46"/><c r="I58" s="50"/><c r="J58" s="53"/><c r="L58" s="18"/><c r="M58" s="37"/><c r="N58" s="38"/><c r="O58" s="39"/><c r="P58" s="152"/><c r="Q58" s="66"/><c r="R58" s="152"/><c r="S58" s="67"/><c r="T58" s="154"/><c r="U58" s="68"/></row><row r="59" spans="1:21" x14ac:dyDescent="0.3"><c r="A59" s="20"/><c r="B59"/><c r="C59" s="40"/><c r="D59" s="22"/><c r="E59" s="22"/><c r="F59" s="23"/><c r="G59" s="1"/><c r="H59" s="46"/><c r="I59" s="50"/><c r="J59" s="53"/><c r="L59" s="18"/><c r="M59" s="37"/><c r="N59" s="38"/><c r="O59" s="39"/><c r="P59" s="152"/><c r="Q59" s="66"/><c r="R59" s="152"/><c r="S59" s="67"/><c r="T59" s="154"/><c r="U59" s="68"/></row><row r="60" spans="1:21" x14ac:dyDescent="0.3"><c r="A60" s="20"/><c r="B60"/><c r="C60" s="40"/><c r="D60" s="22"/><c r="E60" s="22"/><c r="F60" s="23"/><c r="G60" s="1"/><c r="H60" s="46"/><c r="I60" s="50"/><c r="J60" s="53"/><c r="L60" s="18"/><c r="M60" s="37"/><c r="N60" s="38"/><c r="O60" s="39"/><c r="P60" s="152"/><c r="Q60" s="66"/><c r="R60" s="152"/><c r="S60" s="67"/><c r="T60" s="154"/><c r="U60" s="68"/></row><row r="61" spans="1:21" x14ac:dyDescent="0.3"><c r="A61" s="25"/><c r="B61"/><c r="C61" s="40"/><c r="D61" s="166"/><c r="E61" s="166"/><c r="F61" s="23"/><c r="G61" s="1"/><c r="H61" s="46"/><c r="I61" s="50"/><c r="J61" s="53"/><c r="L61" s="18"/><c r="M61" s="37"/><c r="N61" s="38"/><c r="O61" s="39"/><c r="P61" s="152"/><c r="Q61" s="66"/><c r="R61" s="152"/><c r="S61" s="67"/><c r="T61" s="154"/><c r="U61" s="68"/></row><row r="62" spans="1:21" x14ac:dyDescent="0.3"><c r="A62" s="25"/><c r="B62"/><c r="C62" s="40"/><c r="D62" s="22"/><c r="E62" s="22"/><c r="F62" s="23"/><c r="G62" s="1"/><c r="H62" s="46"/><c r="I62" s="50"/><c r="J62" s="53"/><c r="L62" s="18"/><c r="M62" s="37"/><c r="N62" s="38"/><c r="O62" s="39"/><c r="P62" s="152"/><c r="Q62" s="135"/><c r="R62" s="155"/><c r="S62" s="88"/><c r="T62" s="154"/><c r="U62" s="68"/></row><row r="63" spans="1:21" x14ac:dyDescent="0.3"><c r="A63" s="25"/><c r="B63"/><c r="C63" s="40"/><c r="D63" s="22"/><c r="E63" s="22"/><c r="F63" s="23"/><c r="G63" s="1"/><c r="H63" s="46"/><c r="I63" s="50"/><c r="J63" s="53"/><c r="L63" s="18"/><c r="M63" s="37"/><c r="N63" s="38"/><c r="O63" s="39"/><c r="P63" s="152"/><c r="Q63" s="135"/><c r="R63" s="155"/><c r="S63" s="88"/><c r="T63" s="154"/><c r="U63" s="68"/></row><row r="64" spans="1:21" x14ac:dyDescent="0.3"><c r="A64" s="25"/><c r="B64"/><c r="C64" s="40"/><c r="D64" s="22"/><c r="E64" s="22"/><c r="F64" s="23"/><c r="G64" s="1"/><c r="H64" s="46"/><c r="I64" s="50"/><c r="J64" s="53"/><c r="L64" s="18"/><c r="M64" s="37"/><c r="N64" s="38"/><c r="O64" s="39"/><c r="P64" s="152"/><c r="Q64" s="135"/><c r="R64" s="155"/><c r="S64" s="88"/><c r="T64" s="154"/><c r="U64" s="68"/></row><row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A65" s="25"/><c r="B65"/><c r="C65" s="40"/><c r="D65" s="166"/><c r="E65" s="166"/><c r="F65" s="23"/><c r="G65" s="1"/><c r="H65" s="46"/><c r="I65" s="50"/><c r="J65" s="53"/><c r="L65" s="18"/><c r="M65" s="37"/><c r="N65" s="38"/><c r="O65" s="39"/><c r="P65" s="152"/><c r="Q65" s="84"/><c r="R65" s="155"/><c r="S65" s="88"/><c r="T65" s="154"/><c r="U65" s="71"/></row><row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A66" s="25"/><c r="B66"/><c r="C66" s="40"/><c r="D66" s="166"/><c r="E66" s="166"/><c r="F66" s="20"/><c r="G66" s="1"/><c r="H66" s="46"/><c r="I66" s="50"/><c r="J66" s="53"/><c r="L66"/><c r="M66" s="171" t="s"><v>34</v></c><c r="N66" s="172"/><c r="O66" s="42"/><c r="P66" s="52" t="s"><v>11</v></c><c r="Q66" s="42"/><c r="R66" s="52" t="s"><v>11</v></c><c r="S66" s="42"/><c r="T66" s="52" t="s"><v>11</v></c><c r="U66" s="42"/></row><row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A67" s="25"/><c r="B67"/><c r="C67" s="90"/><c r="D67" s="166"/><c r="E67" s="166"/><c r="F67" s="23"/><c r="G67" s="1"/><c r="H67" s="46"/><c r="I67" s="50"/><c r="J67"/><c r="L67"/><c r="M67" s="54"/><c r="N67" s="55"/><c r="O67" s="70"/><c r="P67" s="23"/><c r="Q67" s="69"/><c r="R67" s="70"/><c r="S67" s="70"/><c r="T67" s="6"/></row><row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="A68" s="25"/><c r="B68"/><c r="C68" s="25"/><c r="D68" s="22"/><c r="E68" s="22"/><c r="F68" s="23"/><c r="G68" s="1"/><c r="H68" s="46"/><c r="I68" s="50"/><c r="J68"/><c r="L68"/><c r="M68" s="167" t="s"><v>47</v></c><c r="N68" s="168"/><c r="O68" s="169"/><c r="P68" s="181"/><c r="Q68" s="182"/><c r="R68" s="167" t="s"><v>37</v></c><c r="S68" s="168"/><c r="T68" s="183" t="str"><f>Q25</f></c><c r="U68" s="184"/></row><row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A69" s="25"/><c r="B69"/><c r="C69" s="25"/><c r="D69" s="166"/><c r="E69" s="166"/><c r="F69" s="63"/><c r="G69" s="1"/><c r="H69" s="46"/><c r="I69" s="50"/><c r="J69"/><c r="L69"/><c r="M69" s="56"/><c r="N69" s="83"/><c r="O69" s="83"/><c r="P69" s="57"/><c r="Q69" s="58"/><c r="R69" s="58"/><c r="S69" s="58"/><c r="T69" s="56"/><c r="U69" s="56"/></row><row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A70" s="25"/><c r="B70" s="90"/><c r="C70" s="25"/><c r="D70" s="166"/><c r="E70" s="166"/><c r="F70" s="63"/><c r="G70" s="1"/><c r="H70" s="46"/><c r="I70" s="50"/><c r="J70"/><c r="L70"/><c r="M70" s="171" t="s"><v>35</v></c><c r="N70" s="179"/><c r="O70" s="179"/><c r="P70" s="179"/><c r="Q70" s="179"/><c r="R70" s="179"/><c r="S70" s="179"/><c r="T70" s="179"/><c r="U70" s="180"/><c r="V70" s="51"/></row><row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A71" s="25"/><c r="B71" s="20"/><c r="C71" s="25"/><c r="D71" s="166"/><c r="E71" s="166"/><c r="F71" s="63"/><c r="G71" s="1"/><c r="H71" s="46"/><c r="I71" s="50"/><c r="J71"/><c r="L71" s="49" t="s"><v>59</v></c><c r="M71" s="130" t="s"><v>55</v></c><c r="N71" s="131"/><c r="O71" s="131"/><c r="P71" s="131" t="s"><v>56</v></c><c r="Q71" s="131"/><c r="R71" s="131"/><c r="S71" s="131"/><c r="T71" s="131" t="s"><v>57</v></c><c r="U71" s="132" t="s"><v>60</v></c><c r="V71" s="144" t="s"><v>58</v></c><c r="W71" s="144" t="s"><v>50</v></c></row><row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A72" s="25"/><c r="B72" s="115"/><c r="C72" s="25"/><c r="D72" s="166"/><c r="E72" s="166"/><c r="F72" s="63"/><c r="G72" s="1"/><c r="H72" s="46"/><c r="I72" s="50"/><c r="J72" s="23"/><c r="L72" s="0"/><c r="M72" s="59"/><c r="N72" s="60"/><c r="O72" s="143" t="s"><v>43</v></c><c r="P72" s="62"/><c r="Q72" s="61"/><c r="R72" s="177" t="inlineStr"><is><t xml:space="preserve">CREDITO</t></is></c><c r="S72" s="177"/><c r="T72" s="133"/><c r="U72" s="134"/><c r="V72" s="51"/></row><row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="B73" s="51"/><c r="C73" s="89"/><c r="D73" s="166"/><c r="E73" s="166"/><c r="F73" s="63"/><c r="I73" s="115"/><c r="L73"/><c r="M73" s="85"/><c r="N73" s="86"/><c r="O73" s="18"/><c r="P73" s="87"/><c r="Q73" s="56"/><c r="R73" s="175"/><c r="S73" s="175"/><c r="T73" s="65"/><c r="U73" s="95"/><c r="V73" s="51"/></row><row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A74" s="49"/><c r="B74" s="89"/><c r="C74" s="89"/><c r="D74" s="23"/><c r="E74" s="25"/><c r="F74" s="63"/><c r="I74" s="115"/><c r="L74" s="45" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="M74" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N74" s="86"/><c r="O74" s="18" t="s"><v>43</v></c><c r="P74" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q74" s="56"/><c r="R74" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S74" s="175"/><c r="T74" s="65"><v>150000</v></c><c r="U74" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V74" s="51"/></row><row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L75" s="45" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="M75" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N75" s="86"/><c r="O75" s="123"/><c r="P75" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q75" s="56"/><c r="R75" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S75" s="175"/><c r="T75" s="65"><v>150000</v></c><c r="U75" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V75" s="51"/></row><row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L76" s="45"/><c r="M76" s="137" t="s"><v>61</v></c><c r="N76" s="138"/><c r="O76" s="139"/><c r="P76" s="140"/><c r="Q76" s="141"/><c r="R76" s="176"/><c r="S76" s="176"/><c r="T76" s="173"/><c r="U76" s="174"/><c r="V76" s="51"/></row><row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L77" s="45"/><c r="M77" s="137" t="s"><v>62</v></c><c r="N77" s="138"/><c r="O77" s="139"/><c r="P77" s="140"/><c r="Q77" s="141"/><c r="R77" s="142"/><c r="S77" s="142"/><c r="T77" s="173"/><c r="U77" s="174"/><c r="V77" s="51"/></row><row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L78" s="45"/><c r="M78" s="94"/><c r="N78" s="64"/><c r="O78" s="123"/><c r="P78" s="87"/><c r="Q78" s="56"/><c r="R78" s="56"/><c r="S78" s="56"/><c r="T78" s="65"/><c r="U78" s="95"/><c r="V78" s="51"/></row><row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L79" s="45"/><c r="M79" s="101" t="s"><v>11</v></c><c r="N79" s="102"><f>SUM(N77:N78)</f><v>0</v></c><c r="O79" s="96"/><c r="P79" s="98"/><c r="Q79" s="97"/><c r="R79" s="97"/><c r="S79" s="97"/><c r="T79" s="99"/><c r="U79" s="100"/><c r="V79" s="51"/></row><row r="80" spans="1:23" x14ac:dyDescent="0.3"><c r="M80"/><c r="O80" s="5"/><c r="Q80"/><c r="S80"/><c r="T80" s="6"/><c r="V80" s="51"/></row><row r="81" spans="1:23" x14ac:dyDescent="0.3"><c r="O81"/><c r="V81" s="51"/></row><row r="82" spans="13:22" x14ac:dyDescent="0.3"><c r="M82" s="23"/><c r="N82" s="23"/><c r="O82" s="23"/><c r="P82" s="23"/><c r="Q82" s="23"/><c r="V82" s="51"/></row><row r="83" spans="13:22" x14ac:dyDescent="0.3"><c r="V83" s="51"/></row><row r="84" spans="13:22" x14ac:dyDescent="0.3"><c r="V84" s="51"/></row><row r="85" spans="13:22" x14ac:dyDescent="0.3"><c r="V85" s="51"/></row><row r="86" spans="13:22" x14ac:dyDescent="0.3"><c r="V86" s="51"/></row><row r="87" spans="13:22" x14ac:dyDescent="0.3"><c r="V87" s="51"/></row><row r="88" spans="13:22" x14ac:dyDescent="0.3"><c r="V88" s="51"/></row><row r="89" spans="13:22" x14ac:dyDescent="0.3"><c r="V89" s="51"/></row><row r="90" spans="13:22" x14ac:dyDescent="0.3"><c r="V90" s="51"/></row><row r="91" spans="13:22" x14ac:dyDescent="0.3"><c r="V91" s="51"/></row><row r="92" spans="13:22" x14ac:dyDescent="0.3"><c r="V92" s="51"/></row><row r="93" spans="13:22" x14ac:dyDescent="0.3"><c r="V93" s="51"/></row><row r="94" spans="13:22" x14ac:dyDescent="0.3"><c r="V94" s="51"/></row><row r="95" spans="13:22" x14ac:dyDescent="0.3"><c r="V95" s="51"/></row><row r="96" spans="13:22" x14ac:dyDescent="0.3"><c r="V96" s="51"/></row><row r="97" spans="13:22" x14ac:dyDescent="0.3"><c r="V97" s="51"/></row><row r="98" spans="22:22" x14ac:dyDescent="0.3"><c r="V98" s="51"/></row><row r="99" spans="22:22" x14ac:dyDescent="0.3"><c r="V99" s="51"/></row><row r="100" spans="22:22" x14ac:dyDescent="0.3"><c r="V100" s="51"/></row><row r="101" spans="22:22" x14ac:dyDescent="0.3"><c r="V101" s="51"/></row><row r="102" spans="22:22" x14ac:dyDescent="0.3"><c r="V102" s="51"/></row><row r="103" spans="22:22" x14ac:dyDescent="0.3"><c r="V103" s="51"/></row><row r="104" spans="22:22" x14ac:dyDescent="0.3"><c r="V104" s="51"/></row><row r="105" spans="22:22" x14ac:dyDescent="0.3"><c r="V105" s="51"/></row><row r="106" spans="22:22" x14ac:dyDescent="0.3"><c r="V106" s="51"/></row><row r="107" spans="22:22" x14ac:dyDescent="0.3"><c r="V107" s="51"/></row><row r="108" spans="22:22" x14ac:dyDescent="0.3"><c r="V108" s="51"/></row><row r="109" spans="22:22" x14ac:dyDescent="0.3"><c r="V109" s="51"/></row><row r="110" spans="22:22" x14ac:dyDescent="0.3"><c r="V110" s="51"/></row><row r="111" spans="22:22" x14ac:dyDescent="0.3"><c r="V111" s="51"/></row><row r="112" spans="22:22" x14ac:dyDescent="0.3"><c r="V112" s="51"/></row><row r="113" spans="22:22" x14ac:dyDescent="0.3"><c r="V113" s="51"/></row></sheetData><mergeCells count="70"><mergeCell ref="M25:N25"/><mergeCell ref="O30:P30"/><mergeCell ref="Q30:S30"/><mergeCell ref="T30:U30"/><mergeCell ref="Q32:S32"/><mergeCell ref="M31:N31"/><mergeCell ref="O31:P31"/><mergeCell ref="Q31:S31"/><mergeCell ref="M30:N30"/><mergeCell ref="M32:N32"/><mergeCell ref="O32:P32"/><mergeCell ref="M22:U22"/><mergeCell ref="Q26:S26"/><mergeCell ref="O29:P29"/><mergeCell ref="Q29:S29"/><mergeCell ref="T29:U29"/><mergeCell ref="T28:U28"/><mergeCell ref="O28:P28"/><mergeCell ref="Q28:S28"/><mergeCell ref="M28:N28"/><mergeCell ref="M29:N29"/><mergeCell ref="O27:P27"/><mergeCell ref="Q27:S27"/><mergeCell ref="T27:U27"/><mergeCell ref="N23:S23"/><mergeCell ref="N24:S24"/><mergeCell ref="T25:U25"/><mergeCell ref="D44:E44"/><mergeCell ref="R35:S35"/><mergeCell ref="T35:U35"/><mergeCell ref="O33:P33"/><mergeCell ref="Q33:S33"/><mergeCell ref="M34:N34"/><mergeCell ref="O34:P34"/><mergeCell ref="Q34:S34"/><mergeCell ref="P35:Q35"/><mergeCell ref="M35:O35"/><mergeCell ref="M39:N39"/><mergeCell ref="D72:E72"/><mergeCell ref="D73:E73"/><mergeCell ref="D53:E53"/><mergeCell ref="M70:U70"/><mergeCell ref="R68:S68"/><mergeCell ref="D69:E69"/><mergeCell ref="P68:Q68"/><mergeCell ref="T68:U68"/><mergeCell ref="D61:E61"/><mergeCell ref="D67:E67"/><mergeCell ref="D54:E54"/><mergeCell ref="D66:E66"/><mergeCell ref="D55:E55"/><mergeCell ref="D65:E65"/><mergeCell ref="T77:U77"/><mergeCell ref="R75:S75"/><mergeCell ref="R76:S76"/><mergeCell ref="R72:S72"/><mergeCell ref="R74:S74"/><mergeCell ref="R73:S73"/><mergeCell ref="T76:U76"/><mergeCell ref="D71:E71"/><mergeCell ref="D70:E70"/><mergeCell ref="M68:O68"/><mergeCell ref="D45:E45"/><mergeCell ref="D47:E47"/><mergeCell ref="M66:N66"/><mergeCell ref="D49:E49"/><mergeCell ref="D50:E50"/><mergeCell ref="D48:E48"/><mergeCell ref="D46:E46"/><mergeCell ref="D52:E52"/></mergeCells><pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/><pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/><drawing r:id="rId2"/></worksheet>
 </file>
--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -1950,5 +1950,5 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}"><dimension ref="A1:W113"/><sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/><cols><col min="1" max="1" width="17.33203125" customWidth="1"/><col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/><col min="3" max="3" width="12.6640625" customWidth="1"/><col min="4" max="4" width="12.6640625" style="3" customWidth="1"/><col min="5" max="5" width="12.6640625" customWidth="1"/><col min="6" max="6" width="12.6640625" style="3" customWidth="1"/><col min="7" max="9" width="12.6640625" customWidth="1"/><col min="10" max="10" width="12.6640625" style="3" customWidth="1"/><col min="11" max="11" width="12.6640625" customWidth="1"/><col min="12" max="12" width="12.6640625" style="3" customWidth="1"/><col min="13" max="13" width="11.5546875" style="3" customWidth="1"/><col min="14" max="14" width="11" bestFit="1" customWidth="1"/><col min="15" max="15" width="11.6640625" style="4" customWidth="1"/><col min="16" max="19" width="11.6640625" style="3" customWidth="1"/><col min="20" max="20" width="13.88671875" customWidth="1"/><col min="21" max="21" width="14" customWidth="1"/><col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/><col min="23" max="23" width="16" customWidth="1"/></cols><sheetData><row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A1" s="7" t="s"><v>50</v></c><c r="B1" s="112" t="inlineStr"><is><t xml:space="preserve">JUAN PEREZ</t></is></c><c r="C1" s="120" t="inlineStr"><is><t xml:space="preserve">MARIA LOPEZ</t></is></c><c r="D1" s="120"/><c r="E1" s="112"/><c r="F1" s="120"/><c r="G1" s="120"/><c r="H1" s="112"/><c r="I1" s="112"/><c r="J1" s="120"/><c r="K1" s="120"/><c r="L1" s="112"/><c r="M1" s="112"/><c r="N1" s="112"/><c r="O1" s="112"/><c r="P1" s="112"/><c r="Q1" s="112"/><c r="R1" s="121"/><c r="S1" s="120"/><c r="T1" s="120"/><c r="U1" s="7"/><c r="V1" s="7"/><c r="W1" s="114"/></row><row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A2" s="7" t="s"><v>51</v></c><c r="B2" s="112"/><c r="C2" s="120"/><c r="D2" s="120"/><c r="E2" s="112"/><c r="F2" s="120"/><c r="G2" s="128"/><c r="H2" s="112"/><c r="I2" s="112"/><c r="J2" s="120"/><c r="K2" s="120"/><c r="L2" s="112"/><c r="M2" s="112"/><c r="N2" s="112"/><c r="O2" s="112"/><c r="P2" s="112"/><c r="Q2" s="112"/><c r="R2" s="121"/><c r="S2" s="120"/><c r="T2" s="120"/><c r="U2" s="7"/><c r="V2" s="7"/><c r="W2" s="114"/></row><row r="3" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A3" s="122" t="s"><v>35</v></c><c r="B3" s="120"/><c r="C3" s="120"/><c r="D3" s="120"/><c r="E3" s="120"/><c r="F3" s="120"/><c r="G3" s="120"/><c r="H3" s="120"/><c r="I3" s="120"/><c r="J3" s="120"/><c r="K3" s="120"/><c r="L3" s="120"/><c r="M3" s="120"/><c r="N3" s="120"/><c r="O3" s="120"/><c r="P3" s="120"/><c r="Q3" s="120"/><c r="R3" s="120"/><c r="S3" s="120"/><c r="T3" s="120"/><c r="U3" s="110"/><c r="V3" s="163"/><c r="W3" s="116"/></row><row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A4" s="122" t="s"><v>52</v></c><c r="B4" s="120"/><c r="C4" s="120"/><c r="D4" s="120"/><c r="E4" s="120"/><c r="F4" s="120"/><c r="G4" s="120"/><c r="H4" s="120"/><c r="I4" s="120"/><c r="J4" s="120"/><c r="K4" s="120"/><c r="L4" s="120"/><c r="M4" s="120"/><c r="N4" s="120"/><c r="O4" s="120"/><c r="P4" s="120"/><c r="Q4" s="120"/><c r="R4" s="120"/><c r="S4" s="120"/><c r="T4" s="120"/><c r="U4" s="110"/><c r="V4" s="163"/><c r="W4" s="116"/></row><row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A5" s="122" t="s"><v>0</v></c><c r="B5" s="129" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="C5" s="129" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="D5" s="129"/><c r="E5" s="129"/><c r="F5" s="129"/><c r="G5" s="129"/><c r="H5" s="129"/><c r="I5" s="129"/><c r="J5" s="129"/><c r="K5" s="129"/><c r="L5" s="129"/><c r="M5" s="129"/><c r="N5" s="129"/><c r="O5" s="129"/><c r="P5" s="129"/><c r="Q5" s="129"/><c r="R5" s="120"/><c r="S5" s="120"/><c r="T5" s="120"/><c r="U5" s="111"/><c r="V5" s="111"/><c r="W5" s="111"/></row><row r="6" spans="1:23" s="45" customFormat="1" x14ac:dyDescent="0.3"><c r="A6" s="122" t="s"><v>1</v></c><c r="B6" s="120"><v>10</v></c><c r="C6" s="120"><v>10</v></c><c r="D6" s="120"/><c r="E6" s="120"/><c r="F6" s="120"/><c r="G6" s="120"/><c r="H6" s="120"/><c r="I6" s="120"/><c r="J6" s="120"/><c r="K6" s="120"/><c r="L6" s="120"/><c r="M6" s="111"/><c r="N6" s="111"/><c r="O6" s="111"/><c r="P6" s="111"/><c r="Q6" s="111"/><c r="R6" s="120"/><c r="S6" s="120"/><c r="T6" s="120"/><c r="U6" s="111"/><c r="V6" s="111"/><c r="W6" s="111"/></row><row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3"><c r="A7" s="122" t="s"><v>2</v></c><c r="B7" s="164"><v>1000000</v></c><c r="C7" s="164"><v>1000000</v></c><c r="D7" s="164"/><c r="E7" s="164"/><c r="F7" s="164"/><c r="G7" s="164"/><c r="H7" s="164"/><c r="I7" s="164"/><c r="J7" s="164"/><c r="K7" s="164"/><c r="L7" s="164"/><c r="M7" s="164"/><c r="N7" s="164"/><c r="O7" s="164"/><c r="P7" s="164"/><c r="Q7" s="164"/><c r="R7" s="156"/><c r="S7" s="156"/><c r="T7" s="156"/><c r="U7" s="157"/><c r="V7" s="157"/><c r="W7" s="157"/></row><row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A8" s="112"/><c r="B8" s="157"/><c r="C8" s="111"/><c r="D8" s="157"/><c r="E8" s="111"/><c r="F8" s="110"/><c r="G8" s="111"/><c r="H8" s="157"/><c r="I8" s="111"/><c r="J8" s="157"/><c r="K8" s="111"/><c r="L8" s="110"/><c r="M8" s="111"/><c r="N8" s="110"/><c r="O8" s="111"/><c r="P8" s="158"/><c r="Q8" s="111"/><c r="R8" s="158"/><c r="S8" s="111"/><c r="T8" s="158"/><c r="U8" s="111"/><c r="V8" s="110"/><c r="W8" s="111"/></row><row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A9" s="113" t="s"><v>3</v></c><c r="B9" s="165"><v>450000</v></c><c r="C9" s="165"><v>450000</v></c><c r="D9" s="165"/><c r="E9" s="157"/><c r="F9" s="110"/><c r="G9" s="157"/><c r="H9" s="110"/><c r="I9" s="157"/><c r="J9" s="110"/><c r="K9" s="157"/><c r="L9" s="110"/><c r="M9" s="157"/><c r="N9" s="110"/><c r="O9" s="157"/><c r="P9" s="158"/><c r="Q9" s="157"/><c r="R9" s="158"/><c r="S9" s="159"/><c r="T9" s="159"/><c r="U9" s="157"/><c r="V9" s="110"/><c r="W9" s="157"/></row><row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A10" s="113" t="s"><v>54</v></c><c r="B10" s="165"><v>50000</v></c><c r="C10" s="165"><v>50000</v></c><c r="D10" s="165"/><c r="E10" s="157"/><c r="F10" s="110"/><c r="G10" s="157"/><c r="H10" s="110"/><c r="I10" s="157"/><c r="J10" s="110"/><c r="K10" s="157"/><c r="L10" s="110"/><c r="M10" s="157"/><c r="N10" s="110"/><c r="O10" s="157"/><c r="P10" s="158"/><c r="Q10" s="157"/><c r="R10" s="158"/><c r="S10" s="159"/><c r="T10" s="159"/><c r="U10" s="157"/><c r="V10" s="110"/><c r="W10" s="157"/></row><row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A11" s="113" t="s"><v>4</v></c><c r="B11" s="165"><v>300000</v></c><c r="C11" s="165"><v>300000</v></c><c r="D11" s="165"/><c r="E11" s="157"/><c r="F11" s="110"/><c r="G11" s="157"/><c r="H11" s="110"/><c r="I11" s="157"/><c r="J11" s="110"/><c r="K11" s="157"/><c r="L11" s="110"/><c r="M11" s="157"/><c r="N11" s="110"/><c r="O11" s="157"/><c r="P11" s="158"/><c r="Q11" s="157"/><c r="R11" s="158"/><c r="S11" s="159"/><c r="T11" s="159"/><c r="U11" s="157"/><c r="V11" s="110"/><c r="W11" s="157"/></row><row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A12" s="113" t="s"><v>5</v></c><c r="B12" s="165"/><c r="C12" s="165"/><c r="D12" s="165"/><c r="E12" s="157"/><c r="F12" s="110"/><c r="G12" s="157"/><c r="H12" s="110"/><c r="I12" s="157"/><c r="J12" s="110"/><c r="K12" s="157"/><c r="L12" s="110"/><c r="M12" s="157"/><c r="N12" s="110"/><c r="O12" s="157"/><c r="P12" s="158"/><c r="Q12" s="157"/><c r="R12" s="158"/><c r="S12" s="159"/><c r="T12" s="159"/><c r="U12" s="157"/><c r="V12" s="110"/><c r="W12" s="157"/></row><row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A13" s="113" t="s"><v>6</v></c><c r="B13" s="165"/><c r="C13" s="165"/><c r="D13" s="165"/><c r="E13" s="157"/><c r="F13" s="110"/><c r="G13" s="157"/><c r="H13" s="110"/><c r="I13" s="157"/><c r="J13" s="110"/><c r="K13" s="157"/><c r="L13" s="110"/><c r="M13" s="157"/><c r="N13" s="110"/><c r="O13" s="157"/><c r="P13" s="158"/><c r="Q13" s="157"/><c r="R13" s="158"/><c r="S13" s="159"/><c r="T13" s="159"/><c r="U13" s="157"/><c r="V13" s="110"/><c r="W13" s="157"/></row><row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A14" s="113" t="s"><v>7</v></c><c r="B14" s="165"/><c r="C14" s="165"/><c r="D14" s="165"/><c r="E14" s="157"/><c r="F14" s="110"/><c r="G14" s="157"/><c r="H14" s="110"/><c r="I14" s="157"/><c r="J14" s="110"/><c r="K14" s="157"/><c r="L14" s="110"/><c r="M14" s="157"/><c r="N14" s="110"/><c r="O14" s="157"/><c r="P14" s="158"/><c r="Q14" s="157"/><c r="R14" s="158"/><c r="S14" s="159"/><c r="T14" s="159"/><c r="U14" s="157"/><c r="V14" s="110"/><c r="W14" s="157"/></row><row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A15" s="113" t="s"><v>8</v></c><c r="B15" s="165"/><c r="C15" s="165"/><c r="D15" s="165"/><c r="E15" s="157"/><c r="F15" s="110"/><c r="G15" s="157"/><c r="H15" s="110"/><c r="I15" s="157"/><c r="J15" s="110"/><c r="K15" s="157"/><c r="L15" s="110"/><c r="M15" s="157"/><c r="N15" s="110"/><c r="O15" s="157"/><c r="P15" s="158"/><c r="Q15" s="157"/><c r="R15" s="158"/><c r="S15" s="159"/><c r="T15" s="159"/><c r="U15" s="157"/><c r="V15" s="110"/><c r="W15" s="157"/></row><row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A16" s="113" t="s"><v>9</v></c><c r="B16" s="165"/><c r="C16" s="165"/><c r="D16" s="165"/><c r="E16" s="157"/><c r="F16" s="110"/><c r="G16" s="157"/><c r="H16" s="110"/><c r="I16" s="160"/><c r="J16" s="110"/><c r="K16" s="160"/><c r="L16" s="110"/><c r="M16" s="157"/><c r="N16" s="110"/><c r="O16" s="157"/><c r="P16" s="158"/><c r="Q16" s="157"/><c r="R16" s="158"/><c r="S16" s="159"/><c r="T16" s="159"/><c r="U16" s="157"/><c r="V16" s="110"/><c r="W16" s="157"/></row><row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A17" s="113" t="s"><v>10</v></c><c r="B17" s="165"/><c r="C17" s="165"/><c r="D17" s="165"/><c r="E17" s="157"/><c r="F17" s="110"/><c r="G17" s="157"/><c r="H17" s="110"/><c r="I17" s="160"/><c r="J17" s="110"/><c r="K17" s="157"/><c r="L17" s="110"/><c r="M17" s="157"/><c r="N17" s="110"/><c r="O17" s="157"/><c r="P17" s="158"/><c r="Q17" s="157"/><c r="R17" s="158"/><c r="S17" s="159"/><c r="T17" s="159"/><c r="U17" s="157"/><c r="V17" s="110"/><c r="W17" s="157"/></row><row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A18" s="113" t="s"><v>11</v></c><c r="B18" s="110"><f>SUM(B9:B17)</f><v>0</v></c><c r="C18" s="110"><f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f><v>0</v></c><c r="D18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="E18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="F18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="G18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="H18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="I18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="J18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="K18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="L18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="M18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="N18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="O18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="P18" s="110"><f t="shared" ref="P18" si="1">SUM(P9:P17)</f><v>0</v></c><c r="Q18" s="110"><f>SUM(Q9:Q17)</f><v>0</v></c><c r="R18" s="110"><f>SUM(R9:R17)</f><v>0</v></c><c r="S18" s="116"><f>SUM(S9:S17)</f><v>0</v></c><c r="T18" s="116"><f>SUM(T9:T17)</f><v>0</v></c><c r="U18" s="110"><f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f><v>0</v></c><c r="V18" s="110"><f t="shared" si="2"/><v>0</v></c><c r="W18" s="110"><f t="shared" si="2"/><v>0</v></c></row><row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A19" s="113"/><c r="B19" s="110"/><c r="C19" s="110"/><c r="D19" s="110"/><c r="E19" s="110"/><c r="F19" s="157"/><c r="G19" s="110"/><c r="H19" s="110"/><c r="I19" s="110"/><c r="J19" s="110"/><c r="K19" s="110"/><c r="L19" s="110"/><c r="M19" s="110"/><c r="N19" s="110"/><c r="O19" s="110"/><c r="P19" s="110"/><c r="Q19" s="110"/><c r="R19" s="110"/><c r="S19" s="116"/><c r="T19" s="116"/><c r="U19" s="110"/><c r="V19" s="110"/><c r="W19" s="110"/></row><row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3"><c r="A20" s="113" t="s"><v>12</v></c><c r="B20" s="110" t="e"><f t="shared" ref="B20:O20" si="3">B18-B7</f><v>#VALUE!</v></c><c r="C20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="D20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="E20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="F20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="G20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="H20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="I20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="J20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="K20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="L20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="M20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="N20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="O20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="P20" s="110"><f t="shared" ref="P20" si="4">P18-P7</f><v>0</v></c><c r="Q20" s="110"><f>Q18-Q7</f><v>0</v></c><c r="R20" s="110"><f>R18-R7</f><v>0</v></c><c r="S20" s="110"><f>S18-S7</f><v>0</v></c><c r="T20" s="110"><f>T18-T7</f><v>0</v></c><c r="U20" s="110"><f t="shared" ref="U20:W20" si="5">U18-U7</f><v>0</v></c><c r="V20" s="110"><f t="shared" si="5"/><v>0</v></c><c r="W20" s="110"><f t="shared" si="5"/><v>0</v></c></row><row r="21" spans="1:23" x14ac:dyDescent="0.3"><c r="A21" s="1"/><c r="B21" s="9"/><c r="C21" s="10"/><c r="D21" s="9"/><c r="E21" s="10"/><c r="F21" s="11"/><c r="G21" s="10"/><c r="H21" s="11"/><c r="I21" s="9"/><c r="J21" s="9"/><c r="K21" s="10"/><c r="L21" s="12"/><c r="M21" s="12"/><c r="N21" s="10"/><c r="O21" s="9"/><c r="P21" s="9"/><c r="Q21" s="10"/><c r="R21" s="12"/><c r="S21" s="12"/><c r="T21" s="9"/><c r="U21" s="9"/><c r="V21" s="9"/><c r="W21" s="9"/></row><row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35"><c r="D22" s="2"/><c r="M22" s="198" t="s"><v>48</v></c><c r="N22" s="198"/><c r="O22" s="198"/><c r="P22" s="198"/><c r="Q22" s="198"/><c r="R22" s="198"/><c r="S22" s="198"/><c r="T22" s="198"/><c r="U22" s="198"/></row><row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="D23" s="6"/><c r="J23"/><c r="L23"/><c r="M23" s="14" t="s"><v>13</v></c><c r="N23" s="207" t="inlineStr"><is><t xml:space="preserve">24-06-2026</t></is></c><c r="O23" s="208"/><c r="P23" s="208"/><c r="Q23" s="208"/><c r="R23" s="208"/><c r="S23" s="209"/><c r="T23" s="119" t="s"><v>38</v></c><c r="U23" s="106"><v>20</v></c><c r="W23" s="91" t="s"><v>44</v></c></row><row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="B24" s="2"/><c r="C24" s="18"/><c r="J24"/><c r="K24" s="15"/><c r="L24"/><c r="M24" s="16"/><c r="N24" s="210" t="s"><v>49</v></c><c r="O24" s="211"/><c r="P24" s="211"/><c r="Q24" s="211"/><c r="R24" s="211"/><c r="S24" s="212"/><c r="T24" s="108" t="s"><v>11</v></c><c r="U24" s="107"><v>2000000</v></c><c r="W24" s="118"><v>20</v></c></row><row r="25" spans="1:23" x14ac:dyDescent="0.3"><c r="B25" s="2"/><c r="C25" s="103"/><c r="D25" s="3" t="s"><v>15</v></c><c r="E25" s="4"/><c r="J25"/><c r="L25"/><c r="M25" s="215" t="s"><v>16</v></c><c r="N25" s="216"/><c r="O25" s="148"/><c r="P25" s="149"/><c r="Q25" s="145"><v>900000</v></c><c r="R25" s="146"/><c r="S25" s="147"/><c r="T25" s="213" t="s"><v>17</v></c><c r="U25" s="214"/><c r="V25" s="13"/><c r="W25" s="82" t="s"><v>45</v></c></row><row r="26" spans="1:23" x14ac:dyDescent="0.3"><c r="E26" s="4"/><c r="J26"/><c r="L26"/><c r="M26" s="79" t="s"><v>53</v></c><c r="N26" s="80"/><c r="O26" s="126"/><c r="P26" s="127"/><c r="Q26" s="188"><v>100000</v></c><c r="R26" s="189"/><c r="S26" s="190"/><c r="T26" s="124"/><c r="U26" s="125"/><c r="V26" s="13"/><c r="W26" s="82"/></row><row r="27" spans="1:23" x14ac:dyDescent="0.3"><c r="I27" s="109" t="str"><f>B1</f></c><c r="J27" s="136" t="str"><f>B9</f></c><c r="L27"/><c r="M27" s="79" t="s"><v>18</v></c><c r="N27" s="80"/><c r="O27" s="186"/><c r="P27" s="187"/><c r="Q27" s="188"><v>600000</v></c><c r="R27" s="189"/><c r="S27" s="190"/><c r="T27" s="205" t="s"><v>19</v></c><c r="U27" s="206"/><c r="V27" s="19"/><c r="W27" s="92"><v>2000000</v></c></row><row r="28" spans="1:23" x14ac:dyDescent="0.3"><c r="I28" s="109"><f>C1</f><v>0</v></c><c r="J28" s="136"><f>C9</f><v>0</v></c><c r="L28"/><c r="M28" s="203" t="s"><v>20</v></c><c r="N28" s="204"/><c r="O28" s="186"/><c r="P28" s="187"/><c r="Q28" s="188"/><c r="R28" s="189"/><c r="S28" s="190"/><c r="T28" s="201" t="s"><v>39</v></c><c r="U28" s="202"/><c r="V28" s="21"/><c r="W28" s="13"/></row><row r="29" spans="1:23" x14ac:dyDescent="0.3"><c r="I29" s="109"><f>D1</f><v>0</v></c><c r="J29" s="136"><f>D9</f><v>0</v></c><c r="K29" s="24"/><c r="L29"/><c r="M29" s="203" t="s"><v>21</v></c><c r="N29" s="204"/><c r="O29" s="186"/><c r="P29" s="187"/><c r="Q29" s="188"/><c r="R29" s="189"/><c r="S29" s="190"/><c r="T29" s="199" t="s"><v>40</v></c><c r="U29" s="200"/><c r="W29" s="93" t="str"><f>U23</f></c></row><row r="30" spans="1:23" x14ac:dyDescent="0.3"><c r="A30" s="1"/><c r="I30" s="109"><f>E1</f><v>0</v></c><c r="J30" s="136"><f>E9</f><v>0</v></c><c r="L30"/><c r="M30" s="203" t="s"><v>22</v></c><c r="N30" s="204"/><c r="O30" s="186"/><c r="P30" s="217"/><c r="Q30" s="188"/><c r="R30" s="189"/><c r="S30" s="190"/><c r="T30" s="218" t="s"><v>41</v></c><c r="U30" s="219"/><c r="V30" s="24"/><c r="W30" s="21" t="str"><f>Q34</f></c></row><row r="31" spans="1:23" x14ac:dyDescent="0.3"><c r="A31" s="1"/><c r="I31" s="109"><f>F1</f><v>0</v></c><c r="J31" s="136"><f>F9</f><v>0</v></c><c r="L31"/><c r="M31" s="203" t="s"><v>23</v></c><c r="N31" s="204"/><c r="O31" s="186"/><c r="P31" s="187"/><c r="Q31" s="188"/><c r="R31" s="189"/><c r="S31" s="190"/><c r="T31" s="28"/><c r="U31" s="26"/></row><row r="32" spans="1:23" x14ac:dyDescent="0.3"><c r="A32" s="1"/><c r="I32" s="109"><f>G1</f><v>0</v></c><c r="J32" s="136"><f>G9</f><v>0</v></c><c r="L32"/><c r="M32" s="203" t="s"><v>24</v></c><c r="N32" s="204"/><c r="O32" s="186"/><c r="P32" s="187"/><c r="Q32" s="188"/><c r="R32" s="189"/><c r="S32" s="190"/><c r="T32" s="28"/><c r="U32" s="26"/><c r="W32" s="82" t="s"><v>46</v></c></row><row r="33" spans="1:23" x14ac:dyDescent="0.3"><c r="A33" s="1"/><c r="I33" s="109"><f>H1</f><v>0</v></c><c r="J33" s="136"><f>H9</f><v>0</v></c><c r="L33"/><c r="M33" s="79" t="s"><v>25</v></c><c r="N33" s="81"/><c r="O33" s="186"/><c r="P33" s="187"/><c r="Q33" s="188"/><c r="R33" s="189"/><c r="S33" s="190"/><c r="T33" s="28"/><c r="U33" s="26"/><c r="W33" s="117" t="e"><f>W30-W27</f><v>#VALUE!</v></c></row><row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A34" s="1"/><c r="I34" s="109"><f>I1</f><v>0</v></c><c r="J34" s="136"><f>I9</f><v>0</v></c><c r="L34" s="8"/><c r="M34" s="191" t="s"><v>26</v></c><c r="N34" s="192"/><c r="O34" s="193"/><c r="P34" s="194"/><c r="Q34" s="188"><v>2000000</v></c><c r="R34" s="189"/><c r="S34" s="190"/><c r="T34" s="30"/><c r="U34" s="29"/><c r="V34" s="1"/><c r="W34" s="24"/></row><row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A35" s="1"/><c r="D35" s="31"/><c r="I35" s="41"><f>J1</f><v>0</v></c><c r="J35" s="27"><f>J9</f><v>0</v></c><c r="L35"/><c r="M35" s="195" t="s"><v>27</v></c><c r="N35" s="196"/><c r="O35" s="197"/><c r="P35" s="167" t="s"><v>28</v></c><c r="Q35" s="169"/><c r="R35" s="167" t="s"><v>29</v></c><c r="S35" s="169"/><c r="T35" s="167" t="s"><v>30</v></c><c r="U35" s="169"/><c r="V35" s="1"/><c r="W35" s="1"/></row><row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B36" s="9"/><c r="I36" s="41"><f>K1</f><v>0</v></c><c r="J36" s="27"><f>K9</f><v>0</v></c><c r="L36"/><c r="M36" s="33" t="s"><v>13</v></c><c r="N36" s="34" t="s"><v>31</v></c><c r="O36" s="35" t="s"><v>32</v></c><c r="P36" s="36" t="s"><v>33</v></c><c r="Q36" s="35" t="s"><v>32</v></c><c r="R36" s="36" t="s"><v>33</v></c><c r="S36" s="35" t="s"><v>32</v></c><c r="T36" s="36" t="s"><v>33</v></c><c r="U36" s="35" t="s"><v>32</v></c><c r="V36" s="1"/><c r="W36" s="1"/></row><row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A37" s="1"/><c r="I37" s="41"><f>L$1</f><v>0</v></c><c r="J37" s="27"><f>L9</f><v>0</v></c><c r="K37" s="24"/><c r="L37"/><c r="M37" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N37" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O37" s="39"><v>100000</v></c><c r="P37" s="151"/><c r="Q37" s="77"/><c r="R37" s="153"/><c r="S37" s="78"/><c r="T37" s="152"/><c r="U37" s="74"/><c r="V37" s="1"/><c r="W37" s="18" t="s"><v>14</v></c></row><row r="38"  x14ac:dyDescent="0.3" spans="1:23" x14ac:dyDescent="0.3"><c r="A38" s="1"/><c r="I38" s="41"><f>L$1</f><v>0</v></c><c r="J38" s="27"><f>L9</f><v>0</v></c><c r="K38" s="24"/><c r="L38"/><c r="M38" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N38" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O38" s="39"><v>100000</v></c><c r="P38" s="42"/><c r="Q38" s="72"/><c r="R38" s="44"/><c r="S38" s="77"/><c r="T38" s="42"/><c r="U38" s="72"/><c r="V38" s="1"/><c r="W38" s="18" t="s"><v>14</v></c></row><row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B39" s="20"/><c r="C39" s="32"/><c r="I39" s="41"><f t="shared" ref="I39:I46" si="6">L$1</f><v>0</v></c><c r="J39" s="27"><f t="shared" ref="J39:J46" si="7">L10</f><v>0</v></c><c r="L39" s="105"/><c r="M39" s="171" t="s"><v>42</v></c><c r="N39" s="179"/><c r="O39" s="150"><v>600000</v></c><c r="P39" s="152"/><c r="Q39" s="75"/><c r="R39" s="154"/><c r="S39" s="73"/><c r="T39" s="152"/><c r="U39" s="76"/><c r="V39" s="1"/><c r="W39" s="1"/></row><row r="40" spans="1:23" x14ac:dyDescent="0.3"><c r="O40" s="39"/><c r="N40" s="38"/><c r="M40" s="37"/><c r="B40" s="20"/><c r="C40" s="32"/><c r="I40" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J40" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K40" s="24"/><c r="L40" s="105"/><c r="M40" s="37"/><c r="N40" s="38"/><c r="O40" s="39"/><c r="P40" s="152"/><c r="Q40" s="68"/><c r="R40" s="154"/><c r="S40" s="73"/><c r="T40" s="152"/><c r="U40" s="68"/><c r="V40" s="1"/><c r="W40" s="1"/></row><row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"><c r="B41" s="20"/><c r="C41" s="32"/><c r="D41" s="44"/><c r="E41" s="43"/><c r="I41" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J41" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K41" s="24"/><c r="L41" s="105"/><c r="M41" s="37"/><c r="N41" s="38"/><c r="O41" s="39"/><c r="P41" s="152"/><c r="Q41" s="66"/><c r="R41" s="154"/><c r="S41" s="74"/><c r="T41" s="152"/><c r="U41" s="68"/><c r="V41" s="1"/><c r="W41" s="1"/></row><row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="B42" s="20"/><c r="C42" s="32"/><c r="D42" s="23"/><c r="E42" s="23"/><c r="I42" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J42" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K42" s="24"/><c r="L42" s="105"/><c r="M42" s="37"/><c r="N42" s="38"/><c r="O42" s="39"/><c r="P42" s="152"/><c r="Q42" s="66"/><c r="R42" s="154"/><c r="S42" s="74"/><c r="T42" s="152"/><c r="U42" s="68"/><c r="V42" s="1"/><c r="W42" s="1"/></row><row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6"><c r="B43" s="20"/><c r="C43" s="25"/><c r="D43" s="23"/><c r="E43" s="23"/><c r="F43" s="47"/><c r="I43" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J43" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L43" s="105"/><c r="M43" s="37"/><c r="N43" s="38"/><c r="O43" s="39"/><c r="P43" s="152"/><c r="Q43" s="66"/><c r="R43" s="154"/><c r="S43" s="73"/><c r="T43" s="152"/><c r="U43" s="68"/><c r="V43" s="1"/><c r="W43" s="1"/></row><row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6"><c r="A44" s="104"/><c r="B44" s="20"/><c r="C44" s="32"/><c r="D44" s="170"/><c r="E44" s="170"/><c r="F44" s="47"/><c r="G44" s="8"/><c r="I44" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J44" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K44" s="24"/><c r="L44" s="105"/><c r="M44" s="37"/><c r="N44" s="38"/><c r="O44" s="39"/><c r="P44" s="152"/><c r="Q44" s="66"/><c r="R44" s="152"/><c r="S44" s="67"/><c r="T44" s="152"/><c r="U44" s="68"/></row><row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A45" s="25"/><c r="B45" s="20"/><c r="C45" s="25"/><c r="D45" s="170"/><c r="E45" s="170"/><c r="F45" s="48"/><c r="H45" s="64"/><c r="I45" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J45" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K45" s="24"/><c r="L45" s="105"/><c r="M45" s="37"/><c r="N45" s="38"/><c r="O45" s="39"/><c r="P45" s="152"/><c r="Q45" s="66"/><c r="R45" s="152"/><c r="S45" s="67"/><c r="T45" s="152"/><c r="U45" s="68"/></row><row r="46" spans="1:23" x14ac:dyDescent="0.3"><c r="A46" s="25"/><c r="B46" s="25"/><c r="C46" s="40"/><c r="D46" s="170"/><c r="E46" s="170"/><c r="F46" s="23"/><c r="H46" s="64"/><c r="I46" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J46" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L46" s="105"/><c r="M46" s="37"/><c r="N46" s="38"/><c r="O46" s="39"/><c r="P46" s="152"/><c r="Q46" s="66"/><c r="R46" s="152"/><c r="S46" s="72"/><c r="T46" s="152"/><c r="U46" s="68"/></row><row r="47" spans="1:23" x14ac:dyDescent="0.3"><c r="A47" s="20"/><c r="B47" s="20"/><c r="C47" s="40"/><c r="D47" s="170"/><c r="E47" s="170"/><c r="F47" s="49"/><c r="H47" s="64"/><c r="I47" s="13"/><c r="J47" s="53"><f>SUM(J28:J46)</f><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="67"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="48" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="17"/><c r="G48" s="1"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"/><c r="K48" s="24"/><c r="L48" s="105"/><c r="M48" s="37"/><c r="N48" s="38"/><c r="O48" s="39"/><c r="P48" s="152"/><c r="Q48" s="66"/><c r="R48" s="152"/><c r="S48" s="67"/><c r="T48" s="152"/><c r="U48" s="68"/></row><row r="49" spans="1:23" x14ac:dyDescent="0.3"><c r="A49" s="20"/><c r="B49" s="20"/><c r="C49" s="40"/><c r="D49" s="170"/><c r="E49" s="170"/><c r="F49" s="23"/><c r="G49" s="1"/><c r="H49" s="64"/><c r="I49" s="13"/><c r="J49" s="53"/><c r="L49" s="105"/><c r="M49" s="37"/><c r="N49" s="38"/><c r="O49" s="39"/><c r="P49" s="152"/><c r="Q49" s="66"/><c r="R49" s="152"/><c r="S49" s="67"/><c r="T49" s="154"/><c r="U49" s="68"/></row><row r="50" spans="1:21" x14ac:dyDescent="0.3"><c r="A50" s="20"/><c r="B50" s="20"/><c r="C50" s="40"/><c r="D50" s="170"/><c r="E50" s="170"/><c r="F50" s="23"/><c r="G50" s="1"/><c r="H50" s="46"/><c r="I50" s="13"/><c r="J50" s="53"/><c r="L50" s="105"/><c r="M50" s="37"/><c r="N50" s="38"/><c r="O50" s="39"/><c r="P50" s="152"/><c r="Q50" s="66"/><c r="R50" s="152"/><c r="S50" s="67"/><c r="T50" s="154"/><c r="U50" s="68"/></row><row r="51" spans="1:21" x14ac:dyDescent="0.3"><c r="A51" s="20"/><c r="B51" s="20"/><c r="C51" s="40"/><c r="D51" s="23"/><c r="E51" s="25"/><c r="F51" s="23"/><c r="G51" s="1"/><c r="H51" s="46"/><c r="I51" s="13"/><c r="J51" s="53"/><c r="L51" s="105"/><c r="M51" s="37"/><c r="N51" s="38"/><c r="O51" s="39"/><c r="P51" s="152"/><c r="Q51" s="66"/><c r="R51" s="152"/><c r="S51" s="67"/><c r="T51" s="154"/><c r="U51" s="68"/></row><row r="52" spans="1:21" x14ac:dyDescent="0.3"><c r="A52" s="20"/><c r="B52" s="20"/><c r="C52" s="40"/><c r="D52" s="185"/><c r="E52" s="185"/><c r="F52" s="23"/><c r="G52" s="1"/><c r="H52" s="46"/><c r="I52" s="13"/><c r="J52" s="53"/><c r="L52" s="105"/><c r="M52" s="37"/><c r="N52" s="38"/><c r="O52" s="39"/><c r="P52" s="151"/><c r="Q52" s="66"/><c r="R52" s="152"/><c r="S52" s="67"/><c r="T52" s="154"/><c r="U52" s="68"/></row><row r="53" spans="1:21" x14ac:dyDescent="0.3"><c r="A53" s="20"/><c r="B53" s="51"/><c r="C53" s="40"/><c r="D53" s="178"/><c r="E53" s="178"/><c r="F53" s="23"/><c r="G53" s="1"/><c r="H53" s="46"/><c r="I53" s="50"/><c r="J53" s="53"/><c r="L53" s="105"/><c r="M53" s="37"/><c r="N53" s="38"/><c r="O53" s="39"/><c r="P53" s="151"/><c r="Q53" s="66"/><c r="R53" s="152"/><c r="S53" s="67"/><c r="T53" s="154"/><c r="U53" s="68"/></row><row r="54" spans="1:21" x14ac:dyDescent="0.3"><c r="A54" s="25"/><c r="B54" s="51"/><c r="C54" s="40"/><c r="D54" s="166"/><c r="E54" s="166"/><c r="F54" s="23"/><c r="G54" s="1"/><c r="H54" s="46"/><c r="I54" s="50"/><c r="J54" s="53"/><c r="L54" s="18"/><c r="M54" s="37"/><c r="N54" s="38"/><c r="O54" s="39"/><c r="P54" s="152"/><c r="Q54" s="66"/><c r="R54" s="152"/><c r="S54" s="67"/><c r="T54" s="154"/><c r="U54" s="68"/></row><row r="55" spans="1:21" x14ac:dyDescent="0.3"><c r="A55" s="20"/><c r="B55" s="51"/><c r="C55" s="40"/><c r="D55" s="166"/><c r="E55" s="166"/><c r="F55" s="23"/><c r="G55" s="1"/><c r="H55" s="46"/><c r="I55" s="50"/><c r="J55" s="53"/><c r="L55" s="18"/><c r="M55" s="37"/><c r="N55" s="38"/><c r="O55" s="39"/><c r="P55" s="152"/><c r="Q55" s="66"/><c r="R55" s="152"/><c r="S55" s="67"/><c r="T55" s="154"/><c r="U55" s="68"/></row><row r="56" spans="1:21" x14ac:dyDescent="0.3"><c r="A56" s="20"/><c r="B56" s="51"/><c r="C56" s="40"/><c r="D56" s="22"/><c r="E56" s="22"/><c r="F56" s="23"/><c r="G56" s="1"/><c r="H56" s="46"/><c r="I56" s="50"/><c r="J56" s="53"/><c r="L56" s="18"/><c r="M56" s="37"/><c r="N56" s="38"/><c r="O56" s="39"/><c r="P56" s="152"/><c r="Q56" s="66"/><c r="R56" s="152"/><c r="S56" s="67"/><c r="T56" s="154"/><c r="U56" s="68"/></row><row r="57" spans="1:21" x14ac:dyDescent="0.3"><c r="A57" s="20"/><c r="B57"/><c r="C57" s="40"/><c r="D57" s="22"/><c r="E57" s="22"/><c r="F57" s="23"/><c r="G57" s="1"/><c r="H57" s="46"/><c r="I57" s="50"/><c r="J57" s="53"/><c r="L57" s="18"/><c r="M57" s="37"/><c r="N57" s="38"/><c r="O57" s="39"/><c r="P57" s="152"/><c r="Q57" s="66"/><c r="R57" s="152"/><c r="S57" s="67"/><c r="T57" s="154"/><c r="U57" s="68"/></row><row r="58" spans="1:21" x14ac:dyDescent="0.3"><c r="A58" s="20"/><c r="B58"/><c r="C58" s="40"/><c r="D58" s="22"/><c r="E58" s="22"/><c r="F58" s="23"/><c r="G58" s="1"/><c r="H58" s="46"/><c r="I58" s="50"/><c r="J58" s="53"/><c r="L58" s="18"/><c r="M58" s="37"/><c r="N58" s="38"/><c r="O58" s="39"/><c r="P58" s="152"/><c r="Q58" s="66"/><c r="R58" s="152"/><c r="S58" s="67"/><c r="T58" s="154"/><c r="U58" s="68"/></row><row r="59" spans="1:21" x14ac:dyDescent="0.3"><c r="A59" s="20"/><c r="B59"/><c r="C59" s="40"/><c r="D59" s="22"/><c r="E59" s="22"/><c r="F59" s="23"/><c r="G59" s="1"/><c r="H59" s="46"/><c r="I59" s="50"/><c r="J59" s="53"/><c r="L59" s="18"/><c r="M59" s="37"/><c r="N59" s="38"/><c r="O59" s="39"/><c r="P59" s="152"/><c r="Q59" s="66"/><c r="R59" s="152"/><c r="S59" s="67"/><c r="T59" s="154"/><c r="U59" s="68"/></row><row r="60" spans="1:21" x14ac:dyDescent="0.3"><c r="A60" s="20"/><c r="B60"/><c r="C60" s="40"/><c r="D60" s="22"/><c r="E60" s="22"/><c r="F60" s="23"/><c r="G60" s="1"/><c r="H60" s="46"/><c r="I60" s="50"/><c r="J60" s="53"/><c r="L60" s="18"/><c r="M60" s="37"/><c r="N60" s="38"/><c r="O60" s="39"/><c r="P60" s="152"/><c r="Q60" s="66"/><c r="R60" s="152"/><c r="S60" s="67"/><c r="T60" s="154"/><c r="U60" s="68"/></row><row r="61" spans="1:21" x14ac:dyDescent="0.3"><c r="A61" s="25"/><c r="B61"/><c r="C61" s="40"/><c r="D61" s="166"/><c r="E61" s="166"/><c r="F61" s="23"/><c r="G61" s="1"/><c r="H61" s="46"/><c r="I61" s="50"/><c r="J61" s="53"/><c r="L61" s="18"/><c r="M61" s="37"/><c r="N61" s="38"/><c r="O61" s="39"/><c r="P61" s="152"/><c r="Q61" s="66"/><c r="R61" s="152"/><c r="S61" s="67"/><c r="T61" s="154"/><c r="U61" s="68"/></row><row r="62" spans="1:21" x14ac:dyDescent="0.3"><c r="A62" s="25"/><c r="B62"/><c r="C62" s="40"/><c r="D62" s="22"/><c r="E62" s="22"/><c r="F62" s="23"/><c r="G62" s="1"/><c r="H62" s="46"/><c r="I62" s="50"/><c r="J62" s="53"/><c r="L62" s="18"/><c r="M62" s="37"/><c r="N62" s="38"/><c r="O62" s="39"/><c r="P62" s="152"/><c r="Q62" s="135"/><c r="R62" s="155"/><c r="S62" s="88"/><c r="T62" s="154"/><c r="U62" s="68"/></row><row r="63" spans="1:21" x14ac:dyDescent="0.3"><c r="A63" s="25"/><c r="B63"/><c r="C63" s="40"/><c r="D63" s="22"/><c r="E63" s="22"/><c r="F63" s="23"/><c r="G63" s="1"/><c r="H63" s="46"/><c r="I63" s="50"/><c r="J63" s="53"/><c r="L63" s="18"/><c r="M63" s="37"/><c r="N63" s="38"/><c r="O63" s="39"/><c r="P63" s="152"/><c r="Q63" s="135"/><c r="R63" s="155"/><c r="S63" s="88"/><c r="T63" s="154"/><c r="U63" s="68"/></row><row r="64" spans="1:21" x14ac:dyDescent="0.3"><c r="A64" s="25"/><c r="B64"/><c r="C64" s="40"/><c r="D64" s="22"/><c r="E64" s="22"/><c r="F64" s="23"/><c r="G64" s="1"/><c r="H64" s="46"/><c r="I64" s="50"/><c r="J64" s="53"/><c r="L64" s="18"/><c r="M64" s="37"/><c r="N64" s="38"/><c r="O64" s="39"/><c r="P64" s="152"/><c r="Q64" s="135"/><c r="R64" s="155"/><c r="S64" s="88"/><c r="T64" s="154"/><c r="U64" s="68"/></row><row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A65" s="25"/><c r="B65"/><c r="C65" s="40"/><c r="D65" s="166"/><c r="E65" s="166"/><c r="F65" s="23"/><c r="G65" s="1"/><c r="H65" s="46"/><c r="I65" s="50"/><c r="J65" s="53"/><c r="L65" s="18"/><c r="M65" s="37"/><c r="N65" s="38"/><c r="O65" s="39"/><c r="P65" s="152"/><c r="Q65" s="84"/><c r="R65" s="155"/><c r="S65" s="88"/><c r="T65" s="154"/><c r="U65" s="71"/></row><row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A66" s="25"/><c r="B66"/><c r="C66" s="40"/><c r="D66" s="166"/><c r="E66" s="166"/><c r="F66" s="20"/><c r="G66" s="1"/><c r="H66" s="46"/><c r="I66" s="50"/><c r="J66" s="53"/><c r="L66"/><c r="M66" s="171" t="s"><v>34</v></c><c r="N66" s="172"/><c r="O66" s="42"/><c r="P66" s="52" t="s"><v>11</v></c><c r="Q66" s="42"/><c r="R66" s="52" t="s"><v>11</v></c><c r="S66" s="42"/><c r="T66" s="52" t="s"><v>11</v></c><c r="U66" s="42"/></row><row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A67" s="25"/><c r="B67"/><c r="C67" s="90"/><c r="D67" s="166"/><c r="E67" s="166"/><c r="F67" s="23"/><c r="G67" s="1"/><c r="H67" s="46"/><c r="I67" s="50"/><c r="J67"/><c r="L67"/><c r="M67" s="54"/><c r="N67" s="55"/><c r="O67" s="70"/><c r="P67" s="23"/><c r="Q67" s="69"/><c r="R67" s="70"/><c r="S67" s="70"/><c r="T67" s="6"/></row><row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="A68" s="25"/><c r="B68"/><c r="C68" s="25"/><c r="D68" s="22"/><c r="E68" s="22"/><c r="F68" s="23"/><c r="G68" s="1"/><c r="H68" s="46"/><c r="I68" s="50"/><c r="J68"/><c r="L68"/><c r="M68" s="167" t="s"><v>47</v></c><c r="N68" s="168"/><c r="O68" s="169"/><c r="P68" s="181"/><c r="Q68" s="182"/><c r="R68" s="167" t="s"><v>37</v></c><c r="S68" s="168"/><c r="T68" s="183" t="str"><f>Q25</f></c><c r="U68" s="184"/></row><row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A69" s="25"/><c r="B69"/><c r="C69" s="25"/><c r="D69" s="166"/><c r="E69" s="166"/><c r="F69" s="63"/><c r="G69" s="1"/><c r="H69" s="46"/><c r="I69" s="50"/><c r="J69"/><c r="L69"/><c r="M69" s="56"/><c r="N69" s="83"/><c r="O69" s="83"/><c r="P69" s="57"/><c r="Q69" s="58"/><c r="R69" s="58"/><c r="S69" s="58"/><c r="T69" s="56"/><c r="U69" s="56"/></row><row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A70" s="25"/><c r="B70" s="90"/><c r="C70" s="25"/><c r="D70" s="166"/><c r="E70" s="166"/><c r="F70" s="63"/><c r="G70" s="1"/><c r="H70" s="46"/><c r="I70" s="50"/><c r="J70"/><c r="L70"/><c r="M70" s="171" t="s"><v>35</v></c><c r="N70" s="179"/><c r="O70" s="179"/><c r="P70" s="179"/><c r="Q70" s="179"/><c r="R70" s="179"/><c r="S70" s="179"/><c r="T70" s="179"/><c r="U70" s="180"/><c r="V70" s="51"/></row><row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A71" s="25"/><c r="B71" s="20"/><c r="C71" s="25"/><c r="D71" s="166"/><c r="E71" s="166"/><c r="F71" s="63"/><c r="G71" s="1"/><c r="H71" s="46"/><c r="I71" s="50"/><c r="J71"/><c r="L71" s="49" t="s"><v>59</v></c><c r="M71" s="130" t="s"><v>55</v></c><c r="N71" s="131"/><c r="O71" s="131"/><c r="P71" s="131" t="s"><v>56</v></c><c r="Q71" s="131"/><c r="R71" s="131"/><c r="S71" s="131"/><c r="T71" s="131" t="s"><v>57</v></c><c r="U71" s="132" t="s"><v>60</v></c><c r="V71" s="144" t="s"><v>58</v></c><c r="W71" s="144" t="s"><v>50</v></c></row><row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A72" s="25"/><c r="B72" s="115"/><c r="C72" s="25"/><c r="D72" s="166"/><c r="E72" s="166"/><c r="F72" s="63"/><c r="G72" s="1"/><c r="H72" s="46"/><c r="I72" s="50"/><c r="J72" s="23"/><c r="L72" s="0"/><c r="M72" s="59"/><c r="N72" s="60"/><c r="O72" s="143" t="s"><v>43</v></c><c r="P72" s="62"/><c r="Q72" s="61"/><c r="R72" s="177" t="inlineStr"><is><t xml:space="preserve">CREDITO</t></is></c><c r="S72" s="177"/><c r="T72" s="133"/><c r="U72" s="134"/><c r="V72" s="51"/></row><row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="B73" s="51"/><c r="C73" s="89"/><c r="D73" s="166"/><c r="E73" s="166"/><c r="F73" s="63"/><c r="I73" s="115"/><c r="L73"/><c r="M73" s="85"/><c r="N73" s="86"/><c r="O73" s="18"/><c r="P73" s="87"/><c r="Q73" s="56"/><c r="R73" s="175"/><c r="S73" s="175"/><c r="T73" s="65"/><c r="U73" s="95"/><c r="V73" s="51"/></row><row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A74" s="49"/><c r="B74" s="89"/><c r="C74" s="89"/><c r="D74" s="23"/><c r="E74" s="25"/><c r="F74" s="63"/><c r="I74" s="115"/><c r="L74" s="45" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="M74" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N74" s="86"/><c r="O74" s="18" t="s"><v>43</v></c><c r="P74" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q74" s="56"/><c r="R74" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S74" s="175"/><c r="T74" s="65"><v>150000</v></c><c r="U74" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V74" s="51"/></row><row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L75" s="45" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="M75" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N75" s="86"/><c r="O75" s="123"/><c r="P75" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q75" s="56"/><c r="R75" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S75" s="175"/><c r="T75" s="65"><v>150000</v></c><c r="U75" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V75" s="51"/></row><row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L76" s="45"/><c r="M76" s="137" t="s"><v>61</v></c><c r="N76" s="138"/><c r="O76" s="139"/><c r="P76" s="140"/><c r="Q76" s="141"/><c r="R76" s="176"/><c r="S76" s="176"/><c r="T76" s="173"/><c r="U76" s="174"/><c r="V76" s="51"/></row><row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L77" s="45"/><c r="M77" s="137" t="s"><v>62</v></c><c r="N77" s="138"/><c r="O77" s="139"/><c r="P77" s="140"/><c r="Q77" s="141"/><c r="R77" s="142"/><c r="S77" s="142"/><c r="T77" s="173"/><c r="U77" s="174"/><c r="V77" s="51"/></row><row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L78" s="45"/><c r="M78" s="94"/><c r="N78" s="64"/><c r="O78" s="123"/><c r="P78" s="87"/><c r="Q78" s="56"/><c r="R78" s="56"/><c r="S78" s="56"/><c r="T78" s="65"/><c r="U78" s="95"/><c r="V78" s="51"/></row><row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L79" s="45"/><c r="M79" s="101" t="s"><v>11</v></c><c r="N79" s="102"><f>SUM(N77:N78)</f><v>0</v></c><c r="O79" s="96"/><c r="P79" s="98"/><c r="Q79" s="97"/><c r="R79" s="97"/><c r="S79" s="97"/><c r="T79" s="99"/><c r="U79" s="100"/><c r="V79" s="51"/></row><row r="80" spans="1:23" x14ac:dyDescent="0.3"><c r="M80"/><c r="O80" s="5"/><c r="Q80"/><c r="S80"/><c r="T80" s="6"/><c r="V80" s="51"/></row><row r="81" spans="1:23" x14ac:dyDescent="0.3"><c r="O81"/><c r="V81" s="51"/></row><row r="82" spans="13:22" x14ac:dyDescent="0.3"><c r="M82" s="23"/><c r="N82" s="23"/><c r="O82" s="23"/><c r="P82" s="23"/><c r="Q82" s="23"/><c r="V82" s="51"/></row><row r="83" spans="13:22" x14ac:dyDescent="0.3"><c r="V83" s="51"/></row><row r="84" spans="13:22" x14ac:dyDescent="0.3"><c r="V84" s="51"/></row><row r="85" spans="13:22" x14ac:dyDescent="0.3"><c r="V85" s="51"/></row><row r="86" spans="13:22" x14ac:dyDescent="0.3"><c r="V86" s="51"/></row><row r="87" spans="13:22" x14ac:dyDescent="0.3"><c r="V87" s="51"/></row><row r="88" spans="13:22" x14ac:dyDescent="0.3"><c r="V88" s="51"/></row><row r="89" spans="13:22" x14ac:dyDescent="0.3"><c r="V89" s="51"/></row><row r="90" spans="13:22" x14ac:dyDescent="0.3"><c r="V90" s="51"/></row><row r="91" spans="13:22" x14ac:dyDescent="0.3"><c r="V91" s="51"/></row><row r="92" spans="13:22" x14ac:dyDescent="0.3"><c r="V92" s="51"/></row><row r="93" spans="13:22" x14ac:dyDescent="0.3"><c r="V93" s="51"/></row><row r="94" spans="13:22" x14ac:dyDescent="0.3"><c r="V94" s="51"/></row><row r="95" spans="13:22" x14ac:dyDescent="0.3"><c r="V95" s="51"/></row><row r="96" spans="13:22" x14ac:dyDescent="0.3"><c r="V96" s="51"/></row><row r="97" spans="13:22" x14ac:dyDescent="0.3"><c r="V97" s="51"/></row><row r="98" spans="22:22" x14ac:dyDescent="0.3"><c r="V98" s="51"/></row><row r="99" spans="22:22" x14ac:dyDescent="0.3"><c r="V99" s="51"/></row><row r="100" spans="22:22" x14ac:dyDescent="0.3"><c r="V100" s="51"/></row><row r="101" spans="22:22" x14ac:dyDescent="0.3"><c r="V101" s="51"/></row><row r="102" spans="22:22" x14ac:dyDescent="0.3"><c r="V102" s="51"/></row><row r="103" spans="22:22" x14ac:dyDescent="0.3"><c r="V103" s="51"/></row><row r="104" spans="22:22" x14ac:dyDescent="0.3"><c r="V104" s="51"/></row><row r="105" spans="22:22" x14ac:dyDescent="0.3"><c r="V105" s="51"/></row><row r="106" spans="22:22" x14ac:dyDescent="0.3"><c r="V106" s="51"/></row><row r="107" spans="22:22" x14ac:dyDescent="0.3"><c r="V107" s="51"/></row><row r="108" spans="22:22" x14ac:dyDescent="0.3"><c r="V108" s="51"/></row><row r="109" spans="22:22" x14ac:dyDescent="0.3"><c r="V109" s="51"/></row><row r="110" spans="22:22" x14ac:dyDescent="0.3"><c r="V110" s="51"/></row><row r="111" spans="22:22" x14ac:dyDescent="0.3"><c r="V111" s="51"/></row><row r="112" spans="22:22" x14ac:dyDescent="0.3"><c r="V112" s="51"/></row><row r="113" spans="22:22" x14ac:dyDescent="0.3"><c r="V113" s="51"/></row></sheetData><mergeCells count="70"><mergeCell ref="M25:N25"/><mergeCell ref="O30:P30"/><mergeCell ref="Q30:S30"/><mergeCell ref="T30:U30"/><mergeCell ref="Q32:S32"/><mergeCell ref="M31:N31"/><mergeCell ref="O31:P31"/><mergeCell ref="Q31:S31"/><mergeCell ref="M30:N30"/><mergeCell ref="M32:N32"/><mergeCell ref="O32:P32"/><mergeCell ref="M22:U22"/><mergeCell ref="Q26:S26"/><mergeCell ref="O29:P29"/><mergeCell ref="Q29:S29"/><mergeCell ref="T29:U29"/><mergeCell ref="T28:U28"/><mergeCell ref="O28:P28"/><mergeCell ref="Q28:S28"/><mergeCell ref="M28:N28"/><mergeCell ref="M29:N29"/><mergeCell ref="O27:P27"/><mergeCell ref="Q27:S27"/><mergeCell ref="T27:U27"/><mergeCell ref="N23:S23"/><mergeCell ref="N24:S24"/><mergeCell ref="T25:U25"/><mergeCell ref="D44:E44"/><mergeCell ref="R35:S35"/><mergeCell ref="T35:U35"/><mergeCell ref="O33:P33"/><mergeCell ref="Q33:S33"/><mergeCell ref="M34:N34"/><mergeCell ref="O34:P34"/><mergeCell ref="Q34:S34"/><mergeCell ref="P35:Q35"/><mergeCell ref="M35:O35"/><mergeCell ref="M39:N39"/><mergeCell ref="D72:E72"/><mergeCell ref="D73:E73"/><mergeCell ref="D53:E53"/><mergeCell ref="M70:U70"/><mergeCell ref="R68:S68"/><mergeCell ref="D69:E69"/><mergeCell ref="P68:Q68"/><mergeCell ref="T68:U68"/><mergeCell ref="D61:E61"/><mergeCell ref="D67:E67"/><mergeCell ref="D54:E54"/><mergeCell ref="D66:E66"/><mergeCell ref="D55:E55"/><mergeCell ref="D65:E65"/><mergeCell ref="T77:U77"/><mergeCell ref="R75:S75"/><mergeCell ref="R76:S76"/><mergeCell ref="R72:S72"/><mergeCell ref="R74:S74"/><mergeCell ref="R73:S73"/><mergeCell ref="T76:U76"/><mergeCell ref="D71:E71"/><mergeCell ref="D70:E70"/><mergeCell ref="M68:O68"/><mergeCell ref="D45:E45"/><mergeCell ref="D47:E47"/><mergeCell ref="M66:N66"/><mergeCell ref="D49:E49"/><mergeCell ref="D50:E50"/><mergeCell ref="D48:E48"/><mergeCell ref="D46:E46"/><mergeCell ref="D52:E52"/></mergeCells><pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/><pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/><drawing r:id="rId2"/></worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}"><dimension ref="A1:W113"/><sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/><cols><col min="1" max="1" width="17.33203125" customWidth="1"/><col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/><col min="3" max="3" width="12.6640625" customWidth="1"/><col min="4" max="4" width="12.6640625" style="3" customWidth="1"/><col min="5" max="5" width="12.6640625" customWidth="1"/><col min="6" max="6" width="12.6640625" style="3" customWidth="1"/><col min="7" max="9" width="12.6640625" customWidth="1"/><col min="10" max="10" width="12.6640625" style="3" customWidth="1"/><col min="11" max="11" width="12.6640625" customWidth="1"/><col min="12" max="12" width="12.6640625" style="3" customWidth="1"/><col min="13" max="13" width="11.5546875" style="3" customWidth="1"/><col min="14" max="14" width="11" bestFit="1" customWidth="1"/><col min="15" max="15" width="11.6640625" style="4" customWidth="1"/><col min="16" max="19" width="11.6640625" style="3" customWidth="1"/><col min="20" max="20" width="13.88671875" customWidth="1"/><col min="21" max="21" width="14" customWidth="1"/><col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/><col min="23" max="23" width="16" customWidth="1"/></cols><sheetData><row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A1" s="7" t="s"><v>50</v></c><c r="B1" s="112" t="inlineStr"><is><t xml:space="preserve">JUAN PEREZ</t></is></c><c r="C1" s="120" t="inlineStr"><is><t xml:space="preserve">MARIA LOPEZ</t></is></c><c r="D1" s="120"/><c r="E1" s="112"/><c r="F1" s="120"/><c r="G1" s="120"/><c r="H1" s="112"/><c r="I1" s="112"/><c r="J1" s="120"/><c r="K1" s="120"/><c r="L1" s="112"/><c r="M1" s="112"/><c r="N1" s="112"/><c r="O1" s="112"/><c r="P1" s="112"/><c r="Q1" s="112"/><c r="R1" s="121"/><c r="S1" s="120"/><c r="T1" s="120"/><c r="U1" s="7"/><c r="V1" s="7"/><c r="W1" s="114"/></row><row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A2" s="7" t="s"><v>51</v></c><c r="B2" s="112"/><c r="C2" s="120"/><c r="D2" s="120"/><c r="E2" s="112"/><c r="F2" s="120"/><c r="G2" s="128"/><c r="H2" s="112"/><c r="I2" s="112"/><c r="J2" s="120"/><c r="K2" s="120"/><c r="L2" s="112"/><c r="M2" s="112"/><c r="N2" s="112"/><c r="O2" s="112"/><c r="P2" s="112"/><c r="Q2" s="112"/><c r="R2" s="121"/><c r="S2" s="120"/><c r="T2" s="120"/><c r="U2" s="7"/><c r="V2" s="7"/><c r="W2" s="114"/></row><row r="3" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A3" s="122" t="s"><v>35</v></c><c r="B3" s="120"/><c r="C3" s="120"/><c r="D3" s="120"/><c r="E3" s="120"/><c r="F3" s="120"/><c r="G3" s="120"/><c r="H3" s="120"/><c r="I3" s="120"/><c r="J3" s="120"/><c r="K3" s="120"/><c r="L3" s="120"/><c r="M3" s="120"/><c r="N3" s="120"/><c r="O3" s="120"/><c r="P3" s="120"/><c r="Q3" s="120"/><c r="R3" s="120"/><c r="S3" s="120"/><c r="T3" s="120"/><c r="U3" s="110"/><c r="V3" s="163"/><c r="W3" s="116"/></row><row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A4" s="122" t="s"><v>52</v></c><c r="B4" s="120"/><c r="C4" s="120"/><c r="D4" s="120"/><c r="E4" s="120"/><c r="F4" s="120"/><c r="G4" s="120"/><c r="H4" s="120"/><c r="I4" s="120"/><c r="J4" s="120"/><c r="K4" s="120"/><c r="L4" s="120"/><c r="M4" s="120"/><c r="N4" s="120"/><c r="O4" s="120"/><c r="P4" s="120"/><c r="Q4" s="120"/><c r="R4" s="120"/><c r="S4" s="120"/><c r="T4" s="120"/><c r="U4" s="110"/><c r="V4" s="163"/><c r="W4" s="116"/></row><row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A5" s="122" t="s"><v>0</v></c><c r="B5" s="129" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="C5" s="129" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="D5" s="129"/><c r="E5" s="129"/><c r="F5" s="129"/><c r="G5" s="129"/><c r="H5" s="129"/><c r="I5" s="129"/><c r="J5" s="129"/><c r="K5" s="129"/><c r="L5" s="129"/><c r="M5" s="129"/><c r="N5" s="129"/><c r="O5" s="129"/><c r="P5" s="129"/><c r="Q5" s="129"/><c r="R5" s="120"/><c r="S5" s="120"/><c r="T5" s="120"/><c r="U5" s="111"/><c r="V5" s="111"/><c r="W5" s="111"/></row><row r="6" spans="1:23" s="45" customFormat="1" x14ac:dyDescent="0.3"><c r="A6" s="122" t="s"><v>1</v></c><c r="B6" s="120"><v>10</v></c><c r="C6" s="120"><v>10</v></c><c r="D6" s="120"/><c r="E6" s="120"/><c r="F6" s="120"/><c r="G6" s="120"/><c r="H6" s="120"/><c r="I6" s="120"/><c r="J6" s="120"/><c r="K6" s="120"/><c r="L6" s="120"/><c r="M6" s="111"/><c r="N6" s="111"/><c r="O6" s="111"/><c r="P6" s="111"/><c r="Q6" s="111"/><c r="R6" s="120"/><c r="S6" s="120"/><c r="T6" s="120"/><c r="U6" s="111"/><c r="V6" s="111"/><c r="W6" s="111"/></row><row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3"><c r="A7" s="122" t="s"><v>2</v></c><c r="B7" s="164"><v>1000000</v></c><c r="C7" s="164"><v>1000000</v></c><c r="D7" s="164"/><c r="E7" s="164"/><c r="F7" s="164"/><c r="G7" s="164"/><c r="H7" s="164"/><c r="I7" s="164"/><c r="J7" s="164"/><c r="K7" s="164"/><c r="L7" s="164"/><c r="M7" s="164"/><c r="N7" s="164"/><c r="O7" s="164"/><c r="P7" s="164"/><c r="Q7" s="164"/><c r="R7" s="156"/><c r="S7" s="156"/><c r="T7" s="156"/><c r="U7" s="157"/><c r="V7" s="157"/><c r="W7" s="157"/></row><row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A8" s="112"/><c r="B8" s="157"/><c r="C8" s="111"/><c r="D8" s="157"/><c r="E8" s="111"/><c r="F8" s="110"/><c r="G8" s="111"/><c r="H8" s="157"/><c r="I8" s="111"/><c r="J8" s="157"/><c r="K8" s="111"/><c r="L8" s="110"/><c r="M8" s="111"/><c r="N8" s="110"/><c r="O8" s="111"/><c r="P8" s="158"/><c r="Q8" s="111"/><c r="R8" s="158"/><c r="S8" s="111"/><c r="T8" s="158"/><c r="U8" s="111"/><c r="V8" s="110"/><c r="W8" s="111"/></row><row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A9" s="113" t="s"><v>3</v></c><c r="B9" s="165"><v>450000</v></c><c r="C9" s="165"><v>450000</v></c><c r="D9" s="165"/><c r="E9" s="157"/><c r="F9" s="110"/><c r="G9" s="157"/><c r="H9" s="110"/><c r="I9" s="157"/><c r="J9" s="110"/><c r="K9" s="157"/><c r="L9" s="110"/><c r="M9" s="157"/><c r="N9" s="110"/><c r="O9" s="157"/><c r="P9" s="158"/><c r="Q9" s="157"/><c r="R9" s="158"/><c r="S9" s="159"/><c r="T9" s="159"/><c r="U9" s="157"/><c r="V9" s="110"/><c r="W9" s="157"/></row><row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A10" s="113" t="s"><v>54</v></c><c r="B10" s="165"><v>50000</v></c><c r="C10" s="165"><v>50000</v></c><c r="D10" s="165"/><c r="E10" s="157"/><c r="F10" s="110"/><c r="G10" s="157"/><c r="H10" s="110"/><c r="I10" s="157"/><c r="J10" s="110"/><c r="K10" s="157"/><c r="L10" s="110"/><c r="M10" s="157"/><c r="N10" s="110"/><c r="O10" s="157"/><c r="P10" s="158"/><c r="Q10" s="157"/><c r="R10" s="158"/><c r="S10" s="159"/><c r="T10" s="159"/><c r="U10" s="157"/><c r="V10" s="110"/><c r="W10" s="157"/></row><row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A11" s="113" t="s"><v>4</v></c><c r="B11" s="165"><v>300000</v></c><c r="C11" s="165"><v>300000</v></c><c r="D11" s="165"/><c r="E11" s="157"/><c r="F11" s="110"/><c r="G11" s="157"/><c r="H11" s="110"/><c r="I11" s="157"/><c r="J11" s="110"/><c r="K11" s="157"/><c r="L11" s="110"/><c r="M11" s="157"/><c r="N11" s="110"/><c r="O11" s="157"/><c r="P11" s="158"/><c r="Q11" s="157"/><c r="R11" s="158"/><c r="S11" s="159"/><c r="T11" s="159"/><c r="U11" s="157"/><c r="V11" s="110"/><c r="W11" s="157"/></row><row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A12" s="113" t="s"><v>5</v></c><c r="B12" s="165"/><c r="C12" s="165"/><c r="D12" s="165"/><c r="E12" s="157"/><c r="F12" s="110"/><c r="G12" s="157"/><c r="H12" s="110"/><c r="I12" s="157"/><c r="J12" s="110"/><c r="K12" s="157"/><c r="L12" s="110"/><c r="M12" s="157"/><c r="N12" s="110"/><c r="O12" s="157"/><c r="P12" s="158"/><c r="Q12" s="157"/><c r="R12" s="158"/><c r="S12" s="159"/><c r="T12" s="159"/><c r="U12" s="157"/><c r="V12" s="110"/><c r="W12" s="157"/></row><row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A13" s="113" t="s"><v>6</v></c><c r="B13" s="165"/><c r="C13" s="165"/><c r="D13" s="165"/><c r="E13" s="157"/><c r="F13" s="110"/><c r="G13" s="157"/><c r="H13" s="110"/><c r="I13" s="157"/><c r="J13" s="110"/><c r="K13" s="157"/><c r="L13" s="110"/><c r="M13" s="157"/><c r="N13" s="110"/><c r="O13" s="157"/><c r="P13" s="158"/><c r="Q13" s="157"/><c r="R13" s="158"/><c r="S13" s="159"/><c r="T13" s="159"/><c r="U13" s="157"/><c r="V13" s="110"/><c r="W13" s="157"/></row><row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A14" s="113" t="s"><v>7</v></c><c r="B14" s="165"/><c r="C14" s="165"/><c r="D14" s="165"/><c r="E14" s="157"/><c r="F14" s="110"/><c r="G14" s="157"/><c r="H14" s="110"/><c r="I14" s="157"/><c r="J14" s="110"/><c r="K14" s="157"/><c r="L14" s="110"/><c r="M14" s="157"/><c r="N14" s="110"/><c r="O14" s="157"/><c r="P14" s="158"/><c r="Q14" s="157"/><c r="R14" s="158"/><c r="S14" s="159"/><c r="T14" s="159"/><c r="U14" s="157"/><c r="V14" s="110"/><c r="W14" s="157"/></row><row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A15" s="113" t="s"><v>8</v></c><c r="B15" s="165"/><c r="C15" s="165"/><c r="D15" s="165"/><c r="E15" s="157"/><c r="F15" s="110"/><c r="G15" s="157"/><c r="H15" s="110"/><c r="I15" s="157"/><c r="J15" s="110"/><c r="K15" s="157"/><c r="L15" s="110"/><c r="M15" s="157"/><c r="N15" s="110"/><c r="O15" s="157"/><c r="P15" s="158"/><c r="Q15" s="157"/><c r="R15" s="158"/><c r="S15" s="159"/><c r="T15" s="159"/><c r="U15" s="157"/><c r="V15" s="110"/><c r="W15" s="157"/></row><row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A16" s="113" t="s"><v>9</v></c><c r="B16" s="165"/><c r="C16" s="165"/><c r="D16" s="165"/><c r="E16" s="157"/><c r="F16" s="110"/><c r="G16" s="157"/><c r="H16" s="110"/><c r="I16" s="160"/><c r="J16" s="110"/><c r="K16" s="160"/><c r="L16" s="110"/><c r="M16" s="157"/><c r="N16" s="110"/><c r="O16" s="157"/><c r="P16" s="158"/><c r="Q16" s="157"/><c r="R16" s="158"/><c r="S16" s="159"/><c r="T16" s="159"/><c r="U16" s="157"/><c r="V16" s="110"/><c r="W16" s="157"/></row><row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A17" s="113" t="s"><v>10</v></c><c r="B17" s="165"/><c r="C17" s="165"/><c r="D17" s="165"/><c r="E17" s="157"/><c r="F17" s="110"/><c r="G17" s="157"/><c r="H17" s="110"/><c r="I17" s="160"/><c r="J17" s="110"/><c r="K17" s="157"/><c r="L17" s="110"/><c r="M17" s="157"/><c r="N17" s="110"/><c r="O17" s="157"/><c r="P17" s="158"/><c r="Q17" s="157"/><c r="R17" s="158"/><c r="S17" s="159"/><c r="T17" s="159"/><c r="U17" s="157"/><c r="V17" s="110"/><c r="W17" s="157"/></row><row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A18" s="113" t="s"><v>11</v></c><c r="B18" s="110"><f>SUM(B9:B17)</f><v>0</v></c><c r="C18" s="110"><f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f><v>0</v></c><c r="D18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="E18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="F18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="G18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="H18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="I18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="J18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="K18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="L18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="M18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="N18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="O18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="P18" s="110"><f t="shared" ref="P18" si="1">SUM(P9:P17)</f><v>0</v></c><c r="Q18" s="110"><f>SUM(Q9:Q17)</f><v>0</v></c><c r="R18" s="110"><f>SUM(R9:R17)</f><v>0</v></c><c r="S18" s="116"><f>SUM(S9:S17)</f><v>0</v></c><c r="T18" s="116"><f>SUM(T9:T17)</f><v>0</v></c><c r="U18" s="110"><f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f><v>0</v></c><c r="V18" s="110"><f t="shared" si="2"/><v>0</v></c><c r="W18" s="110"><f t="shared" si="2"/><v>0</v></c></row><row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A19" s="113"/><c r="B19" s="110"/><c r="C19" s="110"/><c r="D19" s="110"/><c r="E19" s="110"/><c r="F19" s="157"/><c r="G19" s="110"/><c r="H19" s="110"/><c r="I19" s="110"/><c r="J19" s="110"/><c r="K19" s="110"/><c r="L19" s="110"/><c r="M19" s="110"/><c r="N19" s="110"/><c r="O19" s="110"/><c r="P19" s="110"/><c r="Q19" s="110"/><c r="R19" s="110"/><c r="S19" s="116"/><c r="T19" s="116"/><c r="U19" s="110"/><c r="V19" s="110"/><c r="W19" s="110"/></row><row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3"><c r="A20" s="113" t="s"><v>12</v></c><c r="B20" s="110" t="e"><f t="shared" ref="B20:O20" si="3">B18-B7</f><v>#VALUE!</v></c><c r="C20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="D20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="E20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="F20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="G20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="H20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="I20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="J20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="K20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="L20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="M20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="N20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="O20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="P20" s="110"><f t="shared" ref="P20" si="4">P18-P7</f><v>0</v></c><c r="Q20" s="110"><f>Q18-Q7</f><v>0</v></c><c r="R20" s="110"><f>R18-R7</f><v>0</v></c><c r="S20" s="110"><f>S18-S7</f><v>0</v></c><c r="T20" s="110"><f>T18-T7</f><v>0</v></c><c r="U20" s="110"><f t="shared" ref="U20:W20" si="5">U18-U7</f><v>0</v></c><c r="V20" s="110"><f t="shared" si="5"/><v>0</v></c><c r="W20" s="110"><f t="shared" si="5"/><v>0</v></c></row><row r="21" spans="1:23" x14ac:dyDescent="0.3"><c r="A21" s="1"/><c r="B21" s="9"/><c r="C21" s="10"/><c r="D21" s="9"/><c r="E21" s="10"/><c r="F21" s="11"/><c r="G21" s="10"/><c r="H21" s="11"/><c r="I21" s="9"/><c r="J21" s="9"/><c r="K21" s="10"/><c r="L21" s="12"/><c r="M21" s="12"/><c r="N21" s="10"/><c r="O21" s="9"/><c r="P21" s="9"/><c r="Q21" s="10"/><c r="R21" s="12"/><c r="S21" s="12"/><c r="T21" s="9"/><c r="U21" s="9"/><c r="V21" s="9"/><c r="W21" s="9"/></row><row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35"><c r="D22" s="2"/><c r="M22" s="198" t="s"><v>48</v></c><c r="N22" s="198"/><c r="O22" s="198"/><c r="P22" s="198"/><c r="Q22" s="198"/><c r="R22" s="198"/><c r="S22" s="198"/><c r="T22" s="198"/><c r="U22" s="198"/></row><row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="D23" s="6"/><c r="J23"/><c r="L23"/><c r="M23" s="14" t="s"><v>13</v></c><c r="N23" s="207" t="inlineStr"><is><t xml:space="preserve">24-06-2026</t></is></c><c r="O23" s="208"/><c r="P23" s="208"/><c r="Q23" s="208"/><c r="R23" s="208"/><c r="S23" s="209"/><c r="T23" s="119" t="s"><v>38</v></c><c r="U23" s="106"><v>20</v></c><c r="W23" s="91" t="s"><v>44</v></c></row><row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="B24" s="2"/><c r="C24" s="18"/><c r="J24"/><c r="K24" s="15"/><c r="L24"/><c r="M24" s="16"/><c r="N24" s="210" t="s"><v>49</v></c><c r="O24" s="211"/><c r="P24" s="211"/><c r="Q24" s="211"/><c r="R24" s="211"/><c r="S24" s="212"/><c r="T24" s="108" t="s"><v>11</v></c><c r="U24" s="107"><v>2000000</v></c><c r="W24" s="118"><v>20</v></c></row><row r="25" spans="1:23" x14ac:dyDescent="0.3"><c r="B25" s="2"/><c r="C25" s="103"/><c r="D25" s="3" t="s"><v>15</v></c><c r="E25" s="4"/><c r="J25"/><c r="L25"/><c r="M25" s="215" t="s"><v>16</v></c><c r="N25" s="216"/><c r="O25" s="148"/><c r="P25" s="149"/><c r="Q25" s="145"><v>900000</v></c><c r="R25" s="146"/><c r="S25" s="147"/><c r="T25" s="213" t="s"><v>17</v></c><c r="U25" s="214"/><c r="V25" s="13"/><c r="W25" s="82" t="s"><v>45</v></c></row><row r="26" spans="1:23" x14ac:dyDescent="0.3"><c r="E26" s="4"/><c r="J26"/><c r="L26"/><c r="M26" s="79" t="s"><v>53</v></c><c r="N26" s="80"/><c r="O26" s="126"/><c r="P26" s="127"/><c r="Q26" s="188"><v>100000</v></c><c r="R26" s="189"/><c r="S26" s="190"/><c r="T26" s="124"/><c r="U26" s="125"/><c r="V26" s="13"/><c r="W26" s="82"/></row><row r="27" spans="1:23" x14ac:dyDescent="0.3"><c r="I27" s="109" t="str"><f>B1</f></c><c r="J27" s="136" t="str"><f>B9</f></c><c r="L27"/><c r="M27" s="79" t="s"><v>18</v></c><c r="N27" s="80"/><c r="O27" s="186"/><c r="P27" s="187"/><c r="Q27" s="188"><v>600000</v></c><c r="R27" s="189"/><c r="S27" s="190"/><c r="T27" s="205" t="s"><v>19</v></c><c r="U27" s="206"/><c r="V27" s="19"/><c r="W27" s="92"><v>2000000</v></c></row><row r="28" spans="1:23" x14ac:dyDescent="0.3"><c r="I28" s="109"><f>C1</f><v>0</v></c><c r="J28" s="136"><f>C9</f><v>0</v></c><c r="L28"/><c r="M28" s="203" t="s"><v>20</v></c><c r="N28" s="204"/><c r="O28" s="186"/><c r="P28" s="187"/><c r="Q28" s="188"/><c r="R28" s="189"/><c r="S28" s="190"/><c r="T28" s="201" t="s"><v>39</v></c><c r="U28" s="202"/><c r="V28" s="21"/><c r="W28" s="13"/></row><row r="29" spans="1:23" x14ac:dyDescent="0.3"><c r="I29" s="109"><f>D1</f><v>0</v></c><c r="J29" s="136"><f>D9</f><v>0</v></c><c r="K29" s="24"/><c r="L29"/><c r="M29" s="203" t="s"><v>21</v></c><c r="N29" s="204"/><c r="O29" s="186"/><c r="P29" s="187"/><c r="Q29" s="188"/><c r="R29" s="189"/><c r="S29" s="190"/><c r="T29" s="199" t="s"><v>40</v></c><c r="U29" s="200"/><c r="W29" s="93" t="str"><f>U23</f></c></row><row r="30" spans="1:23" x14ac:dyDescent="0.3"><c r="A30" s="1"/><c r="I30" s="109"><f>E1</f><v>0</v></c><c r="J30" s="136"><f>E9</f><v>0</v></c><c r="L30"/><c r="M30" s="203" t="s"><v>22</v></c><c r="N30" s="204"/><c r="O30" s="186"/><c r="P30" s="217"/><c r="Q30" s="188"/><c r="R30" s="189"/><c r="S30" s="190"/><c r="T30" s="218" t="s"><v>41</v></c><c r="U30" s="219"/><c r="V30" s="24"/><c r="W30" s="21" t="str"><f>Q34</f></c></row><row r="31" spans="1:23" x14ac:dyDescent="0.3"><c r="A31" s="1"/><c r="I31" s="109"><f>F1</f><v>0</v></c><c r="J31" s="136"><f>F9</f><v>0</v></c><c r="L31"/><c r="M31" s="203" t="s"><v>23</v></c><c r="N31" s="204"/><c r="O31" s="186"/><c r="P31" s="187"/><c r="Q31" s="188"/><c r="R31" s="189"/><c r="S31" s="190"/><c r="T31" s="28"/><c r="U31" s="26"/></row><row r="32" spans="1:23" x14ac:dyDescent="0.3"><c r="A32" s="1"/><c r="I32" s="109"><f>G1</f><v>0</v></c><c r="J32" s="136"><f>G9</f><v>0</v></c><c r="L32"/><c r="M32" s="203" t="s"><v>24</v></c><c r="N32" s="204"/><c r="O32" s="186"/><c r="P32" s="187"/><c r="Q32" s="188"/><c r="R32" s="189"/><c r="S32" s="190"/><c r="T32" s="28"/><c r="U32" s="26"/><c r="W32" s="82" t="s"><v>46</v></c></row><row r="33" spans="1:23" x14ac:dyDescent="0.3"><c r="A33" s="1"/><c r="I33" s="109"><f>H1</f><v>0</v></c><c r="J33" s="136"><f>H9</f><v>0</v></c><c r="L33"/><c r="M33" s="79" t="s"><v>25</v></c><c r="N33" s="81"/><c r="O33" s="186"/><c r="P33" s="187"/><c r="Q33" s="188"/><c r="R33" s="189"/><c r="S33" s="190"/><c r="T33" s="28"/><c r="U33" s="26"/><c r="W33" s="117" t="e"><f>W30-W27</f><v>#VALUE!</v></c></row><row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A34" s="1"/><c r="I34" s="109"><f>I1</f><v>0</v></c><c r="J34" s="136"><f>I9</f><v>0</v></c><c r="L34" s="8"/><c r="M34" s="191" t="s"><v>26</v></c><c r="N34" s="192"/><c r="O34" s="193"/><c r="P34" s="194"/><c r="Q34" s="188"><v>2000000</v></c><c r="R34" s="189"/><c r="S34" s="190"/><c r="T34" s="30"/><c r="U34" s="29"/><c r="V34" s="1"/><c r="W34" s="24"/></row><row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A35" s="1"/><c r="D35" s="31"/><c r="I35" s="41"><f>J1</f><v>0</v></c><c r="J35" s="27"><f>J9</f><v>0</v></c><c r="L35"/><c r="M35" s="195" t="s"><v>27</v></c><c r="N35" s="196"/><c r="O35" s="197"/><c r="P35" s="167" t="s"><v>28</v></c><c r="Q35" s="169"/><c r="R35" s="167" t="s"><v>29</v></c><c r="S35" s="169"/><c r="T35" s="167" t="s"><v>30</v></c><c r="U35" s="169"/><c r="V35" s="1"/><c r="W35" s="1"/></row><row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B36" s="9"/><c r="I36" s="41"><f>K1</f><v>0</v></c><c r="J36" s="27"><f>K9</f><v>0</v></c><c r="L36"/><c r="M36" s="33" t="s"><v>13</v></c><c r="N36" s="34" t="s"><v>31</v></c><c r="O36" s="35" t="s"><v>32</v></c><c r="P36" s="36" t="s"><v>33</v></c><c r="Q36" s="35" t="s"><v>32</v></c><c r="R36" s="36" t="s"><v>33</v></c><c r="S36" s="35" t="s"><v>32</v></c><c r="T36" s="36" t="s"><v>33</v></c><c r="U36" s="35" t="s"><v>32</v></c><c r="V36" s="1"/><c r="W36" s="1"/></row><row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A37" s="1"/><c r="I37" s="41"><f>L$1</f><v>0</v></c><c r="J37" s="27"><f>L9</f><v>0</v></c><c r="K37" s="24"/><c r="L37"/><c r="M37" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N37" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O37" s="39"><v>100000</v></c><c r="P37" s="151"/><c r="Q37" s="77"/><c r="R37" s="153"/><c r="S37" s="78"/><c r="T37" s="152"/><c r="U37" s="74"/><c r="V37" s="1"/><c r="W37" s="18" t="s"><v>14</v></c></row><row r="38"  x14ac:dyDescent="0.3" spans="1:23" x14ac:dyDescent="0.3"><c r="A38" s="1"/><c r="I38" s="41"><f>L$1</f><v>0</v></c><c r="J38" s="27"><f>L9</f><v>0</v></c><c r="K38" s="24"/><c r="L38"/><c r="M38" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N38" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O38" s="39"><v>100000</v></c><c r="P38" s="42"/><c r="Q38" s="72"/><c r="R38" s="44"/><c r="S38" s="77"/><c r="T38" s="42"/><c r="U38" s="72"/><c r="V38" s="1"/><c r="W38" s="18" t="s"><v>14</v></c></row><row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B39" s="20"/><c r="C39" s="32"/><c r="I39" s="41"><f t="shared" ref="I39:I46" si="6">L$1</f><v>0</v></c><c r="J39" s="27"><f t="shared" ref="J39:J46" si="7">L10</f><v>0</v></c><c r="L39" s="105"/><c r="M39" s="171" t="s"><v>42</v></c><c r="N39" s="179"/><c r="O39" s="150"><v>600000</v></c><c r="P39" s="152"/><c r="Q39" s="75"/><c r="R39" s="154"/><c r="S39" s="73"/><c r="T39" s="152"/><c r="U39" s="76"/><c r="V39" s="1"/><c r="W39" s="1"/></row><row r="40" spans="1:23" x14ac:dyDescent="0.3"><c r="O40" s="39"/><c r="N40" s="38"/><c r="M40" s="37"/><c r="B40" s="20"/><c r="C40" s="32"/><c r="I40" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J41" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K41" s="24"/><c r="L41" s="105"/><c r="M41" s="37"/><c r="N41" s="38"/><c r="O41" s="39"/><c r="P41" s="152"/><c r="Q41" s="68"/><c r="R41" s="154"/><c r="S41" s="73"/><c r="T41" s="152"/><c r="U41" s="68"/><c r="V41" s="1"/><c r="W41" s="1"/></row><row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"><c r="B42" s="20"/><c r="C42" s="32"/><c r="D42" s="44"/><c r="E42" s="43"/><c r="I42" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J42" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K42" s="24"/><c r="L42" s="105"/><c r="M42" s="37"/><c r="N42" s="38"/><c r="O42" s="39"/><c r="P42" s="152"/><c r="Q42" s="66"/><c r="R42" s="154"/><c r="S42" s="74"/><c r="T42" s="152"/><c r="U42" s="68"/><c r="V42" s="1"/><c r="W42" s="1"/></row><row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="B43" s="20"/><c r="C43" s="32"/><c r="D43" s="23"/><c r="E43" s="23"/><c r="I43" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J43" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K43" s="24"/><c r="L43" s="105"/><c r="M43" s="37"/><c r="N43" s="38"/><c r="O43" s="39"/><c r="P43" s="152"/><c r="Q43" s="66"/><c r="R43" s="154"/><c r="S43" s="74"/><c r="T43" s="152"/><c r="U43" s="68"/><c r="V43" s="1"/><c r="W43" s="1"/></row><row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6"><c r="B44" s="20"/><c r="C44" s="25"/><c r="D44" s="23"/><c r="E44" s="23"/><c r="F44" s="47"/><c r="I44" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J44" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L44" s="105"/><c r="M44" s="37"/><c r="N44" s="38"/><c r="O44" s="39"/><c r="P44" s="152"/><c r="Q44" s="66"/><c r="R44" s="154"/><c r="S44" s="73"/><c r="T44" s="152"/><c r="U44" s="68"/><c r="V44" s="1"/><c r="W44" s="1"/></row><row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6"><c r="A45" s="104"/><c r="B45" s="20"/><c r="C45" s="32"/><c r="D45" s="170"/><c r="E45" s="170"/><c r="F45" s="47"/><c r="G45" s="8"/><c r="I45" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J45" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K45" s="24"/><c r="L45" s="105"/><c r="M45" s="37"/><c r="N45" s="38"/><c r="O45" s="39"/><c r="P45" s="152"/><c r="Q45" s="66"/><c r="R45" s="152"/><c r="S45" s="67"/><c r="T45" s="152"/><c r="U45" s="68"/></row><row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A46" s="25"/><c r="B46" s="20"/><c r="C46" s="25"/><c r="D46" s="170"/><c r="E46" s="170"/><c r="F46" s="48"/><c r="H46" s="64"/><c r="I46" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J46" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K46" s="24"/><c r="L46" s="105"/><c r="M46" s="37"/><c r="N46" s="38"/><c r="O46" s="39"/><c r="P46" s="152"/><c r="Q46" s="66"/><c r="R46" s="152"/><c r="S46" s="67"/><c r="T46" s="152"/><c r="U46" s="68"/></row><row r="46" spans="1:23" x14ac:dyDescent="0.3"><c r="A47" s="25"/><c r="B47" s="25"/><c r="C47" s="40"/><c r="D47" s="170"/><c r="E47" s="170"/><c r="F47" s="23"/><c r="H47" s="64"/><c r="I47" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J47" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="72"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="47" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="49"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"><f>SUM(J28:J46)</f><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="67"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="48" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="17"/><c r="G48" s="1"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"/><c r="K48" s="24"/><c r="L48" s="105"/><c r="M48" s="37"/><c r="N48" s="38"/><c r="O48" s="39"/><c r="P48" s="152"/><c r="Q48" s="66"/><c r="R48" s="152"/><c r="S48" s="67"/><c r="T48" s="152"/><c r="U48" s="68"/></row><row r="49" spans="1:23" x14ac:dyDescent="0.3"><c r="A49" s="20"/><c r="B49" s="20"/><c r="C49" s="40"/><c r="D49" s="170"/><c r="E49" s="170"/><c r="F49" s="23"/><c r="G49" s="1"/><c r="H49" s="64"/><c r="I49" s="13"/><c r="J49" s="53"/><c r="L49" s="105"/><c r="M49" s="37"/><c r="N49" s="38"/><c r="O49" s="39"/><c r="P49" s="152"/><c r="Q49" s="66"/><c r="R49" s="152"/><c r="S49" s="67"/><c r="T49" s="154"/><c r="U49" s="68"/></row><row r="50" spans="1:21" x14ac:dyDescent="0.3"><c r="A50" s="20"/><c r="B50" s="20"/><c r="C50" s="40"/><c r="D50" s="170"/><c r="E50" s="170"/><c r="F50" s="23"/><c r="G50" s="1"/><c r="H50" s="46"/><c r="I50" s="13"/><c r="J50" s="53"/><c r="L50" s="105"/><c r="M50" s="37"/><c r="N50" s="38"/><c r="O50" s="39"/><c r="P50" s="152"/><c r="Q50" s="66"/><c r="R50" s="152"/><c r="S50" s="67"/><c r="T50" s="154"/><c r="U50" s="68"/></row><row r="51" spans="1:21" x14ac:dyDescent="0.3"><c r="A51" s="20"/><c r="B51" s="20"/><c r="C51" s="40"/><c r="D51" s="23"/><c r="E51" s="25"/><c r="F51" s="23"/><c r="G51" s="1"/><c r="H51" s="46"/><c r="I51" s="13"/><c r="J51" s="53"/><c r="L51" s="105"/><c r="M51" s="37"/><c r="N51" s="38"/><c r="O51" s="39"/><c r="P51" s="152"/><c r="Q51" s="66"/><c r="R51" s="152"/><c r="S51" s="67"/><c r="T51" s="154"/><c r="U51" s="68"/></row><row r="52" spans="1:21" x14ac:dyDescent="0.3"><c r="A52" s="20"/><c r="B52" s="20"/><c r="C52" s="40"/><c r="D52" s="185"/><c r="E52" s="185"/><c r="F52" s="23"/><c r="G52" s="1"/><c r="H52" s="46"/><c r="I52" s="13"/><c r="J52" s="53"/><c r="L52" s="105"/><c r="M52" s="37"/><c r="N52" s="38"/><c r="O52" s="39"/><c r="P52" s="151"/><c r="Q52" s="66"/><c r="R52" s="152"/><c r="S52" s="67"/><c r="T52" s="154"/><c r="U52" s="68"/></row><row r="53" spans="1:21" x14ac:dyDescent="0.3"><c r="A53" s="20"/><c r="B53" s="51"/><c r="C53" s="40"/><c r="D53" s="178"/><c r="E53" s="178"/><c r="F53" s="23"/><c r="G53" s="1"/><c r="H53" s="46"/><c r="I53" s="50"/><c r="J53" s="53"/><c r="L53" s="105"/><c r="M53" s="37"/><c r="N53" s="38"/><c r="O53" s="39"/><c r="P53" s="151"/><c r="Q53" s="66"/><c r="R53" s="152"/><c r="S53" s="67"/><c r="T53" s="154"/><c r="U53" s="68"/></row><row r="54" spans="1:21" x14ac:dyDescent="0.3"><c r="A54" s="25"/><c r="B54" s="51"/><c r="C54" s="40"/><c r="D54" s="166"/><c r="E54" s="166"/><c r="F54" s="23"/><c r="G54" s="1"/><c r="H54" s="46"/><c r="I54" s="50"/><c r="J54" s="53"/><c r="L54" s="18"/><c r="M54" s="37"/><c r="N54" s="38"/><c r="O54" s="39"/><c r="P54" s="152"/><c r="Q54" s="66"/><c r="R54" s="152"/><c r="S54" s="67"/><c r="T54" s="154"/><c r="U54" s="68"/></row><row r="55" spans="1:21" x14ac:dyDescent="0.3"><c r="A55" s="20"/><c r="B55" s="51"/><c r="C55" s="40"/><c r="D55" s="166"/><c r="E55" s="166"/><c r="F55" s="23"/><c r="G55" s="1"/><c r="H55" s="46"/><c r="I55" s="50"/><c r="J55" s="53"/><c r="L55" s="18"/><c r="M55" s="37"/><c r="N55" s="38"/><c r="O55" s="39"/><c r="P55" s="152"/><c r="Q55" s="66"/><c r="R55" s="152"/><c r="S55" s="67"/><c r="T55" s="154"/><c r="U55" s="68"/></row><row r="56" spans="1:21" x14ac:dyDescent="0.3"><c r="A56" s="20"/><c r="B56" s="51"/><c r="C56" s="40"/><c r="D56" s="22"/><c r="E56" s="22"/><c r="F56" s="23"/><c r="G56" s="1"/><c r="H56" s="46"/><c r="I56" s="50"/><c r="J56" s="53"/><c r="L56" s="18"/><c r="M56" s="37"/><c r="N56" s="38"/><c r="O56" s="39"/><c r="P56" s="152"/><c r="Q56" s="66"/><c r="R56" s="152"/><c r="S56" s="67"/><c r="T56" s="154"/><c r="U56" s="68"/></row><row r="57" spans="1:21" x14ac:dyDescent="0.3"><c r="A57" s="20"/><c r="B57"/><c r="C57" s="40"/><c r="D57" s="22"/><c r="E57" s="22"/><c r="F57" s="23"/><c r="G57" s="1"/><c r="H57" s="46"/><c r="I57" s="50"/><c r="J57" s="53"/><c r="L57" s="18"/><c r="M57" s="37"/><c r="N57" s="38"/><c r="O57" s="39"/><c r="P57" s="152"/><c r="Q57" s="66"/><c r="R57" s="152"/><c r="S57" s="67"/><c r="T57" s="154"/><c r="U57" s="68"/></row><row r="58" spans="1:21" x14ac:dyDescent="0.3"><c r="A58" s="20"/><c r="B58"/><c r="C58" s="40"/><c r="D58" s="22"/><c r="E58" s="22"/><c r="F58" s="23"/><c r="G58" s="1"/><c r="H58" s="46"/><c r="I58" s="50"/><c r="J58" s="53"/><c r="L58" s="18"/><c r="M58" s="37"/><c r="N58" s="38"/><c r="O58" s="39"/><c r="P58" s="152"/><c r="Q58" s="66"/><c r="R58" s="152"/><c r="S58" s="67"/><c r="T58" s="154"/><c r="U58" s="68"/></row><row r="59" spans="1:21" x14ac:dyDescent="0.3"><c r="A59" s="20"/><c r="B59"/><c r="C59" s="40"/><c r="D59" s="22"/><c r="E59" s="22"/><c r="F59" s="23"/><c r="G59" s="1"/><c r="H59" s="46"/><c r="I59" s="50"/><c r="J59" s="53"/><c r="L59" s="18"/><c r="M59" s="37"/><c r="N59" s="38"/><c r="O59" s="39"/><c r="P59" s="152"/><c r="Q59" s="66"/><c r="R59" s="152"/><c r="S59" s="67"/><c r="T59" s="154"/><c r="U59" s="68"/></row><row r="60" spans="1:21" x14ac:dyDescent="0.3"><c r="A60" s="20"/><c r="B60"/><c r="C60" s="40"/><c r="D60" s="22"/><c r="E60" s="22"/><c r="F60" s="23"/><c r="G60" s="1"/><c r="H60" s="46"/><c r="I60" s="50"/><c r="J60" s="53"/><c r="L60" s="18"/><c r="M60" s="37"/><c r="N60" s="38"/><c r="O60" s="39"/><c r="P60" s="152"/><c r="Q60" s="66"/><c r="R60" s="152"/><c r="S60" s="67"/><c r="T60" s="154"/><c r="U60" s="68"/></row><row r="61" spans="1:21" x14ac:dyDescent="0.3"><c r="A61" s="25"/><c r="B61"/><c r="C61" s="40"/><c r="D61" s="166"/><c r="E61" s="166"/><c r="F61" s="23"/><c r="G61" s="1"/><c r="H61" s="46"/><c r="I61" s="50"/><c r="J61" s="53"/><c r="L61" s="18"/><c r="M61" s="37"/><c r="N61" s="38"/><c r="O61" s="39"/><c r="P61" s="152"/><c r="Q61" s="66"/><c r="R61" s="152"/><c r="S61" s="67"/><c r="T61" s="154"/><c r="U61" s="68"/></row><row r="62" spans="1:21" x14ac:dyDescent="0.3"><c r="A62" s="25"/><c r="B62"/><c r="C62" s="40"/><c r="D62" s="22"/><c r="E62" s="22"/><c r="F62" s="23"/><c r="G62" s="1"/><c r="H62" s="46"/><c r="I62" s="50"/><c r="J62" s="53"/><c r="L62" s="18"/><c r="M62" s="37"/><c r="N62" s="38"/><c r="O62" s="39"/><c r="P62" s="152"/><c r="Q62" s="135"/><c r="R62" s="155"/><c r="S62" s="88"/><c r="T62" s="154"/><c r="U62" s="68"/></row><row r="63" spans="1:21" x14ac:dyDescent="0.3"><c r="A63" s="25"/><c r="B63"/><c r="C63" s="40"/><c r="D63" s="22"/><c r="E63" s="22"/><c r="F63" s="23"/><c r="G63" s="1"/><c r="H63" s="46"/><c r="I63" s="50"/><c r="J63" s="53"/><c r="L63" s="18"/><c r="M63" s="37"/><c r="N63" s="38"/><c r="O63" s="39"/><c r="P63" s="152"/><c r="Q63" s="135"/><c r="R63" s="155"/><c r="S63" s="88"/><c r="T63" s="154"/><c r="U63" s="68"/></row><row r="64" spans="1:21" x14ac:dyDescent="0.3"><c r="A64" s="25"/><c r="B64"/><c r="C64" s="40"/><c r="D64" s="22"/><c r="E64" s="22"/><c r="F64" s="23"/><c r="G64" s="1"/><c r="H64" s="46"/><c r="I64" s="50"/><c r="J64" s="53"/><c r="L64" s="18"/><c r="M64" s="37"/><c r="N64" s="38"/><c r="O64" s="39"/><c r="P64" s="152"/><c r="Q64" s="135"/><c r="R64" s="155"/><c r="S64" s="88"/><c r="T64" s="154"/><c r="U64" s="68"/></row><row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A65" s="25"/><c r="B65"/><c r="C65" s="40"/><c r="D65" s="166"/><c r="E65" s="166"/><c r="F65" s="23"/><c r="G65" s="1"/><c r="H65" s="46"/><c r="I65" s="50"/><c r="J65" s="53"/><c r="L65" s="18"/><c r="M65" s="37"/><c r="N65" s="38"/><c r="O65" s="39"/><c r="P65" s="152"/><c r="Q65" s="84"/><c r="R65" s="155"/><c r="S65" s="88"/><c r="T65" s="154"/><c r="U65" s="71"/></row><row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A66" s="25"/><c r="B66"/><c r="C66" s="40"/><c r="D66" s="166"/><c r="E66" s="166"/><c r="F66" s="20"/><c r="G66" s="1"/><c r="H66" s="46"/><c r="I66" s="50"/><c r="J66" s="53"/><c r="L66"/><c r="M66" s="171" t="s"><v>34</v></c><c r="N66" s="172"/><c r="O66" s="42"/><c r="P66" s="52" t="s"><v>11</v></c><c r="Q66" s="42"/><c r="R66" s="52" t="s"><v>11</v></c><c r="S66" s="42"/><c r="T66" s="52" t="s"><v>11</v></c><c r="U66" s="42"/></row><row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A67" s="25"/><c r="B67"/><c r="C67" s="90"/><c r="D67" s="166"/><c r="E67" s="166"/><c r="F67" s="23"/><c r="G67" s="1"/><c r="H67" s="46"/><c r="I67" s="50"/><c r="J67"/><c r="L67"/><c r="M67" s="54"/><c r="N67" s="55"/><c r="O67" s="70"/><c r="P67" s="23"/><c r="Q67" s="69"/><c r="R67" s="70"/><c r="S67" s="70"/><c r="T67" s="6"/></row><row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="A68" s="25"/><c r="B68"/><c r="C68" s="25"/><c r="D68" s="22"/><c r="E68" s="22"/><c r="F68" s="23"/><c r="G68" s="1"/><c r="H68" s="46"/><c r="I68" s="50"/><c r="J68"/><c r="L68"/><c r="M68" s="167" t="s"><v>47</v></c><c r="N68" s="168"/><c r="O68" s="169"/><c r="P68" s="181"/><c r="Q68" s="182"/><c r="R68" s="167" t="s"><v>37</v></c><c r="S68" s="168"/><c r="T68" s="183" t="str"><f>Q25</f></c><c r="U68" s="184"/></row><row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A69" s="25"/><c r="B69"/><c r="C69" s="25"/><c r="D69" s="166"/><c r="E69" s="166"/><c r="F69" s="63"/><c r="G69" s="1"/><c r="H69" s="46"/><c r="I69" s="50"/><c r="J69"/><c r="L69"/><c r="M69" s="56"/><c r="N69" s="83"/><c r="O69" s="83"/><c r="P69" s="57"/><c r="Q69" s="58"/><c r="R69" s="58"/><c r="S69" s="58"/><c r="T69" s="56"/><c r="U69" s="56"/></row><row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A70" s="25"/><c r="B70" s="90"/><c r="C70" s="25"/><c r="D70" s="166"/><c r="E70" s="166"/><c r="F70" s="63"/><c r="G70" s="1"/><c r="H70" s="46"/><c r="I70" s="50"/><c r="J70"/><c r="L70"/><c r="M70" s="171" t="s"><v>35</v></c><c r="N70" s="179"/><c r="O70" s="179"/><c r="P70" s="179"/><c r="Q70" s="179"/><c r="R70" s="179"/><c r="S70" s="179"/><c r="T70" s="179"/><c r="U70" s="180"/><c r="V70" s="51"/></row><row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A71" s="25"/><c r="B71" s="20"/><c r="C71" s="25"/><c r="D71" s="166"/><c r="E71" s="166"/><c r="F71" s="63"/><c r="G71" s="1"/><c r="H71" s="46"/><c r="I71" s="50"/><c r="J71"/><c r="L71" s="49" t="s"><v>59</v></c><c r="M71" s="130" t="s"><v>55</v></c><c r="N71" s="131"/><c r="O71" s="131"/><c r="P71" s="131" t="s"><v>56</v></c><c r="Q71" s="131"/><c r="R71" s="131"/><c r="S71" s="131"/><c r="T71" s="131" t="s"><v>57</v></c><c r="U71" s="132" t="s"><v>60</v></c><c r="V71" s="144" t="s"><v>58</v></c><c r="W71" s="144" t="s"><v>50</v></c></row><row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A72" s="25"/><c r="B72" s="115"/><c r="C72" s="25"/><c r="D72" s="166"/><c r="E72" s="166"/><c r="F72" s="63"/><c r="G72" s="1"/><c r="H72" s="46"/><c r="I72" s="50"/><c r="J72" s="23"/><c r="L72" s="0"/><c r="M72" s="59"/><c r="N72" s="60"/><c r="O72" s="143" t="s"><v>43</v></c><c r="P72" s="62"/><c r="Q72" s="61"/><c r="R72" s="177" t="inlineStr"><is><t xml:space="preserve">CREDITO</t></is></c><c r="S72" s="177"/><c r="T72" s="133"/><c r="U72" s="134"/><c r="V72" s="51"/></row><row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="B73" s="51"/><c r="C73" s="89"/><c r="D73" s="166"/><c r="E73" s="166"/><c r="F73" s="63"/><c r="I73" s="115"/><c r="L73"/><c r="M73" s="85"/><c r="N73" s="86"/><c r="O73" s="18"/><c r="P73" s="87"/><c r="Q73" s="56"/><c r="R73" s="175"/><c r="S73" s="175"/><c r="T73" s="65"/><c r="U73" s="95"/><c r="V73" s="51"/></row><row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A74" s="49"/><c r="B74" s="89"/><c r="C74" s="89"/><c r="D74" s="23"/><c r="E74" s="25"/><c r="F74" s="63"/><c r="I74" s="115"/><c r="L74" s="45" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="M74" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N74" s="86"/><c r="O74" s="18" t="s"><v>43</v></c><c r="P74" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q74" s="56"/><c r="R74" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S74" s="175"/><c r="T74" s="65"><v>150000</v></c><c r="U74" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V74" s="51"/></row><row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L75" s="45" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="M75" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N75" s="86"/><c r="O75" s="123"/><c r="P75" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q75" s="56"/><c r="R75" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S75" s="175"/><c r="T75" s="65"><v>150000</v></c><c r="U75" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V75" s="51"/></row><row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L76" s="45"/><c r="M76" s="137" t="s"><v>61</v></c><c r="N76" s="138"/><c r="O76" s="139"/><c r="P76" s="140"/><c r="Q76" s="141"/><c r="R76" s="176"/><c r="S76" s="176"/><c r="T76" s="173"/><c r="U76" s="174"/><c r="V76" s="51"/></row><row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L77" s="45"/><c r="M77" s="137" t="s"><v>62</v></c><c r="N77" s="138"/><c r="O77" s="139"/><c r="P77" s="140"/><c r="Q77" s="141"/><c r="R77" s="142"/><c r="S77" s="142"/><c r="T77" s="173"/><c r="U77" s="174"/><c r="V77" s="51"/></row><row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L78" s="45"/><c r="M78" s="94"/><c r="N78" s="64"/><c r="O78" s="123"/><c r="P78" s="87"/><c r="Q78" s="56"/><c r="R78" s="56"/><c r="S78" s="56"/><c r="T78" s="65"/><c r="U78" s="95"/><c r="V78" s="51"/></row><row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L79" s="45"/><c r="M79" s="101" t="s"><v>11</v></c><c r="N79" s="102"><f>SUM(N77:N78)</f><v>0</v></c><c r="O79" s="96"/><c r="P79" s="98"/><c r="Q79" s="97"/><c r="R79" s="97"/><c r="S79" s="97"/><c r="T79" s="99"/><c r="U79" s="100"/><c r="V79" s="51"/></row><row r="80" spans="1:23" x14ac:dyDescent="0.3"><c r="M80"/><c r="O80" s="5"/><c r="Q80"/><c r="S80"/><c r="T80" s="6"/><c r="V80" s="51"/></row><row r="81" spans="1:23" x14ac:dyDescent="0.3"><c r="O81"/><c r="V81" s="51"/></row><row r="82" spans="13:22" x14ac:dyDescent="0.3"><c r="M82" s="23"/><c r="N82" s="23"/><c r="O82" s="23"/><c r="P82" s="23"/><c r="Q82" s="23"/><c r="V82" s="51"/></row><row r="83" spans="13:22" x14ac:dyDescent="0.3"><c r="V83" s="51"/></row><row r="84" spans="13:22" x14ac:dyDescent="0.3"><c r="V84" s="51"/></row><row r="85" spans="13:22" x14ac:dyDescent="0.3"><c r="V85" s="51"/></row><row r="86" spans="13:22" x14ac:dyDescent="0.3"><c r="V86" s="51"/></row><row r="87" spans="13:22" x14ac:dyDescent="0.3"><c r="V87" s="51"/></row><row r="88" spans="13:22" x14ac:dyDescent="0.3"><c r="V88" s="51"/></row><row r="89" spans="13:22" x14ac:dyDescent="0.3"><c r="V89" s="51"/></row><row r="90" spans="13:22" x14ac:dyDescent="0.3"><c r="V90" s="51"/></row><row r="91" spans="13:22" x14ac:dyDescent="0.3"><c r="V91" s="51"/></row><row r="92" spans="13:22" x14ac:dyDescent="0.3"><c r="V92" s="51"/></row><row r="93" spans="13:22" x14ac:dyDescent="0.3"><c r="V93" s="51"/></row><row r="94" spans="13:22" x14ac:dyDescent="0.3"><c r="V94" s="51"/></row><row r="95" spans="13:22" x14ac:dyDescent="0.3"><c r="V95" s="51"/></row><row r="96" spans="13:22" x14ac:dyDescent="0.3"><c r="V96" s="51"/></row><row r="97" spans="13:22" x14ac:dyDescent="0.3"><c r="V97" s="51"/></row><row r="98" spans="22:22" x14ac:dyDescent="0.3"><c r="V98" s="51"/></row><row r="99" spans="22:22" x14ac:dyDescent="0.3"><c r="V99" s="51"/></row><row r="100" spans="22:22" x14ac:dyDescent="0.3"><c r="V100" s="51"/></row><row r="101" spans="22:22" x14ac:dyDescent="0.3"><c r="V101" s="51"/></row><row r="102" spans="22:22" x14ac:dyDescent="0.3"><c r="V102" s="51"/></row><row r="103" spans="22:22" x14ac:dyDescent="0.3"><c r="V103" s="51"/></row><row r="104" spans="22:22" x14ac:dyDescent="0.3"><c r="V104" s="51"/></row><row r="105" spans="22:22" x14ac:dyDescent="0.3"><c r="V105" s="51"/></row><row r="106" spans="22:22" x14ac:dyDescent="0.3"><c r="V106" s="51"/></row><row r="107" spans="22:22" x14ac:dyDescent="0.3"><c r="V107" s="51"/></row><row r="108" spans="22:22" x14ac:dyDescent="0.3"><c r="V108" s="51"/></row><row r="109" spans="22:22" x14ac:dyDescent="0.3"><c r="V109" s="51"/></row><row r="110" spans="22:22" x14ac:dyDescent="0.3"><c r="V110" s="51"/></row><row r="111" spans="22:22" x14ac:dyDescent="0.3"><c r="V111" s="51"/></row><row r="112" spans="22:22" x14ac:dyDescent="0.3"><c r="V112" s="51"/></row><row r="113" spans="22:22" x14ac:dyDescent="0.3"><c r="V113" s="51"/></row></sheetData><mergeCells count="70"><mergeCell ref="M25:N25"/><mergeCell ref="O30:P30"/><mergeCell ref="Q30:S30"/><mergeCell ref="T30:U30"/><mergeCell ref="Q32:S32"/><mergeCell ref="M31:N31"/><mergeCell ref="O31:P31"/><mergeCell ref="Q31:S31"/><mergeCell ref="M30:N30"/><mergeCell ref="M32:N32"/><mergeCell ref="O32:P32"/><mergeCell ref="M22:U22"/><mergeCell ref="Q26:S26"/><mergeCell ref="O29:P29"/><mergeCell ref="Q29:S29"/><mergeCell ref="T29:U29"/><mergeCell ref="T28:U28"/><mergeCell ref="O28:P28"/><mergeCell ref="Q28:S28"/><mergeCell ref="M28:N28"/><mergeCell ref="M29:N29"/><mergeCell ref="O27:P27"/><mergeCell ref="Q27:S27"/><mergeCell ref="T27:U27"/><mergeCell ref="N23:S23"/><mergeCell ref="N24:S24"/><mergeCell ref="T25:U25"/><mergeCell ref="D44:E44"/><mergeCell ref="R35:S35"/><mergeCell ref="T35:U35"/><mergeCell ref="O33:P33"/><mergeCell ref="Q33:S33"/><mergeCell ref="M34:N34"/><mergeCell ref="O34:P34"/><mergeCell ref="Q34:S34"/><mergeCell ref="P35:Q35"/><mergeCell ref="M35:O35"/><mergeCell ref="M39:N39"/><mergeCell ref="D72:E72"/><mergeCell ref="D73:E73"/><mergeCell ref="D53:E53"/><mergeCell ref="M70:U70"/><mergeCell ref="R68:S68"/><mergeCell ref="D69:E69"/><mergeCell ref="P68:Q68"/><mergeCell ref="T68:U68"/><mergeCell ref="D61:E61"/><mergeCell ref="D67:E67"/><mergeCell ref="D54:E54"/><mergeCell ref="D66:E66"/><mergeCell ref="D55:E55"/><mergeCell ref="D65:E65"/><mergeCell ref="T77:U77"/><mergeCell ref="R75:S75"/><mergeCell ref="R76:S76"/><mergeCell ref="R72:S72"/><mergeCell ref="R74:S74"/><mergeCell ref="R73:S73"/><mergeCell ref="T76:U76"/><mergeCell ref="D71:E71"/><mergeCell ref="D70:E70"/><mergeCell ref="M68:O68"/><mergeCell ref="D45:E45"/><mergeCell ref="D47:E47"/><mergeCell ref="M66:N66"/><mergeCell ref="D49:E49"/><mergeCell ref="D50:E50"/><mergeCell ref="D48:E48"/><mergeCell ref="D46:E46"/><mergeCell ref="D52:E52"/></mergeCells><pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/><pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/><drawing r:id="rId2"/></worksheet>
 </file>
--- a/scripts/.tmp/consolidado-test.xlsx
+++ b/scripts/.tmp/consolidado-test.xlsx
@@ -1950,5 +1950,5 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}"><dimension ref="A1:W113"/><sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/><cols><col min="1" max="1" width="17.33203125" customWidth="1"/><col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/><col min="3" max="3" width="12.6640625" customWidth="1"/><col min="4" max="4" width="12.6640625" style="3" customWidth="1"/><col min="5" max="5" width="12.6640625" customWidth="1"/><col min="6" max="6" width="12.6640625" style="3" customWidth="1"/><col min="7" max="9" width="12.6640625" customWidth="1"/><col min="10" max="10" width="12.6640625" style="3" customWidth="1"/><col min="11" max="11" width="12.6640625" customWidth="1"/><col min="12" max="12" width="12.6640625" style="3" customWidth="1"/><col min="13" max="13" width="11.5546875" style="3" customWidth="1"/><col min="14" max="14" width="11" bestFit="1" customWidth="1"/><col min="15" max="15" width="11.6640625" style="4" customWidth="1"/><col min="16" max="19" width="11.6640625" style="3" customWidth="1"/><col min="20" max="20" width="13.88671875" customWidth="1"/><col min="21" max="21" width="14" customWidth="1"/><col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/><col min="23" max="23" width="16" customWidth="1"/></cols><sheetData><row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A1" s="7" t="s"><v>50</v></c><c r="B1" s="112" t="inlineStr"><is><t xml:space="preserve">JUAN PEREZ</t></is></c><c r="C1" s="120" t="inlineStr"><is><t xml:space="preserve">MARIA LOPEZ</t></is></c><c r="D1" s="120"/><c r="E1" s="112"/><c r="F1" s="120"/><c r="G1" s="120"/><c r="H1" s="112"/><c r="I1" s="112"/><c r="J1" s="120"/><c r="K1" s="120"/><c r="L1" s="112"/><c r="M1" s="112"/><c r="N1" s="112"/><c r="O1" s="112"/><c r="P1" s="112"/><c r="Q1" s="112"/><c r="R1" s="121"/><c r="S1" s="120"/><c r="T1" s="120"/><c r="U1" s="7"/><c r="V1" s="7"/><c r="W1" s="114"/></row><row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A2" s="7" t="s"><v>51</v></c><c r="B2" s="112"/><c r="C2" s="120"/><c r="D2" s="120"/><c r="E2" s="112"/><c r="F2" s="120"/><c r="G2" s="128"/><c r="H2" s="112"/><c r="I2" s="112"/><c r="J2" s="120"/><c r="K2" s="120"/><c r="L2" s="112"/><c r="M2" s="112"/><c r="N2" s="112"/><c r="O2" s="112"/><c r="P2" s="112"/><c r="Q2" s="112"/><c r="R2" s="121"/><c r="S2" s="120"/><c r="T2" s="120"/><c r="U2" s="7"/><c r="V2" s="7"/><c r="W2" s="114"/></row><row r="3" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A3" s="122" t="s"><v>35</v></c><c r="B3" s="120"/><c r="C3" s="120"/><c r="D3" s="120"/><c r="E3" s="120"/><c r="F3" s="120"/><c r="G3" s="120"/><c r="H3" s="120"/><c r="I3" s="120"/><c r="J3" s="120"/><c r="K3" s="120"/><c r="L3" s="120"/><c r="M3" s="120"/><c r="N3" s="120"/><c r="O3" s="120"/><c r="P3" s="120"/><c r="Q3" s="120"/><c r="R3" s="120"/><c r="S3" s="120"/><c r="T3" s="120"/><c r="U3" s="110"/><c r="V3" s="163"/><c r="W3" s="116"/></row><row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A4" s="122" t="s"><v>52</v></c><c r="B4" s="120"/><c r="C4" s="120"/><c r="D4" s="120"/><c r="E4" s="120"/><c r="F4" s="120"/><c r="G4" s="120"/><c r="H4" s="120"/><c r="I4" s="120"/><c r="J4" s="120"/><c r="K4" s="120"/><c r="L4" s="120"/><c r="M4" s="120"/><c r="N4" s="120"/><c r="O4" s="120"/><c r="P4" s="120"/><c r="Q4" s="120"/><c r="R4" s="120"/><c r="S4" s="120"/><c r="T4" s="120"/><c r="U4" s="110"/><c r="V4" s="163"/><c r="W4" s="116"/></row><row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A5" s="122" t="s"><v>0</v></c><c r="B5" s="129" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="C5" s="129" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="D5" s="129"/><c r="E5" s="129"/><c r="F5" s="129"/><c r="G5" s="129"/><c r="H5" s="129"/><c r="I5" s="129"/><c r="J5" s="129"/><c r="K5" s="129"/><c r="L5" s="129"/><c r="M5" s="129"/><c r="N5" s="129"/><c r="O5" s="129"/><c r="P5" s="129"/><c r="Q5" s="129"/><c r="R5" s="120"/><c r="S5" s="120"/><c r="T5" s="120"/><c r="U5" s="111"/><c r="V5" s="111"/><c r="W5" s="111"/></row><row r="6" spans="1:23" s="45" customFormat="1" x14ac:dyDescent="0.3"><c r="A6" s="122" t="s"><v>1</v></c><c r="B6" s="120"><v>10</v></c><c r="C6" s="120"><v>10</v></c><c r="D6" s="120"/><c r="E6" s="120"/><c r="F6" s="120"/><c r="G6" s="120"/><c r="H6" s="120"/><c r="I6" s="120"/><c r="J6" s="120"/><c r="K6" s="120"/><c r="L6" s="120"/><c r="M6" s="111"/><c r="N6" s="111"/><c r="O6" s="111"/><c r="P6" s="111"/><c r="Q6" s="111"/><c r="R6" s="120"/><c r="S6" s="120"/><c r="T6" s="120"/><c r="U6" s="111"/><c r="V6" s="111"/><c r="W6" s="111"/></row><row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3"><c r="A7" s="122" t="s"><v>2</v></c><c r="B7" s="164"><v>1000000</v></c><c r="C7" s="164"><v>1000000</v></c><c r="D7" s="164"/><c r="E7" s="164"/><c r="F7" s="164"/><c r="G7" s="164"/><c r="H7" s="164"/><c r="I7" s="164"/><c r="J7" s="164"/><c r="K7" s="164"/><c r="L7" s="164"/><c r="M7" s="164"/><c r="N7" s="164"/><c r="O7" s="164"/><c r="P7" s="164"/><c r="Q7" s="164"/><c r="R7" s="156"/><c r="S7" s="156"/><c r="T7" s="156"/><c r="U7" s="157"/><c r="V7" s="157"/><c r="W7" s="157"/></row><row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A8" s="112"/><c r="B8" s="157"/><c r="C8" s="111"/><c r="D8" s="157"/><c r="E8" s="111"/><c r="F8" s="110"/><c r="G8" s="111"/><c r="H8" s="157"/><c r="I8" s="111"/><c r="J8" s="157"/><c r="K8" s="111"/><c r="L8" s="110"/><c r="M8" s="111"/><c r="N8" s="110"/><c r="O8" s="111"/><c r="P8" s="158"/><c r="Q8" s="111"/><c r="R8" s="158"/><c r="S8" s="111"/><c r="T8" s="158"/><c r="U8" s="111"/><c r="V8" s="110"/><c r="W8" s="111"/></row><row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A9" s="113" t="s"><v>3</v></c><c r="B9" s="165"><v>450000</v></c><c r="C9" s="165"><v>450000</v></c><c r="D9" s="165"/><c r="E9" s="157"/><c r="F9" s="110"/><c r="G9" s="157"/><c r="H9" s="110"/><c r="I9" s="157"/><c r="J9" s="110"/><c r="K9" s="157"/><c r="L9" s="110"/><c r="M9" s="157"/><c r="N9" s="110"/><c r="O9" s="157"/><c r="P9" s="158"/><c r="Q9" s="157"/><c r="R9" s="158"/><c r="S9" s="159"/><c r="T9" s="159"/><c r="U9" s="157"/><c r="V9" s="110"/><c r="W9" s="157"/></row><row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A10" s="113" t="s"><v>54</v></c><c r="B10" s="165"><v>50000</v></c><c r="C10" s="165"><v>50000</v></c><c r="D10" s="165"/><c r="E10" s="157"/><c r="F10" s="110"/><c r="G10" s="157"/><c r="H10" s="110"/><c r="I10" s="157"/><c r="J10" s="110"/><c r="K10" s="157"/><c r="L10" s="110"/><c r="M10" s="157"/><c r="N10" s="110"/><c r="O10" s="157"/><c r="P10" s="158"/><c r="Q10" s="157"/><c r="R10" s="158"/><c r="S10" s="159"/><c r="T10" s="159"/><c r="U10" s="157"/><c r="V10" s="110"/><c r="W10" s="157"/></row><row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A11" s="113" t="s"><v>4</v></c><c r="B11" s="165"><v>300000</v></c><c r="C11" s="165"><v>300000</v></c><c r="D11" s="165"/><c r="E11" s="157"/><c r="F11" s="110"/><c r="G11" s="157"/><c r="H11" s="110"/><c r="I11" s="157"/><c r="J11" s="110"/><c r="K11" s="157"/><c r="L11" s="110"/><c r="M11" s="157"/><c r="N11" s="110"/><c r="O11" s="157"/><c r="P11" s="158"/><c r="Q11" s="157"/><c r="R11" s="158"/><c r="S11" s="159"/><c r="T11" s="159"/><c r="U11" s="157"/><c r="V11" s="110"/><c r="W11" s="157"/></row><row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A12" s="113" t="s"><v>5</v></c><c r="B12" s="165"/><c r="C12" s="165"/><c r="D12" s="165"/><c r="E12" s="157"/><c r="F12" s="110"/><c r="G12" s="157"/><c r="H12" s="110"/><c r="I12" s="157"/><c r="J12" s="110"/><c r="K12" s="157"/><c r="L12" s="110"/><c r="M12" s="157"/><c r="N12" s="110"/><c r="O12" s="157"/><c r="P12" s="158"/><c r="Q12" s="157"/><c r="R12" s="158"/><c r="S12" s="159"/><c r="T12" s="159"/><c r="U12" s="157"/><c r="V12" s="110"/><c r="W12" s="157"/></row><row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A13" s="113" t="s"><v>6</v></c><c r="B13" s="165"/><c r="C13" s="165"/><c r="D13" s="165"/><c r="E13" s="157"/><c r="F13" s="110"/><c r="G13" s="157"/><c r="H13" s="110"/><c r="I13" s="157"/><c r="J13" s="110"/><c r="K13" s="157"/><c r="L13" s="110"/><c r="M13" s="157"/><c r="N13" s="110"/><c r="O13" s="157"/><c r="P13" s="158"/><c r="Q13" s="157"/><c r="R13" s="158"/><c r="S13" s="159"/><c r="T13" s="159"/><c r="U13" s="157"/><c r="V13" s="110"/><c r="W13" s="157"/></row><row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A14" s="113" t="s"><v>7</v></c><c r="B14" s="165"/><c r="C14" s="165"/><c r="D14" s="165"/><c r="E14" s="157"/><c r="F14" s="110"/><c r="G14" s="157"/><c r="H14" s="110"/><c r="I14" s="157"/><c r="J14" s="110"/><c r="K14" s="157"/><c r="L14" s="110"/><c r="M14" s="157"/><c r="N14" s="110"/><c r="O14" s="157"/><c r="P14" s="158"/><c r="Q14" s="157"/><c r="R14" s="158"/><c r="S14" s="159"/><c r="T14" s="159"/><c r="U14" s="157"/><c r="V14" s="110"/><c r="W14" s="157"/></row><row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A15" s="113" t="s"><v>8</v></c><c r="B15" s="165"/><c r="C15" s="165"/><c r="D15" s="165"/><c r="E15" s="157"/><c r="F15" s="110"/><c r="G15" s="157"/><c r="H15" s="110"/><c r="I15" s="157"/><c r="J15" s="110"/><c r="K15" s="157"/><c r="L15" s="110"/><c r="M15" s="157"/><c r="N15" s="110"/><c r="O15" s="157"/><c r="P15" s="158"/><c r="Q15" s="157"/><c r="R15" s="158"/><c r="S15" s="159"/><c r="T15" s="159"/><c r="U15" s="157"/><c r="V15" s="110"/><c r="W15" s="157"/></row><row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A16" s="113" t="s"><v>9</v></c><c r="B16" s="165"/><c r="C16" s="165"/><c r="D16" s="165"/><c r="E16" s="157"/><c r="F16" s="110"/><c r="G16" s="157"/><c r="H16" s="110"/><c r="I16" s="160"/><c r="J16" s="110"/><c r="K16" s="160"/><c r="L16" s="110"/><c r="M16" s="157"/><c r="N16" s="110"/><c r="O16" s="157"/><c r="P16" s="158"/><c r="Q16" s="157"/><c r="R16" s="158"/><c r="S16" s="159"/><c r="T16" s="159"/><c r="U16" s="157"/><c r="V16" s="110"/><c r="W16" s="157"/></row><row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A17" s="113" t="s"><v>10</v></c><c r="B17" s="165"/><c r="C17" s="165"/><c r="D17" s="165"/><c r="E17" s="157"/><c r="F17" s="110"/><c r="G17" s="157"/><c r="H17" s="110"/><c r="I17" s="160"/><c r="J17" s="110"/><c r="K17" s="157"/><c r="L17" s="110"/><c r="M17" s="157"/><c r="N17" s="110"/><c r="O17" s="157"/><c r="P17" s="158"/><c r="Q17" s="157"/><c r="R17" s="158"/><c r="S17" s="159"/><c r="T17" s="159"/><c r="U17" s="157"/><c r="V17" s="110"/><c r="W17" s="157"/></row><row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A18" s="113" t="s"><v>11</v></c><c r="B18" s="110"><f>SUM(B9:B17)</f><v>0</v></c><c r="C18" s="110"><f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f><v>0</v></c><c r="D18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="E18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="F18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="G18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="H18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="I18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="J18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="K18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="L18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="M18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="N18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="O18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="P18" s="110"><f t="shared" ref="P18" si="1">SUM(P9:P17)</f><v>0</v></c><c r="Q18" s="110"><f>SUM(Q9:Q17)</f><v>0</v></c><c r="R18" s="110"><f>SUM(R9:R17)</f><v>0</v></c><c r="S18" s="116"><f>SUM(S9:S17)</f><v>0</v></c><c r="T18" s="116"><f>SUM(T9:T17)</f><v>0</v></c><c r="U18" s="110"><f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f><v>0</v></c><c r="V18" s="110"><f t="shared" si="2"/><v>0</v></c><c r="W18" s="110"><f t="shared" si="2"/><v>0</v></c></row><row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A19" s="113"/><c r="B19" s="110"/><c r="C19" s="110"/><c r="D19" s="110"/><c r="E19" s="110"/><c r="F19" s="157"/><c r="G19" s="110"/><c r="H19" s="110"/><c r="I19" s="110"/><c r="J19" s="110"/><c r="K19" s="110"/><c r="L19" s="110"/><c r="M19" s="110"/><c r="N19" s="110"/><c r="O19" s="110"/><c r="P19" s="110"/><c r="Q19" s="110"/><c r="R19" s="110"/><c r="S19" s="116"/><c r="T19" s="116"/><c r="U19" s="110"/><c r="V19" s="110"/><c r="W19" s="110"/></row><row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3"><c r="A20" s="113" t="s"><v>12</v></c><c r="B20" s="110" t="e"><f t="shared" ref="B20:O20" si="3">B18-B7</f><v>#VALUE!</v></c><c r="C20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="D20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="E20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="F20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="G20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="H20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="I20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="J20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="K20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="L20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="M20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="N20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="O20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="P20" s="110"><f t="shared" ref="P20" si="4">P18-P7</f><v>0</v></c><c r="Q20" s="110"><f>Q18-Q7</f><v>0</v></c><c r="R20" s="110"><f>R18-R7</f><v>0</v></c><c r="S20" s="110"><f>S18-S7</f><v>0</v></c><c r="T20" s="110"><f>T18-T7</f><v>0</v></c><c r="U20" s="110"><f t="shared" ref="U20:W20" si="5">U18-U7</f><v>0</v></c><c r="V20" s="110"><f t="shared" si="5"/><v>0</v></c><c r="W20" s="110"><f t="shared" si="5"/><v>0</v></c></row><row r="21" spans="1:23" x14ac:dyDescent="0.3"><c r="A21" s="1"/><c r="B21" s="9"/><c r="C21" s="10"/><c r="D21" s="9"/><c r="E21" s="10"/><c r="F21" s="11"/><c r="G21" s="10"/><c r="H21" s="11"/><c r="I21" s="9"/><c r="J21" s="9"/><c r="K21" s="10"/><c r="L21" s="12"/><c r="M21" s="12"/><c r="N21" s="10"/><c r="O21" s="9"/><c r="P21" s="9"/><c r="Q21" s="10"/><c r="R21" s="12"/><c r="S21" s="12"/><c r="T21" s="9"/><c r="U21" s="9"/><c r="V21" s="9"/><c r="W21" s="9"/></row><row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35"><c r="D22" s="2"/><c r="M22" s="198" t="s"><v>48</v></c><c r="N22" s="198"/><c r="O22" s="198"/><c r="P22" s="198"/><c r="Q22" s="198"/><c r="R22" s="198"/><c r="S22" s="198"/><c r="T22" s="198"/><c r="U22" s="198"/></row><row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="D23" s="6"/><c r="J23"/><c r="L23"/><c r="M23" s="14" t="s"><v>13</v></c><c r="N23" s="207" t="inlineStr"><is><t xml:space="preserve">24-06-2026</t></is></c><c r="O23" s="208"/><c r="P23" s="208"/><c r="Q23" s="208"/><c r="R23" s="208"/><c r="S23" s="209"/><c r="T23" s="119" t="s"><v>38</v></c><c r="U23" s="106"><v>20</v></c><c r="W23" s="91" t="s"><v>44</v></c></row><row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="B24" s="2"/><c r="C24" s="18"/><c r="J24"/><c r="K24" s="15"/><c r="L24"/><c r="M24" s="16"/><c r="N24" s="210" t="s"><v>49</v></c><c r="O24" s="211"/><c r="P24" s="211"/><c r="Q24" s="211"/><c r="R24" s="211"/><c r="S24" s="212"/><c r="T24" s="108" t="s"><v>11</v></c><c r="U24" s="107"><v>2000000</v></c><c r="W24" s="118"><v>20</v></c></row><row r="25" spans="1:23" x14ac:dyDescent="0.3"><c r="B25" s="2"/><c r="C25" s="103"/><c r="D25" s="3" t="s"><v>15</v></c><c r="E25" s="4"/><c r="J25"/><c r="L25"/><c r="M25" s="215" t="s"><v>16</v></c><c r="N25" s="216"/><c r="O25" s="148"/><c r="P25" s="149"/><c r="Q25" s="145"><v>900000</v></c><c r="R25" s="146"/><c r="S25" s="147"/><c r="T25" s="213" t="s"><v>17</v></c><c r="U25" s="214"/><c r="V25" s="13"/><c r="W25" s="82" t="s"><v>45</v></c></row><row r="26" spans="1:23" x14ac:dyDescent="0.3"><c r="E26" s="4"/><c r="J26"/><c r="L26"/><c r="M26" s="79" t="s"><v>53</v></c><c r="N26" s="80"/><c r="O26" s="126"/><c r="P26" s="127"/><c r="Q26" s="188"><v>100000</v></c><c r="R26" s="189"/><c r="S26" s="190"/><c r="T26" s="124"/><c r="U26" s="125"/><c r="V26" s="13"/><c r="W26" s="82"/></row><row r="27" spans="1:23" x14ac:dyDescent="0.3"><c r="I27" s="109" t="str"><f>B1</f></c><c r="J27" s="136" t="str"><f>B9</f></c><c r="L27"/><c r="M27" s="79" t="s"><v>18</v></c><c r="N27" s="80"/><c r="O27" s="186"/><c r="P27" s="187"/><c r="Q27" s="188"><v>600000</v></c><c r="R27" s="189"/><c r="S27" s="190"/><c r="T27" s="205" t="s"><v>19</v></c><c r="U27" s="206"/><c r="V27" s="19"/><c r="W27" s="92"><v>2000000</v></c></row><row r="28" spans="1:23" x14ac:dyDescent="0.3"><c r="I28" s="109"><f>C1</f><v>0</v></c><c r="J28" s="136"><f>C9</f><v>0</v></c><c r="L28"/><c r="M28" s="203" t="s"><v>20</v></c><c r="N28" s="204"/><c r="O28" s="186"/><c r="P28" s="187"/><c r="Q28" s="188"/><c r="R28" s="189"/><c r="S28" s="190"/><c r="T28" s="201" t="s"><v>39</v></c><c r="U28" s="202"/><c r="V28" s="21"/><c r="W28" s="13"/></row><row r="29" spans="1:23" x14ac:dyDescent="0.3"><c r="I29" s="109"><f>D1</f><v>0</v></c><c r="J29" s="136"><f>D9</f><v>0</v></c><c r="K29" s="24"/><c r="L29"/><c r="M29" s="203" t="s"><v>21</v></c><c r="N29" s="204"/><c r="O29" s="186"/><c r="P29" s="187"/><c r="Q29" s="188"/><c r="R29" s="189"/><c r="S29" s="190"/><c r="T29" s="199" t="s"><v>40</v></c><c r="U29" s="200"/><c r="W29" s="93" t="str"><f>U23</f></c></row><row r="30" spans="1:23" x14ac:dyDescent="0.3"><c r="A30" s="1"/><c r="I30" s="109"><f>E1</f><v>0</v></c><c r="J30" s="136"><f>E9</f><v>0</v></c><c r="L30"/><c r="M30" s="203" t="s"><v>22</v></c><c r="N30" s="204"/><c r="O30" s="186"/><c r="P30" s="217"/><c r="Q30" s="188"/><c r="R30" s="189"/><c r="S30" s="190"/><c r="T30" s="218" t="s"><v>41</v></c><c r="U30" s="219"/><c r="V30" s="24"/><c r="W30" s="21" t="str"><f>Q34</f></c></row><row r="31" spans="1:23" x14ac:dyDescent="0.3"><c r="A31" s="1"/><c r="I31" s="109"><f>F1</f><v>0</v></c><c r="J31" s="136"><f>F9</f><v>0</v></c><c r="L31"/><c r="M31" s="203" t="s"><v>23</v></c><c r="N31" s="204"/><c r="O31" s="186"/><c r="P31" s="187"/><c r="Q31" s="188"/><c r="R31" s="189"/><c r="S31" s="190"/><c r="T31" s="28"/><c r="U31" s="26"/></row><row r="32" spans="1:23" x14ac:dyDescent="0.3"><c r="A32" s="1"/><c r="I32" s="109"><f>G1</f><v>0</v></c><c r="J32" s="136"><f>G9</f><v>0</v></c><c r="L32"/><c r="M32" s="203" t="s"><v>24</v></c><c r="N32" s="204"/><c r="O32" s="186"/><c r="P32" s="187"/><c r="Q32" s="188"/><c r="R32" s="189"/><c r="S32" s="190"/><c r="T32" s="28"/><c r="U32" s="26"/><c r="W32" s="82" t="s"><v>46</v></c></row><row r="33" spans="1:23" x14ac:dyDescent="0.3"><c r="A33" s="1"/><c r="I33" s="109"><f>H1</f><v>0</v></c><c r="J33" s="136"><f>H9</f><v>0</v></c><c r="L33"/><c r="M33" s="79" t="s"><v>25</v></c><c r="N33" s="81"/><c r="O33" s="186"/><c r="P33" s="187"/><c r="Q33" s="188"/><c r="R33" s="189"/><c r="S33" s="190"/><c r="T33" s="28"/><c r="U33" s="26"/><c r="W33" s="117" t="e"><f>W30-W27</f><v>#VALUE!</v></c></row><row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A34" s="1"/><c r="I34" s="109"><f>I1</f><v>0</v></c><c r="J34" s="136"><f>I9</f><v>0</v></c><c r="L34" s="8"/><c r="M34" s="191" t="s"><v>26</v></c><c r="N34" s="192"/><c r="O34" s="193"/><c r="P34" s="194"/><c r="Q34" s="188"><v>2000000</v></c><c r="R34" s="189"/><c r="S34" s="190"/><c r="T34" s="30"/><c r="U34" s="29"/><c r="V34" s="1"/><c r="W34" s="24"/></row><row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A35" s="1"/><c r="D35" s="31"/><c r="I35" s="41"><f>J1</f><v>0</v></c><c r="J35" s="27"><f>J9</f><v>0</v></c><c r="L35"/><c r="M35" s="195" t="s"><v>27</v></c><c r="N35" s="196"/><c r="O35" s="197"/><c r="P35" s="167" t="s"><v>28</v></c><c r="Q35" s="169"/><c r="R35" s="167" t="s"><v>29</v></c><c r="S35" s="169"/><c r="T35" s="167" t="s"><v>30</v></c><c r="U35" s="169"/><c r="V35" s="1"/><c r="W35" s="1"/></row><row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B36" s="9"/><c r="I36" s="41"><f>K1</f><v>0</v></c><c r="J36" s="27"><f>K9</f><v>0</v></c><c r="L36"/><c r="M36" s="33" t="s"><v>13</v></c><c r="N36" s="34" t="s"><v>31</v></c><c r="O36" s="35" t="s"><v>32</v></c><c r="P36" s="36" t="s"><v>33</v></c><c r="Q36" s="35" t="s"><v>32</v></c><c r="R36" s="36" t="s"><v>33</v></c><c r="S36" s="35" t="s"><v>32</v></c><c r="T36" s="36" t="s"><v>33</v></c><c r="U36" s="35" t="s"><v>32</v></c><c r="V36" s="1"/><c r="W36" s="1"/></row><row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A37" s="1"/><c r="I37" s="41"><f>L$1</f><v>0</v></c><c r="J37" s="27"><f>L9</f><v>0</v></c><c r="K37" s="24"/><c r="L37"/><c r="M37" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N37" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O37" s="39"><v>100000</v></c><c r="P37" s="151"/><c r="Q37" s="77"/><c r="R37" s="153"/><c r="S37" s="78"/><c r="T37" s="152"/><c r="U37" s="74"/><c r="V37" s="1"/><c r="W37" s="18" t="s"><v>14</v></c></row><row r="38"  x14ac:dyDescent="0.3" spans="1:23" x14ac:dyDescent="0.3"><c r="A38" s="1"/><c r="I38" s="41"><f>L$1</f><v>0</v></c><c r="J38" s="27"><f>L9</f><v>0</v></c><c r="K38" s="24"/><c r="L38"/><c r="M38" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N38" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O38" s="39"><v>100000</v></c><c r="P38" s="42"/><c r="Q38" s="72"/><c r="R38" s="44"/><c r="S38" s="77"/><c r="T38" s="42"/><c r="U38" s="72"/><c r="V38" s="1"/><c r="W38" s="18" t="s"><v>14</v></c></row><row r="39" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B39" s="20"/><c r="C39" s="32"/><c r="I39" s="41"><f t="shared" ref="I39:I46" si="6">L$1</f><v>0</v></c><c r="J39" s="27"><f t="shared" ref="J39:J46" si="7">L10</f><v>0</v></c><c r="L39" s="105"/><c r="M39" s="171" t="s"><v>42</v></c><c r="N39" s="179"/><c r="O39" s="150"><v>600000</v></c><c r="P39" s="152"/><c r="Q39" s="75"/><c r="R39" s="154"/><c r="S39" s="73"/><c r="T39" s="152"/><c r="U39" s="76"/><c r="V39" s="1"/><c r="W39" s="1"/></row><row r="40" spans="1:23" x14ac:dyDescent="0.3"><c r="O40" s="39"/><c r="N40" s="38"/><c r="M40" s="37"/><c r="B40" s="20"/><c r="C40" s="32"/><c r="I40" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J41" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K41" s="24"/><c r="L41" s="105"/><c r="M41" s="37"/><c r="N41" s="38"/><c r="O41" s="39"/><c r="P41" s="152"/><c r="Q41" s="68"/><c r="R41" s="154"/><c r="S41" s="73"/><c r="T41" s="152"/><c r="U41" s="68"/><c r="V41" s="1"/><c r="W41" s="1"/></row><row r="41" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"><c r="B42" s="20"/><c r="C42" s="32"/><c r="D42" s="44"/><c r="E42" s="43"/><c r="I42" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J42" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K42" s="24"/><c r="L42" s="105"/><c r="M42" s="37"/><c r="N42" s="38"/><c r="O42" s="39"/><c r="P42" s="152"/><c r="Q42" s="66"/><c r="R42" s="154"/><c r="S42" s="74"/><c r="T42" s="152"/><c r="U42" s="68"/><c r="V42" s="1"/><c r="W42" s="1"/></row><row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="B43" s="20"/><c r="C43" s="32"/><c r="D43" s="23"/><c r="E43" s="23"/><c r="I43" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J43" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K43" s="24"/><c r="L43" s="105"/><c r="M43" s="37"/><c r="N43" s="38"/><c r="O43" s="39"/><c r="P43" s="152"/><c r="Q43" s="66"/><c r="R43" s="154"/><c r="S43" s="74"/><c r="T43" s="152"/><c r="U43" s="68"/><c r="V43" s="1"/><c r="W43" s="1"/></row><row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6"><c r="B44" s="20"/><c r="C44" s="25"/><c r="D44" s="23"/><c r="E44" s="23"/><c r="F44" s="47"/><c r="I44" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J44" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L44" s="105"/><c r="M44" s="37"/><c r="N44" s="38"/><c r="O44" s="39"/><c r="P44" s="152"/><c r="Q44" s="66"/><c r="R44" s="154"/><c r="S44" s="73"/><c r="T44" s="152"/><c r="U44" s="68"/><c r="V44" s="1"/><c r="W44" s="1"/></row><row r="44" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6"><c r="A45" s="104"/><c r="B45" s="20"/><c r="C45" s="32"/><c r="D45" s="170"/><c r="E45" s="170"/><c r="F45" s="47"/><c r="G45" s="8"/><c r="I45" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J45" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K45" s="24"/><c r="L45" s="105"/><c r="M45" s="37"/><c r="N45" s="38"/><c r="O45" s="39"/><c r="P45" s="152"/><c r="Q45" s="66"/><c r="R45" s="152"/><c r="S45" s="67"/><c r="T45" s="152"/><c r="U45" s="68"/></row><row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A46" s="25"/><c r="B46" s="20"/><c r="C46" s="25"/><c r="D46" s="170"/><c r="E46" s="170"/><c r="F46" s="48"/><c r="H46" s="64"/><c r="I46" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J46" s="27"><f t="shared" si="7"/><v>0</v></c><c r="K46" s="24"/><c r="L46" s="105"/><c r="M46" s="37"/><c r="N46" s="38"/><c r="O46" s="39"/><c r="P46" s="152"/><c r="Q46" s="66"/><c r="R46" s="152"/><c r="S46" s="67"/><c r="T46" s="152"/><c r="U46" s="68"/></row><row r="46" spans="1:23" x14ac:dyDescent="0.3"><c r="A47" s="25"/><c r="B47" s="25"/><c r="C47" s="40"/><c r="D47" s="170"/><c r="E47" s="170"/><c r="F47" s="23"/><c r="H47" s="64"/><c r="I47" s="41"><f t="shared" si="6"/><v>0</v></c><c r="J47" s="27"><f t="shared" si="7"/><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="72"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="47" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="49"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"><f>SUM(J28:J46)</f><v>0</v></c><c r="L47" s="105"/><c r="M47" s="37"/><c r="N47" s="38"/><c r="O47" s="39"/><c r="P47" s="152"/><c r="Q47" s="66"/><c r="R47" s="152"/><c r="S47" s="67"/><c r="T47" s="152"/><c r="U47" s="68"/></row><row r="48" spans="1:23" x14ac:dyDescent="0.3"><c r="A48" s="20"/><c r="B48" s="20"/><c r="C48" s="40"/><c r="D48" s="170"/><c r="E48" s="170"/><c r="F48" s="17"/><c r="G48" s="1"/><c r="H48" s="64"/><c r="I48" s="13"/><c r="J48" s="53"/><c r="K48" s="24"/><c r="L48" s="105"/><c r="M48" s="37"/><c r="N48" s="38"/><c r="O48" s="39"/><c r="P48" s="152"/><c r="Q48" s="66"/><c r="R48" s="152"/><c r="S48" s="67"/><c r="T48" s="152"/><c r="U48" s="68"/></row><row r="49" spans="1:23" x14ac:dyDescent="0.3"><c r="A49" s="20"/><c r="B49" s="20"/><c r="C49" s="40"/><c r="D49" s="170"/><c r="E49" s="170"/><c r="F49" s="23"/><c r="G49" s="1"/><c r="H49" s="64"/><c r="I49" s="13"/><c r="J49" s="53"/><c r="L49" s="105"/><c r="M49" s="37"/><c r="N49" s="38"/><c r="O49" s="39"/><c r="P49" s="152"/><c r="Q49" s="66"/><c r="R49" s="152"/><c r="S49" s="67"/><c r="T49" s="154"/><c r="U49" s="68"/></row><row r="50" spans="1:21" x14ac:dyDescent="0.3"><c r="A50" s="20"/><c r="B50" s="20"/><c r="C50" s="40"/><c r="D50" s="170"/><c r="E50" s="170"/><c r="F50" s="23"/><c r="G50" s="1"/><c r="H50" s="46"/><c r="I50" s="13"/><c r="J50" s="53"/><c r="L50" s="105"/><c r="M50" s="37"/><c r="N50" s="38"/><c r="O50" s="39"/><c r="P50" s="152"/><c r="Q50" s="66"/><c r="R50" s="152"/><c r="S50" s="67"/><c r="T50" s="154"/><c r="U50" s="68"/></row><row r="51" spans="1:21" x14ac:dyDescent="0.3"><c r="A51" s="20"/><c r="B51" s="20"/><c r="C51" s="40"/><c r="D51" s="23"/><c r="E51" s="25"/><c r="F51" s="23"/><c r="G51" s="1"/><c r="H51" s="46"/><c r="I51" s="13"/><c r="J51" s="53"/><c r="L51" s="105"/><c r="M51" s="37"/><c r="N51" s="38"/><c r="O51" s="39"/><c r="P51" s="152"/><c r="Q51" s="66"/><c r="R51" s="152"/><c r="S51" s="67"/><c r="T51" s="154"/><c r="U51" s="68"/></row><row r="52" spans="1:21" x14ac:dyDescent="0.3"><c r="A52" s="20"/><c r="B52" s="20"/><c r="C52" s="40"/><c r="D52" s="185"/><c r="E52" s="185"/><c r="F52" s="23"/><c r="G52" s="1"/><c r="H52" s="46"/><c r="I52" s="13"/><c r="J52" s="53"/><c r="L52" s="105"/><c r="M52" s="37"/><c r="N52" s="38"/><c r="O52" s="39"/><c r="P52" s="151"/><c r="Q52" s="66"/><c r="R52" s="152"/><c r="S52" s="67"/><c r="T52" s="154"/><c r="U52" s="68"/></row><row r="53" spans="1:21" x14ac:dyDescent="0.3"><c r="A53" s="20"/><c r="B53" s="51"/><c r="C53" s="40"/><c r="D53" s="178"/><c r="E53" s="178"/><c r="F53" s="23"/><c r="G53" s="1"/><c r="H53" s="46"/><c r="I53" s="50"/><c r="J53" s="53"/><c r="L53" s="105"/><c r="M53" s="37"/><c r="N53" s="38"/><c r="O53" s="39"/><c r="P53" s="151"/><c r="Q53" s="66"/><c r="R53" s="152"/><c r="S53" s="67"/><c r="T53" s="154"/><c r="U53" s="68"/></row><row r="54" spans="1:21" x14ac:dyDescent="0.3"><c r="A54" s="25"/><c r="B54" s="51"/><c r="C54" s="40"/><c r="D54" s="166"/><c r="E54" s="166"/><c r="F54" s="23"/><c r="G54" s="1"/><c r="H54" s="46"/><c r="I54" s="50"/><c r="J54" s="53"/><c r="L54" s="18"/><c r="M54" s="37"/><c r="N54" s="38"/><c r="O54" s="39"/><c r="P54" s="152"/><c r="Q54" s="66"/><c r="R54" s="152"/><c r="S54" s="67"/><c r="T54" s="154"/><c r="U54" s="68"/></row><row r="55" spans="1:21" x14ac:dyDescent="0.3"><c r="A55" s="20"/><c r="B55" s="51"/><c r="C55" s="40"/><c r="D55" s="166"/><c r="E55" s="166"/><c r="F55" s="23"/><c r="G55" s="1"/><c r="H55" s="46"/><c r="I55" s="50"/><c r="J55" s="53"/><c r="L55" s="18"/><c r="M55" s="37"/><c r="N55" s="38"/><c r="O55" s="39"/><c r="P55" s="152"/><c r="Q55" s="66"/><c r="R55" s="152"/><c r="S55" s="67"/><c r="T55" s="154"/><c r="U55" s="68"/></row><row r="56" spans="1:21" x14ac:dyDescent="0.3"><c r="A56" s="20"/><c r="B56" s="51"/><c r="C56" s="40"/><c r="D56" s="22"/><c r="E56" s="22"/><c r="F56" s="23"/><c r="G56" s="1"/><c r="H56" s="46"/><c r="I56" s="50"/><c r="J56" s="53"/><c r="L56" s="18"/><c r="M56" s="37"/><c r="N56" s="38"/><c r="O56" s="39"/><c r="P56" s="152"/><c r="Q56" s="66"/><c r="R56" s="152"/><c r="S56" s="67"/><c r="T56" s="154"/><c r="U56" s="68"/></row><row r="57" spans="1:21" x14ac:dyDescent="0.3"><c r="A57" s="20"/><c r="B57"/><c r="C57" s="40"/><c r="D57" s="22"/><c r="E57" s="22"/><c r="F57" s="23"/><c r="G57" s="1"/><c r="H57" s="46"/><c r="I57" s="50"/><c r="J57" s="53"/><c r="L57" s="18"/><c r="M57" s="37"/><c r="N57" s="38"/><c r="O57" s="39"/><c r="P57" s="152"/><c r="Q57" s="66"/><c r="R57" s="152"/><c r="S57" s="67"/><c r="T57" s="154"/><c r="U57" s="68"/></row><row r="58" spans="1:21" x14ac:dyDescent="0.3"><c r="A58" s="20"/><c r="B58"/><c r="C58" s="40"/><c r="D58" s="22"/><c r="E58" s="22"/><c r="F58" s="23"/><c r="G58" s="1"/><c r="H58" s="46"/><c r="I58" s="50"/><c r="J58" s="53"/><c r="L58" s="18"/><c r="M58" s="37"/><c r="N58" s="38"/><c r="O58" s="39"/><c r="P58" s="152"/><c r="Q58" s="66"/><c r="R58" s="152"/><c r="S58" s="67"/><c r="T58" s="154"/><c r="U58" s="68"/></row><row r="59" spans="1:21" x14ac:dyDescent="0.3"><c r="A59" s="20"/><c r="B59"/><c r="C59" s="40"/><c r="D59" s="22"/><c r="E59" s="22"/><c r="F59" s="23"/><c r="G59" s="1"/><c r="H59" s="46"/><c r="I59" s="50"/><c r="J59" s="53"/><c r="L59" s="18"/><c r="M59" s="37"/><c r="N59" s="38"/><c r="O59" s="39"/><c r="P59" s="152"/><c r="Q59" s="66"/><c r="R59" s="152"/><c r="S59" s="67"/><c r="T59" s="154"/><c r="U59" s="68"/></row><row r="60" spans="1:21" x14ac:dyDescent="0.3"><c r="A60" s="20"/><c r="B60"/><c r="C60" s="40"/><c r="D60" s="22"/><c r="E60" s="22"/><c r="F60" s="23"/><c r="G60" s="1"/><c r="H60" s="46"/><c r="I60" s="50"/><c r="J60" s="53"/><c r="L60" s="18"/><c r="M60" s="37"/><c r="N60" s="38"/><c r="O60" s="39"/><c r="P60" s="152"/><c r="Q60" s="66"/><c r="R60" s="152"/><c r="S60" s="67"/><c r="T60" s="154"/><c r="U60" s="68"/></row><row r="61" spans="1:21" x14ac:dyDescent="0.3"><c r="A61" s="25"/><c r="B61"/><c r="C61" s="40"/><c r="D61" s="166"/><c r="E61" s="166"/><c r="F61" s="23"/><c r="G61" s="1"/><c r="H61" s="46"/><c r="I61" s="50"/><c r="J61" s="53"/><c r="L61" s="18"/><c r="M61" s="37"/><c r="N61" s="38"/><c r="O61" s="39"/><c r="P61" s="152"/><c r="Q61" s="66"/><c r="R61" s="152"/><c r="S61" s="67"/><c r="T61" s="154"/><c r="U61" s="68"/></row><row r="62" spans="1:21" x14ac:dyDescent="0.3"><c r="A62" s="25"/><c r="B62"/><c r="C62" s="40"/><c r="D62" s="22"/><c r="E62" s="22"/><c r="F62" s="23"/><c r="G62" s="1"/><c r="H62" s="46"/><c r="I62" s="50"/><c r="J62" s="53"/><c r="L62" s="18"/><c r="M62" s="37"/><c r="N62" s="38"/><c r="O62" s="39"/><c r="P62" s="152"/><c r="Q62" s="135"/><c r="R62" s="155"/><c r="S62" s="88"/><c r="T62" s="154"/><c r="U62" s="68"/></row><row r="63" spans="1:21" x14ac:dyDescent="0.3"><c r="A63" s="25"/><c r="B63"/><c r="C63" s="40"/><c r="D63" s="22"/><c r="E63" s="22"/><c r="F63" s="23"/><c r="G63" s="1"/><c r="H63" s="46"/><c r="I63" s="50"/><c r="J63" s="53"/><c r="L63" s="18"/><c r="M63" s="37"/><c r="N63" s="38"/><c r="O63" s="39"/><c r="P63" s="152"/><c r="Q63" s="135"/><c r="R63" s="155"/><c r="S63" s="88"/><c r="T63" s="154"/><c r="U63" s="68"/></row><row r="64" spans="1:21" x14ac:dyDescent="0.3"><c r="A64" s="25"/><c r="B64"/><c r="C64" s="40"/><c r="D64" s="22"/><c r="E64" s="22"/><c r="F64" s="23"/><c r="G64" s="1"/><c r="H64" s="46"/><c r="I64" s="50"/><c r="J64" s="53"/><c r="L64" s="18"/><c r="M64" s="37"/><c r="N64" s="38"/><c r="O64" s="39"/><c r="P64" s="152"/><c r="Q64" s="135"/><c r="R64" s="155"/><c r="S64" s="88"/><c r="T64" s="154"/><c r="U64" s="68"/></row><row r="65" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A65" s="25"/><c r="B65"/><c r="C65" s="40"/><c r="D65" s="166"/><c r="E65" s="166"/><c r="F65" s="23"/><c r="G65" s="1"/><c r="H65" s="46"/><c r="I65" s="50"/><c r="J65" s="53"/><c r="L65" s="18"/><c r="M65" s="37"/><c r="N65" s="38"/><c r="O65" s="39"/><c r="P65" s="152"/><c r="Q65" s="84"/><c r="R65" s="155"/><c r="S65" s="88"/><c r="T65" s="154"/><c r="U65" s="71"/></row><row r="66" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A66" s="25"/><c r="B66"/><c r="C66" s="40"/><c r="D66" s="166"/><c r="E66" s="166"/><c r="F66" s="20"/><c r="G66" s="1"/><c r="H66" s="46"/><c r="I66" s="50"/><c r="J66" s="53"/><c r="L66"/><c r="M66" s="171" t="s"><v>34</v></c><c r="N66" s="172"/><c r="O66" s="42"/><c r="P66" s="52" t="s"><v>11</v></c><c r="Q66" s="42"/><c r="R66" s="52" t="s"><v>11</v></c><c r="S66" s="42"/><c r="T66" s="52" t="s"><v>11</v></c><c r="U66" s="42"/></row><row r="67" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A67" s="25"/><c r="B67"/><c r="C67" s="90"/><c r="D67" s="166"/><c r="E67" s="166"/><c r="F67" s="23"/><c r="G67" s="1"/><c r="H67" s="46"/><c r="I67" s="50"/><c r="J67"/><c r="L67"/><c r="M67" s="54"/><c r="N67" s="55"/><c r="O67" s="70"/><c r="P67" s="23"/><c r="Q67" s="69"/><c r="R67" s="70"/><c r="S67" s="70"/><c r="T67" s="6"/></row><row r="68" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="A68" s="25"/><c r="B68"/><c r="C68" s="25"/><c r="D68" s="22"/><c r="E68" s="22"/><c r="F68" s="23"/><c r="G68" s="1"/><c r="H68" s="46"/><c r="I68" s="50"/><c r="J68"/><c r="L68"/><c r="M68" s="167" t="s"><v>47</v></c><c r="N68" s="168"/><c r="O68" s="169"/><c r="P68" s="181"/><c r="Q68" s="182"/><c r="R68" s="167" t="s"><v>37</v></c><c r="S68" s="168"/><c r="T68" s="183" t="str"><f>Q25</f></c><c r="U68" s="184"/></row><row r="69" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A69" s="25"/><c r="B69"/><c r="C69" s="25"/><c r="D69" s="166"/><c r="E69" s="166"/><c r="F69" s="63"/><c r="G69" s="1"/><c r="H69" s="46"/><c r="I69" s="50"/><c r="J69"/><c r="L69"/><c r="M69" s="56"/><c r="N69" s="83"/><c r="O69" s="83"/><c r="P69" s="57"/><c r="Q69" s="58"/><c r="R69" s="58"/><c r="S69" s="58"/><c r="T69" s="56"/><c r="U69" s="56"/></row><row r="70" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A70" s="25"/><c r="B70" s="90"/><c r="C70" s="25"/><c r="D70" s="166"/><c r="E70" s="166"/><c r="F70" s="63"/><c r="G70" s="1"/><c r="H70" s="46"/><c r="I70" s="50"/><c r="J70"/><c r="L70"/><c r="M70" s="171" t="s"><v>35</v></c><c r="N70" s="179"/><c r="O70" s="179"/><c r="P70" s="179"/><c r="Q70" s="179"/><c r="R70" s="179"/><c r="S70" s="179"/><c r="T70" s="179"/><c r="U70" s="180"/><c r="V70" s="51"/></row><row r="71" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A71" s="25"/><c r="B71" s="20"/><c r="C71" s="25"/><c r="D71" s="166"/><c r="E71" s="166"/><c r="F71" s="63"/><c r="G71" s="1"/><c r="H71" s="46"/><c r="I71" s="50"/><c r="J71"/><c r="L71" s="49" t="s"><v>59</v></c><c r="M71" s="130" t="s"><v>55</v></c><c r="N71" s="131"/><c r="O71" s="131"/><c r="P71" s="131" t="s"><v>56</v></c><c r="Q71" s="131"/><c r="R71" s="131"/><c r="S71" s="131"/><c r="T71" s="131" t="s"><v>57</v></c><c r="U71" s="132" t="s"><v>60</v></c><c r="V71" s="144" t="s"><v>58</v></c><c r="W71" s="144" t="s"><v>50</v></c></row><row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A72" s="25"/><c r="B72" s="115"/><c r="C72" s="25"/><c r="D72" s="166"/><c r="E72" s="166"/><c r="F72" s="63"/><c r="G72" s="1"/><c r="H72" s="46"/><c r="I72" s="50"/><c r="J72" s="23"/><c r="L72" s="0"/><c r="M72" s="59"/><c r="N72" s="60"/><c r="O72" s="143" t="s"><v>43</v></c><c r="P72" s="62"/><c r="Q72" s="61"/><c r="R72" s="177" t="inlineStr"><is><t xml:space="preserve">CREDITO</t></is></c><c r="S72" s="177"/><c r="T72" s="133"/><c r="U72" s="134"/><c r="V72" s="51"/></row><row r="73" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="B73" s="51"/><c r="C73" s="89"/><c r="D73" s="166"/><c r="E73" s="166"/><c r="F73" s="63"/><c r="I73" s="115"/><c r="L73"/><c r="M73" s="85"/><c r="N73" s="86"/><c r="O73" s="18"/><c r="P73" s="87"/><c r="Q73" s="56"/><c r="R73" s="175"/><c r="S73" s="175"/><c r="T73" s="65"/><c r="U73" s="95"/><c r="V73" s="51"/></row><row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="A74" s="49"/><c r="B74" s="89"/><c r="C74" s="89"/><c r="D74" s="23"/><c r="E74" s="25"/><c r="F74" s="63"/><c r="I74" s="115"/><c r="L74" s="45" t="inlineStr"><is><t xml:space="preserve">12345</t></is></c><c r="M74" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N74" s="86"/><c r="O74" s="18" t="s"><v>43</v></c><c r="P74" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q74" s="56"/><c r="R74" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S74" s="175"/><c r="T74" s="65"><v>150000</v></c><c r="U74" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V74" s="51"/></row><row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L75" s="45" t="inlineStr"><is><t xml:space="preserve">67890</t></is></c><c r="M75" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="N75" s="86"/><c r="O75" s="123"/><c r="P75" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="Q75" s="56"/><c r="R75" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="S75" s="175"/><c r="T75" s="65"><v>150000</v></c><c r="U75" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="V75" s="51"/></row><row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L76" s="45"/><c r="M76" s="137" t="s"><v>61</v></c><c r="N76" s="138"/><c r="O76" s="139"/><c r="P76" s="140"/><c r="Q76" s="141"/><c r="R76" s="176"/><c r="S76" s="176"/><c r="T76" s="173"/><c r="U76" s="174"/><c r="V76" s="51"/></row><row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L77" s="45"/><c r="M77" s="137" t="s"><v>62</v></c><c r="N77" s="138"/><c r="O77" s="139"/><c r="P77" s="140"/><c r="Q77" s="141"/><c r="R77" s="142"/><c r="S77" s="142"/><c r="T77" s="173"/><c r="U77" s="174"/><c r="V77" s="51"/></row><row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L78" s="45"/><c r="M78" s="94"/><c r="N78" s="64"/><c r="O78" s="123"/><c r="P78" s="87"/><c r="Q78" s="56"/><c r="R78" s="56"/><c r="S78" s="56"/><c r="T78" s="65"/><c r="U78" s="95"/><c r="V78" s="51"/></row><row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L79" s="45"/><c r="M79" s="101" t="s"><v>11</v></c><c r="N79" s="102"><f>SUM(N77:N78)</f><v>0</v></c><c r="O79" s="96"/><c r="P79" s="98"/><c r="Q79" s="97"/><c r="R79" s="97"/><c r="S79" s="97"/><c r="T79" s="99"/><c r="U79" s="100"/><c r="V79" s="51"/></row><row r="80" spans="1:23" x14ac:dyDescent="0.3"><c r="M80"/><c r="O80" s="5"/><c r="Q80"/><c r="S80"/><c r="T80" s="6"/><c r="V80" s="51"/></row><row r="81" spans="1:23" x14ac:dyDescent="0.3"><c r="O81"/><c r="V81" s="51"/></row><row r="82" spans="13:22" x14ac:dyDescent="0.3"><c r="M82" s="23"/><c r="N82" s="23"/><c r="O82" s="23"/><c r="P82" s="23"/><c r="Q82" s="23"/><c r="V82" s="51"/></row><row r="83" spans="13:22" x14ac:dyDescent="0.3"><c r="V83" s="51"/></row><row r="84" spans="13:22" x14ac:dyDescent="0.3"><c r="V84" s="51"/></row><row r="85" spans="13:22" x14ac:dyDescent="0.3"><c r="V85" s="51"/></row><row r="86" spans="13:22" x14ac:dyDescent="0.3"><c r="V86" s="51"/></row><row r="87" spans="13:22" x14ac:dyDescent="0.3"><c r="V87" s="51"/></row><row r="88" spans="13:22" x14ac:dyDescent="0.3"><c r="V88" s="51"/></row><row r="89" spans="13:22" x14ac:dyDescent="0.3"><c r="V89" s="51"/></row><row r="90" spans="13:22" x14ac:dyDescent="0.3"><c r="V90" s="51"/></row><row r="91" spans="13:22" x14ac:dyDescent="0.3"><c r="V91" s="51"/></row><row r="92" spans="13:22" x14ac:dyDescent="0.3"><c r="V92" s="51"/></row><row r="93" spans="13:22" x14ac:dyDescent="0.3"><c r="V93" s="51"/></row><row r="94" spans="13:22" x14ac:dyDescent="0.3"><c r="V94" s="51"/></row><row r="95" spans="13:22" x14ac:dyDescent="0.3"><c r="V95" s="51"/></row><row r="96" spans="13:22" x14ac:dyDescent="0.3"><c r="V96" s="51"/></row><row r="97" spans="13:22" x14ac:dyDescent="0.3"><c r="V97" s="51"/></row><row r="98" spans="22:22" x14ac:dyDescent="0.3"><c r="V98" s="51"/></row><row r="99" spans="22:22" x14ac:dyDescent="0.3"><c r="V99" s="51"/></row><row r="100" spans="22:22" x14ac:dyDescent="0.3"><c r="V100" s="51"/></row><row r="101" spans="22:22" x14ac:dyDescent="0.3"><c r="V101" s="51"/></row><row r="102" spans="22:22" x14ac:dyDescent="0.3"><c r="V102" s="51"/></row><row r="103" spans="22:22" x14ac:dyDescent="0.3"><c r="V103" s="51"/></row><row r="104" spans="22:22" x14ac:dyDescent="0.3"><c r="V104" s="51"/></row><row r="105" spans="22:22" x14ac:dyDescent="0.3"><c r="V105" s="51"/></row><row r="106" spans="22:22" x14ac:dyDescent="0.3"><c r="V106" s="51"/></row><row r="107" spans="22:22" x14ac:dyDescent="0.3"><c r="V107" s="51"/></row><row r="108" spans="22:22" x14ac:dyDescent="0.3"><c r="V108" s="51"/></row><row r="109" spans="22:22" x14ac:dyDescent="0.3"><c r="V109" s="51"/></row><row r="110" spans="22:22" x14ac:dyDescent="0.3"><c r="V110" s="51"/></row><row r="111" spans="22:22" x14ac:dyDescent="0.3"><c r="V111" s="51"/></row><row r="112" spans="22:22" x14ac:dyDescent="0.3"><c r="V112" s="51"/></row><row r="113" spans="22:22" x14ac:dyDescent="0.3"><c r="V113" s="51"/></row></sheetData><mergeCells count="70"><mergeCell ref="M25:N25"/><mergeCell ref="O30:P30"/><mergeCell ref="Q30:S30"/><mergeCell ref="T30:U30"/><mergeCell ref="Q32:S32"/><mergeCell ref="M31:N31"/><mergeCell ref="O31:P31"/><mergeCell ref="Q31:S31"/><mergeCell ref="M30:N30"/><mergeCell ref="M32:N32"/><mergeCell ref="O32:P32"/><mergeCell ref="M22:U22"/><mergeCell ref="Q26:S26"/><mergeCell ref="O29:P29"/><mergeCell ref="Q29:S29"/><mergeCell ref="T29:U29"/><mergeCell ref="T28:U28"/><mergeCell ref="O28:P28"/><mergeCell ref="Q28:S28"/><mergeCell ref="M28:N28"/><mergeCell ref="M29:N29"/><mergeCell ref="O27:P27"/><mergeCell ref="Q27:S27"/><mergeCell ref="T27:U27"/><mergeCell ref="N23:S23"/><mergeCell ref="N24:S24"/><mergeCell ref="T25:U25"/><mergeCell ref="D44:E44"/><mergeCell ref="R35:S35"/><mergeCell ref="T35:U35"/><mergeCell ref="O33:P33"/><mergeCell ref="Q33:S33"/><mergeCell ref="M34:N34"/><mergeCell ref="O34:P34"/><mergeCell ref="Q34:S34"/><mergeCell ref="P35:Q35"/><mergeCell ref="M35:O35"/><mergeCell ref="M39:N39"/><mergeCell ref="D72:E72"/><mergeCell ref="D73:E73"/><mergeCell ref="D53:E53"/><mergeCell ref="M70:U70"/><mergeCell ref="R68:S68"/><mergeCell ref="D69:E69"/><mergeCell ref="P68:Q68"/><mergeCell ref="T68:U68"/><mergeCell ref="D61:E61"/><mergeCell ref="D67:E67"/><mergeCell ref="D54:E54"/><mergeCell ref="D66:E66"/><mergeCell ref="D55:E55"/><mergeCell ref="D65:E65"/><mergeCell ref="T77:U77"/><mergeCell ref="R75:S75"/><mergeCell ref="R76:S76"/><mergeCell ref="R72:S72"/><mergeCell ref="R74:S74"/><mergeCell ref="R73:S73"/><mergeCell ref="T76:U76"/><mergeCell ref="D71:E71"/><mergeCell ref="D70:E70"/><mergeCell ref="M68:O68"/><mergeCell ref="D45:E45"/><mergeCell ref="D47:E47"/><mergeCell ref="M66:N66"/><mergeCell ref="D49:E49"/><mergeCell ref="D50:E50"/><mergeCell ref="D48:E48"/><mergeCell ref="D46:E46"/><mergeCell ref="D52:E52"/></mergeCells><pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/><pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/><drawing r:id="rId2"/></worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac xr xr2 xr3" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{00000000-0001-0000-0000-000000000000}"><dimension ref="A1:W117"/><sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/><cols><col min="1" max="1" width="17.33203125" customWidth="1"/><col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/><col min="3" max="3" width="12.6640625" customWidth="1"/><col min="4" max="4" width="12.6640625" style="3" customWidth="1"/><col min="5" max="5" width="12.6640625" customWidth="1"/><col min="6" max="6" width="12.6640625" style="3" customWidth="1"/><col min="7" max="9" width="12.6640625" customWidth="1"/><col min="10" max="10" width="12.6640625" style="3" customWidth="1"/><col min="11" max="11" width="12.6640625" customWidth="1"/><col min="12" max="12" width="12.6640625" style="3" customWidth="1"/><col min="13" max="13" width="11.5546875" style="3" customWidth="1"/><col min="14" max="14" width="11" bestFit="1" customWidth="1"/><col min="15" max="15" width="11.6640625" style="4" customWidth="1"/><col min="16" max="19" width="11.6640625" style="3" customWidth="1"/><col min="20" max="20" width="13.88671875" customWidth="1"/><col min="21" max="21" width="14" customWidth="1"/><col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/><col min="23" max="23" width="16" customWidth="1"/></cols><sheetData><row r="1" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A1" s="7" t="s"><v>50</v></c><c r="B1" s="112" t="inlineStr"><is><t xml:space="preserve">ANA</t></is></c><c r="C1" s="120" t="inlineStr"><is><t xml:space="preserve">BOB</t></is></c><c r="D1" s="120"/><c r="E1" s="112"/><c r="F1" s="120"/><c r="G1" s="120"/><c r="H1" s="112"/><c r="I1" s="112"/><c r="J1" s="120"/><c r="K1" s="120"/><c r="L1" s="112"/><c r="M1" s="112"/><c r="N1" s="112"/><c r="O1" s="112"/><c r="P1" s="112"/><c r="Q1" s="112"/><c r="R1" s="121"/><c r="S1" s="120"/><c r="T1" s="120"/><c r="U1" s="7"/><c r="V1" s="7"/><c r="W1" s="114"/></row><row r="2" spans="1:23" s="8" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"><c r="A2" s="7" t="s"><v>51</v></c><c r="B2" s="112" t="inlineStr"><is><t xml:space="preserve">AUX ANA</t></is></c><c r="C2" s="120" t="inlineStr"><is><t xml:space="preserve">AUX BOB</t></is></c><c r="D2" s="120"/><c r="E2" s="112"/><c r="F2" s="120"/><c r="G2" s="128"/><c r="H2" s="112"/><c r="I2" s="112"/><c r="J2" s="120"/><c r="K2" s="120"/><c r="L2" s="112"/><c r="M2" s="112"/><c r="N2" s="112"/><c r="O2" s="112"/><c r="P2" s="112"/><c r="Q2" s="112"/><c r="R2" s="121"/><c r="S2" s="120"/><c r="T2" s="120"/><c r="U2" s="7"/><c r="V2" s="7"/><c r="W2" s="114"/></row><row r="3" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A3" s="122" t="s"><v>35</v></c><c r="B3" s="120"/><c r="C3" s="120"/><c r="D3" s="120"/><c r="E3" s="120"/><c r="F3" s="120"/><c r="G3" s="120"/><c r="H3" s="120"/><c r="I3" s="120"/><c r="J3" s="120"/><c r="K3" s="120"/><c r="L3" s="120"/><c r="M3" s="120"/><c r="N3" s="120"/><c r="O3" s="120"/><c r="P3" s="120"/><c r="Q3" s="120"/><c r="R3" s="120"/><c r="S3" s="120"/><c r="T3" s="120"/><c r="U3" s="110"/><c r="V3" s="163"/><c r="W3" s="116"/></row><row r="4" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A4" s="122" t="s"><v>52</v></c><c r="B4" s="120"/><c r="C4" s="120"/><c r="D4" s="120"/><c r="E4" s="120"/><c r="F4" s="120"/><c r="G4" s="120"/><c r="H4" s="120"/><c r="I4" s="120"/><c r="J4" s="120"/><c r="K4" s="120"/><c r="L4" s="120"/><c r="M4" s="120"/><c r="N4" s="120"/><c r="O4" s="120"/><c r="P4" s="120"/><c r="Q4" s="120"/><c r="R4" s="120"/><c r="S4" s="120"/><c r="T4" s="120"/><c r="U4" s="110"/><c r="V4" s="163"/><c r="W4" s="116"/></row><row r="5" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A5" s="122" t="s"><v>0</v></c><c r="B5" s="129" t="inlineStr"><is><t xml:space="preserve">111</t></is></c><c r="C5" s="129" t="inlineStr"><is><t xml:space="preserve">222</t></is></c><c r="D5" s="129"/><c r="E5" s="129"/><c r="F5" s="129"/><c r="G5" s="129"/><c r="H5" s="129"/><c r="I5" s="129"/><c r="J5" s="129"/><c r="K5" s="129"/><c r="L5" s="129"/><c r="M5" s="129"/><c r="N5" s="129"/><c r="O5" s="129"/><c r="P5" s="129"/><c r="Q5" s="129"/><c r="R5" s="120"/><c r="S5" s="120"/><c r="T5" s="120"/><c r="U5" s="111"/><c r="V5" s="111"/><c r="W5" s="111"/></row><row r="6" spans="1:23" s="45" customFormat="1" x14ac:dyDescent="0.3"><c r="A6" s="122" t="s"><v>1</v></c><c r="B6" s="120"><v>10</v></c><c r="C6" s="120"><v>10</v></c><c r="D6" s="120"/><c r="E6" s="120"/><c r="F6" s="120"/><c r="G6" s="120"/><c r="H6" s="120"/><c r="I6" s="120"/><c r="J6" s="120"/><c r="K6" s="120"/><c r="L6" s="120"/><c r="M6" s="111"/><c r="N6" s="111"/><c r="O6" s="111"/><c r="P6" s="111"/><c r="Q6" s="111"/><c r="R6" s="120"/><c r="S6" s="120"/><c r="T6" s="120"/><c r="U6" s="111"/><c r="V6" s="111"/><c r="W6" s="111"/></row><row r="7" spans="1:23" s="45" customFormat="1" ht="72" x14ac:dyDescent="0.3"><c r="A7" s="122" t="s"><v>2</v></c><c r="B7" s="164"><v>1000000</v></c><c r="C7" s="164"><v>1000000</v></c><c r="D7" s="164"/><c r="E7" s="164"/><c r="F7" s="164"/><c r="G7" s="164"/><c r="H7" s="164"/><c r="I7" s="164"/><c r="J7" s="164"/><c r="K7" s="164"/><c r="L7" s="164"/><c r="M7" s="164"/><c r="N7" s="164"/><c r="O7" s="164"/><c r="P7" s="164"/><c r="Q7" s="164"/><c r="R7" s="156"/><c r="S7" s="156"/><c r="T7" s="156"/><c r="U7" s="157"/><c r="V7" s="157"/><c r="W7" s="157"/></row><row r="8" spans="1:23" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A8" s="112"/><c r="B8" s="157"/><c r="C8" s="111"/><c r="D8" s="157"/><c r="E8" s="111"/><c r="F8" s="110"/><c r="G8" s="111"/><c r="H8" s="157"/><c r="I8" s="111"/><c r="J8" s="157"/><c r="K8" s="111"/><c r="L8" s="110"/><c r="M8" s="111"/><c r="N8" s="110"/><c r="O8" s="111"/><c r="P8" s="158"/><c r="Q8" s="111"/><c r="R8" s="158"/><c r="S8" s="111"/><c r="T8" s="158"/><c r="U8" s="111"/><c r="V8" s="110"/><c r="W8" s="111"/></row><row r="9" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A9" s="113" t="s"><v>3</v></c><c r="B9" s="165"><v>450000</v></c><c r="C9" s="165"><v>450000</v></c><c r="D9" s="165"/><c r="E9" s="157"/><c r="F9" s="110"/><c r="G9" s="157"/><c r="H9" s="110"/><c r="I9" s="157"/><c r="J9" s="110"/><c r="K9" s="157"/><c r="L9" s="110"/><c r="M9" s="157"/><c r="N9" s="110"/><c r="O9" s="157"/><c r="P9" s="158"/><c r="Q9" s="157"/><c r="R9" s="158"/><c r="S9" s="159"/><c r="T9" s="159"/><c r="U9" s="157"/><c r="V9" s="110"/><c r="W9" s="157"/></row><row r="10" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A10" s="113" t="s"><v>54</v></c><c r="B10" s="165"><v>50000</v></c><c r="C10" s="165"><v>50000</v></c><c r="D10" s="165"/><c r="E10" s="157"/><c r="F10" s="110"/><c r="G10" s="157"/><c r="H10" s="110"/><c r="I10" s="157"/><c r="J10" s="110"/><c r="K10" s="157"/><c r="L10" s="110"/><c r="M10" s="157"/><c r="N10" s="110"/><c r="O10" s="157"/><c r="P10" s="158"/><c r="Q10" s="157"/><c r="R10" s="158"/><c r="S10" s="159"/><c r="T10" s="159"/><c r="U10" s="157"/><c r="V10" s="110"/><c r="W10" s="157"/></row><row r="11" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A11" s="113" t="s"><v>4</v></c><c r="B11" s="165"><v>300000</v></c><c r="C11" s="165"><v>300000</v></c><c r="D11" s="165"/><c r="E11" s="157"/><c r="F11" s="110"/><c r="G11" s="157"/><c r="H11" s="110"/><c r="I11" s="157"/><c r="J11" s="110"/><c r="K11" s="157"/><c r="L11" s="110"/><c r="M11" s="157"/><c r="N11" s="110"/><c r="O11" s="157"/><c r="P11" s="158"/><c r="Q11" s="157"/><c r="R11" s="158"/><c r="S11" s="159"/><c r="T11" s="159"/><c r="U11" s="157"/><c r="V11" s="110"/><c r="W11" s="157"/></row><row r="12" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A12" s="113" t="s"><v>5</v></c><c r="B12" s="165"/><c r="C12" s="165"/><c r="D12" s="165"/><c r="E12" s="157"/><c r="F12" s="110"/><c r="G12" s="157"/><c r="H12" s="110"/><c r="I12" s="157"/><c r="J12" s="110"/><c r="K12" s="157"/><c r="L12" s="110"/><c r="M12" s="157"/><c r="N12" s="110"/><c r="O12" s="157"/><c r="P12" s="158"/><c r="Q12" s="157"/><c r="R12" s="158"/><c r="S12" s="159"/><c r="T12" s="159"/><c r="U12" s="157"/><c r="V12" s="110"/><c r="W12" s="157"/></row><row r="13" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A13" s="113" t="s"><v>6</v></c><c r="B13" s="165"/><c r="C13" s="165"/><c r="D13" s="165"/><c r="E13" s="157"/><c r="F13" s="110"/><c r="G13" s="157"/><c r="H13" s="110"/><c r="I13" s="157"/><c r="J13" s="110"/><c r="K13" s="157"/><c r="L13" s="110"/><c r="M13" s="157"/><c r="N13" s="110"/><c r="O13" s="157"/><c r="P13" s="158"/><c r="Q13" s="157"/><c r="R13" s="158"/><c r="S13" s="159"/><c r="T13" s="159"/><c r="U13" s="157"/><c r="V13" s="110"/><c r="W13" s="157"/></row><row r="14" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A14" s="113" t="s"><v>7</v></c><c r="B14" s="165"/><c r="C14" s="165"/><c r="D14" s="165"/><c r="E14" s="157"/><c r="F14" s="110"/><c r="G14" s="157"/><c r="H14" s="110"/><c r="I14" s="157"/><c r="J14" s="110"/><c r="K14" s="157"/><c r="L14" s="110"/><c r="M14" s="157"/><c r="N14" s="110"/><c r="O14" s="157"/><c r="P14" s="158"/><c r="Q14" s="157"/><c r="R14" s="158"/><c r="S14" s="159"/><c r="T14" s="159"/><c r="U14" s="157"/><c r="V14" s="110"/><c r="W14" s="157"/></row><row r="15" spans="1:23" s="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"><c r="A15" s="113" t="s"><v>8</v></c><c r="B15" s="165"/><c r="C15" s="165"/><c r="D15" s="165"/><c r="E15" s="157"/><c r="F15" s="110"/><c r="G15" s="157"/><c r="H15" s="110"/><c r="I15" s="157"/><c r="J15" s="110"/><c r="K15" s="157"/><c r="L15" s="110"/><c r="M15" s="157"/><c r="N15" s="110"/><c r="O15" s="157"/><c r="P15" s="158"/><c r="Q15" s="157"/><c r="R15" s="158"/><c r="S15" s="159"/><c r="T15" s="159"/><c r="U15" s="157"/><c r="V15" s="110"/><c r="W15" s="157"/></row><row r="16" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A16" s="113" t="s"><v>9</v></c><c r="B16" s="165"/><c r="C16" s="165"/><c r="D16" s="165"/><c r="E16" s="157"/><c r="F16" s="110"/><c r="G16" s="157"/><c r="H16" s="110"/><c r="I16" s="160"/><c r="J16" s="110"/><c r="K16" s="160"/><c r="L16" s="110"/><c r="M16" s="157"/><c r="N16" s="110"/><c r="O16" s="157"/><c r="P16" s="158"/><c r="Q16" s="157"/><c r="R16" s="158"/><c r="S16" s="159"/><c r="T16" s="159"/><c r="U16" s="157"/><c r="V16" s="110"/><c r="W16" s="157"/></row><row r="17" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A17" s="113" t="s"><v>10</v></c><c r="B17" s="165"/><c r="C17" s="165"/><c r="D17" s="165"/><c r="E17" s="157"/><c r="F17" s="110"/><c r="G17" s="157"/><c r="H17" s="110"/><c r="I17" s="160"/><c r="J17" s="110"/><c r="K17" s="157"/><c r="L17" s="110"/><c r="M17" s="157"/><c r="N17" s="110"/><c r="O17" s="157"/><c r="P17" s="158"/><c r="Q17" s="157"/><c r="R17" s="158"/><c r="S17" s="159"/><c r="T17" s="159"/><c r="U17" s="157"/><c r="V17" s="110"/><c r="W17" s="157"/></row><row r="18" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A18" s="113" t="s"><v>11</v></c><c r="B18" s="110"><f>SUM(B9:B17)</f><v>0</v></c><c r="C18" s="110"><f t="shared" ref="C18:O18" si="0">SUM(C9:C17)</f><v>0</v></c><c r="D18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="E18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="F18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="G18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="H18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="I18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="J18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="K18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="L18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="M18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="N18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="O18" s="110"><f t="shared" si="0"/><v>0</v></c><c r="P18" s="110"><f t="shared" ref="P18" si="1">SUM(P9:P17)</f><v>0</v></c><c r="Q18" s="110"><f>SUM(Q9:Q17)</f><v>0</v></c><c r="R18" s="110"><f>SUM(R9:R17)</f><v>0</v></c><c r="S18" s="116"><f>SUM(S9:S17)</f><v>0</v></c><c r="T18" s="116"><f>SUM(T9:T17)</f><v>0</v></c><c r="U18" s="110"><f t="shared" ref="U18:W18" si="2">SUM(U9:U17)</f><v>0</v></c><c r="V18" s="110"><f t="shared" si="2"/><v>0</v></c><c r="W18" s="110"><f t="shared" si="2"/><v>0</v></c></row><row r="19" spans="1:23" s="161" customFormat="1" x14ac:dyDescent="0.3"><c r="A19" s="113"/><c r="B19" s="110"/><c r="C19" s="110"/><c r="D19" s="110"/><c r="E19" s="110"/><c r="F19" s="157"/><c r="G19" s="110"/><c r="H19" s="110"/><c r="I19" s="110"/><c r="J19" s="110"/><c r="K19" s="110"/><c r="L19" s="110"/><c r="M19" s="110"/><c r="N19" s="110"/><c r="O19" s="110"/><c r="P19" s="110"/><c r="Q19" s="110"/><c r="R19" s="110"/><c r="S19" s="116"/><c r="T19" s="116"/><c r="U19" s="110"/><c r="V19" s="110"/><c r="W19" s="110"/></row><row r="20" spans="1:23" s="162" customFormat="1" x14ac:dyDescent="0.3"><c r="A20" s="113" t="s"><v>12</v></c><c r="B20" s="110" t="e"><f t="shared" ref="B20:O20" si="3">B18-B7</f><v>#VALUE!</v></c><c r="C20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="D20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="E20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="F20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="G20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="H20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="I20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="J20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="K20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="L20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="M20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="N20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="O20" s="110"><f t="shared" si="3"/><v>0</v></c><c r="P20" s="110"><f t="shared" ref="P20" si="4">P18-P7</f><v>0</v></c><c r="Q20" s="110"><f>Q18-Q7</f><v>0</v></c><c r="R20" s="110"><f>R18-R7</f><v>0</v></c><c r="S20" s="110"><f>S18-S7</f><v>0</v></c><c r="T20" s="110"><f>T18-T7</f><v>0</v></c><c r="U20" s="110"><f t="shared" ref="U20:W20" si="5">U18-U7</f><v>0</v></c><c r="V20" s="110"><f t="shared" si="5"/><v>0</v></c><c r="W20" s="110"><f t="shared" si="5"/><v>0</v></c></row><row r="21" spans="1:23" x14ac:dyDescent="0.3"><c r="A21" s="1"/><c r="B21" s="9"/><c r="C21" s="10"/><c r="D21" s="9"/><c r="E21" s="10"/><c r="F21" s="11"/><c r="G21" s="10"/><c r="H21" s="11"/><c r="I21" s="9"/><c r="J21" s="9"/><c r="K21" s="10"/><c r="L21" s="12"/><c r="M21" s="12"/><c r="N21" s="10"/><c r="O21" s="9"/><c r="P21" s="9"/><c r="Q21" s="10"/><c r="R21" s="12"/><c r="S21" s="12"/><c r="T21" s="9"/><c r="U21" s="9"/><c r="V21" s="9"/><c r="W21" s="9"/></row><row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35"><c r="D22" s="2"/><c r="M22" s="198" t="s"><v>48</v></c><c r="N22" s="198"/><c r="O22" s="198"/><c r="P22" s="198"/><c r="Q22" s="198"/><c r="R22" s="198"/><c r="S22" s="198"/><c r="T22" s="198"/><c r="U22" s="198"/></row><row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="D23" s="6"/><c r="J23"/><c r="L23"/><c r="M23" s="14" t="s"><v>13</v></c><c r="N23" s="207" t="inlineStr"><is><t xml:space="preserve">24-06-2026</t></is></c><c r="O23" s="208"/><c r="P23" s="208"/><c r="Q23" s="208"/><c r="R23" s="208"/><c r="S23" s="209"/><c r="T23" s="119" t="s"><v>38</v></c><c r="U23" s="106"><v>20</v></c><c r="W23" s="91" t="s"><v>44</v></c></row><row r="24" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="B24" s="2"/><c r="C24" s="18"/><c r="J24"/><c r="K24" s="15"/><c r="L24"/><c r="M24" s="16"/><c r="N24" s="210" t="s"><v>49</v></c><c r="O24" s="211"/><c r="P24" s="211"/><c r="Q24" s="211"/><c r="R24" s="211"/><c r="S24" s="212"/><c r="T24" s="108" t="s"><v>11</v></c><c r="U24" s="107"><v>2000000</v></c><c r="W24" s="118"><v>20</v></c></row><row r="25" spans="1:23" x14ac:dyDescent="0.3"><c r="B25" s="2"/><c r="C25" s="103"/><c r="D25" s="3" t="s"><v>15</v></c><c r="E25" s="4"/><c r="J25"/><c r="L25"/><c r="M25" s="215" t="s"><v>16</v></c><c r="N25" s="216"/><c r="O25" s="148"/><c r="P25" s="149"/><c r="Q25" s="145"><v>900000</v></c><c r="R25" s="146"/><c r="S25" s="147"/><c r="T25" s="213" t="s"><v>17</v></c><c r="U25" s="214"/><c r="V25" s="13"/><c r="W25" s="82" t="s"><v>45</v></c></row><row r="26" spans="1:23" x14ac:dyDescent="0.3"><c r="E26" s="4"/><c r="J26"/><c r="L26"/><c r="M26" s="79" t="s"><v>53</v></c><c r="N26" s="80"/><c r="O26" s="126"/><c r="P26" s="127"/><c r="Q26" s="188"><v>100000</v></c><c r="R26" s="189"/><c r="S26" s="190"/><c r="T26" s="124"/><c r="U26" s="125"/><c r="V26" s="13"/><c r="W26" s="82"/></row><row r="27" spans="1:23" x14ac:dyDescent="0.3"><c r="I27" s="109" t="str"><f>B1</f></c><c r="J27" s="136" t="str"><f>B9</f></c><c r="L27"/><c r="M27" s="79" t="s"><v>18</v></c><c r="N27" s="80"/><c r="O27" s="186"/><c r="P27" s="187"/><c r="Q27" s="188"><v>600000</v></c><c r="R27" s="189"/><c r="S27" s="190"/><c r="T27" s="205" t="s"><v>19</v></c><c r="U27" s="206"/><c r="V27" s="19"/><c r="W27" s="92"><v>2000000</v></c></row><row r="28" spans="1:23" x14ac:dyDescent="0.3"><c r="I28" s="109"><f>C1</f><v>0</v></c><c r="J28" s="136"><f>C9</f><v>0</v></c><c r="L28"/><c r="M28" s="203" t="s"><v>20</v></c><c r="N28" s="204"/><c r="O28" s="186"/><c r="P28" s="187"/><c r="Q28" s="188"/><c r="R28" s="189"/><c r="S28" s="190"/><c r="T28" s="201" t="s"><v>39</v></c><c r="U28" s="202"/><c r="V28" s="21"/><c r="W28" s="13"/></row><row r="29" spans="1:23" x14ac:dyDescent="0.3"><c r="I29" s="109"><f>D1</f><v>0</v></c><c r="J29" s="136"><f>D9</f><v>0</v></c><c r="K29" s="24"/><c r="L29"/><c r="M29" s="203" t="s"><v>21</v></c><c r="N29" s="204"/><c r="O29" s="186"/><c r="P29" s="187"/><c r="Q29" s="188"/><c r="R29" s="189"/><c r="S29" s="190"/><c r="T29" s="199" t="s"><v>40</v></c><c r="U29" s="200"/><c r="W29" s="93" t="str"><f>U23</f></c></row><row r="30" spans="1:23" x14ac:dyDescent="0.3"><c r="A30" s="1"/><c r="I30" s="109"><f>E1</f><v>0</v></c><c r="J30" s="136"><f>E9</f><v>0</v></c><c r="L30"/><c r="M30" s="203" t="s"><v>22</v></c><c r="N30" s="204"/><c r="O30" s="186"/><c r="P30" s="217"/><c r="Q30" s="188"/><c r="R30" s="189"/><c r="S30" s="190"/><c r="T30" s="218" t="s"><v>41</v></c><c r="U30" s="219"/><c r="V30" s="24"/><c r="W30" s="21" t="str"><f>Q34</f></c></row><row r="31" spans="1:23" x14ac:dyDescent="0.3"><c r="A31" s="1"/><c r="I31" s="109"><f>F1</f><v>0</v></c><c r="J31" s="136"><f>F9</f><v>0</v></c><c r="L31"/><c r="M31" s="203" t="s"><v>23</v></c><c r="N31" s="204"/><c r="O31" s="186"/><c r="P31" s="187"/><c r="Q31" s="188"/><c r="R31" s="189"/><c r="S31" s="190"/><c r="T31" s="28"/><c r="U31" s="26"/></row><row r="32" spans="1:23" x14ac:dyDescent="0.3"><c r="A32" s="1"/><c r="I32" s="109"><f>G1</f><v>0</v></c><c r="J32" s="136"><f>G9</f><v>0</v></c><c r="L32"/><c r="M32" s="203" t="s"><v>24</v></c><c r="N32" s="204"/><c r="O32" s="186"/><c r="P32" s="187"/><c r="Q32" s="188"/><c r="R32" s="189"/><c r="S32" s="190"/><c r="T32" s="28"/><c r="U32" s="26"/><c r="W32" s="82" t="s"><v>46</v></c></row><row r="33" spans="1:23" x14ac:dyDescent="0.3"><c r="A33" s="1"/><c r="I33" s="109"><f>H1</f><v>0</v></c><c r="J33" s="136"><f>H9</f><v>0</v></c><c r="L33"/><c r="M33" s="79" t="s"><v>25</v></c><c r="N33" s="81"/><c r="O33" s="186"/><c r="P33" s="187"/><c r="Q33" s="188"/><c r="R33" s="189"/><c r="S33" s="190"/><c r="T33" s="28"/><c r="U33" s="26"/><c r="W33" s="117" t="e"><f>W30-W27</f><v>#VALUE!</v></c></row><row r="34" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A34" s="1"/><c r="I34" s="109"><f>I1</f><v>0</v></c><c r="J34" s="136"><f>I9</f><v>0</v></c><c r="L34" s="8"/><c r="M34" s="191" t="s"><v>26</v></c><c r="N34" s="192"/><c r="O34" s="193"/><c r="P34" s="194"/><c r="Q34" s="188"><v>2000000</v></c><c r="R34" s="189"/><c r="S34" s="190"/><c r="T34" s="30"/><c r="U34" s="29"/><c r="V34" s="1"/><c r="W34" s="24"/></row><row r="35" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A35" s="1"/><c r="D35" s="31"/><c r="I35" s="41"><f>J1</f><v>0</v></c><c r="J35" s="27"><f>J9</f><v>0</v></c><c r="L35"/><c r="M35" s="195" t="s"><v>27</v></c><c r="N35" s="196"/><c r="O35" s="197"/><c r="P35" s="167" t="s"><v>28</v></c><c r="Q35" s="169"/><c r="R35" s="167" t="s"><v>29</v></c><c r="S35" s="169"/><c r="T35" s="167" t="s"><v>30</v></c><c r="U35" s="169"/><c r="V35" s="1"/><c r="W35" s="1"/></row><row r="36" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B36" s="9"/><c r="I36" s="41"><f>K1</f><v>0</v></c><c r="J36" s="27"><f>K9</f><v>0</v></c><c r="L36"/><c r="M36" s="33" t="s"><v>13</v></c><c r="N36" s="34" t="s"><v>31</v></c><c r="O36" s="35" t="s"><v>32</v></c><c r="P36" s="36" t="s"><v>33</v></c><c r="Q36" s="35" t="s"><v>32</v></c><c r="R36" s="36" t="s"><v>33</v></c><c r="S36" s="35" t="s"><v>32</v></c><c r="T36" s="36" t="s"><v>33</v></c><c r="U36" s="35" t="s"><v>32</v></c><c r="V36" s="1"/><c r="W36" s="1"/></row><row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="M37" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N37" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O37" s="39"><v>100000</v></c><c r="P37" s="151"/><c r="Q37" s="77"/><c r="R37" s="153"/><c r="S37" s="78"/><c r="T37" s="152"/><c r="U37" s="74"/><c r="A37" s="1"/><c r="I37" s="41"><f>L<row r="37" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"></f><v>0</v></c><c r="J37" s="27"><f>L9</f><v>0</v></c><c r="K37" s="24"/><c r="L37"/><c r="V37" s="1"/><c r="W37" s="18" t="s"><v>14</v></c></row><row r="38"     spans="1:23" x14ac:dyDescent="0.3"><c r="M38" s="37" t="inlineStr"><is><t xml:space="preserve">02-01-2026</t></is></c><c r="N38" s="38" t="inlineStr"><is><t xml:space="preserve">BCI</t></is></c><c r="O38" s="39"><v>200000</v></c><c r="P38" s="152"/><c r="Q38" s="66"/><c r="R38" s="154"/><c r="S38" s="74"/><c r="T38" s="152"/><c r="U38" s="68"/><c r="A38" s="1"/><c r="I38" s="41"/><c r="J38" s="27"/><c r="K38" s="24"/><c r="L38" s="105"/><c r="V38" s="1"/><c r="W38" s="1" t="s"><v>14</v></c></row><row r="39"     spans="1:23" x14ac:dyDescent="0.3"><c r="M39" s="37" t="inlineStr"><is><t xml:space="preserve">01-01-2026</t></is></c><c r="N39" s="38" t="inlineStr"><is><t xml:space="preserve">SANTANDER</t></is></c><c r="O39" s="39"><v>100000</v></c><c r="P39" s="152"/><c r="Q39" s="66"/><c r="R39" s="154"/><c r="S39" s="74"/><c r="T39" s="152"/><c r="U39" s="68"/><c r="A39" s="1"/><c r="I39" s="41"/><c r="J39" s="27"/><c r="K39" s="24"/><c r="L39" s="105"/><c r="V39" s="1"/><c r="W39" s="1" t="s"><v>14</v></c></row><row r="40"     spans="1:23" x14ac:dyDescent="0.3"><c r="M40" s="37" t="inlineStr"><is><t xml:space="preserve">02-01-2026</t></is></c><c r="N40" s="38" t="inlineStr"><is><t xml:space="preserve">BCI</t></is></c><c r="O40" s="39"><v>200000</v></c><c r="P40" s="152"/><c r="Q40" s="66"/><c r="R40" s="154"/><c r="S40" s="74"/><c r="T40" s="152"/><c r="U40" s="68"/><c r="A40" s="1"/><c r="I40" s="41"/><c r="J40" s="27"/><c r="K40" s="24"/><c r="L40" s="105"/><c r="V40" s="1"/><c r="W40" s="1" t="s"><v>14</v></c></row><row r="41" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="B41" s="20"/><c r="C41" s="32"/><c r="I41" s="41"><f t="shared" ref="I41:I48" si="6">L$1</f><v>0</v></c><c r="J41" s="27"><f t="shared" ref="J41:J48" si="7">L10</f><v>0</v></c><c r="L41" s="105"/><c r="M41" s="171" t="s"><v>42</v></c><c r="N41" s="179"/><c r="O41" s="150"><v>600000</v></c><c r="P41" s="152"/><c r="Q41" s="75"/><c r="R41" s="154"/><c r="S41" s="73"/><c r="T41" s="152"/><c r="U41" s="76"/><c r="V41" s="1"/><c r="W41" s="1"/></row><row r="42" spans="1:23" x14ac:dyDescent="0.3"><c r="M42" s="37"/><c r="N42" s="38"/><c r="O42" s="39"/><c r="B42" s="20"/><c r="C42" s="32"/><c r="I42" s="41"><f t="shared" si="6"/><v>0</v></c></row><row r="43" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4"></row><row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"></row><row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.6"></row><row r="46" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.6"></row><row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"></row><row r="48" spans="1:23" x14ac:dyDescent="0.3"></row><row r="49" spans="1:23" x14ac:dyDescent="0.3"><c r="L49" s="105"/><c r="M49" s="37"/><c r="N49" s="38"/><c r="O49" s="39"/><c r="P49" s="152"/><c r="Q49" s="66"/><c r="R49" s="152"/><c r="S49" s="67"/><c r="T49" s="152"/><c r="U49" s="68"/></row><row r="50" spans="1:23" x14ac:dyDescent="0.3"><c r="A50" s="20"/><c r="B50" s="20"/><c r="C50" s="40"/><c r="D50" s="170"/><c r="E50" s="170"/><c r="F50" s="17"/><c r="G50" s="1"/><c r="H50" s="64"/><c r="I50" s="13"/><c r="J50" s="53"/><c r="K50" s="24"/><c r="L50" s="105"/><c r="M50" s="37"/><c r="N50" s="38"/><c r="O50" s="39"/><c r="P50" s="152"/><c r="Q50" s="66"/><c r="R50" s="152"/><c r="S50" s="67"/><c r="T50" s="152"/><c r="U50" s="68"/></row><row r="51" spans="1:23" x14ac:dyDescent="0.3"><c r="A51" s="20"/><c r="B51" s="20"/><c r="C51" s="40"/><c r="D51" s="170"/><c r="E51" s="170"/><c r="F51" s="23"/><c r="G51" s="1"/><c r="H51" s="64"/><c r="I51" s="13"/><c r="J51" s="53"/><c r="L51" s="105"/><c r="M51" s="37"/><c r="N51" s="38"/><c r="O51" s="39"/><c r="P51" s="152"/><c r="Q51" s="66"/><c r="R51" s="152"/><c r="S51" s="67"/><c r="T51" s="154"/><c r="U51" s="68"/></row><row r="52" spans="1:21" x14ac:dyDescent="0.3"><c r="A52" s="20"/><c r="B52" s="20"/><c r="C52" s="40"/><c r="D52" s="170"/><c r="E52" s="170"/><c r="F52" s="23"/><c r="G52" s="1"/><c r="H52" s="46"/><c r="I52" s="13"/><c r="J52" s="53"/><c r="L52" s="105"/><c r="M52" s="37"/><c r="N52" s="38"/><c r="O52" s="39"/><c r="P52" s="152"/><c r="Q52" s="66"/><c r="R52" s="152"/><c r="S52" s="67"/><c r="T52" s="154"/><c r="U52" s="68"/></row><row r="53" spans="1:21" x14ac:dyDescent="0.3"><c r="A53" s="20"/><c r="B53" s="20"/><c r="C53" s="40"/><c r="D53" s="23"/><c r="E53" s="25"/><c r="F53" s="23"/><c r="G53" s="1"/><c r="H53" s="46"/><c r="I53" s="13"/><c r="J53" s="53"/><c r="L53" s="105"/><c r="M53" s="37"/><c r="N53" s="38"/><c r="O53" s="39"/><c r="P53" s="152"/><c r="Q53" s="66"/><c r="R53" s="152"/><c r="S53" s="67"/><c r="T53" s="154"/><c r="U53" s="68"/></row><row r="54" spans="1:21" x14ac:dyDescent="0.3"><c r="A54" s="20"/><c r="B54" s="20"/><c r="C54" s="40"/><c r="D54" s="185"/><c r="E54" s="185"/><c r="F54" s="23"/><c r="G54" s="1"/><c r="H54" s="46"/><c r="I54" s="13"/><c r="J54" s="53"/><c r="L54" s="105"/><c r="M54" s="37"/><c r="N54" s="38"/><c r="O54" s="39"/><c r="P54" s="151"/><c r="Q54" s="66"/><c r="R54" s="152"/><c r="S54" s="67"/><c r="T54" s="154"/><c r="U54" s="68"/></row><row r="55" spans="1:21" x14ac:dyDescent="0.3"><c r="A55" s="20"/><c r="B55" s="51"/><c r="C55" s="40"/><c r="D55" s="178"/><c r="E55" s="178"/><c r="F55" s="23"/><c r="G55" s="1"/><c r="H55" s="46"/><c r="I55" s="50"/><c r="J55" s="53"/><c r="L55" s="105"/><c r="M55" s="37"/><c r="N55" s="38"/><c r="O55" s="39"/><c r="P55" s="151"/><c r="Q55" s="66"/><c r="R55" s="152"/><c r="S55" s="67"/><c r="T55" s="154"/><c r="U55" s="68"/></row><row r="56" spans="1:21" x14ac:dyDescent="0.3"><c r="A56" s="25"/><c r="B56" s="51"/><c r="C56" s="40"/><c r="D56" s="166"/><c r="E56" s="166"/><c r="F56" s="23"/><c r="G56" s="1"/><c r="H56" s="46"/><c r="I56" s="50"/><c r="J56" s="53"/><c r="L56" s="18"/><c r="M56" s="37"/><c r="N56" s="38"/><c r="O56" s="39"/><c r="P56" s="152"/><c r="Q56" s="66"/><c r="R56" s="152"/><c r="S56" s="67"/><c r="T56" s="154"/><c r="U56" s="68"/></row><row r="57" spans="1:21" x14ac:dyDescent="0.3"><c r="A57" s="20"/><c r="B57" s="51"/><c r="C57" s="40"/><c r="D57" s="166"/><c r="E57" s="166"/><c r="F57" s="23"/><c r="G57" s="1"/><c r="H57" s="46"/><c r="I57" s="50"/><c r="J57" s="53"/><c r="L57" s="18"/><c r="M57" s="37"/><c r="N57" s="38"/><c r="O57" s="39"/><c r="P57" s="152"/><c r="Q57" s="66"/><c r="R57" s="152"/><c r="S57" s="67"/><c r="T57" s="154"/><c r="U57" s="68"/></row><row r="58" spans="1:21" x14ac:dyDescent="0.3"><c r="A58" s="20"/><c r="B58" s="51"/><c r="C58" s="40"/><c r="D58" s="22"/><c r="E58" s="22"/><c r="F58" s="23"/><c r="G58" s="1"/><c r="H58" s="46"/><c r="I58" s="50"/><c r="J58" s="53"/><c r="L58" s="18"/><c r="M58" s="37"/><c r="N58" s="38"/><c r="O58" s="39"/><c r="P58" s="152"/><c r="Q58" s="66"/><c r="R58" s="152"/><c r="S58" s="67"/><c r="T58" s="154"/><c r="U58" s="68"/></row><row r="59" spans="1:21" x14ac:dyDescent="0.3"><c r="A59" s="20"/><c r="B59"/><c r="C59" s="40"/><c r="D59" s="22"/><c r="E59" s="22"/><c r="F59" s="23"/><c r="G59" s="1"/><c r="H59" s="46"/><c r="I59" s="50"/><c r="J59" s="53"/><c r="L59" s="18"/><c r="M59" s="37"/><c r="N59" s="38"/><c r="O59" s="39"/><c r="P59" s="152"/><c r="Q59" s="66"/><c r="R59" s="152"/><c r="S59" s="67"/><c r="T59" s="154"/><c r="U59" s="68"/></row><row r="60" spans="1:21" x14ac:dyDescent="0.3"><c r="A60" s="20"/><c r="B60"/><c r="C60" s="40"/><c r="D60" s="22"/><c r="E60" s="22"/><c r="F60" s="23"/><c r="G60" s="1"/><c r="H60" s="46"/><c r="I60" s="50"/><c r="J60" s="53"/><c r="L60" s="18"/><c r="M60" s="37"/><c r="N60" s="38"/><c r="O60" s="39"/><c r="P60" s="152"/><c r="Q60" s="66"/><c r="R60" s="152"/><c r="S60" s="67"/><c r="T60" s="154"/><c r="U60" s="68"/></row><row r="61" spans="1:21" x14ac:dyDescent="0.3"><c r="A61" s="20"/><c r="B61"/><c r="C61" s="40"/><c r="D61" s="22"/><c r="E61" s="22"/><c r="F61" s="23"/><c r="G61" s="1"/><c r="H61" s="46"/><c r="I61" s="50"/><c r="J61" s="53"/><c r="L61" s="18"/><c r="M61" s="37"/><c r="N61" s="38"/><c r="O61" s="39"/><c r="P61" s="152"/><c r="Q61" s="66"/><c r="R61" s="152"/><c r="S61" s="67"/><c r="T61" s="154"/><c r="U61" s="68"/></row><row r="62" spans="1:21" x14ac:dyDescent="0.3"><c r="A62" s="20"/><c r="B62"/><c r="C62" s="40"/><c r="D62" s="22"/><c r="E62" s="22"/><c r="F62" s="23"/><c r="G62" s="1"/><c r="H62" s="46"/><c r="I62" s="50"/><c r="J62" s="53"/><c r="L62" s="18"/><c r="M62" s="37"/><c r="N62" s="38"/><c r="O62" s="39"/><c r="P62" s="152"/><c r="Q62" s="66"/><c r="R62" s="152"/><c r="S62" s="67"/><c r="T62" s="154"/><c r="U62" s="68"/></row><row r="63" spans="1:21" x14ac:dyDescent="0.3"><c r="A63" s="25"/><c r="B63"/><c r="C63" s="40"/><c r="D63" s="166"/><c r="E63" s="166"/><c r="F63" s="23"/><c r="G63" s="1"/><c r="H63" s="46"/><c r="I63" s="50"/><c r="J63" s="53"/><c r="L63" s="18"/><c r="M63" s="37"/><c r="N63" s="38"/><c r="O63" s="39"/><c r="P63" s="152"/><c r="Q63" s="66"/><c r="R63" s="152"/><c r="S63" s="67"/><c r="T63" s="154"/><c r="U63" s="68"/></row><row r="64" spans="1:21" x14ac:dyDescent="0.3"><c r="A64" s="25"/><c r="B64"/><c r="C64" s="40"/><c r="D64" s="22"/><c r="E64" s="22"/><c r="F64" s="23"/><c r="G64" s="1"/><c r="H64" s="46"/><c r="I64" s="50"/><c r="J64" s="53"/><c r="L64" s="18"/><c r="M64" s="37"/><c r="N64" s="38"/><c r="O64" s="39"/><c r="P64" s="152"/><c r="Q64" s="135"/><c r="R64" s="155"/><c r="S64" s="88"/><c r="T64" s="154"/><c r="U64" s="68"/></row><row r="65" spans="1:21" x14ac:dyDescent="0.3"><c r="A65" s="25"/><c r="B65"/><c r="C65" s="40"/><c r="D65" s="22"/><c r="E65" s="22"/><c r="F65" s="23"/><c r="G65" s="1"/><c r="H65" s="46"/><c r="I65" s="50"/><c r="J65" s="53"/><c r="L65" s="18"/><c r="M65" s="37"/><c r="N65" s="38"/><c r="O65" s="39"/><c r="P65" s="152"/><c r="Q65" s="135"/><c r="R65" s="155"/><c r="S65" s="88"/><c r="T65" s="154"/><c r="U65" s="68"/></row><row r="66" spans="1:21" x14ac:dyDescent="0.3"><c r="A66" s="25"/><c r="B66"/><c r="C66" s="40"/><c r="D66" s="22"/><c r="E66" s="22"/><c r="F66" s="23"/><c r="G66" s="1"/><c r="H66" s="46"/><c r="I66" s="50"/><c r="J66" s="53"/><c r="L66" s="18"/><c r="M66" s="37"/><c r="N66" s="38"/><c r="O66" s="39"/><c r="P66" s="152"/><c r="Q66" s="135"/><c r="R66" s="155"/><c r="S66" s="88"/><c r="T66" s="154"/><c r="U66" s="68"/></row><row r="67" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A67" s="25"/><c r="B67"/><c r="C67" s="40"/><c r="D67" s="166"/><c r="E67" s="166"/><c r="F67" s="23"/><c r="G67" s="1"/><c r="H67" s="46"/><c r="I67" s="50"/><c r="J67" s="53"/><c r="L67" s="18"/><c r="M67" s="37"/><c r="N67" s="38"/><c r="O67" s="39"/><c r="P67" s="152"/><c r="Q67" s="84"/><c r="R67" s="155"/><c r="S67" s="88"/><c r="T67" s="154"/><c r="U67" s="71"/></row><row r="68" spans="1:23" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A68" s="25"/><c r="B68"/><c r="C68" s="40"/><c r="D68" s="166"/><c r="E68" s="166"/><c r="F68" s="20"/><c r="G68" s="1"/><c r="H68" s="46"/><c r="I68" s="50"/><c r="J68" s="53"/><c r="L68"/><c r="M68" s="171" t="s"><v>34</v></c><c r="N68" s="172"/><c r="O68" s="42"/><c r="P68" s="52" t="s"><v>11</v></c><c r="Q68" s="42"/><c r="R68" s="52" t="s"><v>11</v></c><c r="S68" s="42"/><c r="T68" s="52" t="s"><v>11</v></c><c r="U68" s="42"/></row><row r="69" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A69" s="25"/><c r="B69"/><c r="C69" s="90"/><c r="D69" s="166"/><c r="E69" s="166"/><c r="F69" s="23"/><c r="G69" s="1"/><c r="H69" s="46"/><c r="I69" s="50"/><c r="J69"/><c r="L69"/><c r="M69" s="54"/><c r="N69" s="55"/><c r="O69" s="70"/><c r="P69" s="23"/><c r="Q69" s="69"/><c r="R69" s="70"/><c r="S69" s="70"/><c r="T69" s="6"/></row><row r="70" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="A70" s="25"/><c r="B70"/><c r="C70" s="25"/><c r="D70" s="22"/><c r="E70" s="22"/><c r="F70" s="23"/><c r="G70" s="1"/><c r="H70" s="46"/><c r="I70" s="50"/><c r="J70"/><c r="L70"/><c r="M70" s="167" t="s"><v>47</v></c><c r="N70" s="168"/><c r="O70" s="169"/><c r="P70" s="181"/><c r="Q70" s="182"/><c r="R70" s="167" t="s"><v>37</v></c><c r="S70" s="168"/><c r="T70" s="183" t="str"><f>Q25</f></c><c r="U70" s="184"/></row><row r="71" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A71" s="25"/><c r="B71"/><c r="C71" s="25"/><c r="D71" s="166"/><c r="E71" s="166"/><c r="F71" s="63"/><c r="G71" s="1"/><c r="H71" s="46"/><c r="I71" s="50"/><c r="J71"/><c r="L71"/><c r="M71" s="56"/><c r="N71" s="83"/><c r="O71" s="83"/><c r="P71" s="57"/><c r="Q71" s="58"/><c r="R71" s="58"/><c r="S71" s="58"/><c r="T71" s="56"/><c r="U71" s="56"/></row><row r="72" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"><c r="A72" s="25"/><c r="B72" s="90"/><c r="C72" s="25"/><c r="D72" s="166"/><c r="E72" s="166"/><c r="F72" s="63"/><c r="G72" s="1"/><c r="H72" s="46"/><c r="I72" s="50"/><c r="J72"/><c r="L72"/><c r="M72" s="171" t="s"><v>35</v></c><c r="N72" s="179"/><c r="O72" s="179"/><c r="P72" s="179"/><c r="Q72" s="179"/><c r="R72" s="179"/><c r="S72" s="179"/><c r="T72" s="179"/><c r="U72" s="180"/><c r="V72" s="51"/></row><row r="73" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35"><c r="A73" s="25"/><c r="B73" s="20"/><c r="C73" s="25"/><c r="D73" s="166"/><c r="E73" s="166"/><c r="F73" s="63"/><c r="G73" s="1"/><c r="H73" s="46"/><c r="I73" s="50"/><c r="J73"/><c r="L73" s="49" t="s"><v>59</v></c><c r="M73" s="130" t="s"><v>55</v></c><c r="N73" s="131"/><c r="O73" s="131"/><c r="P73" s="131" t="s"><v>56</v></c><c r="Q73" s="131"/><c r="R73" s="131"/><c r="S73" s="131"/><c r="T73" s="131" t="s"><v>57</v></c><c r="U73" s="132" t="s"><v>60</v></c><c r="V73" s="144" t="s"><v>58</v></c><c r="W73" s="144" t="s"><v>50</v></c></row><row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L74" s="0"/><c r="M74" s="59"/><c r="P74" s="62"/><c r="T74" s="133"/><c r="V74" s="51"/><c r="R74" s="177" t="inlineStr"><is><t xml:space="preserve">CREDITO</t></is></c><c r="A74" s="25"/><c r="B74" s="115"/><c r="C74" s="25"/><c r="D74" s="166"/><c r="E74" s="166"/><c r="F74" s="63"/><c r="G74" s="1"/><c r="H74" s="46"/><c r="I74" s="50"/><c r="J74" s="23"/><c r="N74" s="60"/><c r="O74" s="143" t="s"><v>43</v></c><c r="Q74" s="61"/><c r="S74" s="177"/><c r="U74" s="134"/></row><row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="B75" s="51"/><c r="C75" s="89"/><c r="D75" s="166"/><c r="E75" s="166"/><c r="F75" s="63"/><c r="I75" s="115"/><c r="L75"/><c r="M75" s="85"/><c r="N75" s="86"/><c r="O75" s="18"/><c r="P75" s="87"/><c r="Q75" s="56"/><c r="R75" s="175"/><c r="S75" s="175"/><c r="T75" s="65"/><c r="U75" s="95"/><c r="V75" s="51"/></row><row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L76" s="45" t="inlineStr"><is><t xml:space="preserve">111</t></is></c><c r="M76" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="P76" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="T76" s="65"><v>150000</v></c><c r="U76" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="R76" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="A76" s="49"/><c r="B76" s="89"/><c r="C76" s="89"/><c r="D76" s="23"/><c r="E76" s="25"/><c r="F76" s="63"/><c r="I76" s="115"/><c r="N76" s="86"/><c r="O76" s="18" t="s"><v>43</v></c><c r="Q76" s="56"/><c r="S76" s="175"/><c r="V76" s="51"/></row><row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L77" s="45" t="inlineStr"><is><t xml:space="preserve">111</t></is></c><c r="M77" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE DOS</t></is></c><c r="P77" s="87" t="inlineStr"><is><t xml:space="preserve">F002</t></is></c><c r="T77" s="65"><v>250000</v></c><c r="U77" s="95" t="inlineStr"><is><t xml:space="preserve">BCI</t></is></c><c r="R77" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="N77" s="86"/><c r="O77" s="123"/><c r="Q77" s="56"/><c r="S77" s="175"/><c r="V77" s="51"/></row><row r="78"    spans="1:23" x14ac:dyDescent="0.3"><c r="L78" s="45" t="inlineStr"><is><t xml:space="preserve">222</t></is></c><c r="M78" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE UNO</t></is></c><c r="P78" s="87" t="inlineStr"><is><t xml:space="preserve">F001</t></is></c><c r="T78" s="65"><v>150000</v></c><c r="U78" s="95" t="inlineStr"><is><t xml:space="preserve">Banco Santander</t></is></c><c r="R78" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="N78" s="86"/><c r="O78" s="123"/><c r="Q78" s="56"/><c r="S78" s="175"/><c r="V78" s="51"/></row><row r="79"    spans="1:23" x14ac:dyDescent="0.3"><c r="L79" s="45" t="inlineStr"><is><t xml:space="preserve">222</t></is></c><c r="M79" s="85" t="inlineStr"><is><t xml:space="preserve">CLIENTE DOS</t></is></c><c r="P79" s="87" t="inlineStr"><is><t xml:space="preserve">F002</t></is></c><c r="T79" s="65"><v>250000</v></c><c r="U79" s="95" t="inlineStr"><is><t xml:space="preserve">BCI</t></is></c><c r="R79" s="175" t="inlineStr"><is><t xml:space="preserve">TRANSFERENCIA</t></is></c><c r="N79" s="86"/><c r="O79" s="123"/><c r="Q79" s="56"/><c r="S79" s="175"/><c r="V79" s="51"/></row><row r="80" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L80" s="45"/><c r="M80" s="137" t="s"><v>61</v></c><c r="N80" s="138"/><c r="O80" s="139"/><c r="P80" s="140"/><c r="Q80" s="141"/><c r="R80" s="176"/><c r="S80" s="176"/><c r="T80" s="173"/><c r="U80" s="174"/><c r="V80" s="51"/></row><row r="81" spans="1:23" ht="15.6" x14ac:dyDescent="0.3"><c r="L81" s="45"/><c r="M81" s="137" t="s"><v>62</v></c><c r="N81" s="138"/><c r="O81" s="139"/><c r="P81" s="140"/><c r="Q81" s="141"/><c r="R81" s="142"/><c r="S81" s="142"/><c r="T81" s="173"/><c r="U81" s="174"/><c r="V81" s="51"/></row><row r="82" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L82" s="45"/><c r="M82" s="94"/><c r="N82" s="64"/><c r="O82" s="123"/><c r="P82" s="87"/><c r="Q82" s="56"/><c r="R82" s="56"/><c r="S82" s="56"/><c r="T82" s="65"/><c r="U82" s="95"/><c r="V82" s="51"/></row><row r="83" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"><c r="L83" s="45"/><c r="M83" s="101" t="s"><v>11</v></c><c r="N83" s="102"><f>SUM(N81:N82)</f><v>0</v></c><c r="O83" s="96"/><c r="P83" s="98"/><c r="Q83" s="97"/><c r="R83" s="97"/><c r="S83" s="97"/><c r="T83" s="99"/><c r="U83" s="100"/><c r="V83" s="51"/></row><row r="84" spans="1:23" x14ac:dyDescent="0.3"><c r="M84"/><c r="O84" s="5"/><c r="Q84"/><c r="S84"/><c r="T84" s="6"/><c r="V84" s="51"/></row><row r="85" spans="1:23" x14ac:dyDescent="0.3"><c r="O85"/><c r="V85" s="51"/></row><row r="86" spans="13:22" x14ac:dyDescent="0.3"><c r="M86" s="23"/><c r="N86" s="23"/><c r="O86" s="23"/><c r="P86" s="23"/><c r="Q86" s="23"/><c r="V86" s="51"/></row><row r="87" spans="13:22" x14ac:dyDescent="0.3"><c r="V87" s="51"/></row><row r="88" spans="13:22" x14ac:dyDescent="0.3"><c r="V88" s="51"/></row><row r="89" spans="13:22" x14ac:dyDescent="0.3"><c r="V89" s="51"/></row><row r="90" spans="13:22" x14ac:dyDescent="0.3"><c r="V90" s="51"/></row><row r="91" spans="13:22" x14ac:dyDescent="0.3"><c r="V91" s="51"/></row><row r="92" spans="13:22" x14ac:dyDescent="0.3"><c r="V92" s="51"/></row><row r="93" spans="13:22" x14ac:dyDescent="0.3"><c r="V93" s="51"/></row><row r="94" spans="13:22" x14ac:dyDescent="0.3"><c r="V94" s="51"/></row><row r="95" spans="13:22" x14ac:dyDescent="0.3"><c r="V95" s="51"/></row><row r="96" spans="13:22" x14ac:dyDescent="0.3"><c r="V96" s="51"/></row><row r="97" spans="13:22" x14ac:dyDescent="0.3"><c r="V97" s="51"/></row><row r="98" spans="13:22" x14ac:dyDescent="0.3"><c r="V98" s="51"/></row><row r="99" spans="13:22" x14ac:dyDescent="0.3"><c r="V99" s="51"/></row><row r="100" spans="13:22" x14ac:dyDescent="0.3"><c r="V100" s="51"/></row><row r="101" spans="13:22" x14ac:dyDescent="0.3"><c r="V101" s="51"/></row><row r="102" spans="22:22" x14ac:dyDescent="0.3"><c r="V102" s="51"/></row><row r="103" spans="22:22" x14ac:dyDescent="0.3"><c r="V103" s="51"/></row><row r="104" spans="22:22" x14ac:dyDescent="0.3"><c r="V104" s="51"/></row><row r="105" spans="22:22" x14ac:dyDescent="0.3"><c r="V105" s="51"/></row><row r="106" spans="22:22" x14ac:dyDescent="0.3"><c r="V106" s="51"/></row><row r="107" spans="22:22" x14ac:dyDescent="0.3"><c r="V107" s="51"/></row><row r="108" spans="22:22" x14ac:dyDescent="0.3"><c r="V108" s="51"/></row><row r="109" spans="22:22" x14ac:dyDescent="0.3"><c r="V109" s="51"/></row><row r="110" spans="22:22" x14ac:dyDescent="0.3"><c r="V110" s="51"/></row><row r="111" spans="22:22" x14ac:dyDescent="0.3"><c r="V111" s="51"/></row><row r="112" spans="22:22" x14ac:dyDescent="0.3"><c r="V112" s="51"/></row><row r="113" spans="22:22" x14ac:dyDescent="0.3"><c r="V113" s="51"/></row><row r="114" spans="22:22" x14ac:dyDescent="0.3"><c r="V114" s="51"/></row><row r="115" spans="22:22" x14ac:dyDescent="0.3"><c r="V115" s="51"/></row><row r="116" spans="22:22" x14ac:dyDescent="0.3"><c r="V116" s="51"/></row><row r="117" spans="22:22" x14ac:dyDescent="0.3"><c r="V117" s="51"/></row></sheetData><mergeCells count="72"><mergeCell ref="M25:N25"/><mergeCell ref="O30:P30"/><mergeCell ref="Q30:S30"/><mergeCell ref="T30:U30"/><mergeCell ref="Q32:S32"/><mergeCell ref="M31:N31"/><mergeCell ref="O31:P31"/><mergeCell ref="Q31:S31"/><mergeCell ref="M30:N30"/><mergeCell ref="M32:N32"/><mergeCell ref="O32:P32"/><mergeCell ref="M22:U22"/><mergeCell ref="Q26:S26"/><mergeCell ref="O29:P29"/><mergeCell ref="Q29:S29"/><mergeCell ref="T29:U29"/><mergeCell ref="T28:U28"/><mergeCell ref="O28:P28"/><mergeCell ref="Q28:S28"/><mergeCell ref="M28:N28"/><mergeCell ref="M29:N29"/><mergeCell ref="O27:P27"/><mergeCell ref="Q27:S27"/><mergeCell ref="T27:U27"/><mergeCell ref="N23:S23"/><mergeCell ref="N24:S24"/><mergeCell ref="T25:U25"/><mergeCell ref="D46:E46"/><mergeCell ref="R35:S35"/><mergeCell ref="T35:U35"/><mergeCell ref="O33:P33"/><mergeCell ref="Q33:S33"/><mergeCell ref="M34:N34"/><mergeCell ref="O34:P34"/><mergeCell ref="Q34:S34"/><mergeCell ref="P35:Q35"/><mergeCell ref="M35:O35"/><mergeCell ref="M41:N41"/><mergeCell ref="D74:E74"/><mergeCell ref="D75:E75"/><mergeCell ref="D55:E55"/><mergeCell ref="M72:U72"/><mergeCell ref="R70:S70"/><mergeCell ref="D71:E71"/><mergeCell ref="P70:Q70"/><mergeCell ref="T70:U70"/><mergeCell ref="D63:E63"/><mergeCell ref="D69:E69"/><mergeCell ref="D56:E56"/><mergeCell ref="D68:E68"/><mergeCell ref="D57:E57"/><mergeCell ref="D67:E67"/><mergeCell ref="T81:U81"/><mergeCell ref="R77:S77"/><mergeCell ref="R80:S80"/><mergeCell ref="R74:S74"/><mergeCell ref="R76:S76"/><mergeCell ref="R75:S75"/><mergeCell ref="T80:U80"/><mergeCell ref="D73:E73"/><mergeCell ref="D72:E72"/><mergeCell ref="M70:O70"/><mergeCell ref="D47:E47"/><mergeCell ref="D49:E49"/><mergeCell ref="M68:N68"/><mergeCell ref="D51:E51"/><mergeCell ref="D52:E52"/><mergeCell ref="D50:E50"/><mergeCell ref="D48:E48"/><mergeCell ref="D54:E54"/><mergeCell ref="R78:S78"/><mergeCell ref="R79:S79"/></mergeCells><pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/><pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/><drawing r:id="rId2"/></worksheet>
 </file>